--- a/bill-checker-demo.xlsx
+++ b/bill-checker-demo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alinaaleks\Downloads\GitHub\bill-checker\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B638FB72-AFFD-4913-AD23-9F091BE91099}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF9E9F2E-89E2-485A-AD24-351BCD46814A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CHECK" sheetId="10" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="162">
   <si>
     <t>РЕГИОН</t>
   </si>
@@ -127,9 +127,6 @@
     <t>(объем) * (тариф)</t>
   </si>
   <si>
-    <t>Водоотведение СОИД</t>
-  </si>
-  <si>
     <t>Нагрев ГВ</t>
   </si>
   <si>
@@ -298,30 +295,15 @@
     <t>УК</t>
   </si>
   <si>
-    <t>ГВ снабжение СОИД</t>
-  </si>
-  <si>
     <t>Предельный тариф на услуги регионального оператора - постановление Региональной службы по тарифам РО. К единому тарифу применен понижающий коэфф. - постановление Правительства РО. Норматив накопления утвержден постановлением Мин-ва ЖКХ РО</t>
   </si>
   <si>
-    <t>Правительством Ростовской области</t>
-  </si>
-  <si>
     <t>Нормативы</t>
   </si>
   <si>
     <t>соц.норма</t>
   </si>
   <si>
-    <t>УК (соц.норма)</t>
-  </si>
-  <si>
-    <t>Электроснабжение СОИД</t>
-  </si>
-  <si>
-    <t>ХВ снабжение СОИД</t>
-  </si>
-  <si>
     <t>Электроэнергия - Расчет соц.нормы на объект</t>
   </si>
   <si>
@@ -415,9 +397,6 @@
     <t>ЖКУ_УК</t>
   </si>
   <si>
-    <t>Газоснабжение</t>
-  </si>
-  <si>
     <t>Отклонение (руб)</t>
   </si>
   <si>
@@ -515,19 +494,58 @@
   </si>
   <si>
     <t>Поставщик воды</t>
+  </si>
+  <si>
+    <t>1 п/г 2026</t>
+  </si>
+  <si>
+    <t>2 п/г 2026</t>
+  </si>
+  <si>
+    <t>https://www.donland.ru/activity/353/</t>
+  </si>
+  <si>
+    <t>https://vodokanalrnd.ru/abonentu/tarify/</t>
+  </si>
+  <si>
+    <t>https://www.donland.ru/activity/349/</t>
+  </si>
+  <si>
+    <t>https://www.donland.ru/news/32277/</t>
+  </si>
+  <si>
+    <t>Правительство Ростовской области</t>
+  </si>
+  <si>
+    <t>ГВ снабжение / общедом</t>
+  </si>
+  <si>
+    <t>Электроснабжение / общедом</t>
+  </si>
+  <si>
+    <t>ХВ снабжение  / общедом</t>
+  </si>
+  <si>
+    <t>Водоотведение  / общедом</t>
+  </si>
+  <si>
+    <t>УК (соц.норма) - если не по счетчику</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="4">
+  <numFmts count="7">
     <numFmt numFmtId="164" formatCode="[$-409]mmm\-yy;@"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
-    <numFmt numFmtId="167" formatCode="#,##0.0"/>
-    <numFmt numFmtId="171" formatCode="yyyy\-mm"/>
+    <numFmt numFmtId="166" formatCode="#,##0.0"/>
+    <numFmt numFmtId="167" formatCode="yyyy\-mm"/>
+    <numFmt numFmtId="169" formatCode="#,##0.000"/>
+    <numFmt numFmtId="170" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="172" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -567,6 +585,14 @@
     </font>
     <font>
       <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -824,10 +850,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="103">
+  <cellXfs count="112">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -932,15 +959,6 @@
     <xf numFmtId="2" fontId="1" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="0" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="0" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="4" fontId="0" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -952,12 +970,6 @@
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="0" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -974,7 +986,7 @@
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1035,37 +1047,10 @@
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="4" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="0" fillId="5" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="0" fillId="5" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="0" fillId="3" borderId="15" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1098,11 +1083,20 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="171" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="171" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1122,34 +1116,75 @@
     <xf numFmtId="0" fontId="1" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="0" fillId="8" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="166" fontId="0" fillId="8" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="8" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="0" fillId="8" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="5" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="5" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="9" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="15" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="59">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="57">
     <dxf>
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -4411,8 +4446,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="5841637" y="124279"/>
-              <a:ext cx="4505233" cy="2928438"/>
+              <a:off x="5826397" y="123009"/>
+              <a:ext cx="4503963" cy="2947488"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -4975,21 +5010,6 @@
     <dataField name="Отклонение (%)" fld="21" baseField="13" baseItem="1" numFmtId="10"/>
   </dataFields>
   <formats count="6">
-    <format dxfId="29">
-      <pivotArea field="17" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
-    </format>
-    <format dxfId="28">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="4">
-            <x v="0"/>
-            <x v="1"/>
-            <x v="2"/>
-            <x v="3"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
     <format dxfId="27">
       <pivotArea field="17" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
@@ -5009,6 +5029,21 @@
       <pivotArea field="17" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
     <format dxfId="24">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="4">
+            <x v="0"/>
+            <x v="1"/>
+            <x v="2"/>
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="23">
+      <pivotArea field="17" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="22">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="4">
@@ -5106,7 +5141,7 @@
     <dataField name="Факт (начисления)" fld="4" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="18">
-    <format dxfId="47">
+    <format dxfId="45">
       <pivotArea outline="0" fieldPosition="0">
         <references count="2">
           <reference field="4294967294" count="1" selected="0">
@@ -5118,10 +5153,10 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="46">
+    <format dxfId="44">
       <pivotArea field="17" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
     </format>
-    <format dxfId="45">
+    <format dxfId="43">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="17" count="1">
@@ -5130,7 +5165,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="44">
+    <format dxfId="42">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="4294967294" count="1">
@@ -5142,7 +5177,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="43">
+    <format dxfId="41">
       <pivotArea outline="0" fieldPosition="0">
         <references count="2">
           <reference field="4294967294" count="1" selected="0">
@@ -5154,13 +5189,13 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="42">
+    <format dxfId="40">
       <pivotArea field="-2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="1"/>
     </format>
-    <format dxfId="41">
+    <format dxfId="39">
       <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="40">
+    <format dxfId="38">
       <pivotArea outline="0" fieldPosition="0">
         <references count="2">
           <reference field="4294967294" count="2" selected="0">
@@ -5173,7 +5208,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="39">
+    <format dxfId="37">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="4294967294" count="1" selected="0">
@@ -5185,31 +5220,31 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="38">
+    <format dxfId="36">
       <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="37">
+    <format dxfId="35">
       <pivotArea field="-2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="1"/>
     </format>
-    <format dxfId="36">
+    <format dxfId="34">
       <pivotArea field="17" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
     </format>
-    <format dxfId="35">
+    <format dxfId="33">
       <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="34">
+    <format dxfId="32">
       <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="33">
+    <format dxfId="31">
       <pivotArea field="-2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="1"/>
     </format>
-    <format dxfId="32">
+    <format dxfId="30">
       <pivotArea field="17" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
     </format>
-    <format dxfId="31">
+    <format dxfId="29">
       <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="30">
+    <format dxfId="28">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="17" count="1">
@@ -5395,26 +5430,8 @@
     <dataField name="Отклонение (%)" fld="21" baseField="17" baseItem="0" numFmtId="10"/>
   </dataFields>
   <formats count="11">
-    <format dxfId="58">
+    <format dxfId="56">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="57">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="56">
-      <pivotArea outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
     </format>
     <format dxfId="55">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
@@ -5428,22 +5445,25 @@
     <format dxfId="54">
       <pivotArea outline="0" fieldPosition="0">
         <references count="1">
-          <reference field="4294967294" count="1">
-            <x v="3"/>
+          <reference field="4294967294" count="1" selected="0">
+            <x v="1"/>
           </reference>
         </references>
       </pivotArea>
     </format>
     <format dxfId="53">
-      <pivotArea field="19" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="1"/>
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
     </format>
     <format dxfId="52">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+      <pivotArea outline="0" fieldPosition="0">
         <references count="1">
-          <reference field="4294967294" count="4">
-            <x v="0"/>
-            <x v="1"/>
-            <x v="2"/>
+          <reference field="4294967294" count="1">
             <x v="3"/>
           </reference>
         </references>
@@ -5479,6 +5499,21 @@
         </references>
       </pivotArea>
     </format>
+    <format dxfId="47">
+      <pivotArea field="19" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="1"/>
+    </format>
+    <format dxfId="46">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="4">
+            <x v="0"/>
+            <x v="1"/>
+            <x v="2"/>
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
   </formats>
   <pivotTableStyleInfo name="PivotStyleMedium9" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
@@ -5493,39 +5528,39 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{038A7D06-120E-408B-AEDA-813F2FAAD501}" name="Table2" displayName="Table2" ref="A1:T2" insertRow="1" totalsRowShown="0" headerRowDxfId="23" dataDxfId="22">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{038A7D06-120E-408B-AEDA-813F2FAAD501}" name="Table2" displayName="Table2" ref="A1:T2" insertRow="1" totalsRowShown="0" headerRowDxfId="21" dataDxfId="20">
   <autoFilter ref="A1:T2" xr:uid="{038A7D06-120E-408B-AEDA-813F2FAAD501}"/>
   <tableColumns count="20">
-    <tableColumn id="1" xr3:uid="{A040E5F1-B940-434F-8642-3D7965B0C906}" name="услуга" dataDxfId="21"/>
-    <tableColumn id="2" xr3:uid="{F1E9BBF3-FF65-4BCE-A746-A764AA053336}" name="ед_изм" dataDxfId="20"/>
-    <tableColumn id="3" xr3:uid="{95BCA9F7-93A8-474A-B486-B60193571EE3}" name="объем_квит" dataDxfId="19"/>
-    <tableColumn id="4" xr3:uid="{68D5AF23-9C08-4C25-A70E-D5B9C5258B85}" name="тариф_квит" dataDxfId="18"/>
-    <tableColumn id="5" xr3:uid="{1AE3F8D2-8628-41AA-B125-5D9318037FFC}" name="начислено_квит" dataDxfId="17"/>
-    <tableColumn id="6" xr3:uid="{2352EB12-E5C2-4AD6-8516-1C5A276F0128}" name="объем_откл" dataDxfId="16"/>
-    <tableColumn id="7" xr3:uid="{7BC866F5-0902-4D0A-9F28-F44EC965920C}" name="тариф_откл" dataDxfId="15"/>
-    <tableColumn id="8" xr3:uid="{DCE0FDDD-E687-4FB1-A515-511A0D4227D7}" name="начислено_откл" dataDxfId="14"/>
-    <tableColumn id="9" xr3:uid="{ABA713D2-6A48-414E-8866-3C6F39D5A490}" name="объем_расчет" dataDxfId="13"/>
-    <tableColumn id="10" xr3:uid="{EB157C1F-294F-4DFA-B0C3-E5402FF488C6}" name="тариф_расчет" dataDxfId="12"/>
-    <tableColumn id="11" xr3:uid="{16FD8211-F0B8-47DC-B4C9-EE5186864112}" name="насчислено_расчет" dataDxfId="11"/>
-    <tableColumn id="12" xr3:uid="{E9403770-B09D-40E2-BEFE-72B760354FEB}" name="норматив" dataDxfId="10"/>
-    <tableColumn id="13" xr3:uid="{5E21BED0-908D-4682-8E01-9D5911F61AB9}" name="период" dataDxfId="9"/>
-    <tableColumn id="14" xr3:uid="{6C555CCE-FDE0-4600-A16A-E7977D4C1331}" name="поставщик" dataDxfId="8"/>
-    <tableColumn id="18" xr3:uid="{70B0664C-2BB9-44F5-A956-B8CFF607EBD0}" name="начислено_откл%" dataDxfId="7">
+    <tableColumn id="1" xr3:uid="{A040E5F1-B940-434F-8642-3D7965B0C906}" name="услуга" dataDxfId="19"/>
+    <tableColumn id="2" xr3:uid="{F1E9BBF3-FF65-4BCE-A746-A764AA053336}" name="ед_изм" dataDxfId="18"/>
+    <tableColumn id="3" xr3:uid="{95BCA9F7-93A8-474A-B486-B60193571EE3}" name="объем_квит" dataDxfId="17"/>
+    <tableColumn id="4" xr3:uid="{68D5AF23-9C08-4C25-A70E-D5B9C5258B85}" name="тариф_квит" dataDxfId="16"/>
+    <tableColumn id="5" xr3:uid="{1AE3F8D2-8628-41AA-B125-5D9318037FFC}" name="начислено_квит" dataDxfId="15"/>
+    <tableColumn id="6" xr3:uid="{2352EB12-E5C2-4AD6-8516-1C5A276F0128}" name="объем_откл" dataDxfId="14"/>
+    <tableColumn id="7" xr3:uid="{7BC866F5-0902-4D0A-9F28-F44EC965920C}" name="тариф_откл" dataDxfId="13"/>
+    <tableColumn id="8" xr3:uid="{DCE0FDDD-E687-4FB1-A515-511A0D4227D7}" name="начислено_откл" dataDxfId="12"/>
+    <tableColumn id="9" xr3:uid="{ABA713D2-6A48-414E-8866-3C6F39D5A490}" name="объем_расчет" dataDxfId="11"/>
+    <tableColumn id="10" xr3:uid="{EB157C1F-294F-4DFA-B0C3-E5402FF488C6}" name="тариф_расчет" dataDxfId="10"/>
+    <tableColumn id="11" xr3:uid="{16FD8211-F0B8-47DC-B4C9-EE5186864112}" name="насчислено_расчет" dataDxfId="9"/>
+    <tableColumn id="12" xr3:uid="{E9403770-B09D-40E2-BEFE-72B760354FEB}" name="норматив" dataDxfId="8"/>
+    <tableColumn id="13" xr3:uid="{5E21BED0-908D-4682-8E01-9D5911F61AB9}" name="период" dataDxfId="7"/>
+    <tableColumn id="14" xr3:uid="{6C555CCE-FDE0-4600-A16A-E7977D4C1331}" name="поставщик" dataDxfId="6"/>
+    <tableColumn id="18" xr3:uid="{70B0664C-2BB9-44F5-A956-B8CFF607EBD0}" name="начислено_откл%" dataDxfId="5">
       <calculatedColumnFormula>IF(Table2[[#This Row],[начислено_откл]]=0,0,(Table2[[#This Row],[начислено_квит]]-Table2[[#This Row],[насчислено_расчет]])/Table2[[#This Row],[насчислено_расчет]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="19" xr3:uid="{725C5E98-3B75-474D-9C6F-E06942598B1D}" name="положит_откл" dataDxfId="6">
+    <tableColumn id="19" xr3:uid="{725C5E98-3B75-474D-9C6F-E06942598B1D}" name="положит_откл" dataDxfId="4">
       <calculatedColumnFormula>IF(Table2[[#This Row],[начислено_откл]]&gt;0,Table2[[#This Row],[начислено_откл]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="20" xr3:uid="{307D926C-82F4-46F4-AC93-88CE44B6AD40}" name="отриц_откл" dataDxfId="5">
+    <tableColumn id="20" xr3:uid="{307D926C-82F4-46F4-AC93-88CE44B6AD40}" name="отриц_откл" dataDxfId="3">
       <calculatedColumnFormula>IF(Table2[[#This Row],[начислено_откл]]&lt;0,Table2[[#This Row],[начислено_откл]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{5780D1EA-A409-449C-BCA3-DC86372888EC}" name="год" dataDxfId="4">
+    <tableColumn id="15" xr3:uid="{5780D1EA-A409-449C-BCA3-DC86372888EC}" name="год" dataDxfId="2">
       <calculatedColumnFormula>YEAR(M2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{3889E082-3447-4F9E-A275-7FE45FCFD6FB}" name="месяц_№" dataDxfId="3">
+    <tableColumn id="16" xr3:uid="{3889E082-3447-4F9E-A275-7FE45FCFD6FB}" name="месяц_№" dataDxfId="1">
       <calculatedColumnFormula>MONTH(M2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{E6E9DC5E-485F-4A72-A2BF-41BAB4F90D1B}" name="месяц" dataDxfId="2">
+    <tableColumn id="17" xr3:uid="{E6E9DC5E-485F-4A72-A2BF-41BAB4F90D1B}" name="месяц" dataDxfId="0">
       <calculatedColumnFormula>CHOOSE(S2,"январь","февраль","март","апрель","май","июнь","июль","август","сентябрь","октябрь","ноябрь","декабрь")</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5868,9 +5903,9 @@
   <sheetData>
     <row r="1" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B1" s="83">
+        <v>35</v>
+      </c>
+      <c r="B1" s="69">
         <f>EDATE(B3, -1)</f>
         <v>46023</v>
       </c>
@@ -5882,30 +5917,30 @@
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A3" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B3" s="83">
+        <v>44</v>
+      </c>
+      <c r="B3" s="69">
         <v>46054</v>
       </c>
       <c r="F3"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A4" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="B4" s="102">
+        <v>144</v>
+      </c>
+      <c r="B4" s="81">
         <f>info!B7</f>
-        <v>67.599999999999994</v>
+        <v>55.2</v>
       </c>
       <c r="F4"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A5" s="5" t="s">
-        <v>152</v>
-      </c>
-      <c r="B5" s="93">
+        <v>145</v>
+      </c>
+      <c r="B5" s="79">
         <f>info!B6</f>
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -5914,63 +5949,63 @@
     <row r="7" spans="1:14" s="5" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A7" s="3"/>
       <c r="B7" s="3"/>
-      <c r="C7" s="78" t="s">
+      <c r="C7" s="82" t="s">
+        <v>36</v>
+      </c>
+      <c r="D7" s="83"/>
+      <c r="E7" s="84"/>
+      <c r="F7" s="85" t="s">
         <v>37</v>
       </c>
-      <c r="D7" s="79"/>
-      <c r="E7" s="80"/>
-      <c r="F7" s="96" t="s">
-        <v>38</v>
-      </c>
-      <c r="G7" s="97"/>
-      <c r="H7" s="98"/>
-      <c r="I7" s="99" t="s">
-        <v>153</v>
-      </c>
-      <c r="J7" s="100"/>
-      <c r="K7" s="101"/>
+      <c r="G7" s="86"/>
+      <c r="H7" s="87"/>
+      <c r="I7" s="88" t="s">
+        <v>146</v>
+      </c>
+      <c r="J7" s="89"/>
+      <c r="K7" s="90"/>
       <c r="M7" s="7"/>
       <c r="N7" s="7"/>
     </row>
-    <row r="8" spans="1:14" s="86" customFormat="1" ht="44" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="84" t="s">
+    <row r="8" spans="1:14" s="72" customFormat="1" ht="44" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="70" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="71" t="s">
         <v>39</v>
       </c>
-      <c r="B8" s="85" t="s">
+      <c r="C8" s="73" t="s">
         <v>40</v>
       </c>
-      <c r="C8" s="87" t="s">
+      <c r="D8" s="74" t="s">
         <v>41</v>
       </c>
-      <c r="D8" s="88" t="s">
+      <c r="E8" s="75" t="s">
         <v>42</v>
       </c>
-      <c r="E8" s="89" t="s">
+      <c r="F8" s="77" t="s">
+        <v>40</v>
+      </c>
+      <c r="G8" s="77" t="s">
+        <v>41</v>
+      </c>
+      <c r="H8" s="77" t="s">
+        <v>42</v>
+      </c>
+      <c r="I8" s="78" t="s">
+        <v>138</v>
+      </c>
+      <c r="J8" s="70" t="s">
+        <v>139</v>
+      </c>
+      <c r="K8" s="70" t="s">
+        <v>140</v>
+      </c>
+      <c r="L8" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="M8" s="8" t="s">
         <v>43</v>
-      </c>
-      <c r="F8" s="91" t="s">
-        <v>41</v>
-      </c>
-      <c r="G8" s="91" t="s">
-        <v>42</v>
-      </c>
-      <c r="H8" s="91" t="s">
-        <v>43</v>
-      </c>
-      <c r="I8" s="92" t="s">
-        <v>145</v>
-      </c>
-      <c r="J8" s="84" t="s">
-        <v>146</v>
-      </c>
-      <c r="K8" s="84" t="s">
-        <v>147</v>
-      </c>
-      <c r="L8" s="8" t="s">
-        <v>148</v>
-      </c>
-      <c r="M8" s="8" t="s">
-        <v>44</v>
       </c>
       <c r="N8" s="8" t="s">
         <v>11</v>
@@ -5981,41 +6016,48 @@
         <v>15</v>
       </c>
       <c r="B9" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="C9" s="36"/>
-      <c r="D9" s="37"/>
-      <c r="E9" s="38"/>
-      <c r="F9" s="90" t="str">
+        <v>45</v>
+      </c>
+      <c r="C9" s="102">
+        <v>201</v>
+      </c>
+      <c r="D9" s="103">
+        <v>4.2</v>
+      </c>
+      <c r="E9" s="109">
+        <v>844.2</v>
+      </c>
+      <c r="F9" s="97">
         <f>IFERROR(INDEX(usage!B:B, MATCH(CHECK!$B$3, usage!A:A, 0)) - INDEX(usage!B:B, MATCH(CHECK!$B$1, usage!A:A, 0)),"")</f>
-        <v/>
-      </c>
-      <c r="G9" s="90" t="e">
+        <v>201</v>
+      </c>
+      <c r="G9" s="76">
         <f>IF(F9&lt;M9, INDEX(tariffs!2:2, MATCH(CHECK!$B$3,tariffs!$1:$1, 0)), INDEX(tariffs!3:3, MATCH(CHECK!$B$3,tariffs!$1:$1, 0)))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="H9" s="91" t="str">
+        <v>4.2</v>
+      </c>
+      <c r="H9" s="108">
         <f>IFERROR(F9*G9,"")</f>
-        <v/>
-      </c>
-      <c r="I9" s="39" t="str">
-        <f>IFERROR(F9-C9, "")</f>
-        <v/>
-      </c>
-      <c r="J9" s="40" t="str">
-        <f>IFERROR(G9-D9, "")</f>
-        <v/>
-      </c>
-      <c r="K9" s="41">
-        <v>0.3</v>
+        <v>844.2</v>
+      </c>
+      <c r="I9" s="36">
+        <f t="shared" ref="I9:J11" si="0">IFERROR(F9-C9, "")</f>
+        <v>0</v>
+      </c>
+      <c r="J9" s="37">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K9" s="38">
+        <f>IFERROR(E9-H9,"")</f>
+        <v>0</v>
       </c>
       <c r="L9" s="3" t="str">
         <f>IF(ABS(K9)&lt;=1,"✔ ОК",IF(K9&gt;1,"❗ Превышение","❗ Недосчет"))</f>
         <v>✔ ОК</v>
       </c>
-      <c r="M9" s="42" t="str">
-        <f>IFERROR(INDEX(tariffs!19:19, MATCH(CHECK!$B$3, tariffs!$1:$1, 0)),"")</f>
-        <v/>
+      <c r="M9" s="39">
+        <f>IFERROR(INDEX(tariffs!16:16, MATCH(CHECK!$B$3, tariffs!$1:$1, 0)),"")</f>
+        <v>761</v>
       </c>
       <c r="N9" s="10" t="str">
         <f>VLOOKUP(A9,info!A13:B29, 2,FALSE)</f>
@@ -6027,36 +6069,46 @@
         <v>18</v>
       </c>
       <c r="B10" s="23" t="s">
-        <v>47</v>
-      </c>
-      <c r="C10" s="36"/>
-      <c r="D10" s="37"/>
-      <c r="E10" s="38"/>
-      <c r="F10" s="90" t="str">
+        <v>46</v>
+      </c>
+      <c r="C10" s="93">
+        <v>4.5979999999999999</v>
+      </c>
+      <c r="D10" s="103">
+        <v>62.98</v>
+      </c>
+      <c r="E10" s="109">
+        <v>289.58203999999995</v>
+      </c>
+      <c r="F10" s="95">
         <f>IFERROR(INDEX(usage!C:C, MATCH(CHECK!$B$3, usage!A:A, 0)) - INDEX(usage!C:C, MATCH(CHECK!$B$1, usage!A:A, 0)),"")</f>
-        <v/>
-      </c>
-      <c r="G10" s="90" t="e">
+        <v>4.597999999999999</v>
+      </c>
+      <c r="G10" s="76">
         <f>INDEX(tariffs!4:4, MATCH(CHECK!$B$3,tariffs!$1:$1, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="H10" s="91" t="str">
-        <f>IFERROR(F10*G10,"")</f>
-        <v/>
-      </c>
-      <c r="I10" s="39" t="str">
-        <f>IFERROR(F10-C10, "")</f>
-        <v/>
-      </c>
-      <c r="J10" s="40" t="str">
-        <f>IFERROR(G10-D10, "")</f>
-        <v/>
-      </c>
-      <c r="K10" s="41" t="str">
+        <v>62.98</v>
+      </c>
+      <c r="H10" s="108">
+        <f t="shared" ref="H10:H24" si="1">IFERROR(F10*G10,"")</f>
+        <v>289.58203999999995</v>
+      </c>
+      <c r="I10" s="36">
+        <f t="shared" si="0"/>
+        <v>-8.8817841970012523E-16</v>
+      </c>
+      <c r="J10" s="37">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K10" s="38">
         <f>IFERROR(E10-H10,"")</f>
-        <v/>
-      </c>
-      <c r="M10" s="42"/>
+        <v>0</v>
+      </c>
+      <c r="L10" s="3" t="str">
+        <f t="shared" ref="L10:L24" si="2">IF(ABS(K10)&lt;=1,"✔ ОК",IF(K10&gt;1,"❗ Превышение","❗ Недосчет"))</f>
+        <v>✔ ОК</v>
+      </c>
+      <c r="M10" s="39"/>
       <c r="N10" s="10" t="str">
         <f>VLOOKUP(A10,info!A14:B30, 2,FALSE)</f>
         <v>Поставщик воды</v>
@@ -6064,37 +6116,47 @@
     </row>
     <row r="11" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A11" s="21" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="B11" s="23" t="s">
-        <v>47</v>
-      </c>
-      <c r="C11" s="36"/>
-      <c r="D11" s="37"/>
-      <c r="E11" s="38"/>
-      <c r="F11" s="90" t="str">
-        <f>IFERROR(INDEX(usage!D:D, MATCH(CHECK!$B$3, usage!A:A, 0)) - INDEX(usage!D:D, MATCH(CHECK!$B$1, usage!A:A, 0)),"")</f>
-        <v/>
-      </c>
-      <c r="G11" s="90" t="e">
+        <v>46</v>
+      </c>
+      <c r="C11" s="93">
+        <v>4.5979999999999999</v>
+      </c>
+      <c r="D11" s="103">
+        <v>44.12</v>
+      </c>
+      <c r="E11" s="109">
+        <v>202.86375999999998</v>
+      </c>
+      <c r="F11" s="95">
+        <f>F10</f>
+        <v>4.597999999999999</v>
+      </c>
+      <c r="G11" s="76">
         <f>INDEX(tariffs!5:5, MATCH(CHECK!$B$3,tariffs!$1:$1, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="H11" s="91" t="str">
-        <f>IFERROR(F11*G11,"")</f>
-        <v/>
-      </c>
-      <c r="I11" s="39" t="str">
-        <f>IFERROR(F11-C11, "")</f>
-        <v/>
-      </c>
-      <c r="J11" s="40" t="str">
-        <f>IFERROR(G11-D11, "")</f>
-        <v/>
-      </c>
-      <c r="K11" s="41" t="str">
+        <v>44.12</v>
+      </c>
+      <c r="H11" s="108">
+        <f t="shared" si="1"/>
+        <v>202.86375999999996</v>
+      </c>
+      <c r="I11" s="36">
+        <f t="shared" si="0"/>
+        <v>-8.8817841970012523E-16</v>
+      </c>
+      <c r="J11" s="37">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K11" s="38">
         <f>IFERROR(E11-H11,"")</f>
-        <v/>
+        <v>2.8421709430404007E-14</v>
+      </c>
+      <c r="L11" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>✔ ОК</v>
       </c>
       <c r="N11" s="10" t="str">
         <f>VLOOKUP(A11,info!A15:B31, 2,FALSE)</f>
@@ -6103,20 +6165,39 @@
     </row>
     <row r="12" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A12" s="21" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="B12" s="23" t="s">
-        <v>47</v>
-      </c>
-      <c r="C12" s="36"/>
-      <c r="D12" s="37"/>
-      <c r="E12" s="38"/>
-      <c r="F12" s="90"/>
-      <c r="G12" s="90"/>
-      <c r="H12" s="91"/>
-      <c r="I12" s="39"/>
-      <c r="J12" s="40"/>
-      <c r="K12" s="41"/>
+        <v>46</v>
+      </c>
+      <c r="C12" s="93">
+        <v>3.202</v>
+      </c>
+      <c r="D12" s="103">
+        <v>62.98</v>
+      </c>
+      <c r="E12" s="109">
+        <v>201.66195999999999</v>
+      </c>
+      <c r="F12" s="95">
+        <f>IFERROR(INDEX(usage!D:D, MATCH(CHECK!$B$3, usage!A:A, 0)) - INDEX(usage!D:D, MATCH(CHECK!$B$1, usage!A:A, 0)),"")</f>
+        <v>3.202</v>
+      </c>
+      <c r="G12" s="76">
+        <f>INDEX(tariffs!4:4, MATCH(CHECK!$B$3,tariffs!$1:$1, 0))</f>
+        <v>62.98</v>
+      </c>
+      <c r="H12" s="108">
+        <f t="shared" si="1"/>
+        <v>201.66195999999999</v>
+      </c>
+      <c r="I12" s="36"/>
+      <c r="J12" s="37"/>
+      <c r="K12" s="38"/>
+      <c r="L12" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>✔ ОК</v>
+      </c>
       <c r="N12" s="10" t="str">
         <f>VLOOKUP(A12,info!A16:B32, 2,FALSE)</f>
         <v>Поставщик воды</v>
@@ -6124,39 +6205,49 @@
     </row>
     <row r="13" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A13" s="21" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="B13" s="23" t="s">
-        <v>47</v>
-      </c>
-      <c r="C13" s="36"/>
-      <c r="D13" s="37"/>
-      <c r="E13" s="38"/>
-      <c r="F13" s="90" t="str">
-        <f>IFERROR(INDEX(usage!C:C, MATCH(CHECK!$B$3, usage!A:A, 0)) - INDEX(usage!C:C, MATCH(CHECK!$B$1, usage!A:A, 0)),"")</f>
-        <v/>
-      </c>
-      <c r="G13" s="90" t="e">
-        <f>INDEX(tariffs!6:6, MATCH(CHECK!$B$3,tariffs!$1:$1, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="H13" s="91" t="str">
-        <f>IFERROR(F13*G13,"")</f>
-        <v/>
-      </c>
-      <c r="I13" s="39" t="str">
-        <f>IFERROR(F13-C13, "")</f>
-        <v/>
-      </c>
-      <c r="J13" s="40" t="str">
-        <f>IFERROR(G13-D13, "")</f>
-        <v/>
-      </c>
-      <c r="K13" s="41" t="str">
+        <v>46</v>
+      </c>
+      <c r="C13" s="93">
+        <v>3.202</v>
+      </c>
+      <c r="D13" s="103">
+        <v>44.12</v>
+      </c>
+      <c r="E13" s="109">
+        <v>141.27223999999998</v>
+      </c>
+      <c r="F13" s="95">
+        <f>F12</f>
+        <v>3.202</v>
+      </c>
+      <c r="G13" s="76">
+        <f>INDEX(tariffs!5:5, MATCH(CHECK!$B$3,tariffs!$1:$1, 0))</f>
+        <v>44.12</v>
+      </c>
+      <c r="H13" s="108">
+        <f t="shared" si="1"/>
+        <v>141.27223999999998</v>
+      </c>
+      <c r="I13" s="36">
+        <f t="shared" ref="I13:J15" si="3">IFERROR(F13-C13, "")</f>
+        <v>0</v>
+      </c>
+      <c r="J13" s="37">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K13" s="38">
         <f>IFERROR(E13-H13,"")</f>
-        <v/>
-      </c>
-      <c r="M13" s="42"/>
+        <v>0</v>
+      </c>
+      <c r="L13" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>✔ ОК</v>
+      </c>
+      <c r="M13" s="39"/>
       <c r="N13" s="10" t="str">
         <f>VLOOKUP(A13,info!A17:B33, 2,FALSE)</f>
         <v>Поставщик воды</v>
@@ -6164,41 +6255,51 @@
     </row>
     <row r="14" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A14" s="21" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B14" s="23" t="s">
-        <v>47</v>
-      </c>
-      <c r="C14" s="44"/>
-      <c r="D14" s="43"/>
-      <c r="E14" s="38"/>
-      <c r="F14" s="90" t="str">
-        <f>IFERROR(M14,"")</f>
-        <v/>
-      </c>
-      <c r="G14" s="90" t="e">
-        <f>INDEX(tariffs!10:10, MATCH(CHECK!$B$3,tariffs!$1:$1, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="H14" s="91" t="str">
-        <f>IFERROR(F14*G14,"")</f>
-        <v/>
-      </c>
-      <c r="I14" s="39" t="str">
-        <f>IFERROR(F14-C14, "")</f>
-        <v/>
-      </c>
-      <c r="J14" s="40" t="str">
-        <f>IFERROR(G14-D14, "")</f>
-        <v/>
-      </c>
-      <c r="K14" s="41" t="str">
+        <v>46</v>
+      </c>
+      <c r="C14" s="94">
+        <v>6.5110000000000001</v>
+      </c>
+      <c r="D14" s="104">
+        <v>227.18</v>
+      </c>
+      <c r="E14" s="109">
+        <v>1479.1689800000001</v>
+      </c>
+      <c r="F14" s="95">
+        <f>IFERROR(C14,"")</f>
+        <v>6.5110000000000001</v>
+      </c>
+      <c r="G14" s="76">
+        <f>INDEX(tariffs!6:6, MATCH(CHECK!$B$3,tariffs!$1:$1, 0))</f>
+        <v>227.18</v>
+      </c>
+      <c r="H14" s="108">
+        <f t="shared" si="1"/>
+        <v>1479.1689800000001</v>
+      </c>
+      <c r="I14" s="36">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J14" s="37">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K14" s="38">
         <f>IFERROR(E14-H14,"")</f>
-        <v/>
-      </c>
-      <c r="M14" s="47" t="str">
-        <f>IFERROR(INDEX(tariffs!21:21, MATCH(CHECK!$B$3, tariffs!$1:$1, 0)),"")</f>
-        <v/>
+        <v>0</v>
+      </c>
+      <c r="L14" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>✔ ОК</v>
+      </c>
+      <c r="M14" s="42">
+        <f>IFERROR(INDEX(tariffs!18:18, MATCH(CHECK!$B$3, tariffs!$1:$1, 0)),"")</f>
+        <v>16.2</v>
       </c>
       <c r="N14" s="10" t="str">
         <f>VLOOKUP(A14,info!A18:B34, 2,FALSE)</f>
@@ -6207,39 +6308,49 @@
     </row>
     <row r="15" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A15" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B15" s="23" t="s">
-        <v>49</v>
-      </c>
-      <c r="C15" s="36"/>
-      <c r="D15" s="43"/>
-      <c r="E15" s="38"/>
-      <c r="F15" s="90">
+        <v>48</v>
+      </c>
+      <c r="C15" s="93">
+        <v>3.9864999999999999</v>
+      </c>
+      <c r="D15" s="104">
+        <v>3549.74</v>
+      </c>
+      <c r="E15" s="109">
+        <v>14151.038509999998</v>
+      </c>
+      <c r="F15" s="98">
         <f>IFERROR(C15,"")</f>
+        <v>3.9864999999999999</v>
+      </c>
+      <c r="G15" s="76">
+        <f>INDEX(tariffs!7:7, MATCH(CHECK!$B$3,tariffs!$1:$1, 0))</f>
+        <v>3549.74</v>
+      </c>
+      <c r="H15" s="108">
+        <f t="shared" si="1"/>
+        <v>14151.038509999998</v>
+      </c>
+      <c r="I15" s="36">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="G15" s="90" t="e">
-        <f>INDEX(tariffs!11:11, MATCH(CHECK!$B$3,tariffs!$1:$1, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="H15" s="91" t="str">
-        <f>IFERROR(F15*G15,"")</f>
-        <v/>
-      </c>
-      <c r="I15" s="39">
-        <f>IFERROR(F15-C15, "")</f>
+      <c r="J15" s="37">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J15" s="40" t="str">
-        <f>IFERROR(G15-D15, "")</f>
-        <v/>
-      </c>
-      <c r="K15" s="41" t="str">
+      <c r="K15" s="38">
         <f>IFERROR(E15-H15,"")</f>
-        <v/>
-      </c>
-      <c r="M15" s="42"/>
+        <v>0</v>
+      </c>
+      <c r="L15" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>✔ ОК</v>
+      </c>
+      <c r="M15" s="39"/>
       <c r="N15" s="10" t="str">
         <f>VLOOKUP(A15,info!A19:B35, 2,FALSE)</f>
         <v>Управляющая</v>
@@ -6247,21 +6358,40 @@
     </row>
     <row r="16" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A16" s="21" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="B16" s="23" t="s">
-        <v>47</v>
-      </c>
-      <c r="C16" s="36"/>
-      <c r="D16" s="37"/>
-      <c r="E16" s="38"/>
-      <c r="F16" s="90"/>
-      <c r="G16" s="90"/>
-      <c r="H16" s="91"/>
-      <c r="I16" s="39"/>
-      <c r="J16" s="40"/>
-      <c r="K16" s="41"/>
-      <c r="M16" s="42"/>
+        <v>46</v>
+      </c>
+      <c r="C16" s="93">
+        <v>0.89500000000000002</v>
+      </c>
+      <c r="D16" s="103">
+        <v>227.18</v>
+      </c>
+      <c r="E16" s="109">
+        <v>203.3261</v>
+      </c>
+      <c r="F16" s="95">
+        <f t="shared" ref="F16:F20" si="4">IFERROR(C16,"")</f>
+        <v>0.89500000000000002</v>
+      </c>
+      <c r="G16" s="76">
+        <f>INDEX(tariffs!6:6, MATCH(CHECK!$B$3,tariffs!$1:$1, 0))</f>
+        <v>227.18</v>
+      </c>
+      <c r="H16" s="108">
+        <f t="shared" si="1"/>
+        <v>203.3261</v>
+      </c>
+      <c r="I16" s="36"/>
+      <c r="J16" s="37"/>
+      <c r="K16" s="38"/>
+      <c r="L16" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>✔ ОК</v>
+      </c>
+      <c r="M16" s="39"/>
       <c r="N16" s="10" t="str">
         <f>VLOOKUP(A16,info!A20:B36, 2,FALSE)</f>
         <v>Управляющая</v>
@@ -6269,41 +6399,51 @@
     </row>
     <row r="17" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A17" s="21" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="B17" s="23" t="s">
-        <v>47</v>
-      </c>
-      <c r="C17" s="36"/>
-      <c r="D17" s="37"/>
-      <c r="E17" s="38"/>
-      <c r="F17" s="90" t="str">
-        <f>IFERROR(M17,"")</f>
-        <v/>
-      </c>
-      <c r="G17" s="90" t="e">
-        <f>INDEX(tariffs!9:9, MATCH(CHECK!$B$3,tariffs!$1:$1, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="H17" s="91" t="str">
-        <f>IFERROR(F17*G17,"")</f>
-        <v/>
-      </c>
-      <c r="I17" s="39" t="str">
-        <f>IFERROR(F17-C17, "")</f>
-        <v/>
-      </c>
-      <c r="J17" s="40" t="str">
-        <f>IFERROR(G17-D17, "")</f>
-        <v/>
-      </c>
-      <c r="K17" s="41" t="str">
-        <f>IFERROR(E17-H17,"")</f>
-        <v/>
-      </c>
-      <c r="M17" s="47" t="str">
-        <f>IFERROR(INDEX(tariffs!20:20, MATCH(CHECK!$B$3, tariffs!$1:$1, 0)),"")</f>
-        <v/>
+        <v>46</v>
+      </c>
+      <c r="C17" s="93">
+        <v>0.89500000000000002</v>
+      </c>
+      <c r="D17" s="103">
+        <v>62.98</v>
+      </c>
+      <c r="E17" s="109">
+        <v>56.367100000000001</v>
+      </c>
+      <c r="F17" s="95">
+        <f t="shared" si="4"/>
+        <v>0.89500000000000002</v>
+      </c>
+      <c r="G17" s="76">
+        <f>INDEX(tariffs!4:4, MATCH(CHECK!$B$3,tariffs!$1:$1, 0))</f>
+        <v>62.98</v>
+      </c>
+      <c r="H17" s="108">
+        <f t="shared" si="1"/>
+        <v>56.367100000000001</v>
+      </c>
+      <c r="I17" s="36">
+        <f t="shared" ref="I17:J24" si="5">IFERROR(F17-C17, "")</f>
+        <v>0</v>
+      </c>
+      <c r="J17" s="37">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="K17" s="38">
+        <f t="shared" ref="K17:K24" si="6">IFERROR(E17-H17,"")</f>
+        <v>0</v>
+      </c>
+      <c r="L17" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>✔ ОК</v>
+      </c>
+      <c r="M17" s="42">
+        <f>IFERROR(INDEX(tariffs!17:17, MATCH(CHECK!$B$3, tariffs!$1:$1, 0)),"")</f>
+        <v>0.67909799999999998</v>
       </c>
       <c r="N17" s="10" t="str">
         <f>VLOOKUP(A17,info!A21:B37, 2,FALSE)</f>
@@ -6312,41 +6452,51 @@
     </row>
     <row r="18" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A18" s="21" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="B18" s="23" t="s">
-        <v>47</v>
-      </c>
-      <c r="C18" s="36"/>
-      <c r="D18" s="43"/>
-      <c r="E18" s="38"/>
-      <c r="F18" s="90" t="str">
-        <f>IFERROR(M18,"")</f>
-        <v/>
-      </c>
-      <c r="G18" s="90" t="e">
+        <v>46</v>
+      </c>
+      <c r="C18" s="93">
+        <v>1.3520000000000001</v>
+      </c>
+      <c r="D18" s="104">
+        <v>62.98</v>
+      </c>
+      <c r="E18" s="109">
+        <v>85.148960000000002</v>
+      </c>
+      <c r="F18" s="95">
+        <f t="shared" si="4"/>
+        <v>1.3520000000000001</v>
+      </c>
+      <c r="G18" s="76">
         <f>INDEX(tariffs!4:4, MATCH(CHECK!$B$3,tariffs!$1:$1, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="H18" s="91" t="str">
-        <f>IFERROR(F18*G18,"")</f>
-        <v/>
-      </c>
-      <c r="I18" s="39" t="str">
-        <f>IFERROR(F18-C18, "")</f>
-        <v/>
-      </c>
-      <c r="J18" s="40" t="str">
-        <f>IFERROR(G18-D18, "")</f>
-        <v/>
-      </c>
-      <c r="K18" s="41" t="str">
-        <f>IFERROR(E18-H18,"")</f>
-        <v/>
-      </c>
-      <c r="M18" s="47" t="str">
-        <f>IFERROR(INDEX(tariffs!23:23, MATCH(CHECK!$B$3, tariffs!$1:$1, 0)),"")</f>
-        <v/>
+        <v>62.98</v>
+      </c>
+      <c r="H18" s="108">
+        <f t="shared" si="1"/>
+        <v>85.148960000000002</v>
+      </c>
+      <c r="I18" s="36">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="J18" s="37">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="K18" s="38">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="L18" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>✔ ОК</v>
+      </c>
+      <c r="M18" s="42">
+        <f>IFERROR(INDEX(tariffs!20:20, MATCH(CHECK!$B$3, tariffs!$1:$1, 0)),"")</f>
+        <v>1.358196</v>
       </c>
       <c r="N18" s="10" t="str">
         <f>VLOOKUP(A18,info!A22:B38, 2,FALSE)</f>
@@ -6355,41 +6505,51 @@
     </row>
     <row r="19" spans="1:14" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A19" s="21" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="B19" s="23" t="s">
-        <v>47</v>
-      </c>
-      <c r="C19" s="36"/>
-      <c r="D19" s="43"/>
-      <c r="E19" s="38"/>
-      <c r="F19" s="90" t="str">
-        <f>IFERROR(M19,"")</f>
-        <v/>
-      </c>
-      <c r="G19" s="90" t="e">
-        <f>INDEX(tariffs!6:6, MATCH(CHECK!$B$3,tariffs!$1:$1, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="H19" s="91" t="str">
-        <f>IFERROR(F19*G19,"")</f>
-        <v/>
-      </c>
-      <c r="I19" s="39" t="str">
-        <f>IFERROR(F19-C19, "")</f>
-        <v/>
-      </c>
-      <c r="J19" s="40" t="str">
-        <f>IFERROR(G19-D19, "")</f>
-        <v/>
-      </c>
-      <c r="K19" s="41" t="str">
-        <f>IFERROR(E19-H19,"")</f>
-        <v/>
-      </c>
-      <c r="M19" s="47" t="str">
-        <f>IFERROR(INDEX(tariffs!24:24, MATCH(CHECK!$B$3, tariffs!$1:$1, 0)),"")</f>
-        <v/>
+        <v>46</v>
+      </c>
+      <c r="C19" s="93">
+        <v>1.3520000000000001</v>
+      </c>
+      <c r="D19" s="104">
+        <v>44.12</v>
+      </c>
+      <c r="E19" s="109">
+        <v>59.650240000000004</v>
+      </c>
+      <c r="F19" s="95">
+        <f t="shared" si="4"/>
+        <v>1.3520000000000001</v>
+      </c>
+      <c r="G19" s="76">
+        <f>INDEX(tariffs!5:5, MATCH(CHECK!$B$3,tariffs!$1:$1, 0))</f>
+        <v>44.12</v>
+      </c>
+      <c r="H19" s="108">
+        <f t="shared" si="1"/>
+        <v>59.650240000000004</v>
+      </c>
+      <c r="I19" s="36">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="J19" s="37">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="K19" s="38">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="L19" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>✔ ОК</v>
+      </c>
+      <c r="M19" s="42">
+        <f>IFERROR(INDEX(tariffs!21:21, MATCH(CHECK!$B$3, tariffs!$1:$1, 0)),"")</f>
+        <v>1.358196</v>
       </c>
       <c r="N19" s="10" t="str">
         <f>VLOOKUP(A19,info!A23:B39, 2,FALSE)</f>
@@ -6398,41 +6558,51 @@
     </row>
     <row r="20" spans="1:14" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A20" s="21" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="B20" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="C20" s="36"/>
-      <c r="D20" s="37"/>
-      <c r="E20" s="38"/>
-      <c r="F20" s="90" t="str">
-        <f>IFERROR(M20,"")</f>
-        <v/>
-      </c>
-      <c r="G20" s="90" t="e">
+        <v>45</v>
+      </c>
+      <c r="C20" s="93">
+        <v>32.22</v>
+      </c>
+      <c r="D20" s="103">
+        <v>4.2</v>
+      </c>
+      <c r="E20" s="109">
+        <v>135.32400000000001</v>
+      </c>
+      <c r="F20" s="76">
+        <f t="shared" si="4"/>
+        <v>32.22</v>
+      </c>
+      <c r="G20" s="76">
         <f>INDEX(tariffs!2:2, MATCH(CHECK!$B$3,tariffs!$1:$1, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="H20" s="91" t="str">
-        <f>IFERROR(F20*G20,"")</f>
-        <v/>
-      </c>
-      <c r="I20" s="39" t="str">
-        <f>IFERROR(F20-C20, "")</f>
-        <v/>
-      </c>
-      <c r="J20" s="40" t="str">
-        <f>IFERROR(G20-D20, "")</f>
-        <v/>
-      </c>
-      <c r="K20" s="41" t="str">
-        <f>IFERROR(E20-H20,"")</f>
-        <v/>
-      </c>
-      <c r="M20" s="47" t="str">
-        <f>IFERROR(INDEX(tariffs!22:22, MATCH(CHECK!$B$3, tariffs!$1:$1, 0)),"")</f>
-        <v/>
+        <v>4.2</v>
+      </c>
+      <c r="H20" s="108">
+        <f t="shared" si="1"/>
+        <v>135.32400000000001</v>
+      </c>
+      <c r="I20" s="36">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="J20" s="37">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="K20" s="38">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="L20" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>✔ ОК</v>
+      </c>
+      <c r="M20" s="42">
+        <f>IFERROR(INDEX(tariffs!19:19, MATCH(CHECK!$B$3, tariffs!$1:$1, 0)),"")</f>
+        <v>26.829499999999999</v>
       </c>
       <c r="N20" s="10" t="str">
         <f>VLOOKUP(A20,info!A24:B40, 2,FALSE)</f>
@@ -6441,39 +6611,49 @@
     </row>
     <row r="21" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A21" s="21" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="B21" s="23" t="s">
-        <v>48</v>
-      </c>
-      <c r="C21" s="36"/>
-      <c r="D21" s="37"/>
-      <c r="E21" s="38"/>
-      <c r="F21" s="90">
+        <v>47</v>
+      </c>
+      <c r="C21" s="93">
+        <v>55.2</v>
+      </c>
+      <c r="D21" s="103">
+        <v>11.08</v>
+      </c>
+      <c r="E21" s="109">
+        <v>611.61599999999999</v>
+      </c>
+      <c r="F21" s="96">
         <f>IFERROR(info!$B$7,"")</f>
-        <v>67.599999999999994</v>
-      </c>
-      <c r="G21" s="90" t="e">
+        <v>55.2</v>
+      </c>
+      <c r="G21" s="76">
         <f>INDEX(tariffs!8:8, MATCH(CHECK!$B$3,tariffs!$1:$1, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="H21" s="91" t="str">
-        <f>IFERROR(F21*G21,"")</f>
-        <v/>
-      </c>
-      <c r="I21" s="39">
-        <f>IFERROR(F21-C21, "")</f>
-        <v>67.599999999999994</v>
-      </c>
-      <c r="J21" s="40" t="str">
-        <f>IFERROR(G21-D21, "")</f>
-        <v/>
-      </c>
-      <c r="K21" s="41" t="str">
-        <f>IFERROR(E21-H21,"")</f>
-        <v/>
-      </c>
-      <c r="M21" s="42"/>
+        <v>11.08</v>
+      </c>
+      <c r="H21" s="108">
+        <f t="shared" si="1"/>
+        <v>611.61599999999999</v>
+      </c>
+      <c r="I21" s="36">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="J21" s="37">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="K21" s="38">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="L21" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>✔ ОК</v>
+      </c>
+      <c r="M21" s="39"/>
       <c r="N21" s="10" t="str">
         <f>VLOOKUP(A21,info!A25:B41, 2,FALSE)</f>
         <v>Управляющая</v>
@@ -6484,36 +6664,46 @@
         <v>21</v>
       </c>
       <c r="B22" s="23" t="s">
-        <v>48</v>
-      </c>
-      <c r="C22" s="36"/>
-      <c r="D22" s="37"/>
-      <c r="E22" s="38"/>
-      <c r="F22" s="90">
+        <v>47</v>
+      </c>
+      <c r="C22" s="93">
+        <v>55.2</v>
+      </c>
+      <c r="D22" s="103">
+        <v>5.98</v>
+      </c>
+      <c r="E22" s="109">
+        <v>330.09600000000006</v>
+      </c>
+      <c r="F22" s="96">
         <f>IFERROR(info!$B$7,"")</f>
-        <v>67.599999999999994</v>
-      </c>
-      <c r="G22" s="90" t="e">
-        <f>INDEX(tariffs!7:7, MATCH(CHECK!$B$3,tariffs!$1:$1, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="H22" s="91" t="str">
-        <f>IFERROR(F22*G22,"")</f>
-        <v/>
-      </c>
-      <c r="I22" s="39">
-        <f>IFERROR(F22-C22, "")</f>
-        <v>67.599999999999994</v>
-      </c>
-      <c r="J22" s="40" t="str">
-        <f>IFERROR(G22-D22, "")</f>
-        <v/>
-      </c>
-      <c r="K22" s="41" t="str">
-        <f>IFERROR(E22-H22,"")</f>
-        <v/>
-      </c>
-      <c r="M22" s="42"/>
+        <v>55.2</v>
+      </c>
+      <c r="G22" s="76">
+        <f>INDEX(tariffs!9:9, MATCH(CHECK!$B$3,tariffs!$1:$1, 0))</f>
+        <v>5.98</v>
+      </c>
+      <c r="H22" s="108">
+        <f t="shared" si="1"/>
+        <v>330.09600000000006</v>
+      </c>
+      <c r="I22" s="36">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="J22" s="37">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="K22" s="38">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="L22" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>✔ ОК</v>
+      </c>
+      <c r="M22" s="39"/>
       <c r="N22" s="10" t="str">
         <f>VLOOKUP(A22,info!A26:B42, 2,FALSE)</f>
         <v>Управляющая</v>
@@ -6521,41 +6711,51 @@
     </row>
     <row r="23" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A23" s="21" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="B23" s="23" t="s">
-        <v>50</v>
-      </c>
-      <c r="C23" s="36"/>
-      <c r="D23" s="37"/>
-      <c r="E23" s="38"/>
-      <c r="F23" s="90">
+        <v>49</v>
+      </c>
+      <c r="C23" s="93">
+        <v>2</v>
+      </c>
+      <c r="D23" s="103">
+        <v>161.52260000000001</v>
+      </c>
+      <c r="E23" s="109">
+        <v>323.04520000000002</v>
+      </c>
+      <c r="F23" s="97">
         <f>IFERROR(info!$B$6,"")</f>
-        <v>5</v>
-      </c>
-      <c r="G23" s="90" t="str">
+        <v>2</v>
+      </c>
+      <c r="G23" s="76">
         <f>IF(D23&lt;M23, D23,M23)</f>
-        <v/>
-      </c>
-      <c r="H23" s="91" t="str">
-        <f>IFERROR(F23*G23,"")</f>
-        <v/>
-      </c>
-      <c r="I23" s="39">
-        <f>IFERROR(F23-C23, "")</f>
-        <v>5</v>
-      </c>
-      <c r="J23" s="40" t="str">
-        <f>IFERROR(G23-D23, "")</f>
-        <v/>
-      </c>
-      <c r="K23" s="41" t="str">
-        <f>IFERROR(E23-H23,"")</f>
-        <v/>
-      </c>
-      <c r="M23" s="42" t="str">
-        <f>IFERROR(INDEX(tariffs!12:12, MATCH(CHECK!$B$3, tariffs!$1:$1, 0)),"")</f>
-        <v/>
+        <v>161.52257251624999</v>
+      </c>
+      <c r="H23" s="108">
+        <f t="shared" si="1"/>
+        <v>323.04514503249999</v>
+      </c>
+      <c r="I23" s="36">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="J23" s="37">
+        <f t="shared" si="5"/>
+        <v>-2.7483750017154307E-5</v>
+      </c>
+      <c r="K23" s="38">
+        <f t="shared" si="6"/>
+        <v>5.4967500034308614E-5</v>
+      </c>
+      <c r="L23" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>✔ ОК</v>
+      </c>
+      <c r="M23" s="39">
+        <f>IFERROR(INDEX(tariffs!10:10, MATCH(CHECK!$B$3, tariffs!$1:$1, 0)),"")</f>
+        <v>161.52257251624999</v>
       </c>
       <c r="N23" s="10" t="str">
         <f>VLOOKUP(A23,info!A27:B43, 2,FALSE)</f>
@@ -6564,39 +6764,49 @@
     </row>
     <row r="24" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A24" s="21" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B24" s="23" t="s">
-        <v>48</v>
-      </c>
-      <c r="C24" s="74"/>
-      <c r="D24" s="75"/>
-      <c r="E24" s="76"/>
-      <c r="F24" s="90">
+        <v>47</v>
+      </c>
+      <c r="C24" s="106">
+        <v>55.2</v>
+      </c>
+      <c r="D24" s="105">
+        <v>15.15</v>
+      </c>
+      <c r="E24" s="110">
+        <v>836.28000000000009</v>
+      </c>
+      <c r="F24" s="96">
         <f>IFERROR(info!$B$7,"")</f>
-        <v>67.599999999999994</v>
-      </c>
-      <c r="G24" s="90" t="e">
-        <f>INDEX(tariffs!13:13, MATCH(CHECK!$B$3,tariffs!$1:$1, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="H24" s="91" t="str">
-        <f>IFERROR(F24*G24,"")</f>
-        <v/>
-      </c>
-      <c r="I24" s="39">
-        <f>IFERROR(F24-C24, "")</f>
-        <v>67.599999999999994</v>
-      </c>
-      <c r="J24" s="40" t="str">
-        <f>IFERROR(G24-D24, "")</f>
-        <v/>
-      </c>
-      <c r="K24" s="41" t="str">
-        <f>IFERROR(E24-H24,"")</f>
-        <v/>
-      </c>
-      <c r="M24" s="42"/>
+        <v>55.2</v>
+      </c>
+      <c r="G24" s="76">
+        <f>INDEX(tariffs!11:11, MATCH(CHECK!$B$3,tariffs!$1:$1, 0))</f>
+        <v>15.15</v>
+      </c>
+      <c r="H24" s="108">
+        <f t="shared" si="1"/>
+        <v>836.28000000000009</v>
+      </c>
+      <c r="I24" s="36">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="J24" s="37">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="K24" s="38">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="L24" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>✔ ОК</v>
+      </c>
+      <c r="M24" s="39"/>
       <c r="N24" s="10" t="str">
         <f>VLOOKUP(A24,info!A28:B44, 2,FALSE)</f>
         <v>Капремонт</v>
@@ -6604,178 +6814,178 @@
     </row>
     <row r="25" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A25" s="11"/>
-      <c r="C25" s="45"/>
-      <c r="D25" s="45"/>
-      <c r="E25" s="45"/>
-      <c r="F25" s="45"/>
-      <c r="G25" s="45"/>
-      <c r="H25" s="45"/>
-      <c r="I25" s="45"/>
-      <c r="J25" s="45"/>
-      <c r="K25" s="45"/>
-      <c r="L25" s="45"/>
-      <c r="M25" s="45"/>
+      <c r="C25" s="40"/>
+      <c r="D25" s="40"/>
+      <c r="E25" s="40"/>
+      <c r="F25" s="40"/>
+      <c r="G25" s="40"/>
+      <c r="H25" s="40"/>
+      <c r="I25" s="40"/>
+      <c r="J25" s="40"/>
+      <c r="K25" s="40"/>
+      <c r="L25" s="40"/>
+      <c r="M25" s="40"/>
     </row>
     <row r="26" spans="1:14" s="5" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="51" t="s">
+      <c r="A26" s="46" t="s">
+        <v>50</v>
+      </c>
+      <c r="B26" s="35"/>
+      <c r="C26" s="41"/>
+      <c r="D26" s="41"/>
+      <c r="E26" s="41">
+        <f>SUM(E9:E24)</f>
+        <v>19950.641089999994</v>
+      </c>
+      <c r="F26" s="41"/>
+      <c r="G26" s="41"/>
+      <c r="H26" s="41"/>
+      <c r="I26" s="41"/>
+      <c r="J26" s="41"/>
+      <c r="K26" s="41">
+        <f>SUM(K9:K24)</f>
+        <v>5.4967500062730323E-5</v>
+      </c>
+      <c r="L26" s="41"/>
+      <c r="M26" s="41"/>
+      <c r="N26" s="35"/>
+    </row>
+    <row r="27" spans="1:14" s="50" customFormat="1" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A27" s="47" t="s">
         <v>51</v>
       </c>
-      <c r="B26" s="35"/>
-      <c r="C26" s="46"/>
-      <c r="D26" s="46"/>
-      <c r="E26" s="46">
-        <f>SUM(E9:E24)</f>
+      <c r="B27" s="48"/>
+      <c r="C27" s="49"/>
+      <c r="D27" s="49"/>
+      <c r="E27" s="49"/>
+      <c r="F27" s="49"/>
+      <c r="G27" s="49"/>
+      <c r="H27" s="49"/>
+      <c r="I27" s="49"/>
+      <c r="J27" s="49"/>
+      <c r="K27" s="49"/>
+      <c r="L27" s="49"/>
+      <c r="M27" s="49"/>
+      <c r="N27" s="48"/>
+    </row>
+    <row r="28" spans="1:14" s="5" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A28" s="46" t="s">
+        <v>148</v>
+      </c>
+      <c r="B28" s="35"/>
+      <c r="C28" s="41"/>
+      <c r="D28" s="41"/>
+      <c r="E28" s="41">
+        <f>SUMIF($N:$N,$A28,E:E)</f>
+        <v>844.2</v>
+      </c>
+      <c r="F28" s="41"/>
+      <c r="G28" s="41"/>
+      <c r="H28" s="41"/>
+      <c r="I28" s="41"/>
+      <c r="J28" s="41"/>
+      <c r="K28" s="41">
+        <f>SUMIF($N:$N,$A28,K:K)</f>
         <v>0</v>
       </c>
-      <c r="F26" s="46"/>
-      <c r="G26" s="46"/>
-      <c r="H26" s="46"/>
-      <c r="I26" s="46"/>
-      <c r="J26" s="46"/>
-      <c r="K26" s="46">
-        <f>SUM(K9:K24)</f>
-        <v>0.3</v>
-      </c>
-      <c r="L26" s="46"/>
-      <c r="M26" s="46"/>
-      <c r="N26" s="35"/>
-    </row>
-    <row r="27" spans="1:14" s="55" customFormat="1" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="52" t="s">
-        <v>52</v>
-      </c>
-      <c r="B27" s="53"/>
-      <c r="C27" s="54"/>
-      <c r="D27" s="54"/>
-      <c r="E27" s="54"/>
-      <c r="F27" s="54"/>
-      <c r="G27" s="54"/>
-      <c r="H27" s="54"/>
-      <c r="I27" s="54"/>
-      <c r="J27" s="54"/>
-      <c r="K27" s="54"/>
-      <c r="L27" s="54"/>
-      <c r="M27" s="54"/>
-      <c r="N27" s="53"/>
-    </row>
-    <row r="28" spans="1:14" s="5" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="51" t="s">
-        <v>155</v>
-      </c>
-      <c r="B28" s="35"/>
-      <c r="C28" s="46"/>
-      <c r="D28" s="46"/>
-      <c r="E28" s="46">
-        <f>SUMIF($N:$N,$A28,E:E)</f>
-        <v>0</v>
-      </c>
-      <c r="F28" s="46"/>
-      <c r="G28" s="46"/>
-      <c r="H28" s="46"/>
-      <c r="I28" s="46"/>
-      <c r="J28" s="46"/>
-      <c r="K28" s="46">
-        <f>SUMIF($N:$N,$A28,K:K)</f>
-        <v>0.3</v>
-      </c>
-      <c r="L28" s="46"/>
-      <c r="M28" s="46"/>
+      <c r="L28" s="41"/>
+      <c r="M28" s="41"/>
       <c r="N28" s="35"/>
     </row>
     <row r="29" spans="1:14" s="5" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="51" t="s">
-        <v>156</v>
+      <c r="A29" s="46" t="s">
+        <v>149</v>
       </c>
       <c r="B29" s="35"/>
-      <c r="C29" s="46"/>
-      <c r="D29" s="46"/>
-      <c r="E29" s="46">
+      <c r="C29" s="41"/>
+      <c r="D29" s="41"/>
+      <c r="E29" s="41">
         <f>SUMIF($N:$N,$A29,E:E)</f>
-        <v>0</v>
-      </c>
-      <c r="F29" s="46"/>
-      <c r="G29" s="46"/>
-      <c r="H29" s="46"/>
-      <c r="I29" s="46"/>
-      <c r="J29" s="46"/>
-      <c r="K29" s="46">
+        <v>835.38</v>
+      </c>
+      <c r="F29" s="41"/>
+      <c r="G29" s="41"/>
+      <c r="H29" s="41"/>
+      <c r="I29" s="41"/>
+      <c r="J29" s="41"/>
+      <c r="K29" s="41">
         <f>SUMIF($N:$N,$A29,K:K)</f>
-        <v>0</v>
-      </c>
-      <c r="L29" s="46"/>
-      <c r="M29" s="46"/>
+        <v>2.8421709430404007E-14</v>
+      </c>
+      <c r="L29" s="41"/>
+      <c r="M29" s="41"/>
       <c r="N29" s="35"/>
     </row>
     <row r="30" spans="1:14" s="5" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A30" s="51" t="s">
-        <v>149</v>
+      <c r="A30" s="46" t="s">
+        <v>142</v>
       </c>
       <c r="B30" s="35"/>
-      <c r="C30" s="46"/>
-      <c r="D30" s="46"/>
-      <c r="E30" s="46">
+      <c r="C30" s="41"/>
+      <c r="D30" s="41"/>
+      <c r="E30" s="41">
         <f>SUMIF($N:$N,$A30,E:E)</f>
-        <v>0</v>
-      </c>
-      <c r="F30" s="46"/>
-      <c r="G30" s="46"/>
-      <c r="H30" s="46"/>
-      <c r="I30" s="46"/>
-      <c r="J30" s="46"/>
-      <c r="K30" s="46">
+        <v>17111.73589</v>
+      </c>
+      <c r="F30" s="41"/>
+      <c r="G30" s="41"/>
+      <c r="H30" s="41"/>
+      <c r="I30" s="41"/>
+      <c r="J30" s="41"/>
+      <c r="K30" s="41">
         <f>SUMIF($N:$N,$A30,K:K)</f>
         <v>0</v>
       </c>
-      <c r="L30" s="46"/>
-      <c r="M30" s="46"/>
+      <c r="L30" s="41"/>
+      <c r="M30" s="41"/>
       <c r="N30" s="35"/>
     </row>
     <row r="31" spans="1:14" s="5" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A31" s="51" t="s">
-        <v>150</v>
+      <c r="A31" s="46" t="s">
+        <v>143</v>
       </c>
       <c r="B31" s="35"/>
-      <c r="C31" s="46"/>
-      <c r="D31" s="46"/>
-      <c r="E31" s="46">
+      <c r="C31" s="41"/>
+      <c r="D31" s="41"/>
+      <c r="E31" s="41">
         <f>SUMIF($N:$N,$A31,E:E)</f>
-        <v>0</v>
-      </c>
-      <c r="F31" s="46"/>
-      <c r="G31" s="46"/>
-      <c r="H31" s="46"/>
-      <c r="I31" s="46"/>
-      <c r="J31" s="46"/>
-      <c r="K31" s="46">
+        <v>323.04520000000002</v>
+      </c>
+      <c r="F31" s="41"/>
+      <c r="G31" s="41"/>
+      <c r="H31" s="41"/>
+      <c r="I31" s="41"/>
+      <c r="J31" s="41"/>
+      <c r="K31" s="41">
         <f>SUMIF($N:$N,$A31,K:K)</f>
-        <v>0</v>
-      </c>
-      <c r="L31" s="46"/>
-      <c r="M31" s="46"/>
+        <v>5.4967500034308614E-5</v>
+      </c>
+      <c r="L31" s="41"/>
+      <c r="M31" s="41"/>
       <c r="N31" s="35"/>
     </row>
     <row r="32" spans="1:14" s="5" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A32" s="51" t="s">
-        <v>35</v>
+      <c r="A32" s="46" t="s">
+        <v>34</v>
       </c>
       <c r="B32" s="35"/>
-      <c r="C32" s="46"/>
-      <c r="D32" s="46"/>
-      <c r="E32" s="46">
+      <c r="C32" s="41"/>
+      <c r="D32" s="41"/>
+      <c r="E32" s="41">
         <f>SUMIF($N:$N,$A32,E:E)</f>
-        <v>0</v>
-      </c>
-      <c r="F32" s="46"/>
-      <c r="G32" s="46"/>
-      <c r="H32" s="46"/>
-      <c r="I32" s="46"/>
-      <c r="J32" s="46"/>
-      <c r="K32" s="46">
+        <v>836.28000000000009</v>
+      </c>
+      <c r="F32" s="41"/>
+      <c r="G32" s="41"/>
+      <c r="H32" s="41"/>
+      <c r="I32" s="41"/>
+      <c r="J32" s="41"/>
+      <c r="K32" s="41">
         <f>SUMIF($N:$N,$A32,K:K)</f>
         <v>0</v>
       </c>
-      <c r="L32" s="46"/>
-      <c r="M32" s="46"/>
+      <c r="L32" s="41"/>
+      <c r="M32" s="41"/>
       <c r="N32" s="35"/>
     </row>
   </sheetData>
@@ -6828,13 +7038,13 @@
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="22.7265625" customWidth="1"/>
-    <col min="3" max="4" width="12.26953125" style="59" customWidth="1"/>
-    <col min="5" max="5" width="12.26953125" style="61" customWidth="1"/>
-    <col min="6" max="6" width="12.26953125" style="60" customWidth="1"/>
-    <col min="7" max="8" width="9.90625" style="61" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.90625" style="61" customWidth="1"/>
-    <col min="10" max="10" width="9.90625" style="61" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="26.08984375" style="60" customWidth="1"/>
+    <col min="3" max="4" width="12.26953125" style="54" customWidth="1"/>
+    <col min="5" max="5" width="12.26953125" style="56" customWidth="1"/>
+    <col min="6" max="6" width="12.26953125" style="55" customWidth="1"/>
+    <col min="7" max="8" width="9.90625" style="56" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.90625" style="56" customWidth="1"/>
+    <col min="10" max="10" width="9.90625" style="56" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="26.08984375" style="55" customWidth="1"/>
     <col min="12" max="19" width="9.90625" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="10.453125" bestFit="1" customWidth="1"/>
     <col min="21" max="25" width="10.08984375" hidden="1" customWidth="1"/>
@@ -6879,98 +7089,98 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="81"/>
-      <c r="L1" s="81"/>
-      <c r="M1" s="81"/>
-      <c r="N1" s="81"/>
-      <c r="O1" s="81"/>
+      <c r="K1" s="91"/>
+      <c r="L1" s="91"/>
+      <c r="M1" s="91"/>
+      <c r="N1" s="91"/>
+      <c r="O1" s="91"/>
     </row>
     <row r="2" spans="1:28" s="11" customFormat="1" ht="29" x14ac:dyDescent="0.35">
-      <c r="A2" s="56" t="s">
-        <v>59</v>
-      </c>
-      <c r="B2" s="65" t="s">
+      <c r="A2" s="51" t="s">
+        <v>58</v>
+      </c>
+      <c r="B2" s="60" t="s">
+        <v>53</v>
+      </c>
+      <c r="C2" s="61" t="s">
         <v>54</v>
       </c>
-      <c r="C2" s="66" t="s">
+      <c r="D2" s="62" t="s">
         <v>55</v>
       </c>
-      <c r="D2" s="67" t="s">
+      <c r="E2" s="61" t="s">
+        <v>117</v>
+      </c>
+      <c r="F2" s="61" t="s">
         <v>56</v>
       </c>
-      <c r="E2" s="66" t="s">
-        <v>124</v>
-      </c>
-      <c r="F2" s="66" t="s">
-        <v>57</v>
-      </c>
-      <c r="H2" s="63"/>
-      <c r="I2" s="63"/>
-      <c r="J2" s="63"/>
+      <c r="H2" s="58"/>
+      <c r="I2" s="58"/>
+      <c r="J2" s="58"/>
       <c r="P2"/>
       <c r="Q2"/>
-      <c r="V2" s="64" t="s">
-        <v>126</v>
-      </c>
-      <c r="W2" s="62"/>
+      <c r="V2" s="59" t="s">
+        <v>119</v>
+      </c>
+      <c r="W2" s="57"/>
       <c r="X2"/>
       <c r="Y2"/>
-      <c r="AA2" s="56" t="s">
-        <v>59</v>
+      <c r="AA2" s="51" t="s">
+        <v>58</v>
       </c>
       <c r="AB2" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>133</v>
-      </c>
-      <c r="E3" s="59">
+        <v>126</v>
+      </c>
+      <c r="E3" s="54">
         <v>0</v>
       </c>
       <c r="U3" s="11"/>
       <c r="V3" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
     </row>
     <row r="4" spans="1:28" x14ac:dyDescent="0.35">
       <c r="B4" t="s">
-        <v>133</v>
-      </c>
-      <c r="E4" s="59">
+        <v>126</v>
+      </c>
+      <c r="E4" s="54">
         <v>0</v>
       </c>
-      <c r="U4" s="56" t="s">
-        <v>132</v>
+      <c r="U4" s="51" t="s">
+        <v>125</v>
       </c>
       <c r="V4" t="s">
+        <v>54</v>
+      </c>
+      <c r="W4" t="s">
         <v>55</v>
       </c>
-      <c r="W4" t="s">
-        <v>56</v>
-      </c>
-      <c r="AA4" s="56" t="s">
-        <v>131</v>
+      <c r="AA4" s="51" t="s">
+        <v>124</v>
       </c>
       <c r="AB4" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>58</v>
-      </c>
-      <c r="E5" s="59">
+        <v>57</v>
+      </c>
+      <c r="E5" s="54">
         <v>0</v>
       </c>
       <c r="U5" s="17" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="AA5" s="17" t="s">
-        <v>133</v>
-      </c>
-      <c r="AB5" s="59"/>
+        <v>126</v>
+      </c>
+      <c r="AB5" s="54"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.35">
       <c r="C6"/>
@@ -6979,12 +7189,12 @@
       <c r="F6"/>
       <c r="G6"/>
       <c r="U6" s="17" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AA6" s="17" t="s">
-        <v>58</v>
-      </c>
-      <c r="AB6" s="59"/>
+        <v>57</v>
+      </c>
+      <c r="AB6" s="54"/>
     </row>
     <row r="7" spans="1:28" x14ac:dyDescent="0.35">
       <c r="C7"/>
@@ -7135,13 +7345,13 @@
       <c r="K25"/>
     </row>
     <row r="26" spans="2:11" ht="16" x14ac:dyDescent="0.4">
-      <c r="B26" s="82" t="s">
-        <v>127</v>
-      </c>
-      <c r="C26" s="82"/>
-      <c r="D26" s="82"/>
-      <c r="E26" s="82"/>
-      <c r="F26" s="82"/>
+      <c r="B26" s="92" t="s">
+        <v>120</v>
+      </c>
+      <c r="C26" s="92"/>
+      <c r="D26" s="92"/>
+      <c r="E26" s="92"/>
+      <c r="F26" s="92"/>
       <c r="G26"/>
       <c r="H26"/>
       <c r="I26"/>
@@ -7149,20 +7359,20 @@
       <c r="K26"/>
     </row>
     <row r="27" spans="2:11" ht="29" x14ac:dyDescent="0.35">
-      <c r="B27" s="65" t="s">
-        <v>125</v>
-      </c>
-      <c r="C27" s="66" t="s">
+      <c r="B27" s="60" t="s">
+        <v>118</v>
+      </c>
+      <c r="C27" s="61" t="s">
+        <v>54</v>
+      </c>
+      <c r="D27" s="61" t="s">
         <v>55</v>
       </c>
-      <c r="D27" s="66" t="s">
+      <c r="E27" s="61" t="s">
+        <v>117</v>
+      </c>
+      <c r="F27" s="61" t="s">
         <v>56</v>
-      </c>
-      <c r="E27" s="66" t="s">
-        <v>124</v>
-      </c>
-      <c r="F27" s="66" t="s">
-        <v>57</v>
       </c>
       <c r="G27"/>
       <c r="H27"/>
@@ -7172,9 +7382,9 @@
     </row>
     <row r="28" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B28" s="17" t="s">
-        <v>133</v>
-      </c>
-      <c r="E28" s="59">
+        <v>126</v>
+      </c>
+      <c r="E28" s="54">
         <v>0</v>
       </c>
       <c r="G28"/>
@@ -7184,10 +7394,10 @@
       <c r="K28"/>
     </row>
     <row r="29" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B29" s="68" t="s">
-        <v>133</v>
-      </c>
-      <c r="E29" s="59">
+      <c r="B29" s="63" t="s">
+        <v>126</v>
+      </c>
+      <c r="E29" s="54">
         <v>0</v>
       </c>
       <c r="G29"/>
@@ -7197,10 +7407,10 @@
       <c r="K29"/>
     </row>
     <row r="30" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B30" s="69" t="s">
-        <v>133</v>
-      </c>
-      <c r="E30" s="59">
+      <c r="B30" s="64" t="s">
+        <v>126</v>
+      </c>
+      <c r="E30" s="54">
         <v>0</v>
       </c>
       <c r="J30"/>
@@ -7208,9 +7418,9 @@
     </row>
     <row r="31" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B31" s="17" t="s">
-        <v>58</v>
-      </c>
-      <c r="E31" s="59">
+        <v>57</v>
+      </c>
+      <c r="E31" s="54">
         <v>0</v>
       </c>
       <c r="J31"/>
@@ -7822,7 +8032,7 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" s="24" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
@@ -7844,7 +8054,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="31">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -7852,15 +8062,15 @@
         <v>5</v>
       </c>
       <c r="B7" s="32">
-        <v>67.599999999999994</v>
+        <v>55.2</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A8" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="50">
-        <v>5282.7</v>
+      <c r="B8" s="45">
+        <v>4800</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -7892,7 +8102,7 @@
       <c r="D13" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="E13" s="57" t="s">
+      <c r="E13" s="52" t="s">
         <v>14</v>
       </c>
     </row>
@@ -7901,7 +8111,7 @@
         <v>15</v>
       </c>
       <c r="B14" s="24" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="C14" s="33" t="s">
         <v>16</v>
@@ -7918,7 +8128,7 @@
         <v>18</v>
       </c>
       <c r="B15" s="24" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="C15" s="33" t="s">
         <v>16</v>
@@ -7930,10 +8140,10 @@
     </row>
     <row r="16" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A16" s="24" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="B16" s="24" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="C16" s="33" t="s">
         <v>16</v>
@@ -7943,10 +8153,10 @@
     </row>
     <row r="17" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A17" s="24" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="B17" s="24" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="C17" s="33" t="s">
         <v>16</v>
@@ -7958,10 +8168,10 @@
     </row>
     <row r="18" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A18" s="24" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="B18" s="24" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="C18" s="33" t="s">
         <v>16</v>
@@ -7973,10 +8183,10 @@
     </row>
     <row r="19" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A19" s="24" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B19" s="24" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="C19" s="33" t="s">
         <v>25</v>
@@ -7988,13 +8198,13 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="B20" s="24" t="s">
+        <v>142</v>
+      </c>
+      <c r="C20" s="33" t="s">
         <v>30</v>
-      </c>
-      <c r="B20" s="24" t="s">
-        <v>149</v>
-      </c>
-      <c r="C20" s="33" t="s">
-        <v>31</v>
       </c>
       <c r="D20" s="26" t="s">
         <v>8</v>
@@ -8005,25 +8215,25 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A21" s="24" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="B21" s="24" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="C21" s="33" t="s">
         <v>25</v>
       </c>
       <c r="D21" s="26"/>
       <c r="E21" s="21" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A22" s="24" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="B22" s="24" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="C22" s="33" t="s">
         <v>25</v>
@@ -8035,10 +8245,10 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A23" s="24" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="B23" s="24" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="C23" s="33" t="s">
         <v>25</v>
@@ -8050,10 +8260,10 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A24" s="24" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="B24" s="24" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="C24" s="33" t="s">
         <v>25</v>
@@ -8065,10 +8275,10 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A25" s="24" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="B25" s="24" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="C25" s="33" t="s">
         <v>25</v>
@@ -8080,10 +8290,10 @@
     </row>
     <row r="26" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A26" s="24" t="s">
+        <v>135</v>
+      </c>
+      <c r="B26" s="24" t="s">
         <v>142</v>
-      </c>
-      <c r="B26" s="24" t="s">
-        <v>149</v>
       </c>
       <c r="C26" s="33" t="s">
         <v>22</v>
@@ -8098,7 +8308,7 @@
         <v>21</v>
       </c>
       <c r="B27" s="24" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="C27" s="33" t="s">
         <v>22</v>
@@ -8110,25 +8320,25 @@
     </row>
     <row r="28" spans="1:5" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A28" s="24" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="B28" s="24" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="C28" s="33" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D28" s="26"/>
       <c r="E28" s="21" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A29" s="24" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B29" s="24" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C29" s="33" t="s">
         <v>22</v>
@@ -8176,7 +8386,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF3BD75F-6EAC-448A-8527-0296203F8E7B}">
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D26"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.1796875" customWidth="1"/>
@@ -8184,8 +8394,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" s="1" customFormat="1" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="88" t="s">
-        <v>53</v>
+      <c r="A1" s="74" t="s">
+        <v>52</v>
       </c>
       <c r="B1" s="22" t="s">
         <v>15</v>
@@ -8194,112 +8404,220 @@
         <v>18</v>
       </c>
       <c r="D1" s="22" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="94">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="80">
         <v>45627</v>
       </c>
-      <c r="B2" s="41"/>
-      <c r="C2" s="41"/>
-      <c r="D2" s="41"/>
-    </row>
-    <row r="3" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="94">
+      <c r="B2" s="100"/>
+      <c r="C2" s="99"/>
+      <c r="D2" s="99"/>
+    </row>
+    <row r="3" spans="1:4" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="80">
         <v>45658</v>
       </c>
-      <c r="B3" s="41"/>
-      <c r="C3" s="41"/>
-      <c r="D3" s="41"/>
-    </row>
-    <row r="4" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="94">
+      <c r="B3" s="100"/>
+      <c r="C3" s="99"/>
+      <c r="D3" s="99"/>
+    </row>
+    <row r="4" spans="1:4" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="80">
         <v>45689</v>
       </c>
-      <c r="B4" s="41"/>
-      <c r="C4" s="41"/>
-      <c r="D4" s="41"/>
-    </row>
-    <row r="5" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="94">
+      <c r="B4" s="100"/>
+      <c r="C4" s="99"/>
+      <c r="D4" s="99"/>
+    </row>
+    <row r="5" spans="1:4" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="80">
         <v>45717</v>
       </c>
-      <c r="B5" s="41"/>
-      <c r="C5" s="41"/>
-      <c r="D5" s="41"/>
-    </row>
-    <row r="6" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="94">
+      <c r="B5" s="100"/>
+      <c r="C5" s="99"/>
+      <c r="D5" s="99"/>
+    </row>
+    <row r="6" spans="1:4" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="80">
         <v>45748</v>
       </c>
-      <c r="B6" s="47"/>
-      <c r="C6" s="47"/>
-      <c r="D6" s="47"/>
-    </row>
-    <row r="7" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="94">
+      <c r="B6" s="100"/>
+      <c r="C6" s="99"/>
+      <c r="D6" s="99"/>
+    </row>
+    <row r="7" spans="1:4" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="80">
         <v>45778</v>
       </c>
-      <c r="B7" s="47"/>
-      <c r="C7" s="47"/>
-      <c r="D7" s="47"/>
-    </row>
-    <row r="8" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="94">
+      <c r="B7" s="100"/>
+      <c r="C7" s="99"/>
+      <c r="D7" s="99"/>
+    </row>
+    <row r="8" spans="1:4" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="80">
         <v>45809</v>
       </c>
-      <c r="B8" s="41"/>
-      <c r="C8" s="41"/>
-      <c r="D8" s="41"/>
-    </row>
-    <row r="9" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="94">
+      <c r="B8" s="100"/>
+      <c r="C8" s="99"/>
+      <c r="D8" s="99"/>
+    </row>
+    <row r="9" spans="1:4" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="80">
         <v>45839</v>
       </c>
-      <c r="B9" s="41"/>
-      <c r="C9" s="41"/>
-      <c r="D9" s="41"/>
-    </row>
-    <row r="10" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="94">
+      <c r="B9" s="100"/>
+      <c r="C9" s="99"/>
+      <c r="D9" s="99"/>
+    </row>
+    <row r="10" spans="1:4" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="80">
         <v>45870</v>
       </c>
-      <c r="B10" s="41"/>
-      <c r="C10" s="41"/>
-      <c r="D10" s="41"/>
-    </row>
-    <row r="11" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="94">
+      <c r="B10" s="100"/>
+      <c r="C10" s="99"/>
+      <c r="D10" s="99"/>
+    </row>
+    <row r="11" spans="1:4" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="80">
         <v>45901</v>
       </c>
-      <c r="B11" s="41"/>
-      <c r="C11" s="41"/>
-      <c r="D11" s="41"/>
-    </row>
-    <row r="12" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="94">
+      <c r="B11" s="100"/>
+      <c r="C11" s="99"/>
+      <c r="D11" s="99"/>
+    </row>
+    <row r="12" spans="1:4" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="80">
         <v>45931</v>
       </c>
-      <c r="B12" s="41"/>
-      <c r="C12" s="41"/>
-      <c r="D12" s="41"/>
-    </row>
-    <row r="13" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="94">
+      <c r="B12" s="100"/>
+      <c r="C12" s="99"/>
+      <c r="D12" s="99"/>
+    </row>
+    <row r="13" spans="1:4" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="80">
         <v>45962</v>
       </c>
-      <c r="B13" s="41"/>
-      <c r="C13" s="41"/>
-      <c r="D13" s="41"/>
-    </row>
-    <row r="14" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="94">
+      <c r="B13" s="100"/>
+      <c r="C13" s="99"/>
+      <c r="D13" s="99"/>
+    </row>
+    <row r="14" spans="1:4" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A14" s="80">
         <v>45992</v>
       </c>
-      <c r="B14" s="41"/>
-      <c r="C14" s="41"/>
-      <c r="D14" s="41"/>
+      <c r="B14" s="100"/>
+      <c r="C14" s="99"/>
+      <c r="D14" s="99"/>
+    </row>
+    <row r="15" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="80">
+        <v>46023</v>
+      </c>
+      <c r="B15" s="100">
+        <v>1562</v>
+      </c>
+      <c r="C15" s="99">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="D15" s="99">
+        <v>9.1229999999999993</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="80">
+        <v>46054</v>
+      </c>
+      <c r="B16" s="100">
+        <v>1763</v>
+      </c>
+      <c r="C16" s="99">
+        <v>12.898</v>
+      </c>
+      <c r="D16" s="99">
+        <v>12.324999999999999</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="80">
+        <v>46082</v>
+      </c>
+      <c r="B17" s="100"/>
+      <c r="C17" s="99"/>
+      <c r="D17" s="99"/>
+    </row>
+    <row r="18" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A18" s="80">
+        <v>46113</v>
+      </c>
+      <c r="B18" s="100"/>
+      <c r="C18" s="99"/>
+      <c r="D18" s="99"/>
+    </row>
+    <row r="19" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="80">
+        <v>46143</v>
+      </c>
+      <c r="B19" s="100"/>
+      <c r="C19" s="99"/>
+      <c r="D19" s="99"/>
+    </row>
+    <row r="20" spans="1:4" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="80">
+        <v>46174</v>
+      </c>
+      <c r="B20" s="100"/>
+      <c r="C20" s="99"/>
+      <c r="D20" s="99"/>
+    </row>
+    <row r="21" spans="1:4" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="80">
+        <v>46204</v>
+      </c>
+      <c r="B21" s="100"/>
+      <c r="C21" s="99"/>
+      <c r="D21" s="99"/>
+    </row>
+    <row r="22" spans="1:4" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A22" s="80">
+        <v>46235</v>
+      </c>
+      <c r="B22" s="100"/>
+      <c r="C22" s="99"/>
+      <c r="D22" s="99"/>
+    </row>
+    <row r="23" spans="1:4" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A23" s="80">
+        <v>46266</v>
+      </c>
+      <c r="B23" s="100"/>
+      <c r="C23" s="99"/>
+      <c r="D23" s="99"/>
+    </row>
+    <row r="24" spans="1:4" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A24" s="80">
+        <v>46296</v>
+      </c>
+      <c r="B24" s="100"/>
+      <c r="C24" s="99"/>
+      <c r="D24" s="99"/>
+    </row>
+    <row r="25" spans="1:4" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="80">
+        <v>46327</v>
+      </c>
+      <c r="B25" s="100"/>
+      <c r="C25" s="99"/>
+      <c r="D25" s="99"/>
+    </row>
+    <row r="26" spans="1:4" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A26" s="80">
+        <v>46357</v>
+      </c>
+      <c r="B26" s="100"/>
+      <c r="C26" s="99"/>
+      <c r="D26" s="99"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8326,1108 +8644,2576 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04C2DAD5-C944-49BD-B533-55A4B1F4CE6D}">
-  <dimension ref="A1:AA42"/>
+  <dimension ref="A1:AN39"/>
   <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="25.26953125" style="3" customWidth="1"/>
     <col min="2" max="2" width="14.36328125" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="26" width="9.54296875" style="3" customWidth="1"/>
-    <col min="27" max="27" width="59.7265625" style="3" customWidth="1"/>
-    <col min="28" max="16384" width="9.1796875" style="3"/>
+    <col min="3" max="26" width="9.54296875" style="3" hidden="1" customWidth="1"/>
+    <col min="27" max="38" width="9.54296875" style="3" customWidth="1"/>
+    <col min="39" max="39" width="59.7265625" style="3" customWidth="1"/>
+    <col min="40" max="16384" width="9.1796875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="57" t="s">
+    <row r="1" spans="1:40" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="52" t="s">
+        <v>75</v>
+      </c>
+      <c r="B1" s="52" t="s">
         <v>76</v>
       </c>
-      <c r="B1" s="57" t="s">
+      <c r="C1" s="101">
+        <v>45292</v>
+      </c>
+      <c r="D1" s="101">
+        <v>45323</v>
+      </c>
+      <c r="E1" s="101">
+        <v>45352</v>
+      </c>
+      <c r="F1" s="101">
+        <v>45383</v>
+      </c>
+      <c r="G1" s="101">
+        <v>45413</v>
+      </c>
+      <c r="H1" s="101">
+        <v>45444</v>
+      </c>
+      <c r="I1" s="101">
+        <v>45474</v>
+      </c>
+      <c r="J1" s="101">
+        <v>45505</v>
+      </c>
+      <c r="K1" s="101">
+        <v>45536</v>
+      </c>
+      <c r="L1" s="101">
+        <v>45566</v>
+      </c>
+      <c r="M1" s="101">
+        <v>45597</v>
+      </c>
+      <c r="N1" s="101">
+        <v>45627</v>
+      </c>
+      <c r="O1" s="101">
+        <v>45658</v>
+      </c>
+      <c r="P1" s="101">
+        <v>45689</v>
+      </c>
+      <c r="Q1" s="101">
+        <v>45717</v>
+      </c>
+      <c r="R1" s="101">
+        <v>45748</v>
+      </c>
+      <c r="S1" s="101">
+        <v>45778</v>
+      </c>
+      <c r="T1" s="101">
+        <v>45809</v>
+      </c>
+      <c r="U1" s="101">
+        <v>45839</v>
+      </c>
+      <c r="V1" s="101">
+        <v>45870</v>
+      </c>
+      <c r="W1" s="101">
+        <v>45901</v>
+      </c>
+      <c r="X1" s="101">
+        <v>45931</v>
+      </c>
+      <c r="Y1" s="101">
+        <v>45962</v>
+      </c>
+      <c r="Z1" s="101">
+        <v>45992</v>
+      </c>
+      <c r="AA1" s="101">
+        <v>46023</v>
+      </c>
+      <c r="AB1" s="101">
+        <v>46054</v>
+      </c>
+      <c r="AC1" s="101">
+        <v>46082</v>
+      </c>
+      <c r="AD1" s="101">
+        <v>46113</v>
+      </c>
+      <c r="AE1" s="101">
+        <v>46143</v>
+      </c>
+      <c r="AF1" s="101">
+        <v>46174</v>
+      </c>
+      <c r="AG1" s="101">
+        <v>46204</v>
+      </c>
+      <c r="AH1" s="101">
+        <v>46235</v>
+      </c>
+      <c r="AI1" s="101">
+        <v>46266</v>
+      </c>
+      <c r="AJ1" s="101">
+        <v>46296</v>
+      </c>
+      <c r="AK1" s="101">
+        <v>46327</v>
+      </c>
+      <c r="AL1" s="101">
+        <v>46357</v>
+      </c>
+      <c r="AM1" s="52" t="s">
         <v>77</v>
       </c>
-      <c r="C1" s="95">
-        <v>45292</v>
-      </c>
-      <c r="D1" s="95">
-        <v>45323</v>
-      </c>
-      <c r="E1" s="95">
-        <v>45352</v>
-      </c>
-      <c r="F1" s="95">
-        <v>45383</v>
-      </c>
-      <c r="G1" s="95">
-        <v>45413</v>
-      </c>
-      <c r="H1" s="95">
-        <v>45444</v>
-      </c>
-      <c r="I1" s="95">
-        <v>45474</v>
-      </c>
-      <c r="J1" s="95">
-        <v>45505</v>
-      </c>
-      <c r="K1" s="95">
-        <v>45536</v>
-      </c>
-      <c r="L1" s="95">
-        <v>45566</v>
-      </c>
-      <c r="M1" s="95">
-        <v>45597</v>
-      </c>
-      <c r="N1" s="95">
-        <v>45627</v>
-      </c>
-      <c r="O1" s="95">
-        <v>45658</v>
-      </c>
-      <c r="P1" s="95">
-        <v>45689</v>
-      </c>
-      <c r="Q1" s="95">
-        <v>45717</v>
-      </c>
-      <c r="R1" s="95">
-        <v>45748</v>
-      </c>
-      <c r="S1" s="95">
-        <v>45778</v>
-      </c>
-      <c r="T1" s="95">
-        <v>45809</v>
-      </c>
-      <c r="U1" s="95">
-        <v>45839</v>
-      </c>
-      <c r="V1" s="95">
-        <v>45870</v>
-      </c>
-      <c r="W1" s="95">
-        <v>45901</v>
-      </c>
-      <c r="X1" s="95">
-        <v>45931</v>
-      </c>
-      <c r="Y1" s="95">
-        <v>45962</v>
-      </c>
-      <c r="Z1" s="95">
-        <v>45992</v>
-      </c>
-      <c r="AA1" s="57" t="s">
+    </row>
+    <row r="2" spans="1:40" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="21" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="2" spans="1:27" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="21" t="s">
+      <c r="B2" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C2" s="38">
+        <v>3.36</v>
+      </c>
+      <c r="D2" s="38">
+        <v>3.36</v>
+      </c>
+      <c r="E2" s="38">
+        <v>3.36</v>
+      </c>
+      <c r="F2" s="38">
+        <v>3.36</v>
+      </c>
+      <c r="G2" s="38">
+        <v>3.36</v>
+      </c>
+      <c r="H2" s="38">
+        <v>3.36</v>
+      </c>
+      <c r="I2" s="38">
+        <v>3.67</v>
+      </c>
+      <c r="J2" s="38">
+        <v>3.67</v>
+      </c>
+      <c r="K2" s="38">
+        <v>3.67</v>
+      </c>
+      <c r="L2" s="38">
+        <v>3.67</v>
+      </c>
+      <c r="M2" s="38">
+        <v>3.67</v>
+      </c>
+      <c r="N2" s="38">
+        <v>3.67</v>
+      </c>
+      <c r="O2" s="38">
+        <v>3.67</v>
+      </c>
+      <c r="P2" s="38">
+        <v>3.67</v>
+      </c>
+      <c r="Q2" s="38">
+        <v>3.67</v>
+      </c>
+      <c r="R2" s="38">
+        <v>3.67</v>
+      </c>
+      <c r="S2" s="38">
+        <v>3.67</v>
+      </c>
+      <c r="T2" s="38">
+        <v>3.67</v>
+      </c>
+      <c r="U2" s="38">
+        <v>4.13</v>
+      </c>
+      <c r="V2" s="38">
+        <v>4.13</v>
+      </c>
+      <c r="W2" s="38">
+        <v>4.13</v>
+      </c>
+      <c r="X2" s="38">
+        <v>4.13</v>
+      </c>
+      <c r="Y2" s="38">
+        <v>4.13</v>
+      </c>
+      <c r="Z2" s="38">
+        <v>4.13</v>
+      </c>
+      <c r="AA2" s="38">
+        <v>4.2</v>
+      </c>
+      <c r="AB2" s="38">
+        <v>4.2</v>
+      </c>
+      <c r="AC2" s="38">
+        <v>4.2</v>
+      </c>
+      <c r="AD2" s="38">
+        <v>4.2</v>
+      </c>
+      <c r="AE2" s="38">
+        <v>4.2</v>
+      </c>
+      <c r="AF2" s="38">
+        <v>4.2</v>
+      </c>
+      <c r="AG2" s="38">
+        <v>4.2</v>
+      </c>
+      <c r="AH2" s="38">
+        <v>4.2</v>
+      </c>
+      <c r="AI2" s="38">
+        <v>4.2</v>
+      </c>
+      <c r="AJ2" s="38">
+        <v>4.67</v>
+      </c>
+      <c r="AK2" s="38">
+        <v>4.67</v>
+      </c>
+      <c r="AL2" s="38">
+        <v>4.67</v>
+      </c>
+      <c r="AM2" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="B2" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="C2" s="41"/>
-      <c r="D2" s="41"/>
-      <c r="E2" s="41"/>
-      <c r="F2" s="41"/>
-      <c r="G2" s="41"/>
-      <c r="H2" s="41"/>
-      <c r="I2" s="41"/>
-      <c r="J2" s="41"/>
-      <c r="K2" s="41"/>
-      <c r="L2" s="41"/>
-      <c r="M2" s="41"/>
-      <c r="N2" s="41"/>
-      <c r="O2" s="41"/>
-      <c r="P2" s="41"/>
-      <c r="Q2" s="41"/>
-      <c r="R2" s="73"/>
-      <c r="S2" s="73"/>
-      <c r="T2" s="41"/>
-      <c r="U2" s="41"/>
-      <c r="V2" s="41"/>
-      <c r="W2" s="41"/>
-      <c r="X2" s="41"/>
-      <c r="Y2" s="41"/>
-      <c r="Z2" s="41"/>
-      <c r="AA2" s="4" t="s">
+      <c r="AN2" s="107" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="3" spans="1:40" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="21" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="3" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="21" t="s">
-        <v>81</v>
-      </c>
       <c r="B3" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="C3" s="41"/>
-      <c r="D3" s="41"/>
-      <c r="E3" s="41"/>
-      <c r="F3" s="41"/>
-      <c r="G3" s="41"/>
-      <c r="H3" s="41"/>
-      <c r="I3" s="41"/>
-      <c r="J3" s="41"/>
-      <c r="K3" s="41"/>
-      <c r="L3" s="41"/>
-      <c r="M3" s="41"/>
-      <c r="N3" s="41"/>
-      <c r="O3" s="41"/>
-      <c r="P3" s="41"/>
-      <c r="Q3" s="41"/>
-      <c r="R3" s="73"/>
-      <c r="S3" s="73"/>
-      <c r="T3" s="41"/>
-      <c r="U3" s="41"/>
-      <c r="V3" s="41"/>
-      <c r="W3" s="41"/>
-      <c r="X3" s="41"/>
-      <c r="Y3" s="41"/>
-      <c r="Z3" s="41"/>
-      <c r="AA3" s="4"/>
-    </row>
-    <row r="4" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+        <v>45</v>
+      </c>
+      <c r="C3" s="38">
+        <v>4.71</v>
+      </c>
+      <c r="D3" s="38">
+        <v>4.71</v>
+      </c>
+      <c r="E3" s="38">
+        <v>4.71</v>
+      </c>
+      <c r="F3" s="38">
+        <v>4.71</v>
+      </c>
+      <c r="G3" s="38">
+        <v>4.71</v>
+      </c>
+      <c r="H3" s="38">
+        <v>4.71</v>
+      </c>
+      <c r="I3" s="38">
+        <v>5.12</v>
+      </c>
+      <c r="J3" s="38">
+        <v>5.12</v>
+      </c>
+      <c r="K3" s="38">
+        <v>5.12</v>
+      </c>
+      <c r="L3" s="38">
+        <v>5.12</v>
+      </c>
+      <c r="M3" s="38">
+        <v>5.12</v>
+      </c>
+      <c r="N3" s="38">
+        <v>5.12</v>
+      </c>
+      <c r="O3" s="38">
+        <v>5.12</v>
+      </c>
+      <c r="P3" s="38">
+        <v>5.12</v>
+      </c>
+      <c r="Q3" s="38">
+        <v>5.12</v>
+      </c>
+      <c r="R3" s="38">
+        <v>5.12</v>
+      </c>
+      <c r="S3" s="38">
+        <v>5.12</v>
+      </c>
+      <c r="T3" s="38">
+        <v>5.12</v>
+      </c>
+      <c r="U3" s="38">
+        <v>5.76</v>
+      </c>
+      <c r="V3" s="38">
+        <v>5.76</v>
+      </c>
+      <c r="W3" s="38">
+        <v>5.76</v>
+      </c>
+      <c r="X3" s="38">
+        <v>5.76</v>
+      </c>
+      <c r="Y3" s="38">
+        <v>5.76</v>
+      </c>
+      <c r="Z3" s="38">
+        <v>5.76</v>
+      </c>
+      <c r="AA3" s="38">
+        <v>5.72</v>
+      </c>
+      <c r="AB3" s="38">
+        <v>5.72</v>
+      </c>
+      <c r="AC3" s="38">
+        <v>5.72</v>
+      </c>
+      <c r="AD3" s="38">
+        <v>5.72</v>
+      </c>
+      <c r="AE3" s="38">
+        <v>5.72</v>
+      </c>
+      <c r="AF3" s="38">
+        <v>5.72</v>
+      </c>
+      <c r="AG3" s="38">
+        <v>5.72</v>
+      </c>
+      <c r="AH3" s="38">
+        <v>5.72</v>
+      </c>
+      <c r="AI3" s="38">
+        <v>5.72</v>
+      </c>
+      <c r="AJ3" s="38">
+        <v>6.48</v>
+      </c>
+      <c r="AK3" s="38">
+        <v>6.48</v>
+      </c>
+      <c r="AL3" s="38">
+        <v>6.48</v>
+      </c>
+      <c r="AM3" s="4"/>
+    </row>
+    <row r="4" spans="1:40" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="21" t="s">
         <v>18</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="C4" s="41"/>
-      <c r="D4" s="41"/>
-      <c r="E4" s="41"/>
-      <c r="F4" s="41"/>
-      <c r="G4" s="41"/>
-      <c r="H4" s="41"/>
-      <c r="I4" s="41"/>
-      <c r="J4" s="41"/>
-      <c r="K4" s="41"/>
-      <c r="L4" s="41"/>
-      <c r="M4" s="41"/>
-      <c r="N4" s="41"/>
-      <c r="O4" s="41"/>
-      <c r="P4" s="41"/>
-      <c r="Q4" s="41"/>
-      <c r="R4" s="73"/>
-      <c r="S4" s="73"/>
-      <c r="T4" s="41"/>
-      <c r="U4" s="41"/>
-      <c r="V4" s="41"/>
-      <c r="W4" s="41"/>
-      <c r="X4" s="41"/>
-      <c r="Y4" s="41"/>
-      <c r="Z4" s="41"/>
-      <c r="AA4" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C4" s="38">
+        <v>51.62</v>
+      </c>
+      <c r="D4" s="38">
+        <v>51.62</v>
+      </c>
+      <c r="E4" s="38">
+        <v>51.62</v>
+      </c>
+      <c r="F4" s="38">
+        <v>51.62</v>
+      </c>
+      <c r="G4" s="38">
+        <v>51.62</v>
+      </c>
+      <c r="H4" s="38">
+        <v>51.62</v>
+      </c>
+      <c r="I4" s="38">
+        <v>56.52</v>
+      </c>
+      <c r="J4" s="38">
+        <v>56.52</v>
+      </c>
+      <c r="K4" s="38">
+        <v>56.52</v>
+      </c>
+      <c r="L4" s="38">
+        <v>56.52</v>
+      </c>
+      <c r="M4" s="38">
+        <v>56.52</v>
+      </c>
+      <c r="N4" s="38">
+        <v>56.52</v>
+      </c>
+      <c r="O4" s="38">
+        <v>56.52</v>
+      </c>
+      <c r="P4" s="38">
+        <v>56.52</v>
+      </c>
+      <c r="Q4" s="38">
+        <v>56.52</v>
+      </c>
+      <c r="R4" s="38">
+        <v>56.52</v>
+      </c>
+      <c r="S4" s="38">
+        <v>56.52</v>
+      </c>
+      <c r="T4" s="38">
+        <v>56.52</v>
+      </c>
+      <c r="U4" s="38">
+        <v>61.94</v>
+      </c>
+      <c r="V4" s="38">
+        <v>61.94</v>
+      </c>
+      <c r="W4" s="38">
+        <v>61.94</v>
+      </c>
+      <c r="X4" s="38">
+        <v>61.94</v>
+      </c>
+      <c r="Y4" s="38">
+        <v>61.94</v>
+      </c>
+      <c r="Z4" s="38">
+        <v>61.94</v>
+      </c>
+      <c r="AA4" s="38">
+        <v>62.98</v>
+      </c>
+      <c r="AB4" s="38">
+        <v>62.98</v>
+      </c>
+      <c r="AC4" s="38">
+        <v>62.98</v>
+      </c>
+      <c r="AD4" s="38">
+        <v>62.98</v>
+      </c>
+      <c r="AE4" s="38">
+        <v>62.98</v>
+      </c>
+      <c r="AF4" s="38">
+        <v>62.98</v>
+      </c>
+      <c r="AG4" s="38">
+        <v>62.98</v>
+      </c>
+      <c r="AH4" s="38">
+        <v>62.98</v>
+      </c>
+      <c r="AI4" s="38">
+        <v>62.98</v>
+      </c>
+      <c r="AJ4" s="38">
+        <v>69.150000000000006</v>
+      </c>
+      <c r="AK4" s="38">
+        <v>69.150000000000006</v>
+      </c>
+      <c r="AL4" s="38">
+        <v>69.150000000000006</v>
+      </c>
+      <c r="AM4" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="AN4" s="107" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="5" spans="1:40" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="C5" s="38">
+        <v>36.159999999999997</v>
+      </c>
+      <c r="D5" s="38">
+        <v>36.159999999999997</v>
+      </c>
+      <c r="E5" s="38">
+        <v>36.159999999999997</v>
+      </c>
+      <c r="F5" s="38">
+        <v>36.159999999999997</v>
+      </c>
+      <c r="G5" s="38">
+        <v>36.159999999999997</v>
+      </c>
+      <c r="H5" s="38">
+        <v>36.159999999999997</v>
+      </c>
+      <c r="I5" s="38">
+        <v>39.590000000000003</v>
+      </c>
+      <c r="J5" s="38">
+        <v>39.590000000000003</v>
+      </c>
+      <c r="K5" s="38">
+        <v>39.590000000000003</v>
+      </c>
+      <c r="L5" s="38">
+        <v>39.590000000000003</v>
+      </c>
+      <c r="M5" s="38">
+        <v>39.590000000000003</v>
+      </c>
+      <c r="N5" s="38">
+        <v>39.590000000000003</v>
+      </c>
+      <c r="O5" s="38">
+        <v>39.590000000000003</v>
+      </c>
+      <c r="P5" s="38">
+        <v>39.590000000000003</v>
+      </c>
+      <c r="Q5" s="38">
+        <v>39.590000000000003</v>
+      </c>
+      <c r="R5" s="38">
+        <v>39.590000000000003</v>
+      </c>
+      <c r="S5" s="38">
+        <v>39.590000000000003</v>
+      </c>
+      <c r="T5" s="38">
+        <v>39.590000000000003</v>
+      </c>
+      <c r="U5" s="38">
+        <v>43.39</v>
+      </c>
+      <c r="V5" s="38">
+        <v>43.39</v>
+      </c>
+      <c r="W5" s="38">
+        <v>43.39</v>
+      </c>
+      <c r="X5" s="38">
+        <v>43.39</v>
+      </c>
+      <c r="Y5" s="38">
+        <v>43.39</v>
+      </c>
+      <c r="Z5" s="38">
+        <v>43.39</v>
+      </c>
+      <c r="AA5" s="38">
+        <v>44.12</v>
+      </c>
+      <c r="AB5" s="38">
+        <v>44.12</v>
+      </c>
+      <c r="AC5" s="38">
+        <v>44.12</v>
+      </c>
+      <c r="AD5" s="38">
+        <v>44.12</v>
+      </c>
+      <c r="AE5" s="38">
+        <v>44.12</v>
+      </c>
+      <c r="AF5" s="38">
+        <v>44.12</v>
+      </c>
+      <c r="AG5" s="38">
+        <v>44.12</v>
+      </c>
+      <c r="AH5" s="38">
+        <v>44.12</v>
+      </c>
+      <c r="AI5" s="38">
+        <v>44.12</v>
+      </c>
+      <c r="AJ5" s="38">
+        <v>48.43</v>
+      </c>
+      <c r="AK5" s="38">
+        <v>48.43</v>
+      </c>
+      <c r="AL5" s="38">
+        <v>48.43</v>
+      </c>
+      <c r="AM5" s="4" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="6" spans="1:40" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="C6" s="38">
+        <v>184.96</v>
+      </c>
+      <c r="D6" s="38">
+        <v>184.96</v>
+      </c>
+      <c r="E6" s="38">
+        <v>184.96</v>
+      </c>
+      <c r="F6" s="38">
+        <v>184.96</v>
+      </c>
+      <c r="G6" s="38">
+        <v>184.96</v>
+      </c>
+      <c r="H6" s="38">
+        <v>184.96</v>
+      </c>
+      <c r="I6" s="38">
+        <v>202.53</v>
+      </c>
+      <c r="J6" s="38">
+        <v>202.53</v>
+      </c>
+      <c r="K6" s="38">
+        <v>202.53</v>
+      </c>
+      <c r="L6" s="38">
+        <v>202.53</v>
+      </c>
+      <c r="M6" s="38">
+        <v>202.53</v>
+      </c>
+      <c r="N6" s="38">
+        <v>202.53</v>
+      </c>
+      <c r="O6" s="38">
+        <v>202.53</v>
+      </c>
+      <c r="P6" s="38">
+        <v>202.53</v>
+      </c>
+      <c r="Q6" s="38">
+        <v>202.53</v>
+      </c>
+      <c r="R6" s="38">
+        <v>202.53</v>
+      </c>
+      <c r="S6" s="38">
+        <v>202.53</v>
+      </c>
+      <c r="T6" s="38">
+        <v>202.53</v>
+      </c>
+      <c r="U6" s="38">
+        <v>202.53</v>
+      </c>
+      <c r="V6" s="38">
+        <v>202.53</v>
+      </c>
+      <c r="W6" s="38">
+        <v>202.53</v>
+      </c>
+      <c r="X6" s="38">
+        <v>202.53</v>
+      </c>
+      <c r="Y6" s="38">
+        <v>202.53</v>
+      </c>
+      <c r="Z6" s="38">
+        <v>202.53</v>
+      </c>
+      <c r="AA6" s="38">
+        <v>227.18</v>
+      </c>
+      <c r="AB6" s="38">
+        <v>227.18</v>
+      </c>
+      <c r="AC6" s="38">
+        <v>227.18</v>
+      </c>
+      <c r="AD6" s="38">
+        <v>227.18</v>
+      </c>
+      <c r="AE6" s="38">
+        <v>227.18</v>
+      </c>
+      <c r="AF6" s="38">
+        <v>227.18</v>
+      </c>
+      <c r="AG6" s="38">
+        <v>227.18</v>
+      </c>
+      <c r="AH6" s="38">
+        <v>227.18</v>
+      </c>
+      <c r="AI6" s="38">
+        <v>227.18</v>
+      </c>
+      <c r="AJ6" s="38">
+        <v>227.18</v>
+      </c>
+      <c r="AK6" s="38">
+        <v>227.18</v>
+      </c>
+      <c r="AL6" s="38">
+        <v>227.18</v>
+      </c>
+      <c r="AM6" s="4" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="21" t="s">
-        <v>134</v>
-      </c>
-      <c r="B5" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="C5" s="41"/>
-      <c r="D5" s="41"/>
-      <c r="E5" s="41"/>
-      <c r="F5" s="41"/>
-      <c r="G5" s="41"/>
-      <c r="H5" s="41"/>
-      <c r="I5" s="41"/>
-      <c r="J5" s="41"/>
-      <c r="K5" s="41"/>
-      <c r="L5" s="41"/>
-      <c r="M5" s="41"/>
-      <c r="N5" s="41"/>
-      <c r="O5" s="41"/>
-      <c r="P5" s="41"/>
-      <c r="Q5" s="41"/>
-      <c r="R5" s="73"/>
-      <c r="S5" s="73"/>
-      <c r="T5" s="41"/>
-      <c r="U5" s="41"/>
-      <c r="V5" s="41"/>
-      <c r="W5" s="41"/>
-      <c r="X5" s="41"/>
-      <c r="Y5" s="41"/>
-      <c r="Z5" s="41"/>
-      <c r="AA5" s="4"/>
-    </row>
-    <row r="6" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="21" t="s">
-        <v>20</v>
-      </c>
-      <c r="B6" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="C6" s="41"/>
-      <c r="D6" s="41"/>
-      <c r="E6" s="41"/>
-      <c r="F6" s="41"/>
-      <c r="G6" s="41"/>
-      <c r="H6" s="41"/>
-      <c r="I6" s="41"/>
-      <c r="J6" s="41"/>
-      <c r="K6" s="41"/>
-      <c r="L6" s="41"/>
-      <c r="M6" s="41"/>
-      <c r="N6" s="41"/>
-      <c r="O6" s="41"/>
-      <c r="P6" s="41"/>
-      <c r="Q6" s="41"/>
-      <c r="R6" s="73"/>
-      <c r="S6" s="73"/>
-      <c r="T6" s="41"/>
-      <c r="U6" s="41"/>
-      <c r="V6" s="41"/>
-      <c r="W6" s="41"/>
-      <c r="X6" s="41"/>
-      <c r="Y6" s="41"/>
-      <c r="Z6" s="41"/>
-      <c r="AA6" s="4" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="7" spans="1:27" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:40" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A7" s="21" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="B7" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="C7" s="41"/>
-      <c r="D7" s="41"/>
-      <c r="E7" s="41"/>
-      <c r="F7" s="41"/>
-      <c r="G7" s="41"/>
-      <c r="H7" s="41"/>
-      <c r="I7" s="41"/>
-      <c r="J7" s="41"/>
-      <c r="K7" s="41"/>
-      <c r="L7" s="41"/>
-      <c r="M7" s="41"/>
-      <c r="N7" s="41"/>
-      <c r="O7" s="41"/>
-      <c r="P7" s="41"/>
-      <c r="Q7" s="41"/>
-      <c r="R7" s="73"/>
-      <c r="S7" s="73"/>
-      <c r="T7" s="41"/>
-      <c r="U7" s="41"/>
-      <c r="V7" s="41"/>
-      <c r="W7" s="41"/>
-      <c r="X7" s="41"/>
-      <c r="Y7" s="41"/>
-      <c r="Z7" s="41"/>
-      <c r="AA7" s="4" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="8" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C7" s="38">
+        <v>2889.93</v>
+      </c>
+      <c r="D7" s="38">
+        <v>2889.93</v>
+      </c>
+      <c r="E7" s="38">
+        <v>2889.93</v>
+      </c>
+      <c r="F7" s="38">
+        <v>2889.93</v>
+      </c>
+      <c r="G7" s="38">
+        <v>2889.93</v>
+      </c>
+      <c r="H7" s="38">
+        <v>2889.93</v>
+      </c>
+      <c r="I7" s="38">
+        <v>3164.47</v>
+      </c>
+      <c r="J7" s="38">
+        <v>3164.47</v>
+      </c>
+      <c r="K7" s="38">
+        <v>3164.47</v>
+      </c>
+      <c r="L7" s="38">
+        <v>3164.47</v>
+      </c>
+      <c r="M7" s="38">
+        <v>3164.47</v>
+      </c>
+      <c r="N7" s="38">
+        <v>3164.47</v>
+      </c>
+      <c r="O7" s="38">
+        <v>3164.47</v>
+      </c>
+      <c r="P7" s="38">
+        <v>3164.47</v>
+      </c>
+      <c r="Q7" s="38">
+        <v>3164.47</v>
+      </c>
+      <c r="R7" s="38">
+        <v>3164.47</v>
+      </c>
+      <c r="S7" s="38">
+        <v>3164.47</v>
+      </c>
+      <c r="T7" s="38">
+        <v>3164.47</v>
+      </c>
+      <c r="U7" s="38">
+        <v>3164.47</v>
+      </c>
+      <c r="V7" s="38">
+        <v>3164.47</v>
+      </c>
+      <c r="W7" s="38">
+        <v>3164.47</v>
+      </c>
+      <c r="X7" s="38">
+        <v>3164.47</v>
+      </c>
+      <c r="Y7" s="38">
+        <v>3164.47</v>
+      </c>
+      <c r="Z7" s="38">
+        <v>3164.47</v>
+      </c>
+      <c r="AA7" s="38">
+        <v>3549.74</v>
+      </c>
+      <c r="AB7" s="38">
+        <v>3549.74</v>
+      </c>
+      <c r="AC7" s="38">
+        <v>3549.74</v>
+      </c>
+      <c r="AD7" s="38">
+        <v>3549.74</v>
+      </c>
+      <c r="AE7" s="38"/>
+      <c r="AF7" s="38"/>
+      <c r="AG7" s="38"/>
+      <c r="AH7" s="38"/>
+      <c r="AI7" s="38"/>
+      <c r="AJ7" s="38">
+        <v>3549.74</v>
+      </c>
+      <c r="AK7" s="38">
+        <v>3549.74</v>
+      </c>
+      <c r="AL7" s="38">
+        <v>3549.74</v>
+      </c>
+      <c r="AM7" s="4" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="8" spans="1:40" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A8" s="21" t="s">
         <v>24</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="C8" s="41"/>
-      <c r="D8" s="41"/>
-      <c r="E8" s="41"/>
-      <c r="F8" s="41"/>
-      <c r="G8" s="41"/>
-      <c r="H8" s="41"/>
-      <c r="I8" s="41"/>
-      <c r="J8" s="41"/>
-      <c r="K8" s="41"/>
-      <c r="L8" s="41"/>
-      <c r="M8" s="41"/>
-      <c r="N8" s="41"/>
-      <c r="O8" s="41"/>
-      <c r="P8" s="41"/>
-      <c r="Q8" s="41"/>
-      <c r="R8" s="73"/>
-      <c r="S8" s="73"/>
-      <c r="T8" s="41"/>
-      <c r="U8" s="41"/>
-      <c r="V8" s="41"/>
-      <c r="W8" s="41"/>
-      <c r="X8" s="41"/>
-      <c r="Y8" s="41"/>
-      <c r="Z8" s="41"/>
-      <c r="AA8" s="4" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="9" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+        <v>47</v>
+      </c>
+      <c r="C8" s="38">
+        <v>9.81</v>
+      </c>
+      <c r="D8" s="38">
+        <v>10.08</v>
+      </c>
+      <c r="E8" s="38">
+        <v>10.55</v>
+      </c>
+      <c r="F8" s="38">
+        <v>10.55</v>
+      </c>
+      <c r="G8" s="38">
+        <v>10.55</v>
+      </c>
+      <c r="H8" s="38">
+        <v>10.55</v>
+      </c>
+      <c r="I8" s="38">
+        <v>10.55</v>
+      </c>
+      <c r="J8" s="38">
+        <v>10.55</v>
+      </c>
+      <c r="K8" s="38">
+        <v>10.55</v>
+      </c>
+      <c r="L8" s="38">
+        <v>10.55</v>
+      </c>
+      <c r="M8" s="38">
+        <v>10.55</v>
+      </c>
+      <c r="N8" s="38">
+        <v>10.55</v>
+      </c>
+      <c r="O8" s="38">
+        <v>11.08</v>
+      </c>
+      <c r="P8" s="38">
+        <v>11.08</v>
+      </c>
+      <c r="Q8" s="38">
+        <v>11.08</v>
+      </c>
+      <c r="R8" s="38">
+        <v>11.08</v>
+      </c>
+      <c r="S8" s="38">
+        <v>11.08</v>
+      </c>
+      <c r="T8" s="38">
+        <v>11.08</v>
+      </c>
+      <c r="U8" s="38">
+        <v>11.08</v>
+      </c>
+      <c r="V8" s="38">
+        <v>11.08</v>
+      </c>
+      <c r="W8" s="38">
+        <v>11.08</v>
+      </c>
+      <c r="X8" s="38">
+        <v>11.08</v>
+      </c>
+      <c r="Y8" s="38">
+        <v>11.08</v>
+      </c>
+      <c r="Z8" s="38">
+        <v>11.08</v>
+      </c>
+      <c r="AA8" s="38">
+        <v>11.08</v>
+      </c>
+      <c r="AB8" s="38">
+        <v>11.08</v>
+      </c>
+      <c r="AC8" s="38">
+        <v>11.08</v>
+      </c>
+      <c r="AD8" s="38">
+        <v>11.08</v>
+      </c>
+      <c r="AE8" s="38">
+        <v>11.08</v>
+      </c>
+      <c r="AF8" s="38">
+        <v>11.08</v>
+      </c>
+      <c r="AG8" s="38">
+        <v>11.08</v>
+      </c>
+      <c r="AH8" s="38">
+        <v>11.08</v>
+      </c>
+      <c r="AI8" s="38">
+        <v>11.08</v>
+      </c>
+      <c r="AJ8" s="38">
+        <v>11.08</v>
+      </c>
+      <c r="AK8" s="38">
+        <v>11.08</v>
+      </c>
+      <c r="AL8" s="38">
+        <v>11.08</v>
+      </c>
+      <c r="AM8" s="4" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="9" spans="1:40" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A9" s="21" t="s">
-        <v>84</v>
+        <v>21</v>
       </c>
       <c r="B9" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="C9" s="41"/>
-      <c r="D9" s="41"/>
-      <c r="E9" s="41"/>
-      <c r="F9" s="41"/>
-      <c r="G9" s="41"/>
-      <c r="H9" s="41"/>
-      <c r="I9" s="41"/>
-      <c r="J9" s="41"/>
-      <c r="K9" s="41"/>
-      <c r="L9" s="41"/>
-      <c r="M9" s="41"/>
-      <c r="N9" s="41"/>
-      <c r="O9" s="41"/>
-      <c r="P9" s="41"/>
-      <c r="Q9" s="41"/>
-      <c r="R9" s="73"/>
-      <c r="S9" s="73"/>
-      <c r="T9" s="41"/>
-      <c r="U9" s="41"/>
-      <c r="V9" s="41"/>
-      <c r="W9" s="41"/>
-      <c r="X9" s="41"/>
-      <c r="Y9" s="41"/>
-      <c r="Z9" s="41"/>
-      <c r="AA9" s="4" t="s">
+      <c r="C9" s="38">
+        <v>5.44</v>
+      </c>
+      <c r="D9" s="38">
+        <v>5.44</v>
+      </c>
+      <c r="E9" s="38">
+        <v>5.7</v>
+      </c>
+      <c r="F9" s="38">
+        <v>5.7</v>
+      </c>
+      <c r="G9" s="38">
+        <v>5.7</v>
+      </c>
+      <c r="H9" s="38">
+        <v>5.7</v>
+      </c>
+      <c r="I9" s="38">
+        <v>5.7</v>
+      </c>
+      <c r="J9" s="38">
+        <v>5.7</v>
+      </c>
+      <c r="K9" s="38">
+        <v>5.7</v>
+      </c>
+      <c r="L9" s="38">
+        <v>5.7</v>
+      </c>
+      <c r="M9" s="38">
+        <v>5.7</v>
+      </c>
+      <c r="N9" s="38">
+        <v>5.7</v>
+      </c>
+      <c r="O9" s="38">
+        <v>5.98</v>
+      </c>
+      <c r="P9" s="38">
+        <v>5.98</v>
+      </c>
+      <c r="Q9" s="38">
+        <v>5.98</v>
+      </c>
+      <c r="R9" s="38">
+        <v>5.98</v>
+      </c>
+      <c r="S9" s="38">
+        <v>5.98</v>
+      </c>
+      <c r="T9" s="38">
+        <v>5.98</v>
+      </c>
+      <c r="U9" s="38">
+        <v>5.98</v>
+      </c>
+      <c r="V9" s="38">
+        <v>5.98</v>
+      </c>
+      <c r="W9" s="38">
+        <v>5.98</v>
+      </c>
+      <c r="X9" s="38">
+        <v>5.98</v>
+      </c>
+      <c r="Y9" s="38">
+        <v>5.98</v>
+      </c>
+      <c r="Z9" s="38">
+        <v>5.98</v>
+      </c>
+      <c r="AA9" s="38">
+        <v>5.98</v>
+      </c>
+      <c r="AB9" s="38">
+        <v>5.98</v>
+      </c>
+      <c r="AC9" s="38">
+        <v>5.98</v>
+      </c>
+      <c r="AD9" s="38">
+        <v>5.98</v>
+      </c>
+      <c r="AE9" s="38">
+        <v>5.98</v>
+      </c>
+      <c r="AF9" s="38">
+        <v>5.98</v>
+      </c>
+      <c r="AG9" s="38">
+        <v>5.98</v>
+      </c>
+      <c r="AH9" s="38">
+        <v>5.98</v>
+      </c>
+      <c r="AI9" s="38">
+        <v>5.98</v>
+      </c>
+      <c r="AJ9" s="38">
+        <v>5.98</v>
+      </c>
+      <c r="AK9" s="38">
+        <v>5.98</v>
+      </c>
+      <c r="AL9" s="38">
+        <v>5.98</v>
+      </c>
+      <c r="AM9" s="4" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="10" spans="1:40" ht="48.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="C10" s="38">
+        <f>$C$38</f>
+        <v>132.34105224799995</v>
+      </c>
+      <c r="D10" s="38">
+        <f t="shared" ref="D10:H10" si="0">$C$38</f>
+        <v>132.34105224799995</v>
+      </c>
+      <c r="E10" s="38">
+        <f t="shared" si="0"/>
+        <v>132.34105224799995</v>
+      </c>
+      <c r="F10" s="38">
+        <f t="shared" si="0"/>
+        <v>132.34105224799995</v>
+      </c>
+      <c r="G10" s="38">
+        <f t="shared" si="0"/>
+        <v>132.34105224799995</v>
+      </c>
+      <c r="H10" s="38">
+        <f t="shared" si="0"/>
+        <v>132.34105224799995</v>
+      </c>
+      <c r="I10" s="38">
+        <f>$I$38</f>
+        <v>144.91470621139999</v>
+      </c>
+      <c r="J10" s="38">
+        <f t="shared" ref="J10:N10" si="1">$I$38</f>
+        <v>144.91470621139999</v>
+      </c>
+      <c r="K10" s="38">
+        <f t="shared" si="1"/>
+        <v>144.91470621139999</v>
+      </c>
+      <c r="L10" s="38">
+        <f t="shared" si="1"/>
+        <v>144.91470621139999</v>
+      </c>
+      <c r="M10" s="38">
+        <f t="shared" si="1"/>
+        <v>144.91470621139999</v>
+      </c>
+      <c r="N10" s="38">
+        <f t="shared" si="1"/>
+        <v>144.91470621139999</v>
+      </c>
+      <c r="O10" s="38">
+        <f>$O$38</f>
+        <v>171.78310199199996</v>
+      </c>
+      <c r="P10" s="38">
+        <f t="shared" ref="P10:T10" si="2">$O$38</f>
+        <v>171.78310199199996</v>
+      </c>
+      <c r="Q10" s="38">
+        <f t="shared" si="2"/>
+        <v>171.78310199199996</v>
+      </c>
+      <c r="R10" s="38">
+        <f t="shared" si="2"/>
+        <v>171.78310199199996</v>
+      </c>
+      <c r="S10" s="38">
+        <f t="shared" si="2"/>
+        <v>171.78310199199996</v>
+      </c>
+      <c r="T10" s="38">
+        <f t="shared" si="2"/>
+        <v>171.78310199199996</v>
+      </c>
+      <c r="U10" s="38">
+        <f>$U$38</f>
+        <v>158.82299893999999</v>
+      </c>
+      <c r="V10" s="38">
+        <f t="shared" ref="V10:Z10" si="3">$U$38</f>
+        <v>158.82299893999999</v>
+      </c>
+      <c r="W10" s="38">
+        <f t="shared" si="3"/>
+        <v>158.82299893999999</v>
+      </c>
+      <c r="X10" s="38">
+        <f t="shared" si="3"/>
+        <v>158.82299893999999</v>
+      </c>
+      <c r="Y10" s="38">
+        <f t="shared" si="3"/>
+        <v>158.82299893999999</v>
+      </c>
+      <c r="Z10" s="38">
+        <f t="shared" si="3"/>
+        <v>158.82299893999999</v>
+      </c>
+      <c r="AA10" s="38">
+        <f>$AA$38</f>
+        <v>161.52257251624999</v>
+      </c>
+      <c r="AB10" s="38">
+        <f t="shared" ref="AB10:AF10" si="4">$AA$38</f>
+        <v>161.52257251624999</v>
+      </c>
+      <c r="AC10" s="38">
+        <f t="shared" si="4"/>
+        <v>161.52257251624999</v>
+      </c>
+      <c r="AD10" s="38">
+        <f t="shared" si="4"/>
+        <v>161.52257251624999</v>
+      </c>
+      <c r="AE10" s="38">
+        <f t="shared" si="4"/>
+        <v>161.52257251624999</v>
+      </c>
+      <c r="AF10" s="38">
+        <f t="shared" si="4"/>
+        <v>161.52257251624999</v>
+      </c>
+      <c r="AG10" s="38">
+        <f>$AG$38</f>
+        <v>161.52257251624999</v>
+      </c>
+      <c r="AH10" s="38">
+        <f t="shared" ref="AH10:AL10" si="5">$AG$38</f>
+        <v>161.52257251624999</v>
+      </c>
+      <c r="AI10" s="38">
+        <f t="shared" si="5"/>
+        <v>161.52257251624999</v>
+      </c>
+      <c r="AJ10" s="38">
+        <f t="shared" si="5"/>
+        <v>161.52257251624999</v>
+      </c>
+      <c r="AK10" s="38">
+        <f t="shared" si="5"/>
+        <v>161.52257251624999</v>
+      </c>
+      <c r="AL10" s="38">
+        <f t="shared" si="5"/>
+        <v>161.52257251624999</v>
+      </c>
+      <c r="AM10" s="4" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="10" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="B10" s="9" t="s">
+      <c r="AN10" s="107" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="11" spans="1:40" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="B11" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="C10" s="41"/>
-      <c r="D10" s="41"/>
-      <c r="E10" s="41"/>
-      <c r="F10" s="41"/>
-      <c r="G10" s="41"/>
-      <c r="H10" s="41"/>
-      <c r="I10" s="41"/>
-      <c r="J10" s="41"/>
-      <c r="K10" s="41"/>
-      <c r="L10" s="41"/>
-      <c r="M10" s="41"/>
-      <c r="N10" s="41"/>
-      <c r="O10" s="41"/>
-      <c r="P10" s="41"/>
-      <c r="Q10" s="41"/>
-      <c r="R10" s="73"/>
-      <c r="S10" s="73"/>
-      <c r="T10" s="41"/>
-      <c r="U10" s="41"/>
-      <c r="V10" s="41"/>
-      <c r="W10" s="41"/>
-      <c r="X10" s="41"/>
-      <c r="Y10" s="41"/>
-      <c r="Z10" s="41"/>
-      <c r="AA10" s="4" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="11" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="21" t="s">
-        <v>30</v>
-      </c>
-      <c r="B11" s="9" t="s">
+      <c r="C11" s="38">
+        <v>12.61</v>
+      </c>
+      <c r="D11" s="38">
+        <v>12.61</v>
+      </c>
+      <c r="E11" s="38">
+        <v>12.61</v>
+      </c>
+      <c r="F11" s="38">
+        <v>12.61</v>
+      </c>
+      <c r="G11" s="38">
+        <v>12.61</v>
+      </c>
+      <c r="H11" s="38">
+        <v>12.61</v>
+      </c>
+      <c r="I11" s="38">
+        <v>12.61</v>
+      </c>
+      <c r="J11" s="38">
+        <v>14.08</v>
+      </c>
+      <c r="K11" s="38">
+        <v>14.08</v>
+      </c>
+      <c r="L11" s="38">
+        <v>14.08</v>
+      </c>
+      <c r="M11" s="38">
+        <v>14.08</v>
+      </c>
+      <c r="N11" s="38">
+        <v>14.08</v>
+      </c>
+      <c r="O11" s="38">
+        <v>14.08</v>
+      </c>
+      <c r="P11" s="38">
+        <v>14.08</v>
+      </c>
+      <c r="Q11" s="38">
+        <v>14.08</v>
+      </c>
+      <c r="R11" s="38">
+        <v>14.08</v>
+      </c>
+      <c r="S11" s="38">
+        <v>14.08</v>
+      </c>
+      <c r="T11" s="38">
+        <v>14.08</v>
+      </c>
+      <c r="U11" s="38">
+        <v>14.08</v>
+      </c>
+      <c r="V11" s="38">
+        <v>14.08</v>
+      </c>
+      <c r="W11" s="38">
+        <v>14.08</v>
+      </c>
+      <c r="X11" s="38">
+        <v>14.08</v>
+      </c>
+      <c r="Y11" s="38">
+        <v>14.08</v>
+      </c>
+      <c r="Z11" s="38">
+        <v>15.15</v>
+      </c>
+      <c r="AA11" s="38">
+        <v>15.15</v>
+      </c>
+      <c r="AB11" s="38">
+        <v>15.15</v>
+      </c>
+      <c r="AC11" s="38">
+        <v>15.15</v>
+      </c>
+      <c r="AD11" s="38">
+        <v>15.15</v>
+      </c>
+      <c r="AE11" s="38">
+        <v>15.15</v>
+      </c>
+      <c r="AF11" s="38">
+        <v>15.15</v>
+      </c>
+      <c r="AG11" s="38">
+        <v>15.15</v>
+      </c>
+      <c r="AH11" s="38">
+        <v>15.15</v>
+      </c>
+      <c r="AI11" s="38">
+        <v>15.15</v>
+      </c>
+      <c r="AJ11" s="38">
+        <v>15.15</v>
+      </c>
+      <c r="AK11" s="38">
+        <v>15.15</v>
+      </c>
+      <c r="AL11" s="38">
+        <v>15.15</v>
+      </c>
+      <c r="AM11" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="AN11" s="107" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="12" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A12" s="11"/>
+    </row>
+    <row r="13" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A13" s="11"/>
+    </row>
+    <row r="15" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A15" s="5" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="16" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A16" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C16" s="12">
+        <f>tariffs!$C$29</f>
+        <v>846</v>
+      </c>
+      <c r="D16" s="12">
+        <f>tariffs!$C$30</f>
+        <v>761</v>
+      </c>
+      <c r="E16" s="12">
+        <f>tariffs!$C$30</f>
+        <v>761</v>
+      </c>
+      <c r="F16" s="12">
+        <f>tariffs!$C$30</f>
+        <v>761</v>
+      </c>
+      <c r="G16" s="12">
+        <f>tariffs!$C$29</f>
+        <v>846</v>
+      </c>
+      <c r="H16" s="12">
+        <f>tariffs!$C$31</f>
+        <v>931</v>
+      </c>
+      <c r="I16" s="12">
+        <f>tariffs!$C$31</f>
+        <v>931</v>
+      </c>
+      <c r="J16" s="12">
+        <f>tariffs!$C$31</f>
+        <v>931</v>
+      </c>
+      <c r="K16" s="12">
+        <f>tariffs!$C$29</f>
+        <v>846</v>
+      </c>
+      <c r="L16" s="12">
+        <f>tariffs!$C$29</f>
+        <v>846</v>
+      </c>
+      <c r="M16" s="12">
+        <f>tariffs!$C$29</f>
+        <v>846</v>
+      </c>
+      <c r="N16" s="12">
+        <f>tariffs!$C$29</f>
+        <v>846</v>
+      </c>
+      <c r="O16" s="12">
+        <f>$C$16</f>
+        <v>846</v>
+      </c>
+      <c r="P16" s="12">
+        <f>$D$16</f>
+        <v>761</v>
+      </c>
+      <c r="Q16" s="12">
+        <f>$E$16</f>
+        <v>761</v>
+      </c>
+      <c r="R16" s="12">
+        <f>$F$16</f>
+        <v>761</v>
+      </c>
+      <c r="S16" s="12">
+        <f>$G$16</f>
+        <v>846</v>
+      </c>
+      <c r="T16" s="12">
+        <f>$H$16</f>
+        <v>931</v>
+      </c>
+      <c r="U16" s="12">
+        <f>$I$16</f>
+        <v>931</v>
+      </c>
+      <c r="V16" s="12">
+        <f>$J$16</f>
+        <v>931</v>
+      </c>
+      <c r="W16" s="12">
+        <f>$K$16</f>
+        <v>846</v>
+      </c>
+      <c r="X16" s="12">
+        <f>$L$16</f>
+        <v>846</v>
+      </c>
+      <c r="Y16" s="12">
+        <f>$M$16</f>
+        <v>846</v>
+      </c>
+      <c r="Z16" s="12">
+        <f>$N$16</f>
+        <v>846</v>
+      </c>
+      <c r="AA16" s="12">
+        <f>$C$16</f>
+        <v>846</v>
+      </c>
+      <c r="AB16" s="12">
+        <f>$D$16</f>
+        <v>761</v>
+      </c>
+      <c r="AC16" s="12">
+        <f>$E$16</f>
+        <v>761</v>
+      </c>
+      <c r="AD16" s="12">
+        <f>$F$16</f>
+        <v>761</v>
+      </c>
+      <c r="AE16" s="12">
+        <f>$G$16</f>
+        <v>846</v>
+      </c>
+      <c r="AF16" s="12">
+        <f>$H$16</f>
+        <v>931</v>
+      </c>
+      <c r="AG16" s="12">
+        <f>$I$16</f>
+        <v>931</v>
+      </c>
+      <c r="AH16" s="12">
+        <f>$J$16</f>
+        <v>931</v>
+      </c>
+      <c r="AI16" s="12">
+        <f>$K$16</f>
+        <v>846</v>
+      </c>
+      <c r="AJ16" s="12">
+        <f>$L$16</f>
+        <v>846</v>
+      </c>
+      <c r="AK16" s="12">
+        <f>$M$16</f>
+        <v>846</v>
+      </c>
+      <c r="AL16" s="12">
+        <f>$N$16</f>
+        <v>846</v>
+      </c>
+      <c r="AM16" s="11" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="17" spans="1:39" x14ac:dyDescent="0.35">
+      <c r="A17" s="11" t="s">
+        <v>157</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C17" s="12">
+        <f>info!$B$7/info!$B$8*59.052</f>
+        <v>0.67909799999999998</v>
+      </c>
+      <c r="D17" s="12">
+        <f>info!$B$7/info!$B$8*59.052</f>
+        <v>0.67909799999999998</v>
+      </c>
+      <c r="E17" s="12">
+        <f>info!$B$7/info!$B$8*59.052</f>
+        <v>0.67909799999999998</v>
+      </c>
+      <c r="F17" s="12">
+        <f>info!$B$7/info!$B$8*59.052</f>
+        <v>0.67909799999999998</v>
+      </c>
+      <c r="G17" s="12">
+        <f>info!$B$7/info!$B$8*59.052</f>
+        <v>0.67909799999999998</v>
+      </c>
+      <c r="H17" s="12">
+        <f>info!$B$7/info!$B$8*59.052</f>
+        <v>0.67909799999999998</v>
+      </c>
+      <c r="I17" s="12">
+        <f>info!$B$7/info!$B$8*59.052</f>
+        <v>0.67909799999999998</v>
+      </c>
+      <c r="J17" s="12">
+        <f>info!$B$7/info!$B$8*59.052</f>
+        <v>0.67909799999999998</v>
+      </c>
+      <c r="K17" s="12">
+        <f>info!$B$7/info!$B$8*59.052</f>
+        <v>0.67909799999999998</v>
+      </c>
+      <c r="L17" s="12">
+        <f>info!$B$7/info!$B$8*59.052</f>
+        <v>0.67909799999999998</v>
+      </c>
+      <c r="M17" s="12">
+        <f>info!$B$7/info!$B$8*59.052</f>
+        <v>0.67909799999999998</v>
+      </c>
+      <c r="N17" s="12">
+        <f>info!$B$7/info!$B$8*59.052</f>
+        <v>0.67909799999999998</v>
+      </c>
+      <c r="O17" s="12">
+        <f>info!$B$7/info!$B$8*59.052</f>
+        <v>0.67909799999999998</v>
+      </c>
+      <c r="P17" s="12">
+        <f>info!$B$7/info!$B$8*59.052</f>
+        <v>0.67909799999999998</v>
+      </c>
+      <c r="Q17" s="12">
+        <f>info!$B$7/info!$B$8*59.052</f>
+        <v>0.67909799999999998</v>
+      </c>
+      <c r="R17" s="12">
+        <f>info!$B$7/info!$B$8*59.052</f>
+        <v>0.67909799999999998</v>
+      </c>
+      <c r="S17" s="12">
+        <f>info!$B$7/info!$B$8*59.052</f>
+        <v>0.67909799999999998</v>
+      </c>
+      <c r="T17" s="12">
+        <f>info!$B$7/info!$B$8*59.052</f>
+        <v>0.67909799999999998</v>
+      </c>
+      <c r="U17" s="12">
+        <f>info!$B$7/info!$B$8*59.052</f>
+        <v>0.67909799999999998</v>
+      </c>
+      <c r="V17" s="12">
+        <f>info!$B$7/info!$B$8*59.052</f>
+        <v>0.67909799999999998</v>
+      </c>
+      <c r="W17" s="12">
+        <f>info!$B$7/info!$B$8*59.052</f>
+        <v>0.67909799999999998</v>
+      </c>
+      <c r="X17" s="12">
+        <f>info!$B$7/info!$B$8*59.052</f>
+        <v>0.67909799999999998</v>
+      </c>
+      <c r="Y17" s="12">
+        <f>info!$B$7/info!$B$8*59.052</f>
+        <v>0.67909799999999998</v>
+      </c>
+      <c r="Z17" s="12">
+        <f>info!$B$7/info!$B$8*59.052</f>
+        <v>0.67909799999999998</v>
+      </c>
+      <c r="AA17" s="12">
+        <f>info!$B$7/info!$B$8*59.052</f>
+        <v>0.67909799999999998</v>
+      </c>
+      <c r="AB17" s="12">
+        <f>info!$B$7/info!$B$8*59.052</f>
+        <v>0.67909799999999998</v>
+      </c>
+      <c r="AC17" s="12">
+        <f>info!$B$7/info!$B$8*59.052</f>
+        <v>0.67909799999999998</v>
+      </c>
+      <c r="AD17" s="12">
+        <f>info!$B$7/info!$B$8*59.052</f>
+        <v>0.67909799999999998</v>
+      </c>
+      <c r="AE17" s="12">
+        <f>info!$B$7/info!$B$8*59.052</f>
+        <v>0.67909799999999998</v>
+      </c>
+      <c r="AF17" s="12">
+        <f>info!$B$7/info!$B$8*59.052</f>
+        <v>0.67909799999999998</v>
+      </c>
+      <c r="AG17" s="12">
+        <f>info!$B$7/info!$B$8*59.052</f>
+        <v>0.67909799999999998</v>
+      </c>
+      <c r="AH17" s="12">
+        <f>info!$B$7/info!$B$8*59.052</f>
+        <v>0.67909799999999998</v>
+      </c>
+      <c r="AI17" s="12">
+        <f>info!$B$7/info!$B$8*59.052</f>
+        <v>0.67909799999999998</v>
+      </c>
+      <c r="AJ17" s="12">
+        <f>info!$B$7/info!$B$8*59.052</f>
+        <v>0.67909799999999998</v>
+      </c>
+      <c r="AK17" s="12">
+        <f>info!$B$7/info!$B$8*59.052</f>
+        <v>0.67909799999999998</v>
+      </c>
+      <c r="AL17" s="12">
+        <f>info!$B$7/info!$B$8*59.052</f>
+        <v>0.67909799999999998</v>
+      </c>
+      <c r="AM17" s="11" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="18" spans="1:39" x14ac:dyDescent="0.35">
+      <c r="A18" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C18" s="12">
+        <v>16.2</v>
+      </c>
+      <c r="D18" s="12">
+        <v>16.2</v>
+      </c>
+      <c r="E18" s="12">
+        <v>16.2</v>
+      </c>
+      <c r="F18" s="12">
+        <v>16.2</v>
+      </c>
+      <c r="G18" s="12">
+        <v>16.2</v>
+      </c>
+      <c r="H18" s="12">
+        <v>16.2</v>
+      </c>
+      <c r="I18" s="12">
+        <v>16.2</v>
+      </c>
+      <c r="J18" s="12">
+        <v>16.2</v>
+      </c>
+      <c r="K18" s="12">
+        <v>16.2</v>
+      </c>
+      <c r="L18" s="12">
+        <v>16.2</v>
+      </c>
+      <c r="M18" s="12">
+        <v>16.2</v>
+      </c>
+      <c r="N18" s="12">
+        <v>16.2</v>
+      </c>
+      <c r="O18" s="12">
+        <v>16.2</v>
+      </c>
+      <c r="P18" s="12">
+        <v>16.2</v>
+      </c>
+      <c r="Q18" s="12">
+        <v>16.2</v>
+      </c>
+      <c r="R18" s="12">
+        <v>16.2</v>
+      </c>
+      <c r="S18" s="12">
+        <v>16.2</v>
+      </c>
+      <c r="T18" s="12">
+        <v>16.2</v>
+      </c>
+      <c r="U18" s="12">
+        <v>16.2</v>
+      </c>
+      <c r="V18" s="12">
+        <v>16.2</v>
+      </c>
+      <c r="W18" s="12">
+        <v>16.2</v>
+      </c>
+      <c r="X18" s="12">
+        <v>16.2</v>
+      </c>
+      <c r="Y18" s="12">
+        <v>16.2</v>
+      </c>
+      <c r="Z18" s="12">
+        <v>16.2</v>
+      </c>
+      <c r="AA18" s="12">
+        <v>16.2</v>
+      </c>
+      <c r="AB18" s="12">
+        <v>16.2</v>
+      </c>
+      <c r="AC18" s="12">
+        <v>16.2</v>
+      </c>
+      <c r="AD18" s="12">
+        <v>16.2</v>
+      </c>
+      <c r="AE18" s="12">
+        <v>16.2</v>
+      </c>
+      <c r="AF18" s="12">
+        <v>16.2</v>
+      </c>
+      <c r="AG18" s="12">
+        <v>16.2</v>
+      </c>
+      <c r="AH18" s="12">
+        <v>16.2</v>
+      </c>
+      <c r="AI18" s="12">
+        <v>16.2</v>
+      </c>
+      <c r="AJ18" s="12">
+        <v>16.2</v>
+      </c>
+      <c r="AK18" s="12">
+        <v>16.2</v>
+      </c>
+      <c r="AL18" s="12">
+        <v>16.2</v>
+      </c>
+      <c r="AM18" s="3" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="19" spans="1:39" ht="29" x14ac:dyDescent="0.35">
+      <c r="A19" s="11" t="s">
+        <v>158</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C19" s="12">
+        <f>info!$B$7/info!$B$8*2333</f>
+        <v>26.829499999999999</v>
+      </c>
+      <c r="D19" s="12">
+        <f>info!$B$7/info!$B$8*2333</f>
+        <v>26.829499999999999</v>
+      </c>
+      <c r="E19" s="12">
+        <f>info!$B$7/info!$B$8*2333</f>
+        <v>26.829499999999999</v>
+      </c>
+      <c r="F19" s="12">
+        <f>info!$B$7/info!$B$8*2333</f>
+        <v>26.829499999999999</v>
+      </c>
+      <c r="G19" s="12">
+        <f>info!$B$7/info!$B$8*2333</f>
+        <v>26.829499999999999</v>
+      </c>
+      <c r="H19" s="12">
+        <f>info!$B$7/info!$B$8*2333</f>
+        <v>26.829499999999999</v>
+      </c>
+      <c r="I19" s="12">
+        <f>info!$B$7/info!$B$8*2333</f>
+        <v>26.829499999999999</v>
+      </c>
+      <c r="J19" s="12">
+        <f>info!$B$7/info!$B$8*2333</f>
+        <v>26.829499999999999</v>
+      </c>
+      <c r="K19" s="12">
+        <f>info!$B$7/info!$B$8*2333</f>
+        <v>26.829499999999999</v>
+      </c>
+      <c r="L19" s="12">
+        <f>info!$B$7/info!$B$8*2333</f>
+        <v>26.829499999999999</v>
+      </c>
+      <c r="M19" s="12">
+        <f>info!$B$7/info!$B$8*2333</f>
+        <v>26.829499999999999</v>
+      </c>
+      <c r="N19" s="12">
+        <f>info!$B$7/info!$B$8*2333</f>
+        <v>26.829499999999999</v>
+      </c>
+      <c r="O19" s="12">
+        <f>info!$B$7/info!$B$8*2333</f>
+        <v>26.829499999999999</v>
+      </c>
+      <c r="P19" s="12">
+        <f>info!$B$7/info!$B$8*2333</f>
+        <v>26.829499999999999</v>
+      </c>
+      <c r="Q19" s="12">
+        <f>info!$B$7/info!$B$8*2333</f>
+        <v>26.829499999999999</v>
+      </c>
+      <c r="R19" s="12">
+        <f>info!$B$7/info!$B$8*2333</f>
+        <v>26.829499999999999</v>
+      </c>
+      <c r="S19" s="12">
+        <f>info!$B$7/info!$B$8*2333</f>
+        <v>26.829499999999999</v>
+      </c>
+      <c r="T19" s="12">
+        <f>info!$B$7/info!$B$8*2333</f>
+        <v>26.829499999999999</v>
+      </c>
+      <c r="U19" s="12">
+        <f>info!$B$7/info!$B$8*2333</f>
+        <v>26.829499999999999</v>
+      </c>
+      <c r="V19" s="12">
+        <f>info!$B$7/info!$B$8*2333</f>
+        <v>26.829499999999999</v>
+      </c>
+      <c r="W19" s="12">
+        <f>info!$B$7/info!$B$8*2333</f>
+        <v>26.829499999999999</v>
+      </c>
+      <c r="X19" s="12">
+        <f>info!$B$7/info!$B$8*2333</f>
+        <v>26.829499999999999</v>
+      </c>
+      <c r="Y19" s="12">
+        <f>info!$B$7/info!$B$8*2333</f>
+        <v>26.829499999999999</v>
+      </c>
+      <c r="Z19" s="12">
+        <f>info!$B$7/info!$B$8*2333</f>
+        <v>26.829499999999999</v>
+      </c>
+      <c r="AA19" s="12">
+        <f>info!$B$7/info!$B$8*2333</f>
+        <v>26.829499999999999</v>
+      </c>
+      <c r="AB19" s="12">
+        <f>info!$B$7/info!$B$8*2333</f>
+        <v>26.829499999999999</v>
+      </c>
+      <c r="AC19" s="12">
+        <f>info!$B$7/info!$B$8*2333</f>
+        <v>26.829499999999999</v>
+      </c>
+      <c r="AD19" s="12">
+        <f>info!$B$7/info!$B$8*2333</f>
+        <v>26.829499999999999</v>
+      </c>
+      <c r="AE19" s="12">
+        <f>info!$B$7/info!$B$8*2333</f>
+        <v>26.829499999999999</v>
+      </c>
+      <c r="AF19" s="12">
+        <f>info!$B$7/info!$B$8*2333</f>
+        <v>26.829499999999999</v>
+      </c>
+      <c r="AG19" s="12">
+        <f>info!$B$7/info!$B$8*2333</f>
+        <v>26.829499999999999</v>
+      </c>
+      <c r="AH19" s="12">
+        <f>info!$B$7/info!$B$8*2333</f>
+        <v>26.829499999999999</v>
+      </c>
+      <c r="AI19" s="12">
+        <f>info!$B$7/info!$B$8*2333</f>
+        <v>26.829499999999999</v>
+      </c>
+      <c r="AJ19" s="12">
+        <f>info!$B$7/info!$B$8*2333</f>
+        <v>26.829499999999999</v>
+      </c>
+      <c r="AK19" s="12">
+        <f>info!$B$7/info!$B$8*2333</f>
+        <v>26.829499999999999</v>
+      </c>
+      <c r="AL19" s="12">
+        <f>info!$B$7/info!$B$8*2333</f>
+        <v>26.829499999999999</v>
+      </c>
+      <c r="AM19" s="3" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="20" spans="1:39" x14ac:dyDescent="0.35">
+      <c r="A20" s="11" t="s">
+        <v>159</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C20" s="12">
+        <f>info!$B$7/info!$B$8*118.104</f>
+        <v>1.358196</v>
+      </c>
+      <c r="D20" s="12">
+        <f>info!$B$7/info!$B$8*118.104</f>
+        <v>1.358196</v>
+      </c>
+      <c r="E20" s="12">
+        <f>info!$B$7/info!$B$8*118.104</f>
+        <v>1.358196</v>
+      </c>
+      <c r="F20" s="12">
+        <f>info!$B$7/info!$B$8*118.104</f>
+        <v>1.358196</v>
+      </c>
+      <c r="G20" s="12">
+        <f>info!$B$7/info!$B$8*118.104</f>
+        <v>1.358196</v>
+      </c>
+      <c r="H20" s="12">
+        <f>info!$B$7/info!$B$8*118.104</f>
+        <v>1.358196</v>
+      </c>
+      <c r="I20" s="12">
+        <f>info!$B$7/info!$B$8*118.104</f>
+        <v>1.358196</v>
+      </c>
+      <c r="J20" s="12">
+        <f>info!$B$7/info!$B$8*118.104</f>
+        <v>1.358196</v>
+      </c>
+      <c r="K20" s="12">
+        <f>info!$B$7/info!$B$8*118.104</f>
+        <v>1.358196</v>
+      </c>
+      <c r="L20" s="12">
+        <f>info!$B$7/info!$B$8*118.104</f>
+        <v>1.358196</v>
+      </c>
+      <c r="M20" s="12">
+        <f>info!$B$7/info!$B$8*118.104</f>
+        <v>1.358196</v>
+      </c>
+      <c r="N20" s="12">
+        <f>info!$B$7/info!$B$8*118.104</f>
+        <v>1.358196</v>
+      </c>
+      <c r="O20" s="12">
+        <f>info!$B$7/info!$B$8*118.104</f>
+        <v>1.358196</v>
+      </c>
+      <c r="P20" s="12">
+        <f>info!$B$7/info!$B$8*118.104</f>
+        <v>1.358196</v>
+      </c>
+      <c r="Q20" s="12">
+        <f>info!$B$7/info!$B$8*118.104</f>
+        <v>1.358196</v>
+      </c>
+      <c r="R20" s="12">
+        <f>info!$B$7/info!$B$8*118.104</f>
+        <v>1.358196</v>
+      </c>
+      <c r="S20" s="12">
+        <f>info!$B$7/info!$B$8*118.104</f>
+        <v>1.358196</v>
+      </c>
+      <c r="T20" s="12">
+        <f>info!$B$7/info!$B$8*118.104</f>
+        <v>1.358196</v>
+      </c>
+      <c r="U20" s="12">
+        <f>info!$B$7/info!$B$8*118.104</f>
+        <v>1.358196</v>
+      </c>
+      <c r="V20" s="12">
+        <f>info!$B$7/info!$B$8*118.104</f>
+        <v>1.358196</v>
+      </c>
+      <c r="W20" s="12">
+        <f>info!$B$7/info!$B$8*118.104</f>
+        <v>1.358196</v>
+      </c>
+      <c r="X20" s="12">
+        <f>info!$B$7/info!$B$8*118.104</f>
+        <v>1.358196</v>
+      </c>
+      <c r="Y20" s="12">
+        <f>info!$B$7/info!$B$8*118.104</f>
+        <v>1.358196</v>
+      </c>
+      <c r="Z20" s="12">
+        <f>info!$B$7/info!$B$8*118.104</f>
+        <v>1.358196</v>
+      </c>
+      <c r="AA20" s="12">
+        <f>info!$B$7/info!$B$8*118.104</f>
+        <v>1.358196</v>
+      </c>
+      <c r="AB20" s="12">
+        <f>info!$B$7/info!$B$8*118.104</f>
+        <v>1.358196</v>
+      </c>
+      <c r="AC20" s="12">
+        <f>info!$B$7/info!$B$8*118.104</f>
+        <v>1.358196</v>
+      </c>
+      <c r="AD20" s="12">
+        <f>info!$B$7/info!$B$8*118.104</f>
+        <v>1.358196</v>
+      </c>
+      <c r="AE20" s="12">
+        <f>info!$B$7/info!$B$8*118.104</f>
+        <v>1.358196</v>
+      </c>
+      <c r="AF20" s="12">
+        <f>info!$B$7/info!$B$8*118.104</f>
+        <v>1.358196</v>
+      </c>
+      <c r="AG20" s="12">
+        <f>info!$B$7/info!$B$8*118.104</f>
+        <v>1.358196</v>
+      </c>
+      <c r="AH20" s="12">
+        <f>info!$B$7/info!$B$8*118.104</f>
+        <v>1.358196</v>
+      </c>
+      <c r="AI20" s="12">
+        <f>info!$B$7/info!$B$8*118.104</f>
+        <v>1.358196</v>
+      </c>
+      <c r="AJ20" s="12">
+        <f>info!$B$7/info!$B$8*118.104</f>
+        <v>1.358196</v>
+      </c>
+      <c r="AK20" s="12">
+        <f>info!$B$7/info!$B$8*118.104</f>
+        <v>1.358196</v>
+      </c>
+      <c r="AL20" s="12">
+        <f>info!$B$7/info!$B$8*118.104</f>
+        <v>1.358196</v>
+      </c>
+      <c r="AM20" s="3" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="21" spans="1:39" x14ac:dyDescent="0.35">
+      <c r="A21" s="11" t="s">
+        <v>160</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C21" s="12">
+        <f>info!$B$7/info!$B$8*118.104</f>
+        <v>1.358196</v>
+      </c>
+      <c r="D21" s="12">
+        <f>info!$B$7/info!$B$8*118.104</f>
+        <v>1.358196</v>
+      </c>
+      <c r="E21" s="12">
+        <f>info!$B$7/info!$B$8*118.104</f>
+        <v>1.358196</v>
+      </c>
+      <c r="F21" s="12">
+        <f>info!$B$7/info!$B$8*118.104</f>
+        <v>1.358196</v>
+      </c>
+      <c r="G21" s="12">
+        <f>info!$B$7/info!$B$8*118.104</f>
+        <v>1.358196</v>
+      </c>
+      <c r="H21" s="12">
+        <f>info!$B$7/info!$B$8*118.104</f>
+        <v>1.358196</v>
+      </c>
+      <c r="I21" s="12">
+        <f>info!$B$7/info!$B$8*118.104</f>
+        <v>1.358196</v>
+      </c>
+      <c r="J21" s="12">
+        <f>info!$B$7/info!$B$8*118.104</f>
+        <v>1.358196</v>
+      </c>
+      <c r="K21" s="12">
+        <f>info!$B$7/info!$B$8*118.104</f>
+        <v>1.358196</v>
+      </c>
+      <c r="L21" s="12">
+        <f>info!$B$7/info!$B$8*118.104</f>
+        <v>1.358196</v>
+      </c>
+      <c r="M21" s="12">
+        <f>info!$B$7/info!$B$8*118.104</f>
+        <v>1.358196</v>
+      </c>
+      <c r="N21" s="12">
+        <f>info!$B$7/info!$B$8*118.104</f>
+        <v>1.358196</v>
+      </c>
+      <c r="O21" s="12">
+        <f>info!$B$7/info!$B$8*118.104</f>
+        <v>1.358196</v>
+      </c>
+      <c r="P21" s="12">
+        <f>info!$B$7/info!$B$8*118.104</f>
+        <v>1.358196</v>
+      </c>
+      <c r="Q21" s="12">
+        <f>info!$B$7/info!$B$8*118.104</f>
+        <v>1.358196</v>
+      </c>
+      <c r="R21" s="12">
+        <f>info!$B$7/info!$B$8*118.104</f>
+        <v>1.358196</v>
+      </c>
+      <c r="S21" s="12">
+        <f>info!$B$7/info!$B$8*118.104</f>
+        <v>1.358196</v>
+      </c>
+      <c r="T21" s="12">
+        <f>info!$B$7/info!$B$8*118.104</f>
+        <v>1.358196</v>
+      </c>
+      <c r="U21" s="12">
+        <f>info!$B$7/info!$B$8*118.104</f>
+        <v>1.358196</v>
+      </c>
+      <c r="V21" s="12">
+        <f>info!$B$7/info!$B$8*118.104</f>
+        <v>1.358196</v>
+      </c>
+      <c r="W21" s="12">
+        <f>info!$B$7/info!$B$8*118.104</f>
+        <v>1.358196</v>
+      </c>
+      <c r="X21" s="12">
+        <f>info!$B$7/info!$B$8*118.104</f>
+        <v>1.358196</v>
+      </c>
+      <c r="Y21" s="12">
+        <f>info!$B$7/info!$B$8*118.104</f>
+        <v>1.358196</v>
+      </c>
+      <c r="Z21" s="12">
+        <f>info!$B$7/info!$B$8*118.104</f>
+        <v>1.358196</v>
+      </c>
+      <c r="AA21" s="12">
+        <f>info!$B$7/info!$B$8*118.104</f>
+        <v>1.358196</v>
+      </c>
+      <c r="AB21" s="12">
+        <f>info!$B$7/info!$B$8*118.104</f>
+        <v>1.358196</v>
+      </c>
+      <c r="AC21" s="12">
+        <f>info!$B$7/info!$B$8*118.104</f>
+        <v>1.358196</v>
+      </c>
+      <c r="AD21" s="12">
+        <f>info!$B$7/info!$B$8*118.104</f>
+        <v>1.358196</v>
+      </c>
+      <c r="AE21" s="12">
+        <f>info!$B$7/info!$B$8*118.104</f>
+        <v>1.358196</v>
+      </c>
+      <c r="AF21" s="12">
+        <f>info!$B$7/info!$B$8*118.104</f>
+        <v>1.358196</v>
+      </c>
+      <c r="AG21" s="12">
+        <f>info!$B$7/info!$B$8*118.104</f>
+        <v>1.358196</v>
+      </c>
+      <c r="AH21" s="12">
+        <f>info!$B$7/info!$B$8*118.104</f>
+        <v>1.358196</v>
+      </c>
+      <c r="AI21" s="12">
+        <f>info!$B$7/info!$B$8*118.104</f>
+        <v>1.358196</v>
+      </c>
+      <c r="AJ21" s="12">
+        <f>info!$B$7/info!$B$8*118.104</f>
+        <v>1.358196</v>
+      </c>
+      <c r="AK21" s="12">
+        <f>info!$B$7/info!$B$8*118.104</f>
+        <v>1.358196</v>
+      </c>
+      <c r="AL21" s="12">
+        <f>info!$B$7/info!$B$8*118.104</f>
+        <v>1.358196</v>
+      </c>
+      <c r="AM21" s="3" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="22" spans="1:39" x14ac:dyDescent="0.35">
+      <c r="A22" s="11"/>
+    </row>
+    <row r="24" spans="1:39" ht="29" x14ac:dyDescent="0.35">
+      <c r="A24" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="25" spans="1:39" x14ac:dyDescent="0.35">
+      <c r="A25" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="B25" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="C11" s="41"/>
-      <c r="D11" s="41"/>
-      <c r="E11" s="41"/>
-      <c r="F11" s="41"/>
-      <c r="G11" s="41"/>
-      <c r="H11" s="41"/>
-      <c r="I11" s="41"/>
-      <c r="J11" s="41"/>
-      <c r="K11" s="41"/>
-      <c r="L11" s="41"/>
-      <c r="M11" s="41"/>
-      <c r="N11" s="41"/>
-      <c r="O11" s="41"/>
-      <c r="P11" s="41"/>
-      <c r="Q11" s="41"/>
-      <c r="R11" s="73"/>
-      <c r="S11" s="73"/>
-      <c r="T11" s="41"/>
-      <c r="U11" s="41"/>
-      <c r="V11" s="41"/>
-      <c r="W11" s="41"/>
-      <c r="X11" s="41"/>
-      <c r="Y11" s="41"/>
-      <c r="Z11" s="41"/>
-      <c r="AA11" s="4" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="12" spans="1:27" ht="48.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="21" t="s">
-        <v>32</v>
-      </c>
-      <c r="B12" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="C12" s="41"/>
-      <c r="D12" s="41"/>
-      <c r="E12" s="41"/>
-      <c r="F12" s="41"/>
-      <c r="G12" s="41"/>
-      <c r="H12" s="41"/>
-      <c r="I12" s="41"/>
-      <c r="J12" s="41"/>
-      <c r="K12" s="41"/>
-      <c r="L12" s="41"/>
-      <c r="M12" s="41"/>
-      <c r="N12" s="41"/>
-      <c r="O12" s="41"/>
-      <c r="P12" s="41"/>
-      <c r="Q12" s="41"/>
-      <c r="R12" s="73"/>
-      <c r="S12" s="73"/>
-      <c r="T12" s="41"/>
-      <c r="U12" s="41"/>
-      <c r="V12" s="41"/>
-      <c r="W12" s="41"/>
-      <c r="X12" s="41"/>
-      <c r="Y12" s="41"/>
-      <c r="Z12" s="41"/>
-      <c r="AA12" s="4" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="13" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="B13" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="C13" s="41"/>
-      <c r="D13" s="41"/>
-      <c r="E13" s="41"/>
-      <c r="F13" s="41"/>
-      <c r="G13" s="41"/>
-      <c r="H13" s="41"/>
-      <c r="I13" s="41"/>
-      <c r="J13" s="41"/>
-      <c r="K13" s="41"/>
-      <c r="L13" s="41"/>
-      <c r="M13" s="41"/>
-      <c r="N13" s="41"/>
-      <c r="O13" s="41"/>
-      <c r="P13" s="41"/>
-      <c r="Q13" s="41"/>
-      <c r="R13" s="73"/>
-      <c r="S13" s="73"/>
-      <c r="T13" s="41"/>
-      <c r="U13" s="41"/>
-      <c r="V13" s="41"/>
-      <c r="W13" s="41"/>
-      <c r="X13" s="41"/>
-      <c r="Y13" s="41"/>
-      <c r="Z13" s="41"/>
-      <c r="AA13" s="4" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="14" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="21" t="s">
-        <v>123</v>
-      </c>
-      <c r="B14" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="C14" s="41"/>
-      <c r="D14" s="41"/>
-      <c r="E14" s="41"/>
-      <c r="F14" s="41"/>
-      <c r="G14" s="41"/>
-      <c r="H14" s="41"/>
-      <c r="I14" s="41"/>
-      <c r="J14" s="41"/>
-      <c r="K14" s="41"/>
-      <c r="L14" s="41"/>
-      <c r="M14" s="41"/>
-      <c r="N14" s="41"/>
-      <c r="O14" s="41"/>
-      <c r="P14" s="41"/>
-      <c r="Q14" s="41"/>
-      <c r="R14" s="73"/>
-      <c r="S14" s="73"/>
-      <c r="T14" s="41"/>
-      <c r="U14" s="41"/>
-      <c r="V14" s="41"/>
-      <c r="W14" s="41"/>
-      <c r="X14" s="41"/>
-      <c r="Y14" s="41"/>
-      <c r="Z14" s="41"/>
-      <c r="AA14" s="4" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="A15" s="11"/>
-    </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="A16" s="11"/>
-    </row>
-    <row r="18" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="A18" s="5" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="19" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="C19" s="12">
-        <f>tariffs!$C$32</f>
-        <v>1991</v>
-      </c>
-      <c r="D19" s="12">
-        <f>tariffs!$C$33</f>
-        <v>1792</v>
-      </c>
-      <c r="E19" s="12">
-        <f>tariffs!$C$33</f>
-        <v>1792</v>
-      </c>
-      <c r="F19" s="12">
-        <f>tariffs!$C$33</f>
-        <v>1792</v>
-      </c>
-      <c r="G19" s="12">
-        <f>tariffs!$C$32</f>
-        <v>1991</v>
-      </c>
-      <c r="H19" s="12">
-        <f>tariffs!$C$34</f>
-        <v>2190</v>
-      </c>
-      <c r="I19" s="12">
-        <f>tariffs!$C$34</f>
-        <v>2190</v>
-      </c>
-      <c r="J19" s="12">
-        <f>tariffs!$C$34</f>
-        <v>2190</v>
-      </c>
-      <c r="K19" s="12">
-        <f>tariffs!$C$32</f>
-        <v>1991</v>
-      </c>
-      <c r="L19" s="12">
-        <f>tariffs!$C$32</f>
-        <v>1991</v>
-      </c>
-      <c r="M19" s="12">
-        <f>tariffs!$C$32</f>
-        <v>1991</v>
-      </c>
-      <c r="N19" s="12">
-        <f>tariffs!$C$32</f>
-        <v>1991</v>
-      </c>
-      <c r="O19" s="12">
-        <f>tariffs!$C$32</f>
-        <v>1991</v>
-      </c>
-      <c r="P19" s="12">
-        <f>tariffs!$C$33</f>
-        <v>1792</v>
-      </c>
-      <c r="Q19" s="12">
-        <f>tariffs!$C$33</f>
-        <v>1792</v>
-      </c>
-      <c r="R19" s="12">
-        <f>tariffs!$C$33</f>
-        <v>1792</v>
-      </c>
-      <c r="S19" s="12">
-        <f>tariffs!$C$32</f>
-        <v>1991</v>
-      </c>
-      <c r="T19" s="12">
-        <f>tariffs!$C$34</f>
-        <v>2190</v>
-      </c>
-      <c r="U19" s="12">
-        <f>tariffs!$C$34</f>
-        <v>2190</v>
-      </c>
-      <c r="V19" s="12">
-        <f>tariffs!$C$34</f>
-        <v>2190</v>
-      </c>
-      <c r="W19" s="12">
-        <f>tariffs!$C$32</f>
-        <v>1991</v>
-      </c>
-      <c r="X19" s="12">
-        <f>tariffs!$C$32</f>
-        <v>1991</v>
-      </c>
-      <c r="Y19" s="12">
-        <f>tariffs!$C$32</f>
-        <v>1991</v>
-      </c>
-      <c r="Z19" s="12">
-        <f>tariffs!$C$32</f>
-        <v>1991</v>
-      </c>
-      <c r="AA19" s="11" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="20" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="11" t="s">
-        <v>84</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="C20" s="12"/>
-      <c r="D20" s="12"/>
-      <c r="E20" s="12"/>
-      <c r="F20" s="12"/>
-      <c r="G20" s="12"/>
-      <c r="H20" s="12"/>
-      <c r="I20" s="12"/>
-      <c r="J20" s="12"/>
-      <c r="K20" s="12"/>
-      <c r="L20" s="12"/>
-      <c r="M20" s="12"/>
-      <c r="N20" s="12"/>
-      <c r="O20" s="12"/>
-      <c r="P20" s="12"/>
-      <c r="Q20" s="12"/>
-      <c r="R20" s="73"/>
-      <c r="S20" s="73"/>
-      <c r="T20" s="12"/>
-      <c r="U20" s="12"/>
-      <c r="V20" s="12"/>
-      <c r="W20" s="12"/>
-      <c r="X20" s="12"/>
-      <c r="Y20" s="12"/>
-      <c r="Z20" s="12"/>
-      <c r="AA20" s="11" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="21" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="C21" s="12"/>
-      <c r="D21" s="12"/>
-      <c r="E21" s="12"/>
-      <c r="F21" s="12"/>
-      <c r="G21" s="12"/>
-      <c r="H21" s="12"/>
-      <c r="I21" s="12"/>
-      <c r="J21" s="12"/>
-      <c r="K21" s="12"/>
-      <c r="L21" s="12"/>
-      <c r="M21" s="12"/>
-      <c r="N21" s="12"/>
-      <c r="O21" s="12"/>
-      <c r="P21" s="12"/>
-      <c r="Q21" s="12"/>
-      <c r="R21" s="73"/>
-      <c r="S21" s="73"/>
-      <c r="T21" s="12"/>
-      <c r="U21" s="12"/>
-      <c r="V21" s="12"/>
-      <c r="W21" s="12"/>
-      <c r="X21" s="12"/>
-      <c r="Y21" s="12"/>
-      <c r="Z21" s="12"/>
-      <c r="AA21" s="3" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="22" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="11" t="s">
+      <c r="C25" s="68">
+        <f>info!$B$6</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:39" ht="29" x14ac:dyDescent="0.35">
+      <c r="A26" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C26" s="3">
+        <f>IF(C25=1, D26, IF(C25=2,D26+E26, D26+E26+(C25-2)*F26))</f>
+        <v>156</v>
+      </c>
+      <c r="D26" s="3">
+        <v>96</v>
+      </c>
+      <c r="E26" s="3">
+        <v>60</v>
+      </c>
+      <c r="F26" s="3">
+        <v>40</v>
+      </c>
+      <c r="H26" s="14" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="27" spans="1:39" x14ac:dyDescent="0.35">
+      <c r="A27" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C27" s="3">
+        <f>IF(info!B9="да", MAX(D27*C25,G27), 0)</f>
         <v>90</v>
       </c>
-      <c r="B22" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="C22" s="12"/>
-      <c r="D22" s="12"/>
-      <c r="E22" s="12"/>
-      <c r="F22" s="12"/>
-      <c r="G22" s="12"/>
-      <c r="H22" s="12"/>
-      <c r="I22" s="12"/>
-      <c r="J22" s="12"/>
-      <c r="K22" s="12"/>
-      <c r="L22" s="12"/>
-      <c r="M22" s="12"/>
-      <c r="N22" s="12"/>
-      <c r="O22" s="12"/>
-      <c r="P22" s="12"/>
-      <c r="Q22" s="12"/>
-      <c r="R22" s="73"/>
-      <c r="S22" s="73"/>
-      <c r="T22" s="12"/>
-      <c r="U22" s="12"/>
-      <c r="V22" s="12"/>
-      <c r="W22" s="12"/>
-      <c r="X22" s="12"/>
-      <c r="Y22" s="12"/>
-      <c r="Z22" s="12"/>
-      <c r="AA22" s="3" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="23" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="11" t="s">
-        <v>91</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="C23" s="12"/>
-      <c r="D23" s="12"/>
-      <c r="E23" s="12"/>
-      <c r="F23" s="12"/>
-      <c r="G23" s="12"/>
-      <c r="H23" s="12"/>
-      <c r="I23" s="12"/>
-      <c r="J23" s="12"/>
-      <c r="K23" s="12"/>
-      <c r="L23" s="12"/>
-      <c r="M23" s="12"/>
-      <c r="N23" s="12"/>
-      <c r="O23" s="12"/>
-      <c r="P23" s="12"/>
-      <c r="Q23" s="12"/>
-      <c r="R23" s="73"/>
-      <c r="S23" s="73"/>
-      <c r="T23" s="12"/>
-      <c r="U23" s="12"/>
-      <c r="V23" s="12"/>
-      <c r="W23" s="12"/>
-      <c r="X23" s="12"/>
-      <c r="Y23" s="12"/>
-      <c r="Z23" s="12"/>
-      <c r="AA23" s="3" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="24" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="C24" s="12"/>
-      <c r="D24" s="12"/>
-      <c r="E24" s="12"/>
-      <c r="F24" s="12"/>
-      <c r="G24" s="12"/>
-      <c r="H24" s="12"/>
-      <c r="I24" s="12"/>
-      <c r="J24" s="12"/>
-      <c r="K24" s="12"/>
-      <c r="L24" s="12"/>
-      <c r="M24" s="12"/>
-      <c r="N24" s="12"/>
-      <c r="O24" s="12"/>
-      <c r="P24" s="12"/>
-      <c r="Q24" s="12"/>
-      <c r="R24" s="73"/>
-      <c r="S24" s="73"/>
-      <c r="T24" s="12"/>
-      <c r="U24" s="12"/>
-      <c r="V24" s="12"/>
-      <c r="W24" s="12"/>
-      <c r="X24" s="12"/>
-      <c r="Y24" s="12"/>
-      <c r="Z24" s="12"/>
-      <c r="AA24" s="3" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="25" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="A25" s="11"/>
-    </row>
-    <row r="27" spans="1:27" ht="29" x14ac:dyDescent="0.35">
-      <c r="A27" s="13" t="s">
-        <v>92</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="E27" s="3" t="s">
+      <c r="D27" s="3">
+        <v>43</v>
+      </c>
+      <c r="E27" s="3">
+        <v>43</v>
+      </c>
+      <c r="F27" s="3">
+        <v>43</v>
+      </c>
+      <c r="G27" s="3">
+        <v>90</v>
+      </c>
+      <c r="H27" s="14" t="s">
         <v>94</v>
       </c>
-      <c r="F27" s="3" t="s">
+    </row>
+    <row r="28" spans="1:39" x14ac:dyDescent="0.35">
+      <c r="A28" s="11" t="s">
         <v>95</v>
       </c>
-      <c r="G27" s="3" t="s">
+      <c r="B28" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C28" s="3">
+        <f>IF(info!B10="да", D28*C25, 0)</f>
+        <v>600</v>
+      </c>
+      <c r="D28" s="3">
+        <v>300</v>
+      </c>
+      <c r="E28" s="3">
+        <v>300</v>
+      </c>
+      <c r="F28" s="3">
+        <v>300</v>
+      </c>
+      <c r="H28" s="14" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="28" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="A28" s="11" t="s">
+    <row r="29" spans="1:39" x14ac:dyDescent="0.35">
+      <c r="A29" s="11" t="s">
         <v>97</v>
       </c>
-      <c r="B28" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="C28" s="77">
-        <f>info!$B$6</f>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="29" spans="1:27" ht="29" x14ac:dyDescent="0.35">
-      <c r="A29" s="11" t="s">
+      <c r="B29" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C29" s="3">
+        <f>SUM(C26:C28)</f>
+        <v>846</v>
+      </c>
+    </row>
+    <row r="30" spans="1:39" ht="29" x14ac:dyDescent="0.35">
+      <c r="A30" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="B29" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="C29" s="3">
-        <f>IF(C28=1, D29, IF(C28=2,D29+E29, D29+E29+(C28-2)*F29))</f>
-        <v>276</v>
-      </c>
-      <c r="D29" s="3">
-        <v>96</v>
-      </c>
-      <c r="E29" s="3">
-        <v>60</v>
-      </c>
-      <c r="F29" s="3">
-        <v>40</v>
-      </c>
-      <c r="H29" s="14" t="s">
+      <c r="B30" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C30" s="3">
+        <f>ROUND($C$29*0.9, 0)</f>
+        <v>761</v>
+      </c>
+      <c r="D30" s="14"/>
+    </row>
+    <row r="31" spans="1:39" ht="29" x14ac:dyDescent="0.35">
+      <c r="A31" s="11" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="30" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="A30" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="C30" s="3">
-        <f>IF(info!B9="да", MAX(D30*C28,G30), 0)</f>
-        <v>215</v>
-      </c>
-      <c r="D30" s="3">
-        <v>43</v>
-      </c>
-      <c r="E30" s="3">
-        <v>43</v>
-      </c>
-      <c r="F30" s="3">
-        <v>43</v>
-      </c>
-      <c r="G30" s="3">
-        <v>90</v>
-      </c>
-      <c r="H30" s="14" t="s">
+      <c r="B31" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C31" s="3">
+        <f>ROUND($C$29*1.1, 0)</f>
+        <v>931</v>
+      </c>
+      <c r="D31" s="14"/>
+    </row>
+    <row r="32" spans="1:39" x14ac:dyDescent="0.35">
+      <c r="A32" s="11"/>
+    </row>
+    <row r="33" spans="1:33" x14ac:dyDescent="0.35">
+      <c r="A33" s="11"/>
+    </row>
+    <row r="34" spans="1:33" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A34" s="13" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="31" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="A31" s="11" t="s">
+      <c r="C34" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="B31" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="C31" s="3">
-        <f>IF(info!B10="да", D31*C28, 0)</f>
-        <v>1500</v>
-      </c>
-      <c r="D31" s="3">
-        <v>300</v>
-      </c>
-      <c r="E31" s="3">
-        <v>300</v>
-      </c>
-      <c r="F31" s="3">
-        <v>300</v>
-      </c>
-      <c r="H31" s="14" t="s">
+      <c r="I34" s="3" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="32" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="A32" s="11" t="s">
+      <c r="O34" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="B32" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="C32" s="3">
-        <f>SUM(C29:C31)</f>
-        <v>1991</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" ht="29" x14ac:dyDescent="0.35">
-      <c r="A33" s="11" t="s">
+      <c r="U34" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="B33" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="C33" s="3">
-        <f>ROUND($C$32*0.9, 0)</f>
-        <v>1792</v>
-      </c>
-      <c r="D33" s="14"/>
-    </row>
-    <row r="34" spans="1:6" ht="29" x14ac:dyDescent="0.35">
-      <c r="A34" s="11" t="s">
+      <c r="AA34" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="AG34" s="3" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="35" spans="1:33" x14ac:dyDescent="0.35">
+      <c r="A35" s="11" t="s">
         <v>105</v>
       </c>
-      <c r="B34" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="C34" s="3">
-        <f>ROUND($C$32*1.1, 0)</f>
-        <v>2190</v>
-      </c>
-      <c r="D34" s="14"/>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A35" s="11"/>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A36" s="11"/>
-    </row>
-    <row r="37" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A37" s="13" t="s">
+      <c r="B35" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="C37" s="3" t="s">
+      <c r="C35" s="3">
+        <v>697.64</v>
+      </c>
+      <c r="I35" s="3">
+        <v>1246.3399999999999</v>
+      </c>
+      <c r="O35" s="12">
+        <v>905.56</v>
+      </c>
+      <c r="U35" s="12">
+        <v>905.56</v>
+      </c>
+      <c r="AA35" s="3">
+        <v>702.35</v>
+      </c>
+      <c r="AG35" s="3">
+        <v>702.35</v>
+      </c>
+    </row>
+    <row r="36" spans="1:33" ht="29" x14ac:dyDescent="0.35">
+      <c r="A36" s="11" t="s">
         <v>107</v>
       </c>
-      <c r="D37" s="3" t="s">
+      <c r="C36" s="3">
+        <v>0.75127999999999995</v>
+      </c>
+      <c r="I36" s="3">
+        <v>0.460484</v>
+      </c>
+      <c r="O36" s="3">
+        <v>0.75127999999999995</v>
+      </c>
+      <c r="U36" s="3">
+        <v>0.6946</v>
+      </c>
+      <c r="AA36" s="3">
+        <v>0.91078999999999999</v>
+      </c>
+      <c r="AG36" s="3">
+        <v>0.91078999999999999</v>
+      </c>
+    </row>
+    <row r="37" spans="1:33" x14ac:dyDescent="0.35">
+      <c r="A37" s="11" t="s">
         <v>108</v>
       </c>
-      <c r="E37" s="3" t="s">
+      <c r="B37" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="F37" s="3" t="s">
+      <c r="C37" s="3">
+        <v>3.03</v>
+      </c>
+      <c r="I37" s="3">
+        <v>3.03</v>
+      </c>
+      <c r="O37" s="3">
+        <v>3.03</v>
+      </c>
+      <c r="U37" s="3">
+        <v>3.03</v>
+      </c>
+      <c r="AA37" s="3">
+        <v>3.03</v>
+      </c>
+      <c r="AG37" s="3">
+        <v>3.03</v>
+      </c>
+    </row>
+    <row r="38" spans="1:33" x14ac:dyDescent="0.35">
+      <c r="A38" s="11" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A38" s="11" t="s">
+      <c r="B38" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="B38" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="C38" s="3">
-        <v>697.64</v>
-      </c>
-      <c r="D38" s="3">
-        <v>1246.3399999999999</v>
-      </c>
-      <c r="E38" s="12">
-        <v>905.56</v>
-      </c>
-      <c r="F38" s="12">
-        <v>905.56</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" ht="29" x14ac:dyDescent="0.35">
-      <c r="A39" s="11" t="s">
-        <v>113</v>
-      </c>
-      <c r="C39" s="3">
-        <v>0.75127999999999995</v>
-      </c>
-      <c r="D39" s="3">
-        <v>0.460484</v>
-      </c>
-      <c r="E39" s="3">
-        <v>0.75127999999999995</v>
-      </c>
-      <c r="F39" s="3">
-        <v>0.6946</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A40" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="C40" s="3">
-        <v>3.03</v>
-      </c>
-      <c r="D40" s="3">
-        <v>3.03</v>
-      </c>
-      <c r="E40" s="3">
-        <v>3.03</v>
-      </c>
-      <c r="F40" s="3">
-        <v>3.03</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A41" s="11" t="s">
-        <v>116</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="C41" s="12">
-        <f>C40*C39*C38/12</f>
+      <c r="C38" s="111">
+        <f>C37*C36*C35/12</f>
         <v>132.34105224799995</v>
       </c>
-      <c r="D41" s="12">
-        <f>D40*D39*D38/12</f>
+      <c r="I38" s="111">
+        <f>I37*I36*I35/12</f>
         <v>144.91470621139999</v>
       </c>
-      <c r="E41" s="12">
-        <f>E40*E39*E38/12</f>
+      <c r="O38" s="111">
+        <f>O37*O36*O35/12</f>
         <v>171.78310199199996</v>
       </c>
-      <c r="F41" s="12">
-        <f>F40*F39*F38/12</f>
+      <c r="U38" s="111">
+        <f>U37*U36*U35/12</f>
         <v>158.82299893999999</v>
       </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A42" s="11"/>
+      <c r="AA38" s="111">
+        <f t="shared" ref="AA38:AB38" si="6">AA37*AA36*AA35/12</f>
+        <v>161.52257251624999</v>
+      </c>
+      <c r="AG38" s="111">
+        <f>AG37*AG36*AG35/12</f>
+        <v>161.52257251624999</v>
+      </c>
+    </row>
+    <row r="39" spans="1:33" x14ac:dyDescent="0.35">
+      <c r="A39" s="11"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A16 A19:A24 B38" xr:uid="{D8613508-C5BB-4385-8912-C0DC41588D40}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A16:A21 B35 A2:A13" xr:uid="{D8613508-C5BB-4385-8912-C0DC41588D40}"/>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="AN4" r:id="rId1" xr:uid="{EB965509-102D-4B53-B456-99C7325AFDBA}"/>
+    <hyperlink ref="AN2" r:id="rId2" xr:uid="{DEEC3F70-95CD-4EA7-B6E2-C3A7B4A28179}"/>
+    <hyperlink ref="AN11" r:id="rId3" xr:uid="{D8FE59FA-DF15-4357-AD6A-782774547E87}"/>
+    <hyperlink ref="AN10" r:id="rId4" xr:uid="{6B729592-441D-4F3A-A3C7-C5752F9D3454}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{9820BB39-D1DD-4C29-8A81-68EB24E19078}">
           <x14:formula1>
             <xm:f>helper!$D$2:$D$12</xm:f>
           </x14:formula1>
-          <xm:sqref>B19:B24 B2:B16 B28:B34</xm:sqref>
+          <xm:sqref>B16:B21 B25:B31 B2:B13</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{449E7DB2-14BE-4D4D-9015-D76E8830A331}">
+          <x14:formula1>
+            <xm:f>helper!$F$2:$F$28</xm:f>
+          </x14:formula1>
+          <xm:sqref>K1:AL1</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -9454,93 +11240,93 @@
     <col min="12" max="12" width="11" style="17" customWidth="1"/>
     <col min="13" max="13" width="13.54296875" style="17" customWidth="1"/>
     <col min="14" max="14" width="12.08984375" style="17" customWidth="1"/>
-    <col min="15" max="15" width="12.08984375" style="72" customWidth="1"/>
+    <col min="15" max="15" width="12.08984375" style="67" customWidth="1"/>
     <col min="16" max="17" width="11.08984375" style="17" customWidth="1"/>
     <col min="18" max="18" width="9.1796875" style="17"/>
     <col min="19" max="19" width="10.7265625" style="17" customWidth="1"/>
     <col min="20" max="16384" width="9.1796875" style="17"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" s="58" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:20" s="53" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="B1" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="16" t="s">
+      <c r="C1" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="C1" s="16" t="s">
+      <c r="D1" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="D1" s="16" t="s">
+      <c r="E1" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="E1" s="16" t="s">
+      <c r="F1" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="F1" s="16" t="s">
+      <c r="G1" s="16" t="s">
         <v>65</v>
       </c>
-      <c r="G1" s="16" t="s">
+      <c r="H1" s="16" t="s">
         <v>66</v>
       </c>
-      <c r="H1" s="16" t="s">
+      <c r="I1" s="16" t="s">
         <v>67</v>
       </c>
-      <c r="I1" s="16" t="s">
+      <c r="J1" s="16" t="s">
         <v>68</v>
       </c>
-      <c r="J1" s="16" t="s">
+      <c r="K1" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="K1" s="16" t="s">
+      <c r="L1" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="L1" s="16" t="s">
+      <c r="M1" s="20" t="s">
         <v>71</v>
       </c>
-      <c r="M1" s="20" t="s">
+      <c r="N1" s="16" t="s">
         <v>72</v>
       </c>
-      <c r="N1" s="16" t="s">
+      <c r="O1" s="65" t="s">
         <v>73</v>
       </c>
-      <c r="O1" s="70" t="s">
+      <c r="P1" s="16" t="s">
+        <v>121</v>
+      </c>
+      <c r="Q1" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="R1" s="53" t="s">
+        <v>58</v>
+      </c>
+      <c r="S1" s="53" t="s">
         <v>74</v>
       </c>
-      <c r="P1" s="16" t="s">
-        <v>128</v>
-      </c>
-      <c r="Q1" s="16" t="s">
-        <v>129</v>
-      </c>
-      <c r="R1" s="58" t="s">
-        <v>59</v>
-      </c>
-      <c r="S1" s="58" t="s">
-        <v>75</v>
-      </c>
-      <c r="T1" s="58" t="s">
-        <v>54</v>
+      <c r="T1" s="53" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A2" s="15"/>
       <c r="B2" s="18"/>
-      <c r="C2" s="48"/>
-      <c r="D2" s="48"/>
-      <c r="E2" s="48"/>
-      <c r="F2" s="48"/>
-      <c r="G2" s="49"/>
-      <c r="H2" s="48"/>
-      <c r="I2" s="48"/>
-      <c r="J2" s="48"/>
-      <c r="K2" s="48"/>
+      <c r="C2" s="43"/>
+      <c r="D2" s="43"/>
+      <c r="E2" s="43"/>
+      <c r="F2" s="43"/>
+      <c r="G2" s="44"/>
+      <c r="H2" s="43"/>
+      <c r="I2" s="43"/>
+      <c r="J2" s="43"/>
+      <c r="K2" s="43"/>
       <c r="L2" s="15"/>
       <c r="M2" s="19"/>
       <c r="N2" s="18"/>
-      <c r="O2" s="71"/>
-      <c r="P2" s="48"/>
-      <c r="Q2" s="48"/>
+      <c r="O2" s="66"/>
+      <c r="P2" s="43"/>
+      <c r="Q2" s="43"/>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A3" s="15"/>
@@ -9557,7 +11343,7 @@
       <c r="L3" s="15"/>
       <c r="M3" s="19"/>
       <c r="N3" s="18"/>
-      <c r="O3" s="71"/>
+      <c r="O3" s="66"/>
       <c r="P3" s="15"/>
       <c r="Q3" s="15"/>
     </row>
@@ -9576,7 +11362,7 @@
       <c r="L4" s="15"/>
       <c r="M4" s="19"/>
       <c r="N4" s="18"/>
-      <c r="O4" s="71"/>
+      <c r="O4" s="66"/>
       <c r="P4" s="15"/>
       <c r="Q4" s="15"/>
     </row>
@@ -9595,7 +11381,7 @@
       <c r="L5" s="15"/>
       <c r="M5" s="19"/>
       <c r="N5" s="18"/>
-      <c r="O5" s="71"/>
+      <c r="O5" s="66"/>
       <c r="P5" s="15"/>
       <c r="Q5" s="15"/>
     </row>
@@ -9614,7 +11400,7 @@
       <c r="L6" s="15"/>
       <c r="M6" s="19"/>
       <c r="N6" s="18"/>
-      <c r="O6" s="71"/>
+      <c r="O6" s="66"/>
       <c r="P6" s="15"/>
       <c r="Q6" s="15"/>
     </row>
@@ -9633,7 +11419,7 @@
       <c r="L7" s="15"/>
       <c r="M7" s="19"/>
       <c r="N7" s="18"/>
-      <c r="O7" s="71"/>
+      <c r="O7" s="66"/>
       <c r="P7" s="15"/>
       <c r="Q7" s="15"/>
     </row>
@@ -9652,7 +11438,7 @@
       <c r="L8" s="15"/>
       <c r="M8" s="19"/>
       <c r="N8" s="18"/>
-      <c r="O8" s="71"/>
+      <c r="O8" s="66"/>
       <c r="P8" s="15"/>
       <c r="Q8" s="15"/>
     </row>
@@ -9671,7 +11457,7 @@
       <c r="L9" s="15"/>
       <c r="M9" s="19"/>
       <c r="N9" s="18"/>
-      <c r="O9" s="71"/>
+      <c r="O9" s="66"/>
       <c r="P9" s="15"/>
       <c r="Q9" s="15"/>
     </row>
@@ -9690,7 +11476,7 @@
       <c r="L10" s="15"/>
       <c r="M10" s="19"/>
       <c r="N10" s="18"/>
-      <c r="O10" s="71"/>
+      <c r="O10" s="66"/>
       <c r="P10" s="15"/>
       <c r="Q10" s="15"/>
     </row>
@@ -9709,7 +11495,7 @@
       <c r="L11" s="15"/>
       <c r="M11" s="19"/>
       <c r="N11" s="18"/>
-      <c r="O11" s="71"/>
+      <c r="O11" s="66"/>
       <c r="P11" s="15"/>
       <c r="Q11" s="15"/>
     </row>
@@ -9728,7 +11514,7 @@
       <c r="L12" s="15"/>
       <c r="M12" s="19"/>
       <c r="N12" s="18"/>
-      <c r="O12" s="71"/>
+      <c r="O12" s="66"/>
       <c r="P12" s="15"/>
       <c r="Q12" s="15"/>
     </row>
@@ -9747,7 +11533,7 @@
       <c r="L13" s="15"/>
       <c r="M13" s="19"/>
       <c r="N13" s="18"/>
-      <c r="O13" s="71"/>
+      <c r="O13" s="66"/>
       <c r="P13" s="15"/>
       <c r="Q13" s="15"/>
     </row>
@@ -9766,7 +11552,7 @@
       <c r="L14" s="15"/>
       <c r="M14" s="19"/>
       <c r="N14" s="18"/>
-      <c r="O14" s="71"/>
+      <c r="O14" s="66"/>
       <c r="P14" s="15"/>
       <c r="Q14" s="15"/>
     </row>
@@ -9785,7 +11571,7 @@
       <c r="L15" s="15"/>
       <c r="M15" s="19"/>
       <c r="N15" s="18"/>
-      <c r="O15" s="71"/>
+      <c r="O15" s="66"/>
       <c r="P15" s="15"/>
       <c r="Q15" s="15"/>
     </row>
@@ -9804,7 +11590,7 @@
       <c r="L16" s="15"/>
       <c r="M16" s="19"/>
       <c r="N16" s="18"/>
-      <c r="O16" s="71"/>
+      <c r="O16" s="66"/>
       <c r="P16" s="15"/>
       <c r="Q16" s="15"/>
     </row>
@@ -9823,7 +11609,7 @@
       <c r="L17" s="15"/>
       <c r="M17" s="19"/>
       <c r="N17" s="18"/>
-      <c r="O17" s="71"/>
+      <c r="O17" s="66"/>
       <c r="P17" s="15"/>
       <c r="Q17" s="15"/>
     </row>
@@ -9842,7 +11628,7 @@
       <c r="L18" s="15"/>
       <c r="M18" s="19"/>
       <c r="N18" s="18"/>
-      <c r="O18" s="71"/>
+      <c r="O18" s="66"/>
       <c r="P18" s="15"/>
       <c r="Q18" s="15"/>
     </row>
@@ -9861,7 +11647,7 @@
       <c r="L19" s="15"/>
       <c r="M19" s="19"/>
       <c r="N19" s="18"/>
-      <c r="O19" s="71"/>
+      <c r="O19" s="66"/>
       <c r="P19" s="15"/>
       <c r="Q19" s="15"/>
     </row>
@@ -9880,7 +11666,7 @@
       <c r="L20" s="15"/>
       <c r="M20" s="19"/>
       <c r="N20" s="18"/>
-      <c r="O20" s="71"/>
+      <c r="O20" s="66"/>
       <c r="P20" s="15"/>
       <c r="Q20" s="15"/>
     </row>
@@ -9899,7 +11685,7 @@
       <c r="L21" s="15"/>
       <c r="M21" s="19"/>
       <c r="N21" s="18"/>
-      <c r="O21" s="71"/>
+      <c r="O21" s="66"/>
       <c r="P21" s="15"/>
       <c r="Q21" s="15"/>
     </row>
@@ -9918,7 +11704,7 @@
       <c r="L22" s="15"/>
       <c r="M22" s="19"/>
       <c r="N22" s="18"/>
-      <c r="O22" s="71"/>
+      <c r="O22" s="66"/>
       <c r="P22" s="15"/>
       <c r="Q22" s="15"/>
     </row>
@@ -9937,7 +11723,7 @@
       <c r="L23" s="15"/>
       <c r="M23" s="19"/>
       <c r="N23" s="18"/>
-      <c r="O23" s="71"/>
+      <c r="O23" s="66"/>
       <c r="P23" s="15"/>
       <c r="Q23" s="15"/>
     </row>
@@ -9956,7 +11742,7 @@
       <c r="L24" s="15"/>
       <c r="M24" s="19"/>
       <c r="N24" s="18"/>
-      <c r="O24" s="71"/>
+      <c r="O24" s="66"/>
       <c r="P24" s="15"/>
       <c r="Q24" s="15"/>
     </row>
@@ -9975,7 +11761,7 @@
       <c r="L25" s="15"/>
       <c r="M25" s="19"/>
       <c r="N25" s="18"/>
-      <c r="O25" s="71"/>
+      <c r="O25" s="66"/>
       <c r="P25" s="15"/>
       <c r="Q25" s="15"/>
     </row>
@@ -9994,7 +11780,7 @@
       <c r="L26" s="15"/>
       <c r="M26" s="19"/>
       <c r="N26" s="18"/>
-      <c r="O26" s="71"/>
+      <c r="O26" s="66"/>
       <c r="P26" s="15"/>
       <c r="Q26" s="15"/>
     </row>
@@ -10013,7 +11799,7 @@
       <c r="L27" s="15"/>
       <c r="M27" s="19"/>
       <c r="N27" s="18"/>
-      <c r="O27" s="71"/>
+      <c r="O27" s="66"/>
       <c r="P27" s="15"/>
       <c r="Q27" s="15"/>
     </row>
@@ -10032,7 +11818,7 @@
       <c r="L28" s="15"/>
       <c r="M28" s="19"/>
       <c r="N28" s="18"/>
-      <c r="O28" s="71"/>
+      <c r="O28" s="66"/>
       <c r="P28" s="15"/>
       <c r="Q28" s="15"/>
     </row>
@@ -10051,7 +11837,7 @@
       <c r="L29" s="15"/>
       <c r="M29" s="19"/>
       <c r="N29" s="18"/>
-      <c r="O29" s="71"/>
+      <c r="O29" s="66"/>
       <c r="P29" s="15"/>
       <c r="Q29" s="15"/>
     </row>
@@ -10070,7 +11856,7 @@
       <c r="L30" s="15"/>
       <c r="M30" s="19"/>
       <c r="N30" s="18"/>
-      <c r="O30" s="71"/>
+      <c r="O30" s="66"/>
       <c r="P30" s="15"/>
       <c r="Q30" s="15"/>
     </row>
@@ -10089,7 +11875,7 @@
       <c r="L31" s="15"/>
       <c r="M31" s="19"/>
       <c r="N31" s="18"/>
-      <c r="O31" s="71"/>
+      <c r="O31" s="66"/>
       <c r="P31" s="15"/>
       <c r="Q31" s="15"/>
     </row>
@@ -10108,7 +11894,7 @@
       <c r="L32" s="15"/>
       <c r="M32" s="19"/>
       <c r="N32" s="18"/>
-      <c r="O32" s="71"/>
+      <c r="O32" s="66"/>
       <c r="P32" s="15"/>
       <c r="Q32" s="15"/>
     </row>
@@ -10127,7 +11913,7 @@
       <c r="L33" s="15"/>
       <c r="M33" s="19"/>
       <c r="N33" s="18"/>
-      <c r="O33" s="71"/>
+      <c r="O33" s="66"/>
       <c r="P33" s="15"/>
       <c r="Q33" s="15"/>
     </row>
@@ -10146,7 +11932,7 @@
       <c r="L34" s="15"/>
       <c r="M34" s="19"/>
       <c r="N34" s="18"/>
-      <c r="O34" s="71"/>
+      <c r="O34" s="66"/>
       <c r="P34" s="15"/>
       <c r="Q34" s="15"/>
     </row>
@@ -10165,7 +11951,7 @@
       <c r="L35" s="15"/>
       <c r="M35" s="19"/>
       <c r="N35" s="18"/>
-      <c r="O35" s="71"/>
+      <c r="O35" s="66"/>
       <c r="P35" s="15"/>
       <c r="Q35" s="15"/>
     </row>
@@ -10184,7 +11970,7 @@
       <c r="L36" s="15"/>
       <c r="M36" s="19"/>
       <c r="N36" s="18"/>
-      <c r="O36" s="71"/>
+      <c r="O36" s="66"/>
       <c r="P36" s="15"/>
       <c r="Q36" s="15"/>
     </row>
@@ -10203,7 +11989,7 @@
       <c r="L37" s="15"/>
       <c r="M37" s="19"/>
       <c r="N37" s="18"/>
-      <c r="O37" s="71"/>
+      <c r="O37" s="66"/>
       <c r="P37" s="15"/>
       <c r="Q37" s="15"/>
     </row>
@@ -10222,7 +12008,7 @@
       <c r="L38" s="15"/>
       <c r="M38" s="19"/>
       <c r="N38" s="18"/>
-      <c r="O38" s="71"/>
+      <c r="O38" s="66"/>
       <c r="P38" s="15"/>
       <c r="Q38" s="15"/>
     </row>
@@ -10241,7 +12027,7 @@
       <c r="L39" s="15"/>
       <c r="M39" s="19"/>
       <c r="N39" s="18"/>
-      <c r="O39" s="71"/>
+      <c r="O39" s="66"/>
       <c r="P39" s="15"/>
       <c r="Q39" s="15"/>
     </row>
@@ -10260,7 +12046,7 @@
       <c r="L40" s="15"/>
       <c r="M40" s="19"/>
       <c r="N40" s="18"/>
-      <c r="O40" s="71"/>
+      <c r="O40" s="66"/>
       <c r="P40" s="15"/>
       <c r="Q40" s="15"/>
     </row>
@@ -10291,22 +12077,22 @@
   <sheetData>
     <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>61</v>
-      </c>
       <c r="E1" s="1" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
@@ -10320,1428 +12106,1442 @@
         <v>16</v>
       </c>
       <c r="D2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E2" t="s">
-        <v>155</v>
-      </c>
-      <c r="F2" s="83">
+        <v>148</v>
+      </c>
+      <c r="F2" s="69">
         <v>45627</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="B3" t="s">
         <v>18</v>
       </c>
       <c r="C3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E3" t="s">
-        <v>156</v>
-      </c>
-      <c r="F3" s="83">
+        <v>149</v>
+      </c>
+      <c r="F3" s="69">
         <v>45658</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="B4" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="C4" t="s">
         <v>22</v>
       </c>
       <c r="D4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E4" t="s">
-        <v>149</v>
-      </c>
-      <c r="F4" s="83">
+        <v>142</v>
+      </c>
+      <c r="F4" s="69">
         <v>45689</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="B5" t="s">
+        <v>136</v>
+      </c>
+      <c r="C5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D5" t="s">
+        <v>48</v>
+      </c>
+      <c r="E5" t="s">
         <v>143</v>
       </c>
-      <c r="C5" t="s">
-        <v>31</v>
-      </c>
-      <c r="D5" t="s">
-        <v>49</v>
-      </c>
-      <c r="E5" t="s">
-        <v>150</v>
-      </c>
-      <c r="F5" s="83">
+      <c r="F5" s="69">
         <v>45717</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="B6" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="C6" t="s">
         <v>25</v>
       </c>
       <c r="D6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E6" t="s">
-        <v>35</v>
-      </c>
-      <c r="F6" s="83">
+        <v>34</v>
+      </c>
+      <c r="F6" s="69">
         <v>45748</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="B7" t="s">
-        <v>28</v>
-      </c>
-      <c r="F7" s="83">
+        <v>27</v>
+      </c>
+      <c r="F7" s="69">
         <v>45778</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="B8" t="s">
-        <v>30</v>
-      </c>
-      <c r="F8" s="83">
+        <v>29</v>
+      </c>
+      <c r="F8" s="69">
         <v>45809</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="B9" t="s">
-        <v>144</v>
-      </c>
-      <c r="F9" s="83">
+        <v>137</v>
+      </c>
+      <c r="F9" s="69">
         <v>45839</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="B10" t="s">
-        <v>136</v>
-      </c>
-      <c r="F10" s="83">
+        <v>129</v>
+      </c>
+      <c r="F10" s="69">
         <v>45870</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="B11" t="s">
-        <v>137</v>
-      </c>
-      <c r="F11" s="83">
+        <v>130</v>
+      </c>
+      <c r="F11" s="69">
         <v>45901</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="B12" t="s">
-        <v>138</v>
-      </c>
-      <c r="F12" s="83">
+        <v>131</v>
+      </c>
+      <c r="F12" s="69">
         <v>45931</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="B13" t="s">
-        <v>135</v>
-      </c>
-      <c r="F13" s="83">
+        <v>128</v>
+      </c>
+      <c r="F13" s="69">
         <v>45962</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="B14" t="s">
-        <v>142</v>
-      </c>
-      <c r="F14" s="83">
+        <v>135</v>
+      </c>
+      <c r="F14" s="69">
         <v>45992</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="B15" t="s">
         <v>21</v>
       </c>
-      <c r="F15" s="83">
+      <c r="F15" s="69">
         <v>46023</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="B16" t="s">
-        <v>139</v>
-      </c>
-      <c r="F16" s="83">
+        <v>132</v>
+      </c>
+      <c r="F16" s="69">
         <v>46054</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B17" t="s">
-        <v>35</v>
-      </c>
-      <c r="F17" s="83">
+        <v>34</v>
+      </c>
+      <c r="F17" s="69">
         <v>46082</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="F18" s="83">
+      <c r="F18" s="69">
         <v>46113</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="F19" s="83">
+      <c r="F19" s="69">
         <v>46143</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="F20" s="83"/>
+      <c r="F20" s="69">
+        <v>46174</v>
+      </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="F21" s="83"/>
+      <c r="F21" s="69">
+        <v>46204</v>
+      </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="F22" s="83"/>
+      <c r="F22" s="69">
+        <v>46235</v>
+      </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="F23" s="83"/>
+      <c r="F23" s="69">
+        <v>46266</v>
+      </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="F24" s="83"/>
+      <c r="F24" s="69">
+        <v>46296</v>
+      </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="F25" s="83"/>
+      <c r="F25" s="69">
+        <v>46327</v>
+      </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="F26" s="83"/>
+      <c r="F26" s="69">
+        <v>46357</v>
+      </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="F27" s="83"/>
+      <c r="F27" s="69"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="F28" s="83"/>
+      <c r="F28" s="69"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="F29" s="83"/>
+      <c r="F29" s="69"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="F30" s="83"/>
+      <c r="F30" s="69"/>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="F31" s="83"/>
+      <c r="F31" s="69"/>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="F32" s="83"/>
+      <c r="F32" s="69"/>
     </row>
     <row r="33" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F33" s="83"/>
+      <c r="F33" s="69"/>
     </row>
     <row r="34" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F34" s="83"/>
+      <c r="F34" s="69"/>
     </row>
     <row r="35" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F35" s="83"/>
+      <c r="F35" s="69"/>
     </row>
     <row r="36" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F36" s="83"/>
+      <c r="F36" s="69"/>
     </row>
     <row r="37" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F37" s="83"/>
+      <c r="F37" s="69"/>
     </row>
     <row r="38" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F38" s="83"/>
+      <c r="F38" s="69"/>
     </row>
     <row r="39" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F39" s="83"/>
+      <c r="F39" s="69"/>
     </row>
     <row r="40" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F40" s="83"/>
+      <c r="F40" s="69"/>
     </row>
     <row r="41" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F41" s="83"/>
+      <c r="F41" s="69"/>
     </row>
     <row r="42" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F42" s="83"/>
+      <c r="F42" s="69"/>
     </row>
     <row r="43" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F43" s="83"/>
+      <c r="F43" s="69"/>
     </row>
     <row r="44" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F44" s="83"/>
+      <c r="F44" s="69"/>
     </row>
     <row r="45" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F45" s="83"/>
+      <c r="F45" s="69"/>
     </row>
     <row r="46" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F46" s="83"/>
+      <c r="F46" s="69"/>
     </row>
     <row r="47" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F47" s="83"/>
+      <c r="F47" s="69"/>
     </row>
     <row r="48" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F48" s="83"/>
+      <c r="F48" s="69"/>
     </row>
     <row r="49" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F49" s="83"/>
+      <c r="F49" s="69"/>
     </row>
     <row r="50" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F50" s="83"/>
+      <c r="F50" s="69"/>
     </row>
     <row r="51" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F51" s="83"/>
+      <c r="F51" s="69"/>
     </row>
     <row r="52" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F52" s="83"/>
+      <c r="F52" s="69"/>
     </row>
     <row r="53" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F53" s="83"/>
+      <c r="F53" s="69"/>
     </row>
     <row r="54" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F54" s="83"/>
+      <c r="F54" s="69"/>
     </row>
     <row r="55" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F55" s="83"/>
+      <c r="F55" s="69"/>
     </row>
     <row r="56" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F56" s="83"/>
+      <c r="F56" s="69"/>
     </row>
     <row r="57" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F57" s="83"/>
+      <c r="F57" s="69"/>
     </row>
     <row r="58" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F58" s="83"/>
+      <c r="F58" s="69"/>
     </row>
     <row r="59" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F59" s="83"/>
+      <c r="F59" s="69"/>
     </row>
     <row r="60" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F60" s="83"/>
+      <c r="F60" s="69"/>
     </row>
     <row r="61" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F61" s="83"/>
+      <c r="F61" s="69"/>
     </row>
     <row r="62" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F62" s="83"/>
+      <c r="F62" s="69"/>
     </row>
     <row r="63" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F63" s="83"/>
+      <c r="F63" s="69"/>
     </row>
     <row r="64" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F64" s="83"/>
+      <c r="F64" s="69"/>
     </row>
     <row r="65" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F65" s="83"/>
+      <c r="F65" s="69"/>
     </row>
     <row r="66" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F66" s="83"/>
+      <c r="F66" s="69"/>
     </row>
     <row r="67" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F67" s="83"/>
+      <c r="F67" s="69"/>
     </row>
     <row r="68" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F68" s="83"/>
+      <c r="F68" s="69"/>
     </row>
     <row r="69" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F69" s="83"/>
+      <c r="F69" s="69"/>
     </row>
     <row r="70" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F70" s="83"/>
+      <c r="F70" s="69"/>
     </row>
     <row r="71" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F71" s="83"/>
+      <c r="F71" s="69"/>
     </row>
     <row r="72" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F72" s="83"/>
+      <c r="F72" s="69"/>
     </row>
     <row r="73" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F73" s="83"/>
+      <c r="F73" s="69"/>
     </row>
     <row r="74" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F74" s="83"/>
+      <c r="F74" s="69"/>
     </row>
     <row r="75" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F75" s="83"/>
+      <c r="F75" s="69"/>
     </row>
     <row r="76" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F76" s="83"/>
+      <c r="F76" s="69"/>
     </row>
     <row r="77" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F77" s="83"/>
+      <c r="F77" s="69"/>
     </row>
     <row r="78" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F78" s="83"/>
+      <c r="F78" s="69"/>
     </row>
     <row r="79" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F79" s="83"/>
+      <c r="F79" s="69"/>
     </row>
     <row r="80" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F80" s="83"/>
+      <c r="F80" s="69"/>
     </row>
     <row r="81" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F81" s="83"/>
+      <c r="F81" s="69"/>
     </row>
     <row r="82" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F82" s="83"/>
+      <c r="F82" s="69"/>
     </row>
     <row r="83" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F83" s="83"/>
+      <c r="F83" s="69"/>
     </row>
     <row r="84" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F84" s="83"/>
+      <c r="F84" s="69"/>
     </row>
     <row r="85" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F85" s="83"/>
+      <c r="F85" s="69"/>
     </row>
     <row r="86" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F86" s="83"/>
+      <c r="F86" s="69"/>
     </row>
     <row r="87" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F87" s="83"/>
+      <c r="F87" s="69"/>
     </row>
     <row r="88" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F88" s="83"/>
+      <c r="F88" s="69"/>
     </row>
     <row r="89" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F89" s="83"/>
+      <c r="F89" s="69"/>
     </row>
     <row r="90" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F90" s="83"/>
+      <c r="F90" s="69"/>
     </row>
     <row r="91" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F91" s="83"/>
+      <c r="F91" s="69"/>
     </row>
     <row r="92" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F92" s="83"/>
+      <c r="F92" s="69"/>
     </row>
     <row r="93" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F93" s="83"/>
+      <c r="F93" s="69"/>
     </row>
     <row r="94" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F94" s="83"/>
+      <c r="F94" s="69"/>
     </row>
     <row r="95" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F95" s="83"/>
+      <c r="F95" s="69"/>
     </row>
     <row r="96" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F96" s="83"/>
+      <c r="F96" s="69"/>
     </row>
     <row r="97" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F97" s="83"/>
+      <c r="F97" s="69"/>
     </row>
     <row r="98" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F98" s="83"/>
+      <c r="F98" s="69"/>
     </row>
     <row r="99" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F99" s="83"/>
+      <c r="F99" s="69"/>
     </row>
     <row r="100" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F100" s="83"/>
+      <c r="F100" s="69"/>
     </row>
     <row r="101" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F101" s="83"/>
+      <c r="F101" s="69"/>
     </row>
     <row r="102" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F102" s="83"/>
+      <c r="F102" s="69"/>
     </row>
     <row r="103" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F103" s="83"/>
+      <c r="F103" s="69"/>
     </row>
     <row r="104" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F104" s="83"/>
+      <c r="F104" s="69"/>
     </row>
     <row r="105" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F105" s="83"/>
+      <c r="F105" s="69"/>
     </row>
     <row r="106" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F106" s="83"/>
+      <c r="F106" s="69"/>
     </row>
     <row r="107" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F107" s="83"/>
+      <c r="F107" s="69"/>
     </row>
     <row r="108" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F108" s="83"/>
+      <c r="F108" s="69"/>
     </row>
     <row r="109" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F109" s="83"/>
+      <c r="F109" s="69"/>
     </row>
     <row r="110" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F110" s="83"/>
+      <c r="F110" s="69"/>
     </row>
     <row r="111" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F111" s="83"/>
+      <c r="F111" s="69"/>
     </row>
     <row r="112" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F112" s="83"/>
+      <c r="F112" s="69"/>
     </row>
     <row r="113" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F113" s="83"/>
+      <c r="F113" s="69"/>
     </row>
     <row r="114" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F114" s="83"/>
+      <c r="F114" s="69"/>
     </row>
     <row r="115" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F115" s="83"/>
+      <c r="F115" s="69"/>
     </row>
     <row r="116" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F116" s="83"/>
+      <c r="F116" s="69"/>
     </row>
     <row r="117" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F117" s="83"/>
+      <c r="F117" s="69"/>
     </row>
     <row r="118" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F118" s="83"/>
+      <c r="F118" s="69"/>
     </row>
     <row r="119" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F119" s="83"/>
+      <c r="F119" s="69"/>
     </row>
     <row r="120" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F120" s="83"/>
+      <c r="F120" s="69"/>
     </row>
     <row r="121" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F121" s="83"/>
+      <c r="F121" s="69"/>
     </row>
     <row r="122" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F122" s="83"/>
+      <c r="F122" s="69"/>
     </row>
     <row r="123" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F123" s="83"/>
+      <c r="F123" s="69"/>
     </row>
     <row r="124" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F124" s="83"/>
+      <c r="F124" s="69"/>
     </row>
     <row r="125" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F125" s="83"/>
+      <c r="F125" s="69"/>
     </row>
     <row r="126" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F126" s="83"/>
+      <c r="F126" s="69"/>
     </row>
     <row r="127" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F127" s="83"/>
+      <c r="F127" s="69"/>
     </row>
     <row r="128" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F128" s="83"/>
+      <c r="F128" s="69"/>
     </row>
     <row r="129" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F129" s="83"/>
+      <c r="F129" s="69"/>
     </row>
     <row r="130" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F130" s="83"/>
+      <c r="F130" s="69"/>
     </row>
     <row r="131" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F131" s="83"/>
+      <c r="F131" s="69"/>
     </row>
     <row r="132" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F132" s="83"/>
+      <c r="F132" s="69"/>
     </row>
     <row r="133" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F133" s="83"/>
+      <c r="F133" s="69"/>
     </row>
     <row r="134" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F134" s="83"/>
+      <c r="F134" s="69"/>
     </row>
     <row r="135" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F135" s="83"/>
+      <c r="F135" s="69"/>
     </row>
     <row r="136" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F136" s="83"/>
+      <c r="F136" s="69"/>
     </row>
     <row r="137" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F137" s="83"/>
+      <c r="F137" s="69"/>
     </row>
     <row r="138" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F138" s="83"/>
+      <c r="F138" s="69"/>
     </row>
     <row r="139" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F139" s="83"/>
+      <c r="F139" s="69"/>
     </row>
     <row r="140" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F140" s="83"/>
+      <c r="F140" s="69"/>
     </row>
     <row r="141" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F141" s="83"/>
+      <c r="F141" s="69"/>
     </row>
     <row r="142" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F142" s="83"/>
+      <c r="F142" s="69"/>
     </row>
     <row r="143" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F143" s="83"/>
+      <c r="F143" s="69"/>
     </row>
     <row r="144" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F144" s="83"/>
+      <c r="F144" s="69"/>
     </row>
     <row r="145" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F145" s="83"/>
+      <c r="F145" s="69"/>
     </row>
     <row r="146" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F146" s="83"/>
+      <c r="F146" s="69"/>
     </row>
     <row r="147" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F147" s="83"/>
+      <c r="F147" s="69"/>
     </row>
     <row r="148" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F148" s="83"/>
+      <c r="F148" s="69"/>
     </row>
     <row r="149" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F149" s="83"/>
+      <c r="F149" s="69"/>
     </row>
     <row r="150" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F150" s="83"/>
+      <c r="F150" s="69"/>
     </row>
     <row r="151" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F151" s="83"/>
+      <c r="F151" s="69"/>
     </row>
     <row r="152" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F152" s="83"/>
+      <c r="F152" s="69"/>
     </row>
     <row r="153" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F153" s="83"/>
+      <c r="F153" s="69"/>
     </row>
     <row r="154" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F154" s="83"/>
+      <c r="F154" s="69"/>
     </row>
     <row r="155" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F155" s="83"/>
+      <c r="F155" s="69"/>
     </row>
     <row r="156" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F156" s="83"/>
+      <c r="F156" s="69"/>
     </row>
     <row r="157" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F157" s="83"/>
+      <c r="F157" s="69"/>
     </row>
     <row r="158" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F158" s="83"/>
+      <c r="F158" s="69"/>
     </row>
     <row r="159" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F159" s="83"/>
+      <c r="F159" s="69"/>
     </row>
     <row r="160" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F160" s="83"/>
+      <c r="F160" s="69"/>
     </row>
     <row r="161" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F161" s="83"/>
+      <c r="F161" s="69"/>
     </row>
     <row r="162" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F162" s="83"/>
+      <c r="F162" s="69"/>
     </row>
     <row r="163" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F163" s="83"/>
+      <c r="F163" s="69"/>
     </row>
     <row r="164" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F164" s="83"/>
+      <c r="F164" s="69"/>
     </row>
     <row r="165" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F165" s="83"/>
+      <c r="F165" s="69"/>
     </row>
     <row r="166" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F166" s="83"/>
+      <c r="F166" s="69"/>
     </row>
     <row r="167" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F167" s="83"/>
+      <c r="F167" s="69"/>
     </row>
     <row r="168" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F168" s="83"/>
+      <c r="F168" s="69"/>
     </row>
     <row r="169" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F169" s="83"/>
+      <c r="F169" s="69"/>
     </row>
     <row r="170" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F170" s="83"/>
+      <c r="F170" s="69"/>
     </row>
     <row r="171" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F171" s="83"/>
+      <c r="F171" s="69"/>
     </row>
     <row r="172" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F172" s="83"/>
+      <c r="F172" s="69"/>
     </row>
     <row r="173" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F173" s="83"/>
+      <c r="F173" s="69"/>
     </row>
     <row r="174" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F174" s="83"/>
+      <c r="F174" s="69"/>
     </row>
     <row r="175" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F175" s="83"/>
+      <c r="F175" s="69"/>
     </row>
     <row r="176" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F176" s="83"/>
+      <c r="F176" s="69"/>
     </row>
     <row r="177" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F177" s="83"/>
+      <c r="F177" s="69"/>
     </row>
     <row r="178" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F178" s="83"/>
+      <c r="F178" s="69"/>
     </row>
     <row r="179" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F179" s="83"/>
+      <c r="F179" s="69"/>
     </row>
     <row r="180" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F180" s="83"/>
+      <c r="F180" s="69"/>
     </row>
     <row r="181" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F181" s="83"/>
+      <c r="F181" s="69"/>
     </row>
     <row r="182" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F182" s="83"/>
+      <c r="F182" s="69"/>
     </row>
     <row r="183" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F183" s="83"/>
+      <c r="F183" s="69"/>
     </row>
     <row r="184" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F184" s="83"/>
+      <c r="F184" s="69"/>
     </row>
     <row r="185" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F185" s="83"/>
+      <c r="F185" s="69"/>
     </row>
     <row r="186" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F186" s="83"/>
+      <c r="F186" s="69"/>
     </row>
     <row r="187" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F187" s="83"/>
+      <c r="F187" s="69"/>
     </row>
     <row r="188" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F188" s="83"/>
+      <c r="F188" s="69"/>
     </row>
     <row r="189" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F189" s="83"/>
+      <c r="F189" s="69"/>
     </row>
     <row r="190" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F190" s="83"/>
+      <c r="F190" s="69"/>
     </row>
     <row r="191" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F191" s="83"/>
+      <c r="F191" s="69"/>
     </row>
     <row r="192" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F192" s="83"/>
+      <c r="F192" s="69"/>
     </row>
     <row r="193" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F193" s="83"/>
+      <c r="F193" s="69"/>
     </row>
     <row r="194" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F194" s="83"/>
+      <c r="F194" s="69"/>
     </row>
     <row r="195" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F195" s="83"/>
+      <c r="F195" s="69"/>
     </row>
     <row r="196" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F196" s="83"/>
+      <c r="F196" s="69"/>
     </row>
     <row r="197" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F197" s="83"/>
+      <c r="F197" s="69"/>
     </row>
     <row r="198" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F198" s="83"/>
+      <c r="F198" s="69"/>
     </row>
     <row r="199" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F199" s="83"/>
+      <c r="F199" s="69"/>
     </row>
     <row r="200" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F200" s="83"/>
+      <c r="F200" s="69"/>
     </row>
     <row r="201" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F201" s="83"/>
+      <c r="F201" s="69"/>
     </row>
     <row r="202" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F202" s="83"/>
+      <c r="F202" s="69"/>
     </row>
     <row r="203" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F203" s="83"/>
+      <c r="F203" s="69"/>
     </row>
     <row r="204" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F204" s="83"/>
+      <c r="F204" s="69"/>
     </row>
     <row r="205" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F205" s="83"/>
+      <c r="F205" s="69"/>
     </row>
     <row r="206" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F206" s="83"/>
+      <c r="F206" s="69"/>
     </row>
     <row r="207" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F207" s="83"/>
+      <c r="F207" s="69"/>
     </row>
     <row r="208" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F208" s="83"/>
+      <c r="F208" s="69"/>
     </row>
     <row r="209" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F209" s="83"/>
+      <c r="F209" s="69"/>
     </row>
     <row r="210" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F210" s="83"/>
+      <c r="F210" s="69"/>
     </row>
     <row r="211" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F211" s="83"/>
+      <c r="F211" s="69"/>
     </row>
     <row r="212" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F212" s="83"/>
+      <c r="F212" s="69"/>
     </row>
     <row r="213" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F213" s="83"/>
+      <c r="F213" s="69"/>
     </row>
     <row r="214" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F214" s="83"/>
+      <c r="F214" s="69"/>
     </row>
     <row r="215" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F215" s="83"/>
+      <c r="F215" s="69"/>
     </row>
     <row r="216" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F216" s="83"/>
+      <c r="F216" s="69"/>
     </row>
     <row r="217" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F217" s="83"/>
+      <c r="F217" s="69"/>
     </row>
     <row r="218" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F218" s="83"/>
+      <c r="F218" s="69"/>
     </row>
     <row r="219" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F219" s="83"/>
+      <c r="F219" s="69"/>
     </row>
     <row r="220" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F220" s="83"/>
+      <c r="F220" s="69"/>
     </row>
     <row r="221" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F221" s="83"/>
+      <c r="F221" s="69"/>
     </row>
     <row r="222" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F222" s="83"/>
+      <c r="F222" s="69"/>
     </row>
     <row r="223" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F223" s="83"/>
+      <c r="F223" s="69"/>
     </row>
     <row r="224" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F224" s="83"/>
+      <c r="F224" s="69"/>
     </row>
     <row r="225" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F225" s="83"/>
+      <c r="F225" s="69"/>
     </row>
     <row r="226" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F226" s="83"/>
+      <c r="F226" s="69"/>
     </row>
     <row r="227" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F227" s="83"/>
+      <c r="F227" s="69"/>
     </row>
     <row r="228" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F228" s="83"/>
+      <c r="F228" s="69"/>
     </row>
     <row r="229" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F229" s="83"/>
+      <c r="F229" s="69"/>
     </row>
     <row r="230" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F230" s="83"/>
+      <c r="F230" s="69"/>
     </row>
     <row r="231" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F231" s="83"/>
+      <c r="F231" s="69"/>
     </row>
     <row r="232" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F232" s="83"/>
+      <c r="F232" s="69"/>
     </row>
     <row r="233" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F233" s="83"/>
+      <c r="F233" s="69"/>
     </row>
     <row r="234" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F234" s="83"/>
+      <c r="F234" s="69"/>
     </row>
     <row r="235" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F235" s="83"/>
+      <c r="F235" s="69"/>
     </row>
     <row r="236" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F236" s="83"/>
+      <c r="F236" s="69"/>
     </row>
     <row r="237" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F237" s="83"/>
+      <c r="F237" s="69"/>
     </row>
     <row r="238" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F238" s="83"/>
+      <c r="F238" s="69"/>
     </row>
     <row r="239" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F239" s="83"/>
+      <c r="F239" s="69"/>
     </row>
     <row r="240" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F240" s="83"/>
+      <c r="F240" s="69"/>
     </row>
     <row r="241" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F241" s="83"/>
+      <c r="F241" s="69"/>
     </row>
     <row r="242" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F242" s="83"/>
+      <c r="F242" s="69"/>
     </row>
     <row r="243" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F243" s="83"/>
+      <c r="F243" s="69"/>
     </row>
     <row r="244" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F244" s="83"/>
+      <c r="F244" s="69"/>
     </row>
     <row r="245" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F245" s="83"/>
+      <c r="F245" s="69"/>
     </row>
     <row r="246" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F246" s="83"/>
+      <c r="F246" s="69"/>
     </row>
     <row r="247" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F247" s="83"/>
+      <c r="F247" s="69"/>
     </row>
     <row r="248" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F248" s="83"/>
+      <c r="F248" s="69"/>
     </row>
     <row r="249" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F249" s="83"/>
+      <c r="F249" s="69"/>
     </row>
     <row r="250" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F250" s="83"/>
+      <c r="F250" s="69"/>
     </row>
     <row r="251" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F251" s="83"/>
+      <c r="F251" s="69"/>
     </row>
     <row r="252" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F252" s="83"/>
+      <c r="F252" s="69"/>
     </row>
     <row r="253" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F253" s="83"/>
+      <c r="F253" s="69"/>
     </row>
     <row r="254" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F254" s="83"/>
+      <c r="F254" s="69"/>
     </row>
     <row r="255" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F255" s="83"/>
+      <c r="F255" s="69"/>
     </row>
     <row r="256" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F256" s="83"/>
+      <c r="F256" s="69"/>
     </row>
     <row r="257" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F257" s="83"/>
+      <c r="F257" s="69"/>
     </row>
     <row r="258" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F258" s="83"/>
+      <c r="F258" s="69"/>
     </row>
     <row r="259" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F259" s="83"/>
+      <c r="F259" s="69"/>
     </row>
     <row r="260" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F260" s="83"/>
+      <c r="F260" s="69"/>
     </row>
     <row r="261" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F261" s="83"/>
+      <c r="F261" s="69"/>
     </row>
     <row r="262" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F262" s="83"/>
+      <c r="F262" s="69"/>
     </row>
     <row r="263" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F263" s="83"/>
+      <c r="F263" s="69"/>
     </row>
     <row r="264" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F264" s="83"/>
+      <c r="F264" s="69"/>
     </row>
     <row r="265" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F265" s="83"/>
+      <c r="F265" s="69"/>
     </row>
     <row r="266" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F266" s="83"/>
+      <c r="F266" s="69"/>
     </row>
     <row r="267" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F267" s="83"/>
+      <c r="F267" s="69"/>
     </row>
     <row r="268" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F268" s="83"/>
+      <c r="F268" s="69"/>
     </row>
     <row r="269" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F269" s="83"/>
+      <c r="F269" s="69"/>
     </row>
     <row r="270" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F270" s="83"/>
+      <c r="F270" s="69"/>
     </row>
     <row r="271" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F271" s="83"/>
+      <c r="F271" s="69"/>
     </row>
     <row r="272" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F272" s="83"/>
+      <c r="F272" s="69"/>
     </row>
     <row r="273" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F273" s="83"/>
+      <c r="F273" s="69"/>
     </row>
     <row r="274" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F274" s="83"/>
+      <c r="F274" s="69"/>
     </row>
     <row r="275" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F275" s="83"/>
+      <c r="F275" s="69"/>
     </row>
     <row r="276" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F276" s="83"/>
+      <c r="F276" s="69"/>
     </row>
     <row r="277" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F277" s="83"/>
+      <c r="F277" s="69"/>
     </row>
     <row r="278" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F278" s="83"/>
+      <c r="F278" s="69"/>
     </row>
     <row r="279" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F279" s="83"/>
+      <c r="F279" s="69"/>
     </row>
     <row r="280" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F280" s="83"/>
+      <c r="F280" s="69"/>
     </row>
     <row r="281" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F281" s="83"/>
+      <c r="F281" s="69"/>
     </row>
     <row r="282" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F282" s="83"/>
+      <c r="F282" s="69"/>
     </row>
     <row r="283" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F283" s="83"/>
+      <c r="F283" s="69"/>
     </row>
     <row r="284" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F284" s="83"/>
+      <c r="F284" s="69"/>
     </row>
     <row r="285" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F285" s="83"/>
+      <c r="F285" s="69"/>
     </row>
     <row r="286" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F286" s="83"/>
+      <c r="F286" s="69"/>
     </row>
     <row r="287" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F287" s="83"/>
+      <c r="F287" s="69"/>
     </row>
     <row r="288" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F288" s="83"/>
+      <c r="F288" s="69"/>
     </row>
     <row r="289" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F289" s="83"/>
+      <c r="F289" s="69"/>
     </row>
     <row r="290" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F290" s="83"/>
+      <c r="F290" s="69"/>
     </row>
     <row r="291" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F291" s="83"/>
+      <c r="F291" s="69"/>
     </row>
     <row r="292" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F292" s="83"/>
+      <c r="F292" s="69"/>
     </row>
     <row r="293" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F293" s="83"/>
+      <c r="F293" s="69"/>
     </row>
     <row r="294" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F294" s="83"/>
+      <c r="F294" s="69"/>
     </row>
     <row r="295" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F295" s="83"/>
+      <c r="F295" s="69"/>
     </row>
     <row r="296" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F296" s="83"/>
+      <c r="F296" s="69"/>
     </row>
     <row r="297" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F297" s="83"/>
+      <c r="F297" s="69"/>
     </row>
     <row r="298" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F298" s="83"/>
+      <c r="F298" s="69"/>
     </row>
     <row r="299" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F299" s="83"/>
+      <c r="F299" s="69"/>
     </row>
     <row r="300" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F300" s="83"/>
+      <c r="F300" s="69"/>
     </row>
     <row r="301" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F301" s="83"/>
+      <c r="F301" s="69"/>
     </row>
     <row r="302" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F302" s="83"/>
+      <c r="F302" s="69"/>
     </row>
     <row r="303" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F303" s="83"/>
+      <c r="F303" s="69"/>
     </row>
     <row r="304" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F304" s="83"/>
+      <c r="F304" s="69"/>
     </row>
     <row r="305" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F305" s="83"/>
+      <c r="F305" s="69"/>
     </row>
     <row r="306" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F306" s="83"/>
+      <c r="F306" s="69"/>
     </row>
     <row r="307" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F307" s="83"/>
+      <c r="F307" s="69"/>
     </row>
     <row r="308" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F308" s="83"/>
+      <c r="F308" s="69"/>
     </row>
     <row r="309" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F309" s="83"/>
+      <c r="F309" s="69"/>
     </row>
     <row r="310" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F310" s="83"/>
+      <c r="F310" s="69"/>
     </row>
     <row r="311" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F311" s="83"/>
+      <c r="F311" s="69"/>
     </row>
     <row r="312" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F312" s="83"/>
+      <c r="F312" s="69"/>
     </row>
     <row r="313" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F313" s="83"/>
+      <c r="F313" s="69"/>
     </row>
     <row r="314" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F314" s="83"/>
+      <c r="F314" s="69"/>
     </row>
     <row r="315" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F315" s="83"/>
+      <c r="F315" s="69"/>
     </row>
     <row r="316" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F316" s="83"/>
+      <c r="F316" s="69"/>
     </row>
     <row r="317" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F317" s="83"/>
+      <c r="F317" s="69"/>
     </row>
     <row r="318" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F318" s="83"/>
+      <c r="F318" s="69"/>
     </row>
     <row r="319" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F319" s="83"/>
+      <c r="F319" s="69"/>
     </row>
     <row r="320" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F320" s="83"/>
+      <c r="F320" s="69"/>
     </row>
     <row r="321" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F321" s="83"/>
+      <c r="F321" s="69"/>
     </row>
     <row r="322" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F322" s="83"/>
+      <c r="F322" s="69"/>
     </row>
     <row r="323" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F323" s="83"/>
+      <c r="F323" s="69"/>
     </row>
     <row r="324" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F324" s="83"/>
+      <c r="F324" s="69"/>
     </row>
     <row r="325" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F325" s="83"/>
+      <c r="F325" s="69"/>
     </row>
     <row r="326" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F326" s="83"/>
+      <c r="F326" s="69"/>
     </row>
     <row r="327" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F327" s="83"/>
+      <c r="F327" s="69"/>
     </row>
     <row r="328" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F328" s="83"/>
+      <c r="F328" s="69"/>
     </row>
     <row r="329" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F329" s="83"/>
+      <c r="F329" s="69"/>
     </row>
     <row r="330" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F330" s="83"/>
+      <c r="F330" s="69"/>
     </row>
     <row r="331" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F331" s="83"/>
+      <c r="F331" s="69"/>
     </row>
     <row r="332" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F332" s="83"/>
+      <c r="F332" s="69"/>
     </row>
     <row r="333" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F333" s="83"/>
+      <c r="F333" s="69"/>
     </row>
     <row r="334" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F334" s="83"/>
+      <c r="F334" s="69"/>
     </row>
     <row r="335" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F335" s="83"/>
+      <c r="F335" s="69"/>
     </row>
     <row r="336" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F336" s="83"/>
+      <c r="F336" s="69"/>
     </row>
     <row r="337" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F337" s="83"/>
+      <c r="F337" s="69"/>
     </row>
     <row r="338" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F338" s="83"/>
+      <c r="F338" s="69"/>
     </row>
     <row r="339" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F339" s="83"/>
+      <c r="F339" s="69"/>
     </row>
     <row r="340" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F340" s="83"/>
+      <c r="F340" s="69"/>
     </row>
     <row r="341" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F341" s="83"/>
+      <c r="F341" s="69"/>
     </row>
     <row r="342" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F342" s="83"/>
+      <c r="F342" s="69"/>
     </row>
     <row r="343" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F343" s="83"/>
+      <c r="F343" s="69"/>
     </row>
     <row r="344" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F344" s="83"/>
+      <c r="F344" s="69"/>
     </row>
     <row r="345" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F345" s="83"/>
+      <c r="F345" s="69"/>
     </row>
     <row r="346" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F346" s="83"/>
+      <c r="F346" s="69"/>
     </row>
     <row r="347" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F347" s="83"/>
+      <c r="F347" s="69"/>
     </row>
     <row r="348" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F348" s="83"/>
+      <c r="F348" s="69"/>
     </row>
     <row r="349" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F349" s="83"/>
+      <c r="F349" s="69"/>
     </row>
     <row r="350" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F350" s="83"/>
+      <c r="F350" s="69"/>
     </row>
     <row r="351" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F351" s="83"/>
+      <c r="F351" s="69"/>
     </row>
     <row r="352" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F352" s="83"/>
+      <c r="F352" s="69"/>
     </row>
     <row r="353" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F353" s="83"/>
+      <c r="F353" s="69"/>
     </row>
     <row r="354" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F354" s="83"/>
+      <c r="F354" s="69"/>
     </row>
     <row r="355" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F355" s="83"/>
+      <c r="F355" s="69"/>
     </row>
     <row r="356" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F356" s="83"/>
+      <c r="F356" s="69"/>
     </row>
     <row r="357" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F357" s="83"/>
+      <c r="F357" s="69"/>
     </row>
     <row r="358" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F358" s="83"/>
+      <c r="F358" s="69"/>
     </row>
     <row r="359" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F359" s="83"/>
+      <c r="F359" s="69"/>
     </row>
     <row r="360" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F360" s="83"/>
+      <c r="F360" s="69"/>
     </row>
     <row r="361" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F361" s="83"/>
+      <c r="F361" s="69"/>
     </row>
     <row r="362" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F362" s="83"/>
+      <c r="F362" s="69"/>
     </row>
     <row r="363" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F363" s="83"/>
+      <c r="F363" s="69"/>
     </row>
     <row r="364" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F364" s="83"/>
+      <c r="F364" s="69"/>
     </row>
     <row r="365" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F365" s="83"/>
+      <c r="F365" s="69"/>
     </row>
     <row r="366" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F366" s="83"/>
+      <c r="F366" s="69"/>
     </row>
     <row r="367" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F367" s="83"/>
+      <c r="F367" s="69"/>
     </row>
     <row r="368" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F368" s="83"/>
+      <c r="F368" s="69"/>
     </row>
     <row r="369" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F369" s="83"/>
+      <c r="F369" s="69"/>
     </row>
     <row r="370" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F370" s="83"/>
+      <c r="F370" s="69"/>
     </row>
     <row r="371" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F371" s="83"/>
+      <c r="F371" s="69"/>
     </row>
     <row r="372" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F372" s="83"/>
+      <c r="F372" s="69"/>
     </row>
     <row r="373" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F373" s="83"/>
+      <c r="F373" s="69"/>
     </row>
     <row r="374" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F374" s="83"/>
+      <c r="F374" s="69"/>
     </row>
     <row r="375" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F375" s="83"/>
+      <c r="F375" s="69"/>
     </row>
     <row r="376" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F376" s="83"/>
+      <c r="F376" s="69"/>
     </row>
     <row r="377" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F377" s="83"/>
+      <c r="F377" s="69"/>
     </row>
     <row r="378" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F378" s="83"/>
+      <c r="F378" s="69"/>
     </row>
     <row r="379" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F379" s="83"/>
+      <c r="F379" s="69"/>
     </row>
     <row r="380" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F380" s="83"/>
+      <c r="F380" s="69"/>
     </row>
     <row r="381" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F381" s="83"/>
+      <c r="F381" s="69"/>
     </row>
     <row r="382" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F382" s="83"/>
+      <c r="F382" s="69"/>
     </row>
     <row r="383" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F383" s="83"/>
+      <c r="F383" s="69"/>
     </row>
     <row r="384" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F384" s="83"/>
+      <c r="F384" s="69"/>
     </row>
     <row r="385" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F385" s="83"/>
+      <c r="F385" s="69"/>
     </row>
     <row r="386" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F386" s="83"/>
+      <c r="F386" s="69"/>
     </row>
     <row r="387" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F387" s="83"/>
+      <c r="F387" s="69"/>
     </row>
     <row r="388" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F388" s="83"/>
+      <c r="F388" s="69"/>
     </row>
     <row r="389" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F389" s="83"/>
+      <c r="F389" s="69"/>
     </row>
     <row r="390" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F390" s="83"/>
+      <c r="F390" s="69"/>
     </row>
     <row r="391" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F391" s="83"/>
+      <c r="F391" s="69"/>
     </row>
     <row r="392" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F392" s="83"/>
+      <c r="F392" s="69"/>
     </row>
     <row r="393" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F393" s="83"/>
+      <c r="F393" s="69"/>
     </row>
     <row r="394" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F394" s="83"/>
+      <c r="F394" s="69"/>
     </row>
     <row r="395" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F395" s="83"/>
+      <c r="F395" s="69"/>
     </row>
     <row r="396" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F396" s="83"/>
+      <c r="F396" s="69"/>
     </row>
     <row r="397" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F397" s="83"/>
+      <c r="F397" s="69"/>
     </row>
     <row r="398" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F398" s="83"/>
+      <c r="F398" s="69"/>
     </row>
     <row r="399" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F399" s="83"/>
+      <c r="F399" s="69"/>
     </row>
     <row r="400" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F400" s="83"/>
+      <c r="F400" s="69"/>
     </row>
     <row r="401" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F401" s="83"/>
+      <c r="F401" s="69"/>
     </row>
     <row r="402" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F402" s="83"/>
+      <c r="F402" s="69"/>
     </row>
     <row r="403" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F403" s="83"/>
+      <c r="F403" s="69"/>
     </row>
     <row r="404" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F404" s="83"/>
+      <c r="F404" s="69"/>
     </row>
     <row r="405" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F405" s="83"/>
+      <c r="F405" s="69"/>
     </row>
     <row r="406" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F406" s="83"/>
+      <c r="F406" s="69"/>
     </row>
     <row r="407" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F407" s="83"/>
+      <c r="F407" s="69"/>
     </row>
     <row r="408" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F408" s="83"/>
+      <c r="F408" s="69"/>
     </row>
     <row r="409" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F409" s="83"/>
+      <c r="F409" s="69"/>
     </row>
     <row r="410" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F410" s="83"/>
+      <c r="F410" s="69"/>
     </row>
     <row r="411" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F411" s="83"/>
+      <c r="F411" s="69"/>
     </row>
     <row r="412" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F412" s="83"/>
+      <c r="F412" s="69"/>
     </row>
     <row r="413" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F413" s="83"/>
+      <c r="F413" s="69"/>
     </row>
     <row r="414" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F414" s="83"/>
+      <c r="F414" s="69"/>
     </row>
     <row r="415" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F415" s="83"/>
+      <c r="F415" s="69"/>
     </row>
     <row r="416" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F416" s="83"/>
+      <c r="F416" s="69"/>
     </row>
     <row r="417" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F417" s="83"/>
+      <c r="F417" s="69"/>
     </row>
     <row r="418" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F418" s="83"/>
+      <c r="F418" s="69"/>
     </row>
     <row r="419" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F419" s="83"/>
+      <c r="F419" s="69"/>
     </row>
     <row r="420" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F420" s="83"/>
+      <c r="F420" s="69"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/bill-checker-demo.xlsx
+++ b/bill-checker-demo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alinaaleks\Downloads\GitHub\bill-checker\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF9E9F2E-89E2-485A-AD24-351BCD46814A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{553D1359-A41E-40EE-887F-D6392D611513}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CHECK" sheetId="10" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="157">
   <si>
     <t>РЕГИОН</t>
   </si>
@@ -460,15 +460,6 @@
     <t>Нагрев ГВ / общедом</t>
   </si>
   <si>
-    <t>Δ ОБЪЕМ</t>
-  </si>
-  <si>
-    <t>Δ ТАРИФ</t>
-  </si>
-  <si>
-    <t>Δ НАЧИСЛЕНО</t>
-  </si>
-  <si>
     <t>Статус</t>
   </si>
   <si>
@@ -484,9 +475,6 @@
     <t>Проживающие, чел</t>
   </si>
   <si>
-    <t>ОТКЛОНЕНИЕ</t>
-  </si>
-  <si>
     <t>Ростовская область</t>
   </si>
   <si>
@@ -517,19 +505,16 @@
     <t>Правительство Ростовской области</t>
   </si>
   <si>
-    <t>ГВ снабжение / общедом</t>
-  </si>
-  <si>
-    <t>Электроснабжение / общедом</t>
-  </si>
-  <si>
-    <t>ХВ снабжение  / общедом</t>
-  </si>
-  <si>
     <t>Водоотведение  / общедом</t>
   </si>
   <si>
     <t>УК (соц.норма) - если не по счетчику</t>
+  </si>
+  <si>
+    <t>Δ ОТКЛОНЕНИЕ</t>
+  </si>
+  <si>
+    <t>ХВС  / общедом</t>
   </si>
 </sst>
 </file>
@@ -654,7 +639,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="16">
+  <borders count="21">
     <border>
       <left/>
       <right/>
@@ -745,11 +730,11 @@
     </border>
     <border>
       <left style="medium">
-        <color rgb="FF000000"/>
+        <color indexed="64"/>
       </left>
       <right/>
       <top style="medium">
-        <color rgb="FF000000"/>
+        <color indexed="64"/>
       </top>
       <bottom style="medium">
         <color theme="0"/>
@@ -760,7 +745,7 @@
       <left/>
       <right/>
       <top style="medium">
-        <color rgb="FF000000"/>
+        <color indexed="64"/>
       </top>
       <bottom style="medium">
         <color theme="0"/>
@@ -770,10 +755,10 @@
     <border>
       <left/>
       <right style="medium">
-        <color rgb="FF000000"/>
+        <color indexed="64"/>
       </right>
       <top style="medium">
-        <color rgb="FF000000"/>
+        <color indexed="64"/>
       </top>
       <bottom style="medium">
         <color theme="0"/>
@@ -782,7 +767,7 @@
     </border>
     <border>
       <left style="medium">
-        <color rgb="FF000000"/>
+        <color indexed="64"/>
       </left>
       <right style="medium">
         <color theme="0"/>
@@ -800,7 +785,7 @@
         <color theme="0"/>
       </left>
       <right style="medium">
-        <color rgb="FF000000"/>
+        <color indexed="64"/>
       </right>
       <top style="medium">
         <color theme="0"/>
@@ -812,7 +797,7 @@
     </border>
     <border>
       <left style="medium">
-        <color rgb="FF000000"/>
+        <color indexed="64"/>
       </left>
       <right style="medium">
         <color theme="0"/>
@@ -820,7 +805,9 @@
       <top style="medium">
         <color theme="0"/>
       </top>
-      <bottom/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -833,7 +820,9 @@
       <top style="medium">
         <color theme="0"/>
       </top>
-      <bottom/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -841,12 +830,77 @@
         <color theme="0"/>
       </left>
       <right style="medium">
-        <color rgb="FF000000"/>
+        <color indexed="64"/>
       </right>
       <top style="medium">
         <color theme="0"/>
       </top>
-      <bottom/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color theme="0"/>
+      </top>
+      <bottom style="medium">
+        <color theme="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color theme="0"/>
+      </top>
+      <bottom style="medium">
+        <color theme="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color theme="0"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color theme="0"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color theme="0"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -854,7 +908,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="112">
+  <cellXfs count="124">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -959,9 +1013,6 @@
     <xf numFmtId="2" fontId="1" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="0" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="4" fontId="0" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1062,22 +1113,13 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="8" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -1089,6 +1131,33 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1097,6 +1166,33 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="5" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="5" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="15" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1107,6 +1203,42 @@
     <xf numFmtId="0" fontId="1" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="8" borderId="16" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="9" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="0" fillId="8" borderId="16" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="0" fillId="8" borderId="16" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="8" borderId="16" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="8" borderId="16" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="8" borderId="18" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="8" borderId="19" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="9" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1116,75 +1248,465 @@
     <xf numFmtId="0" fontId="1" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="0" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="0" fillId="8" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="0" fillId="6" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="8" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="8" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="0" fillId="8" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="0" fillId="7" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="0" fillId="7" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="5" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="5" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="1" fillId="9" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="0" fillId="6" borderId="15" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="3" borderId="15" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="172" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="57">
+  <dxfs count="105">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="9" tint="-0.499984740745262"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="9" tint="-0.499984740745262"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="9" tint="-0.499984740745262"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="9" tint="-0.499984740745262"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="9" tint="-0.499984740745262"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="9" tint="-0.499984740745262"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="9" tint="-0.499984740745262"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="9" tint="-0.499984740745262"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="9" tint="-0.499984740745262"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="9" tint="-0.499984740745262"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="9" tint="-0.499984740745262"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="9" tint="-0.499984740745262"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -5010,10 +5532,10 @@
     <dataField name="Отклонение (%)" fld="21" baseField="13" baseItem="1" numFmtId="10"/>
   </dataFields>
   <formats count="6">
-    <format dxfId="27">
+    <format dxfId="75">
       <pivotArea field="17" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="26">
+    <format dxfId="74">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="4">
@@ -5025,10 +5547,10 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="25">
+    <format dxfId="73">
       <pivotArea field="17" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="24">
+    <format dxfId="72">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="4">
@@ -5040,10 +5562,10 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="23">
+    <format dxfId="71">
       <pivotArea field="17" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="22">
+    <format dxfId="70">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="4">
@@ -5141,7 +5663,7 @@
     <dataField name="Факт (начисления)" fld="4" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="18">
-    <format dxfId="45">
+    <format dxfId="93">
       <pivotArea outline="0" fieldPosition="0">
         <references count="2">
           <reference field="4294967294" count="1" selected="0">
@@ -5153,10 +5675,10 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="44">
+    <format dxfId="92">
       <pivotArea field="17" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
     </format>
-    <format dxfId="43">
+    <format dxfId="91">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="17" count="1">
@@ -5165,7 +5687,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="42">
+    <format dxfId="90">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="4294967294" count="1">
@@ -5177,7 +5699,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="41">
+    <format dxfId="89">
       <pivotArea outline="0" fieldPosition="0">
         <references count="2">
           <reference field="4294967294" count="1" selected="0">
@@ -5189,13 +5711,13 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="40">
+    <format dxfId="88">
       <pivotArea field="-2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="1"/>
     </format>
-    <format dxfId="39">
+    <format dxfId="87">
       <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="38">
+    <format dxfId="86">
       <pivotArea outline="0" fieldPosition="0">
         <references count="2">
           <reference field="4294967294" count="2" selected="0">
@@ -5208,7 +5730,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="37">
+    <format dxfId="85">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="4294967294" count="1" selected="0">
@@ -5220,31 +5742,31 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="36">
+    <format dxfId="84">
       <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="35">
+    <format dxfId="83">
       <pivotArea field="-2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="1"/>
     </format>
-    <format dxfId="34">
+    <format dxfId="82">
       <pivotArea field="17" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
     </format>
-    <format dxfId="33">
+    <format dxfId="81">
       <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="32">
+    <format dxfId="80">
       <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="31">
+    <format dxfId="79">
       <pivotArea field="-2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="1"/>
     </format>
-    <format dxfId="30">
+    <format dxfId="78">
       <pivotArea field="17" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
     </format>
-    <format dxfId="29">
+    <format dxfId="77">
       <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="28">
+    <format dxfId="76">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="17" count="1">
@@ -5430,10 +5952,10 @@
     <dataField name="Отклонение (%)" fld="21" baseField="17" baseItem="0" numFmtId="10"/>
   </dataFields>
   <formats count="11">
-    <format dxfId="56">
+    <format dxfId="104">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="55">
+    <format dxfId="103">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1">
@@ -5442,7 +5964,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="54">
+    <format dxfId="102">
       <pivotArea outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
@@ -5451,7 +5973,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="53">
+    <format dxfId="101">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1">
@@ -5460,7 +5982,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="52">
+    <format dxfId="100">
       <pivotArea outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1">
@@ -5469,10 +5991,10 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="51">
+    <format dxfId="99">
       <pivotArea field="19" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="1"/>
     </format>
-    <format dxfId="50">
+    <format dxfId="98">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="4">
@@ -5484,10 +6006,10 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="49">
+    <format dxfId="97">
       <pivotArea field="19" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="1"/>
     </format>
-    <format dxfId="48">
+    <format dxfId="96">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="4">
@@ -5499,10 +6021,10 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="47">
+    <format dxfId="95">
       <pivotArea field="19" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="1"/>
     </format>
-    <format dxfId="46">
+    <format dxfId="94">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="4">
@@ -5528,39 +6050,39 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{038A7D06-120E-408B-AEDA-813F2FAAD501}" name="Table2" displayName="Table2" ref="A1:T2" insertRow="1" totalsRowShown="0" headerRowDxfId="21" dataDxfId="20">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{038A7D06-120E-408B-AEDA-813F2FAAD501}" name="Table2" displayName="Table2" ref="A1:T2" insertRow="1" totalsRowShown="0" headerRowDxfId="69" dataDxfId="68">
   <autoFilter ref="A1:T2" xr:uid="{038A7D06-120E-408B-AEDA-813F2FAAD501}"/>
   <tableColumns count="20">
-    <tableColumn id="1" xr3:uid="{A040E5F1-B940-434F-8642-3D7965B0C906}" name="услуга" dataDxfId="19"/>
-    <tableColumn id="2" xr3:uid="{F1E9BBF3-FF65-4BCE-A746-A764AA053336}" name="ед_изм" dataDxfId="18"/>
-    <tableColumn id="3" xr3:uid="{95BCA9F7-93A8-474A-B486-B60193571EE3}" name="объем_квит" dataDxfId="17"/>
-    <tableColumn id="4" xr3:uid="{68D5AF23-9C08-4C25-A70E-D5B9C5258B85}" name="тариф_квит" dataDxfId="16"/>
-    <tableColumn id="5" xr3:uid="{1AE3F8D2-8628-41AA-B125-5D9318037FFC}" name="начислено_квит" dataDxfId="15"/>
-    <tableColumn id="6" xr3:uid="{2352EB12-E5C2-4AD6-8516-1C5A276F0128}" name="объем_откл" dataDxfId="14"/>
-    <tableColumn id="7" xr3:uid="{7BC866F5-0902-4D0A-9F28-F44EC965920C}" name="тариф_откл" dataDxfId="13"/>
-    <tableColumn id="8" xr3:uid="{DCE0FDDD-E687-4FB1-A515-511A0D4227D7}" name="начислено_откл" dataDxfId="12"/>
-    <tableColumn id="9" xr3:uid="{ABA713D2-6A48-414E-8866-3C6F39D5A490}" name="объем_расчет" dataDxfId="11"/>
-    <tableColumn id="10" xr3:uid="{EB157C1F-294F-4DFA-B0C3-E5402FF488C6}" name="тариф_расчет" dataDxfId="10"/>
-    <tableColumn id="11" xr3:uid="{16FD8211-F0B8-47DC-B4C9-EE5186864112}" name="насчислено_расчет" dataDxfId="9"/>
-    <tableColumn id="12" xr3:uid="{E9403770-B09D-40E2-BEFE-72B760354FEB}" name="норматив" dataDxfId="8"/>
-    <tableColumn id="13" xr3:uid="{5E21BED0-908D-4682-8E01-9D5911F61AB9}" name="период" dataDxfId="7"/>
-    <tableColumn id="14" xr3:uid="{6C555CCE-FDE0-4600-A16A-E7977D4C1331}" name="поставщик" dataDxfId="6"/>
-    <tableColumn id="18" xr3:uid="{70B0664C-2BB9-44F5-A956-B8CFF607EBD0}" name="начислено_откл%" dataDxfId="5">
+    <tableColumn id="1" xr3:uid="{A040E5F1-B940-434F-8642-3D7965B0C906}" name="услуга" dataDxfId="67"/>
+    <tableColumn id="2" xr3:uid="{F1E9BBF3-FF65-4BCE-A746-A764AA053336}" name="ед_изм" dataDxfId="66"/>
+    <tableColumn id="3" xr3:uid="{95BCA9F7-93A8-474A-B486-B60193571EE3}" name="объем_квит" dataDxfId="65"/>
+    <tableColumn id="4" xr3:uid="{68D5AF23-9C08-4C25-A70E-D5B9C5258B85}" name="тариф_квит" dataDxfId="64"/>
+    <tableColumn id="5" xr3:uid="{1AE3F8D2-8628-41AA-B125-5D9318037FFC}" name="начислено_квит" dataDxfId="63"/>
+    <tableColumn id="6" xr3:uid="{2352EB12-E5C2-4AD6-8516-1C5A276F0128}" name="объем_откл" dataDxfId="62"/>
+    <tableColumn id="7" xr3:uid="{7BC866F5-0902-4D0A-9F28-F44EC965920C}" name="тариф_откл" dataDxfId="61"/>
+    <tableColumn id="8" xr3:uid="{DCE0FDDD-E687-4FB1-A515-511A0D4227D7}" name="начислено_откл" dataDxfId="60"/>
+    <tableColumn id="9" xr3:uid="{ABA713D2-6A48-414E-8866-3C6F39D5A490}" name="объем_расчет" dataDxfId="59"/>
+    <tableColumn id="10" xr3:uid="{EB157C1F-294F-4DFA-B0C3-E5402FF488C6}" name="тариф_расчет" dataDxfId="58"/>
+    <tableColumn id="11" xr3:uid="{16FD8211-F0B8-47DC-B4C9-EE5186864112}" name="насчислено_расчет" dataDxfId="57"/>
+    <tableColumn id="12" xr3:uid="{E9403770-B09D-40E2-BEFE-72B760354FEB}" name="норматив" dataDxfId="56"/>
+    <tableColumn id="13" xr3:uid="{5E21BED0-908D-4682-8E01-9D5911F61AB9}" name="период" dataDxfId="55"/>
+    <tableColumn id="14" xr3:uid="{6C555CCE-FDE0-4600-A16A-E7977D4C1331}" name="поставщик" dataDxfId="54"/>
+    <tableColumn id="18" xr3:uid="{70B0664C-2BB9-44F5-A956-B8CFF607EBD0}" name="начислено_откл%" dataDxfId="53">
       <calculatedColumnFormula>IF(Table2[[#This Row],[начислено_откл]]=0,0,(Table2[[#This Row],[начислено_квит]]-Table2[[#This Row],[насчислено_расчет]])/Table2[[#This Row],[насчислено_расчет]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="19" xr3:uid="{725C5E98-3B75-474D-9C6F-E06942598B1D}" name="положит_откл" dataDxfId="4">
+    <tableColumn id="19" xr3:uid="{725C5E98-3B75-474D-9C6F-E06942598B1D}" name="положит_откл" dataDxfId="52">
       <calculatedColumnFormula>IF(Table2[[#This Row],[начислено_откл]]&gt;0,Table2[[#This Row],[начислено_откл]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="20" xr3:uid="{307D926C-82F4-46F4-AC93-88CE44B6AD40}" name="отриц_откл" dataDxfId="3">
+    <tableColumn id="20" xr3:uid="{307D926C-82F4-46F4-AC93-88CE44B6AD40}" name="отриц_откл" dataDxfId="51">
       <calculatedColumnFormula>IF(Table2[[#This Row],[начислено_откл]]&lt;0,Table2[[#This Row],[начислено_откл]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{5780D1EA-A409-449C-BCA3-DC86372888EC}" name="год" dataDxfId="2">
+    <tableColumn id="15" xr3:uid="{5780D1EA-A409-449C-BCA3-DC86372888EC}" name="год" dataDxfId="50">
       <calculatedColumnFormula>YEAR(M2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{3889E082-3447-4F9E-A275-7FE45FCFD6FB}" name="месяц_№" dataDxfId="1">
+    <tableColumn id="16" xr3:uid="{3889E082-3447-4F9E-A275-7FE45FCFD6FB}" name="месяц_№" dataDxfId="49">
       <calculatedColumnFormula>MONTH(M2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{E6E9DC5E-485F-4A72-A2BF-41BAB4F90D1B}" name="месяц" dataDxfId="0">
+    <tableColumn id="17" xr3:uid="{E6E9DC5E-485F-4A72-A2BF-41BAB4F90D1B}" name="месяц" dataDxfId="48">
       <calculatedColumnFormula>CHOOSE(S2,"январь","февраль","март","апрель","май","июнь","июль","август","сентябрь","октябрь","ноябрь","декабрь")</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5893,7 +6415,10 @@
     <col min="3" max="3" width="9" style="3" customWidth="1"/>
     <col min="4" max="4" width="11" style="3" customWidth="1"/>
     <col min="5" max="5" width="11.26953125" style="3" bestFit="1" customWidth="1"/>
-    <col min="6" max="11" width="11.26953125" style="3" customWidth="1"/>
+    <col min="6" max="7" width="11.26953125" style="3" customWidth="1"/>
+    <col min="8" max="8" width="11.36328125" style="3" customWidth="1"/>
+    <col min="9" max="10" width="11.26953125" style="3" customWidth="1"/>
+    <col min="11" max="11" width="11.36328125" style="3" customWidth="1"/>
     <col min="12" max="12" width="14.90625" style="3" customWidth="1"/>
     <col min="13" max="13" width="11.26953125" style="3" hidden="1" customWidth="1"/>
     <col min="14" max="14" width="16.7265625" style="3" customWidth="1"/>
@@ -5905,7 +6430,7 @@
       <c r="A1" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="B1" s="69">
+      <c r="B1" s="68">
         <f>EDATE(B3, -1)</f>
         <v>46023</v>
       </c>
@@ -5919,16 +6444,16 @@
       <c r="A3" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B3" s="69">
+      <c r="B3" s="68">
         <v>46054</v>
       </c>
       <c r="F3"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A4" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="B4" s="81">
+        <v>141</v>
+      </c>
+      <c r="B4" s="77">
         <f>info!B7</f>
         <v>55.2</v>
       </c>
@@ -5936,9 +6461,9 @@
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A5" s="5" t="s">
-        <v>145</v>
-      </c>
-      <c r="B5" s="79">
+        <v>142</v>
+      </c>
+      <c r="B5" s="75">
         <f>info!B6</f>
         <v>2</v>
       </c>
@@ -5949,60 +6474,60 @@
     <row r="7" spans="1:14" s="5" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A7" s="3"/>
       <c r="B7" s="3"/>
-      <c r="C7" s="82" t="s">
+      <c r="C7" s="87" t="s">
         <v>36</v>
       </c>
-      <c r="D7" s="83"/>
-      <c r="E7" s="84"/>
-      <c r="F7" s="85" t="s">
+      <c r="D7" s="88"/>
+      <c r="E7" s="89"/>
+      <c r="F7" s="99" t="s">
         <v>37</v>
       </c>
-      <c r="G7" s="86"/>
-      <c r="H7" s="87"/>
-      <c r="I7" s="88" t="s">
-        <v>146</v>
-      </c>
-      <c r="J7" s="89"/>
-      <c r="K7" s="90"/>
+      <c r="G7" s="100"/>
+      <c r="H7" s="101"/>
+      <c r="I7" s="114" t="s">
+        <v>155</v>
+      </c>
+      <c r="J7" s="115"/>
+      <c r="K7" s="116"/>
       <c r="M7" s="7"/>
       <c r="N7" s="7"/>
     </row>
-    <row r="8" spans="1:14" s="72" customFormat="1" ht="44" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="70" t="s">
+    <row r="8" spans="1:14" s="71" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="69" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="71" t="s">
+      <c r="B8" s="70" t="s">
         <v>39</v>
       </c>
-      <c r="C8" s="73" t="s">
+      <c r="C8" s="90" t="s">
         <v>40</v>
       </c>
-      <c r="D8" s="74" t="s">
+      <c r="D8" s="72" t="s">
         <v>41</v>
       </c>
-      <c r="E8" s="75" t="s">
+      <c r="E8" s="91" t="s">
         <v>42</v>
       </c>
-      <c r="F8" s="77" t="s">
+      <c r="F8" s="102" t="s">
         <v>40</v>
       </c>
-      <c r="G8" s="77" t="s">
+      <c r="G8" s="74" t="s">
         <v>41</v>
       </c>
-      <c r="H8" s="77" t="s">
+      <c r="H8" s="103" t="s">
         <v>42</v>
       </c>
-      <c r="I8" s="78" t="s">
+      <c r="I8" s="117" t="s">
+        <v>40</v>
+      </c>
+      <c r="J8" s="69" t="s">
+        <v>41</v>
+      </c>
+      <c r="K8" s="118" t="s">
+        <v>42</v>
+      </c>
+      <c r="L8" s="113" t="s">
         <v>138</v>
-      </c>
-      <c r="J8" s="70" t="s">
-        <v>139</v>
-      </c>
-      <c r="K8" s="70" t="s">
-        <v>140</v>
-      </c>
-      <c r="L8" s="8" t="s">
-        <v>141</v>
       </c>
       <c r="M8" s="8" t="s">
         <v>43</v>
@@ -6018,44 +6543,44 @@
       <c r="B9" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="C9" s="102">
-        <v>201</v>
-      </c>
-      <c r="D9" s="103">
+      <c r="C9" s="92">
+        <v>204</v>
+      </c>
+      <c r="D9" s="83">
         <v>4.2</v>
       </c>
-      <c r="E9" s="109">
-        <v>844.2</v>
-      </c>
-      <c r="F9" s="97">
+      <c r="E9" s="93">
+        <v>856.80000000000007</v>
+      </c>
+      <c r="F9" s="104">
         <f>IFERROR(INDEX(usage!B:B, MATCH(CHECK!$B$3, usage!A:A, 0)) - INDEX(usage!B:B, MATCH(CHECK!$B$1, usage!A:A, 0)),"")</f>
         <v>201</v>
       </c>
-      <c r="G9" s="76">
+      <c r="G9" s="73">
         <f>IF(F9&lt;M9, INDEX(tariffs!2:2, MATCH(CHECK!$B$3,tariffs!$1:$1, 0)), INDEX(tariffs!3:3, MATCH(CHECK!$B$3,tariffs!$1:$1, 0)))</f>
         <v>4.2</v>
       </c>
-      <c r="H9" s="108">
+      <c r="H9" s="105">
         <f>IFERROR(F9*G9,"")</f>
         <v>844.2</v>
       </c>
-      <c r="I9" s="36">
-        <f t="shared" ref="I9:J11" si="0">IFERROR(F9-C9, "")</f>
+      <c r="I9" s="119">
+        <f>IF(C9="", "", C9-F9)</f>
+        <v>3</v>
+      </c>
+      <c r="J9" s="36">
+        <f t="shared" ref="J9:K24" si="0">IF(D9="", "", D9-G9)</f>
         <v>0</v>
       </c>
-      <c r="J9" s="37">
+      <c r="K9" s="120">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K9" s="38">
-        <f>IFERROR(E9-H9,"")</f>
-        <v>0</v>
+        <v>12.600000000000023</v>
       </c>
       <c r="L9" s="3" t="str">
-        <f>IF(ABS(K9)&lt;=1,"✔ ОК",IF(K9&gt;1,"❗ Превышение","❗ Недосчет"))</f>
-        <v>✔ ОК</v>
-      </c>
-      <c r="M9" s="39">
+        <f>IF(K9="","",IF(ABS(K9)&lt;=1,"✔ ОК",IF(K9&gt;1,"❗ Превышение","❗ Недосчет")))</f>
+        <v>❗ Превышение</v>
+      </c>
+      <c r="M9" s="38">
         <f>IFERROR(INDEX(tariffs!16:16, MATCH(CHECK!$B$3, tariffs!$1:$1, 0)),"")</f>
         <v>761</v>
       </c>
@@ -6071,44 +6596,44 @@
       <c r="B10" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="C10" s="93">
-        <v>4.5979999999999999</v>
-      </c>
-      <c r="D10" s="103">
+      <c r="C10" s="94">
+        <v>4.597999999999999</v>
+      </c>
+      <c r="D10" s="83">
         <v>62.98</v>
       </c>
-      <c r="E10" s="109">
+      <c r="E10" s="93">
         <v>289.58203999999995</v>
       </c>
-      <c r="F10" s="95">
+      <c r="F10" s="106">
         <f>IFERROR(INDEX(usage!C:C, MATCH(CHECK!$B$3, usage!A:A, 0)) - INDEX(usage!C:C, MATCH(CHECK!$B$1, usage!A:A, 0)),"")</f>
         <v>4.597999999999999</v>
       </c>
-      <c r="G10" s="76">
+      <c r="G10" s="73">
         <f>INDEX(tariffs!4:4, MATCH(CHECK!$B$3,tariffs!$1:$1, 0))</f>
         <v>62.98</v>
       </c>
-      <c r="H10" s="108">
+      <c r="H10" s="105">
         <f t="shared" ref="H10:H24" si="1">IFERROR(F10*G10,"")</f>
         <v>289.58203999999995</v>
       </c>
-      <c r="I10" s="36">
-        <f t="shared" si="0"/>
-        <v>-8.8817841970012523E-16</v>
-      </c>
-      <c r="J10" s="37">
+      <c r="I10" s="119">
+        <f t="shared" ref="I10:I24" si="2">IF(C10="", "", C10-F10)</f>
+        <v>0</v>
+      </c>
+      <c r="J10" s="36">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K10" s="38">
-        <f>IFERROR(E10-H10,"")</f>
+      <c r="K10" s="120">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="L10" s="3" t="str">
-        <f t="shared" ref="L10:L24" si="2">IF(ABS(K10)&lt;=1,"✔ ОК",IF(K10&gt;1,"❗ Превышение","❗ Недосчет"))</f>
+        <f t="shared" ref="L10:L24" si="3">IF(K10="","",IF(ABS(K10)&lt;=1,"✔ ОК",IF(K10&gt;1,"❗ Превышение","❗ Недосчет")))</f>
         <v>✔ ОК</v>
       </c>
-      <c r="M10" s="39"/>
+      <c r="M10" s="38"/>
       <c r="N10" s="10" t="str">
         <f>VLOOKUP(A10,info!A14:B30, 2,FALSE)</f>
         <v>Поставщик воды</v>
@@ -6121,41 +6646,41 @@
       <c r="B11" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="C11" s="93">
-        <v>4.5979999999999999</v>
-      </c>
-      <c r="D11" s="103">
+      <c r="C11" s="94">
+        <v>4.597999999999999</v>
+      </c>
+      <c r="D11" s="83">
         <v>44.12</v>
       </c>
-      <c r="E11" s="109">
-        <v>202.86375999999998</v>
-      </c>
-      <c r="F11" s="95">
+      <c r="E11" s="93">
+        <v>202.86375999999996</v>
+      </c>
+      <c r="F11" s="106">
         <f>F10</f>
         <v>4.597999999999999</v>
       </c>
-      <c r="G11" s="76">
+      <c r="G11" s="73">
         <f>INDEX(tariffs!5:5, MATCH(CHECK!$B$3,tariffs!$1:$1, 0))</f>
         <v>44.12</v>
       </c>
-      <c r="H11" s="108">
+      <c r="H11" s="105">
         <f t="shared" si="1"/>
         <v>202.86375999999996</v>
       </c>
-      <c r="I11" s="36">
-        <f t="shared" si="0"/>
-        <v>-8.8817841970012523E-16</v>
-      </c>
-      <c r="J11" s="37">
+      <c r="I11" s="119">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J11" s="36">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K11" s="38">
-        <f>IFERROR(E11-H11,"")</f>
-        <v>2.8421709430404007E-14</v>
+      <c r="K11" s="120">
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="L11" s="3" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>✔ ОК</v>
       </c>
       <c r="N11" s="10" t="str">
@@ -6170,32 +6695,41 @@
       <c r="B12" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="C12" s="93">
+      <c r="C12" s="94">
         <v>3.202</v>
       </c>
-      <c r="D12" s="103">
+      <c r="D12" s="83">
         <v>62.98</v>
       </c>
-      <c r="E12" s="109">
+      <c r="E12" s="93">
         <v>201.66195999999999</v>
       </c>
-      <c r="F12" s="95">
+      <c r="F12" s="106">
         <f>IFERROR(INDEX(usage!D:D, MATCH(CHECK!$B$3, usage!A:A, 0)) - INDEX(usage!D:D, MATCH(CHECK!$B$1, usage!A:A, 0)),"")</f>
         <v>3.202</v>
       </c>
-      <c r="G12" s="76">
+      <c r="G12" s="73">
         <f>INDEX(tariffs!4:4, MATCH(CHECK!$B$3,tariffs!$1:$1, 0))</f>
         <v>62.98</v>
       </c>
-      <c r="H12" s="108">
+      <c r="H12" s="105">
         <f t="shared" si="1"/>
         <v>201.66195999999999</v>
       </c>
-      <c r="I12" s="36"/>
-      <c r="J12" s="37"/>
-      <c r="K12" s="38"/>
+      <c r="I12" s="119">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J12" s="36">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K12" s="120">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="L12" s="3" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>✔ ОК</v>
       </c>
       <c r="N12" s="10" t="str">
@@ -6210,44 +6744,44 @@
       <c r="B13" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="C13" s="93">
+      <c r="C13" s="94">
         <v>3.202</v>
       </c>
-      <c r="D13" s="103">
+      <c r="D13" s="83">
         <v>44.12</v>
       </c>
-      <c r="E13" s="109">
+      <c r="E13" s="93">
         <v>141.27223999999998</v>
       </c>
-      <c r="F13" s="95">
+      <c r="F13" s="106">
         <f>F12</f>
         <v>3.202</v>
       </c>
-      <c r="G13" s="76">
+      <c r="G13" s="73">
         <f>INDEX(tariffs!5:5, MATCH(CHECK!$B$3,tariffs!$1:$1, 0))</f>
         <v>44.12</v>
       </c>
-      <c r="H13" s="108">
+      <c r="H13" s="105">
         <f t="shared" si="1"/>
         <v>141.27223999999998</v>
       </c>
-      <c r="I13" s="36">
-        <f t="shared" ref="I13:J15" si="3">IFERROR(F13-C13, "")</f>
+      <c r="I13" s="119">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J13" s="37">
+      <c r="J13" s="36">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K13" s="120">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L13" s="3" t="str">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="K13" s="38">
-        <f>IFERROR(E13-H13,"")</f>
-        <v>0</v>
-      </c>
-      <c r="L13" s="3" t="str">
-        <f t="shared" si="2"/>
         <v>✔ ОК</v>
       </c>
-      <c r="M13" s="39"/>
+      <c r="M13" s="38"/>
       <c r="N13" s="10" t="str">
         <f>VLOOKUP(A13,info!A17:B33, 2,FALSE)</f>
         <v>Поставщик воды</v>
@@ -6260,44 +6794,44 @@
       <c r="B14" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="C14" s="94">
-        <v>6.5110000000000001</v>
-      </c>
-      <c r="D14" s="104">
+      <c r="C14" s="95">
+        <v>6.952</v>
+      </c>
+      <c r="D14" s="84">
         <v>227.18</v>
       </c>
-      <c r="E14" s="109">
-        <v>1479.1689800000001</v>
-      </c>
-      <c r="F14" s="95">
+      <c r="E14" s="93">
+        <v>1579.35536</v>
+      </c>
+      <c r="F14" s="106">
         <f>IFERROR(C14,"")</f>
-        <v>6.5110000000000001</v>
-      </c>
-      <c r="G14" s="76">
+        <v>6.952</v>
+      </c>
+      <c r="G14" s="73">
         <f>INDEX(tariffs!6:6, MATCH(CHECK!$B$3,tariffs!$1:$1, 0))</f>
         <v>227.18</v>
       </c>
-      <c r="H14" s="108">
+      <c r="H14" s="105">
         <f t="shared" si="1"/>
-        <v>1479.1689800000001</v>
-      </c>
-      <c r="I14" s="36">
+        <v>1579.35536</v>
+      </c>
+      <c r="I14" s="119">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J14" s="36">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K14" s="120">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L14" s="3" t="str">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="J14" s="37">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="K14" s="38">
-        <f>IFERROR(E14-H14,"")</f>
-        <v>0</v>
-      </c>
-      <c r="L14" s="3" t="str">
-        <f t="shared" si="2"/>
         <v>✔ ОК</v>
       </c>
-      <c r="M14" s="42">
+      <c r="M14" s="41">
         <f>IFERROR(INDEX(tariffs!18:18, MATCH(CHECK!$B$3, tariffs!$1:$1, 0)),"")</f>
         <v>16.2</v>
       </c>
@@ -6313,44 +6847,44 @@
       <c r="B15" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="C15" s="93">
-        <v>3.9864999999999999</v>
-      </c>
-      <c r="D15" s="104">
+      <c r="C15" s="94">
+        <v>1.7152000000000001</v>
+      </c>
+      <c r="D15" s="84">
         <v>3549.74</v>
       </c>
-      <c r="E15" s="109">
-        <v>14151.038509999998</v>
-      </c>
-      <c r="F15" s="98">
+      <c r="E15" s="93">
+        <v>6535.25</v>
+      </c>
+      <c r="F15" s="107">
         <f>IFERROR(C15,"")</f>
-        <v>3.9864999999999999</v>
-      </c>
-      <c r="G15" s="76">
+        <v>1.7152000000000001</v>
+      </c>
+      <c r="G15" s="73">
         <f>INDEX(tariffs!7:7, MATCH(CHECK!$B$3,tariffs!$1:$1, 0))</f>
         <v>3549.74</v>
       </c>
-      <c r="H15" s="108">
+      <c r="H15" s="105">
         <f t="shared" si="1"/>
-        <v>14151.038509999998</v>
-      </c>
-      <c r="I15" s="36">
+        <v>6088.514048</v>
+      </c>
+      <c r="I15" s="119">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J15" s="36">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K15" s="120">
+        <f t="shared" si="0"/>
+        <v>446.735952</v>
+      </c>
+      <c r="L15" s="3" t="str">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="J15" s="37">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="K15" s="38">
-        <f>IFERROR(E15-H15,"")</f>
-        <v>0</v>
-      </c>
-      <c r="L15" s="3" t="str">
-        <f t="shared" si="2"/>
-        <v>✔ ОК</v>
-      </c>
-      <c r="M15" s="39"/>
+        <v>❗ Превышение</v>
+      </c>
+      <c r="M15" s="38"/>
       <c r="N15" s="10" t="str">
         <f>VLOOKUP(A15,info!A19:B35, 2,FALSE)</f>
         <v>Управляющая</v>
@@ -6363,35 +6897,44 @@
       <c r="B16" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="C16" s="93">
-        <v>0.89500000000000002</v>
-      </c>
-      <c r="D16" s="103">
+      <c r="C16" s="94">
+        <v>3</v>
+      </c>
+      <c r="D16" s="83">
         <v>227.18</v>
       </c>
-      <c r="E16" s="109">
-        <v>203.3261</v>
-      </c>
-      <c r="F16" s="95">
+      <c r="E16" s="93">
+        <v>681.54</v>
+      </c>
+      <c r="F16" s="106">
         <f t="shared" ref="F16:F20" si="4">IFERROR(C16,"")</f>
-        <v>0.89500000000000002</v>
-      </c>
-      <c r="G16" s="76">
+        <v>3</v>
+      </c>
+      <c r="G16" s="73">
         <f>INDEX(tariffs!6:6, MATCH(CHECK!$B$3,tariffs!$1:$1, 0))</f>
         <v>227.18</v>
       </c>
-      <c r="H16" s="108">
+      <c r="H16" s="105">
         <f t="shared" si="1"/>
-        <v>203.3261</v>
-      </c>
-      <c r="I16" s="36"/>
-      <c r="J16" s="37"/>
-      <c r="K16" s="38"/>
+        <v>681.54</v>
+      </c>
+      <c r="I16" s="119">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J16" s="36">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K16" s="120">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="L16" s="3" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>✔ ОК</v>
       </c>
-      <c r="M16" s="39"/>
+      <c r="M16" s="38"/>
       <c r="N16" s="10" t="str">
         <f>VLOOKUP(A16,info!A20:B36, 2,FALSE)</f>
         <v>Управляющая</v>
@@ -6404,44 +6947,44 @@
       <c r="B17" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="C17" s="93">
-        <v>0.89500000000000002</v>
-      </c>
-      <c r="D17" s="103">
+      <c r="C17" s="94">
+        <v>0.68</v>
+      </c>
+      <c r="D17" s="83">
         <v>62.98</v>
       </c>
-      <c r="E17" s="109">
-        <v>56.367100000000001</v>
-      </c>
-      <c r="F17" s="95">
+      <c r="E17" s="93">
+        <v>42.8264</v>
+      </c>
+      <c r="F17" s="106">
         <f t="shared" si="4"/>
-        <v>0.89500000000000002</v>
-      </c>
-      <c r="G17" s="76">
+        <v>0.68</v>
+      </c>
+      <c r="G17" s="73">
         <f>INDEX(tariffs!4:4, MATCH(CHECK!$B$3,tariffs!$1:$1, 0))</f>
         <v>62.98</v>
       </c>
-      <c r="H17" s="108">
+      <c r="H17" s="105">
         <f t="shared" si="1"/>
-        <v>56.367100000000001</v>
-      </c>
-      <c r="I17" s="36">
-        <f t="shared" ref="I17:J24" si="5">IFERROR(F17-C17, "")</f>
+        <v>42.8264</v>
+      </c>
+      <c r="I17" s="119">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J17" s="37">
-        <f t="shared" si="5"/>
+      <c r="J17" s="36">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K17" s="38">
-        <f t="shared" ref="K17:K24" si="6">IFERROR(E17-H17,"")</f>
+      <c r="K17" s="120">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="L17" s="3" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>✔ ОК</v>
       </c>
-      <c r="M17" s="42">
+      <c r="M17" s="41">
         <f>IFERROR(INDEX(tariffs!17:17, MATCH(CHECK!$B$3, tariffs!$1:$1, 0)),"")</f>
         <v>0.67909799999999998</v>
       </c>
@@ -6457,44 +7000,44 @@
       <c r="B18" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="C18" s="93">
-        <v>1.3520000000000001</v>
-      </c>
-      <c r="D18" s="104">
+      <c r="C18" s="94">
+        <v>1.36</v>
+      </c>
+      <c r="D18" s="84">
         <v>62.98</v>
       </c>
-      <c r="E18" s="109">
-        <v>85.148960000000002</v>
-      </c>
-      <c r="F18" s="95">
+      <c r="E18" s="93">
+        <v>85.652799999999999</v>
+      </c>
+      <c r="F18" s="106">
         <f t="shared" si="4"/>
-        <v>1.3520000000000001</v>
-      </c>
-      <c r="G18" s="76">
+        <v>1.36</v>
+      </c>
+      <c r="G18" s="73">
         <f>INDEX(tariffs!4:4, MATCH(CHECK!$B$3,tariffs!$1:$1, 0))</f>
         <v>62.98</v>
       </c>
-      <c r="H18" s="108">
+      <c r="H18" s="105">
         <f t="shared" si="1"/>
-        <v>85.148960000000002</v>
-      </c>
-      <c r="I18" s="36">
-        <f t="shared" si="5"/>
+        <v>85.652799999999999</v>
+      </c>
+      <c r="I18" s="119">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J18" s="37">
-        <f t="shared" si="5"/>
+      <c r="J18" s="36">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K18" s="38">
-        <f t="shared" si="6"/>
+      <c r="K18" s="120">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="L18" s="3" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>✔ ОК</v>
       </c>
-      <c r="M18" s="42">
+      <c r="M18" s="41">
         <f>IFERROR(INDEX(tariffs!20:20, MATCH(CHECK!$B$3, tariffs!$1:$1, 0)),"")</f>
         <v>1.358196</v>
       </c>
@@ -6510,44 +7053,44 @@
       <c r="B19" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="C19" s="93">
-        <v>1.3520000000000001</v>
-      </c>
-      <c r="D19" s="104">
+      <c r="C19" s="94">
+        <v>1.36</v>
+      </c>
+      <c r="D19" s="84">
         <v>44.12</v>
       </c>
-      <c r="E19" s="109">
-        <v>59.650240000000004</v>
-      </c>
-      <c r="F19" s="95">
+      <c r="E19" s="93">
+        <v>60.0032</v>
+      </c>
+      <c r="F19" s="106">
         <f t="shared" si="4"/>
-        <v>1.3520000000000001</v>
-      </c>
-      <c r="G19" s="76">
+        <v>1.36</v>
+      </c>
+      <c r="G19" s="73">
         <f>INDEX(tariffs!5:5, MATCH(CHECK!$B$3,tariffs!$1:$1, 0))</f>
         <v>44.12</v>
       </c>
-      <c r="H19" s="108">
+      <c r="H19" s="105">
         <f t="shared" si="1"/>
-        <v>59.650240000000004</v>
-      </c>
-      <c r="I19" s="36">
-        <f t="shared" si="5"/>
+        <v>60.0032</v>
+      </c>
+      <c r="I19" s="119">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J19" s="37">
-        <f t="shared" si="5"/>
+      <c r="J19" s="36">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K19" s="38">
-        <f t="shared" si="6"/>
+      <c r="K19" s="120">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="L19" s="3" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>✔ ОК</v>
       </c>
-      <c r="M19" s="42">
+      <c r="M19" s="41">
         <f>IFERROR(INDEX(tariffs!21:21, MATCH(CHECK!$B$3, tariffs!$1:$1, 0)),"")</f>
         <v>1.358196</v>
       </c>
@@ -6563,44 +7106,44 @@
       <c r="B20" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="C20" s="93">
-        <v>32.22</v>
-      </c>
-      <c r="D20" s="103">
+      <c r="C20" s="94">
+        <v>26.83</v>
+      </c>
+      <c r="D20" s="83">
         <v>4.2</v>
       </c>
-      <c r="E20" s="109">
-        <v>135.32400000000001</v>
-      </c>
-      <c r="F20" s="76">
+      <c r="E20" s="93">
+        <v>112.68599999999999</v>
+      </c>
+      <c r="F20" s="108">
         <f t="shared" si="4"/>
-        <v>32.22</v>
-      </c>
-      <c r="G20" s="76">
+        <v>26.83</v>
+      </c>
+      <c r="G20" s="73">
         <f>INDEX(tariffs!2:2, MATCH(CHECK!$B$3,tariffs!$1:$1, 0))</f>
         <v>4.2</v>
       </c>
-      <c r="H20" s="108">
+      <c r="H20" s="105">
         <f t="shared" si="1"/>
-        <v>135.32400000000001</v>
-      </c>
-      <c r="I20" s="36">
-        <f t="shared" si="5"/>
+        <v>112.68599999999999</v>
+      </c>
+      <c r="I20" s="119">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J20" s="37">
-        <f t="shared" si="5"/>
+      <c r="J20" s="36">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K20" s="38">
-        <f t="shared" si="6"/>
+      <c r="K20" s="120">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="L20" s="3" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>✔ ОК</v>
       </c>
-      <c r="M20" s="42">
+      <c r="M20" s="41">
         <f>IFERROR(INDEX(tariffs!19:19, MATCH(CHECK!$B$3, tariffs!$1:$1, 0)),"")</f>
         <v>26.829499999999999</v>
       </c>
@@ -6616,44 +7159,44 @@
       <c r="B21" s="23" t="s">
         <v>47</v>
       </c>
-      <c r="C21" s="93">
+      <c r="C21" s="94">
         <v>55.2</v>
       </c>
-      <c r="D21" s="103">
+      <c r="D21" s="83">
         <v>11.08</v>
       </c>
-      <c r="E21" s="109">
+      <c r="E21" s="93">
         <v>611.61599999999999</v>
       </c>
-      <c r="F21" s="96">
+      <c r="F21" s="109">
         <f>IFERROR(info!$B$7,"")</f>
         <v>55.2</v>
       </c>
-      <c r="G21" s="76">
+      <c r="G21" s="73">
         <f>INDEX(tariffs!8:8, MATCH(CHECK!$B$3,tariffs!$1:$1, 0))</f>
         <v>11.08</v>
       </c>
-      <c r="H21" s="108">
+      <c r="H21" s="105">
         <f t="shared" si="1"/>
         <v>611.61599999999999</v>
       </c>
-      <c r="I21" s="36">
-        <f t="shared" si="5"/>
+      <c r="I21" s="119">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J21" s="37">
-        <f t="shared" si="5"/>
+      <c r="J21" s="36">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K21" s="38">
-        <f t="shared" si="6"/>
+      <c r="K21" s="120">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="L21" s="3" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>✔ ОК</v>
       </c>
-      <c r="M21" s="39"/>
+      <c r="M21" s="38"/>
       <c r="N21" s="10" t="str">
         <f>VLOOKUP(A21,info!A25:B41, 2,FALSE)</f>
         <v>Управляющая</v>
@@ -6666,44 +7209,44 @@
       <c r="B22" s="23" t="s">
         <v>47</v>
       </c>
-      <c r="C22" s="93">
+      <c r="C22" s="94">
         <v>55.2</v>
       </c>
-      <c r="D22" s="103">
+      <c r="D22" s="83">
         <v>5.98</v>
       </c>
-      <c r="E22" s="109">
+      <c r="E22" s="93">
         <v>330.09600000000006</v>
       </c>
-      <c r="F22" s="96">
+      <c r="F22" s="109">
         <f>IFERROR(info!$B$7,"")</f>
         <v>55.2</v>
       </c>
-      <c r="G22" s="76">
+      <c r="G22" s="73">
         <f>INDEX(tariffs!9:9, MATCH(CHECK!$B$3,tariffs!$1:$1, 0))</f>
         <v>5.98</v>
       </c>
-      <c r="H22" s="108">
+      <c r="H22" s="105">
         <f t="shared" si="1"/>
         <v>330.09600000000006</v>
       </c>
-      <c r="I22" s="36">
-        <f t="shared" si="5"/>
+      <c r="I22" s="119">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J22" s="37">
-        <f t="shared" si="5"/>
+      <c r="J22" s="36">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K22" s="38">
-        <f t="shared" si="6"/>
+      <c r="K22" s="120">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="L22" s="3" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>✔ ОК</v>
       </c>
-      <c r="M22" s="39"/>
+      <c r="M22" s="38"/>
       <c r="N22" s="10" t="str">
         <f>VLOOKUP(A22,info!A26:B42, 2,FALSE)</f>
         <v>Управляющая</v>
@@ -6716,44 +7259,44 @@
       <c r="B23" s="23" t="s">
         <v>49</v>
       </c>
-      <c r="C23" s="93">
+      <c r="C23" s="94">
         <v>2</v>
       </c>
-      <c r="D23" s="103">
-        <v>161.52260000000001</v>
-      </c>
-      <c r="E23" s="109">
-        <v>323.04520000000002</v>
-      </c>
-      <c r="F23" s="97">
+      <c r="D23" s="83">
+        <v>158</v>
+      </c>
+      <c r="E23" s="93">
+        <v>316</v>
+      </c>
+      <c r="F23" s="104">
         <f>IFERROR(info!$B$6,"")</f>
         <v>2</v>
       </c>
-      <c r="G23" s="76">
-        <f>IF(D23&lt;M23, D23,M23)</f>
+      <c r="G23" s="73">
+        <f>INDEX(tariffs!10:10, MATCH(CHECK!$B$3,tariffs!$1:$1, 0))</f>
         <v>161.52257251624999</v>
       </c>
-      <c r="H23" s="108">
+      <c r="H23" s="105">
         <f t="shared" si="1"/>
         <v>323.04514503249999</v>
       </c>
-      <c r="I23" s="36">
-        <f t="shared" si="5"/>
+      <c r="I23" s="119">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J23" s="37">
-        <f t="shared" si="5"/>
-        <v>-2.7483750017154307E-5</v>
-      </c>
-      <c r="K23" s="38">
-        <f t="shared" si="6"/>
-        <v>5.4967500034308614E-5</v>
+      <c r="J23" s="36">
+        <f t="shared" si="0"/>
+        <v>-3.5225725162499941</v>
+      </c>
+      <c r="K23" s="120">
+        <f t="shared" si="0"/>
+        <v>-7.0451450324999882</v>
       </c>
       <c r="L23" s="3" t="str">
-        <f t="shared" si="2"/>
-        <v>✔ ОК</v>
-      </c>
-      <c r="M23" s="39">
+        <f t="shared" si="3"/>
+        <v>❗ Недосчет</v>
+      </c>
+      <c r="M23" s="38">
         <f>IFERROR(INDEX(tariffs!10:10, MATCH(CHECK!$B$3, tariffs!$1:$1, 0)),"")</f>
         <v>161.52257251624999</v>
       </c>
@@ -6769,44 +7312,44 @@
       <c r="B24" s="23" t="s">
         <v>47</v>
       </c>
-      <c r="C24" s="106">
+      <c r="C24" s="96">
         <v>55.2</v>
       </c>
-      <c r="D24" s="105">
+      <c r="D24" s="97">
         <v>15.15</v>
       </c>
-      <c r="E24" s="110">
+      <c r="E24" s="98">
         <v>836.28000000000009</v>
       </c>
-      <c r="F24" s="96">
+      <c r="F24" s="110">
         <f>IFERROR(info!$B$7,"")</f>
         <v>55.2</v>
       </c>
-      <c r="G24" s="76">
+      <c r="G24" s="111">
         <f>INDEX(tariffs!11:11, MATCH(CHECK!$B$3,tariffs!$1:$1, 0))</f>
         <v>15.15</v>
       </c>
-      <c r="H24" s="108">
+      <c r="H24" s="112">
         <f t="shared" si="1"/>
         <v>836.28000000000009</v>
       </c>
-      <c r="I24" s="36">
-        <f t="shared" si="5"/>
+      <c r="I24" s="121">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J24" s="37">
-        <f t="shared" si="5"/>
+      <c r="J24" s="122">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K24" s="38">
-        <f t="shared" si="6"/>
+      <c r="K24" s="123">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="L24" s="3" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>✔ ОК</v>
       </c>
-      <c r="M24" s="39"/>
+      <c r="M24" s="38"/>
       <c r="N24" s="10" t="str">
         <f>VLOOKUP(A24,info!A28:B44, 2,FALSE)</f>
         <v>Капремонт</v>
@@ -6814,178 +7357,184 @@
     </row>
     <row r="25" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A25" s="11"/>
-      <c r="C25" s="40"/>
-      <c r="D25" s="40"/>
-      <c r="E25" s="40"/>
-      <c r="F25" s="40"/>
-      <c r="G25" s="40"/>
-      <c r="H25" s="40"/>
-      <c r="I25" s="40"/>
-      <c r="J25" s="40"/>
-      <c r="K25" s="40"/>
-      <c r="L25" s="40"/>
-      <c r="M25" s="40"/>
+      <c r="C25" s="39"/>
+      <c r="D25" s="39"/>
+      <c r="E25" s="39"/>
+      <c r="F25" s="39"/>
+      <c r="G25" s="39"/>
+      <c r="H25" s="39"/>
+      <c r="I25" s="39"/>
+      <c r="J25" s="39"/>
+      <c r="K25" s="39"/>
+      <c r="L25" s="39"/>
+      <c r="M25" s="39"/>
     </row>
     <row r="26" spans="1:14" s="5" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="46" t="s">
+      <c r="A26" s="45" t="s">
         <v>50</v>
       </c>
       <c r="B26" s="35"/>
-      <c r="C26" s="41"/>
-      <c r="D26" s="41"/>
-      <c r="E26" s="41">
+      <c r="C26" s="40"/>
+      <c r="D26" s="40"/>
+      <c r="E26" s="40">
         <f>SUM(E9:E24)</f>
-        <v>19950.641089999994</v>
-      </c>
-      <c r="F26" s="41"/>
-      <c r="G26" s="41"/>
-      <c r="H26" s="41"/>
-      <c r="I26" s="41"/>
-      <c r="J26" s="41"/>
-      <c r="K26" s="41">
+        <v>12883.485759999998</v>
+      </c>
+      <c r="F26" s="40"/>
+      <c r="G26" s="40"/>
+      <c r="H26" s="40">
+        <f>SUM(H9:H24)</f>
+        <v>12431.1949530325</v>
+      </c>
+      <c r="I26" s="40"/>
+      <c r="J26" s="40"/>
+      <c r="K26" s="40">
         <f>SUM(K9:K24)</f>
-        <v>5.4967500062730323E-5</v>
-      </c>
-      <c r="L26" s="41"/>
-      <c r="M26" s="41"/>
+        <v>452.29080696750003</v>
+      </c>
+      <c r="L26" s="3" t="str">
+        <f t="shared" ref="L10:L32" si="5">IF(ABS(K26)&lt;=1,"✔ ОК",IF(K26&gt;1,"❗ Превышение","❗ Недосчет"))</f>
+        <v>❗ Превышение</v>
+      </c>
+      <c r="M26" s="40"/>
       <c r="N26" s="35"/>
     </row>
-    <row r="27" spans="1:14" s="50" customFormat="1" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="47" t="s">
+    <row r="27" spans="1:14" s="49" customFormat="1" ht="29.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A27" s="46" t="s">
         <v>51</v>
       </c>
-      <c r="B27" s="48"/>
-      <c r="C27" s="49"/>
-      <c r="D27" s="49"/>
-      <c r="E27" s="49"/>
-      <c r="F27" s="49"/>
-      <c r="G27" s="49"/>
-      <c r="H27" s="49"/>
-      <c r="I27" s="49"/>
-      <c r="J27" s="49"/>
-      <c r="K27" s="49"/>
-      <c r="L27" s="49"/>
-      <c r="M27" s="49"/>
-      <c r="N27" s="48"/>
-    </row>
-    <row r="28" spans="1:14" s="5" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="46" t="s">
-        <v>148</v>
+      <c r="B27" s="47"/>
+      <c r="C27" s="48"/>
+      <c r="D27" s="48"/>
+      <c r="E27" s="48"/>
+      <c r="F27" s="48"/>
+      <c r="G27" s="48"/>
+      <c r="H27" s="48"/>
+      <c r="I27" s="48"/>
+      <c r="J27" s="48"/>
+      <c r="K27" s="48"/>
+      <c r="L27" s="48"/>
+      <c r="M27" s="48"/>
+      <c r="N27" s="47"/>
+    </row>
+    <row r="28" spans="1:14" s="5" customFormat="1" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A28" s="45" t="s">
+        <v>144</v>
       </c>
       <c r="B28" s="35"/>
-      <c r="C28" s="41"/>
-      <c r="D28" s="41"/>
-      <c r="E28" s="41">
+      <c r="C28" s="40"/>
+      <c r="D28" s="40"/>
+      <c r="E28" s="40">
         <f>SUMIF($N:$N,$A28,E:E)</f>
-        <v>844.2</v>
-      </c>
-      <c r="F28" s="41"/>
-      <c r="G28" s="41"/>
-      <c r="H28" s="41"/>
-      <c r="I28" s="41"/>
-      <c r="J28" s="41"/>
-      <c r="K28" s="41">
+        <v>856.80000000000007</v>
+      </c>
+      <c r="F28" s="40"/>
+      <c r="G28" s="40"/>
+      <c r="H28" s="40"/>
+      <c r="I28" s="40"/>
+      <c r="J28" s="40"/>
+      <c r="K28" s="40">
         <f>SUMIF($N:$N,$A28,K:K)</f>
+        <v>12.600000000000023</v>
+      </c>
+      <c r="L28" s="40"/>
+      <c r="M28" s="40"/>
+      <c r="N28" s="35"/>
+    </row>
+    <row r="29" spans="1:14" s="5" customFormat="1" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A29" s="45" t="s">
+        <v>145</v>
+      </c>
+      <c r="B29" s="35"/>
+      <c r="C29" s="40"/>
+      <c r="D29" s="40"/>
+      <c r="E29" s="40">
+        <f>SUMIF($N:$N,$A29,E:E)</f>
+        <v>835.37999999999988</v>
+      </c>
+      <c r="F29" s="40"/>
+      <c r="G29" s="40"/>
+      <c r="H29" s="40"/>
+      <c r="I29" s="40"/>
+      <c r="J29" s="40"/>
+      <c r="K29" s="40">
+        <f>SUMIF($N:$N,$A29,K:K)</f>
         <v>0</v>
       </c>
-      <c r="L28" s="41"/>
-      <c r="M28" s="41"/>
-      <c r="N28" s="35"/>
-    </row>
-    <row r="29" spans="1:14" s="5" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="46" t="s">
-        <v>149</v>
-      </c>
-      <c r="B29" s="35"/>
-      <c r="C29" s="41"/>
-      <c r="D29" s="41"/>
-      <c r="E29" s="41">
-        <f>SUMIF($N:$N,$A29,E:E)</f>
-        <v>835.38</v>
-      </c>
-      <c r="F29" s="41"/>
-      <c r="G29" s="41"/>
-      <c r="H29" s="41"/>
-      <c r="I29" s="41"/>
-      <c r="J29" s="41"/>
-      <c r="K29" s="41">
-        <f>SUMIF($N:$N,$A29,K:K)</f>
-        <v>2.8421709430404007E-14</v>
-      </c>
-      <c r="L29" s="41"/>
-      <c r="M29" s="41"/>
+      <c r="L29" s="40"/>
+      <c r="M29" s="40"/>
       <c r="N29" s="35"/>
     </row>
-    <row r="30" spans="1:14" s="5" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A30" s="46" t="s">
-        <v>142</v>
+    <row r="30" spans="1:14" s="5" customFormat="1" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A30" s="45" t="s">
+        <v>139</v>
       </c>
       <c r="B30" s="35"/>
-      <c r="C30" s="41"/>
-      <c r="D30" s="41"/>
-      <c r="E30" s="41">
+      <c r="C30" s="40"/>
+      <c r="D30" s="40"/>
+      <c r="E30" s="40">
         <f>SUMIF($N:$N,$A30,E:E)</f>
-        <v>17111.73589</v>
-      </c>
-      <c r="F30" s="41"/>
-      <c r="G30" s="41"/>
-      <c r="H30" s="41"/>
-      <c r="I30" s="41"/>
-      <c r="J30" s="41"/>
-      <c r="K30" s="41">
+        <v>10039.025759999997</v>
+      </c>
+      <c r="F30" s="40"/>
+      <c r="G30" s="40"/>
+      <c r="H30" s="40"/>
+      <c r="I30" s="40"/>
+      <c r="J30" s="40"/>
+      <c r="K30" s="40">
         <f>SUMIF($N:$N,$A30,K:K)</f>
-        <v>0</v>
-      </c>
-      <c r="L30" s="41"/>
-      <c r="M30" s="41"/>
+        <v>446.735952</v>
+      </c>
+      <c r="L30" s="40"/>
+      <c r="M30" s="40"/>
       <c r="N30" s="35"/>
     </row>
-    <row r="31" spans="1:14" s="5" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A31" s="46" t="s">
-        <v>143</v>
+    <row r="31" spans="1:14" s="5" customFormat="1" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A31" s="45" t="s">
+        <v>140</v>
       </c>
       <c r="B31" s="35"/>
-      <c r="C31" s="41"/>
-      <c r="D31" s="41"/>
-      <c r="E31" s="41">
+      <c r="C31" s="40"/>
+      <c r="D31" s="40"/>
+      <c r="E31" s="40">
         <f>SUMIF($N:$N,$A31,E:E)</f>
-        <v>323.04520000000002</v>
-      </c>
-      <c r="F31" s="41"/>
-      <c r="G31" s="41"/>
-      <c r="H31" s="41"/>
-      <c r="I31" s="41"/>
-      <c r="J31" s="41"/>
-      <c r="K31" s="41">
+        <v>316</v>
+      </c>
+      <c r="F31" s="40"/>
+      <c r="G31" s="40"/>
+      <c r="H31" s="40"/>
+      <c r="I31" s="40"/>
+      <c r="J31" s="40"/>
+      <c r="K31" s="40">
         <f>SUMIF($N:$N,$A31,K:K)</f>
-        <v>5.4967500034308614E-5</v>
-      </c>
-      <c r="L31" s="41"/>
-      <c r="M31" s="41"/>
+        <v>-7.0451450324999882</v>
+      </c>
+      <c r="L31" s="40"/>
+      <c r="M31" s="40"/>
       <c r="N31" s="35"/>
     </row>
-    <row r="32" spans="1:14" s="5" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A32" s="46" t="s">
+    <row r="32" spans="1:14" s="5" customFormat="1" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A32" s="45" t="s">
         <v>34</v>
       </c>
       <c r="B32" s="35"/>
-      <c r="C32" s="41"/>
-      <c r="D32" s="41"/>
-      <c r="E32" s="41">
+      <c r="C32" s="40"/>
+      <c r="D32" s="40"/>
+      <c r="E32" s="40">
         <f>SUMIF($N:$N,$A32,E:E)</f>
         <v>836.28000000000009</v>
       </c>
-      <c r="F32" s="41"/>
-      <c r="G32" s="41"/>
-      <c r="H32" s="41"/>
-      <c r="I32" s="41"/>
-      <c r="J32" s="41"/>
-      <c r="K32" s="41">
+      <c r="F32" s="40"/>
+      <c r="G32" s="40"/>
+      <c r="H32" s="40"/>
+      <c r="I32" s="40"/>
+      <c r="J32" s="40"/>
+      <c r="K32" s="40">
         <f>SUMIF($N:$N,$A32,K:K)</f>
         <v>0</v>
       </c>
-      <c r="L32" s="41"/>
-      <c r="M32" s="41"/>
+      <c r="L32" s="40"/>
+      <c r="M32" s="40"/>
       <c r="N32" s="35"/>
     </row>
   </sheetData>
@@ -6994,14 +7543,33 @@
     <mergeCell ref="F7:H7"/>
     <mergeCell ref="I7:K7"/>
   </mergeCells>
-  <dataValidations count="1">
+  <conditionalFormatting sqref="L1:L24 L26:L1048576">
+    <cfRule type="containsText" dxfId="9" priority="7" operator="containsText" text="✔ ОК">
+      <formula>NOT(ISERROR(SEARCH("✔ ОК",L1)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="8" priority="6" operator="containsText" text="❗ Превышение">
+      <formula>NOT(ISERROR(SEARCH("❗ Превышение",L1)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="7" priority="5" operator="containsText" text="❗ Недосчет">
+      <formula>NOT(ISERROR(SEARCH("❗ Недосчет",L1)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I9:K24 K26 K28:K32">
+    <cfRule type="expression" dxfId="6" priority="2">
+      <formula>AND($K9&lt;&gt;"",$K9&gt;0.1)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="5" priority="1">
+      <formula>AND($K9&lt;&gt;"",$K9&lt;-0.1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations disablePrompts="1" count="1">
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C9:D9" xr:uid="{EEAF0B01-A716-45A5-80B9-6D59D6176D06}"/>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="4">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" disablePrompts="1" count="4">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{6E04C081-2925-4DDE-9260-64EC5751E787}">
           <x14:formula1>
             <xm:f>helper!$E$2:$E$10</xm:f>
@@ -7038,13 +7606,13 @@
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="22.7265625" customWidth="1"/>
-    <col min="3" max="4" width="12.26953125" style="54" customWidth="1"/>
-    <col min="5" max="5" width="12.26953125" style="56" customWidth="1"/>
-    <col min="6" max="6" width="12.26953125" style="55" customWidth="1"/>
-    <col min="7" max="8" width="9.90625" style="56" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.90625" style="56" customWidth="1"/>
-    <col min="10" max="10" width="9.90625" style="56" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="26.08984375" style="55" customWidth="1"/>
+    <col min="3" max="4" width="12.26953125" style="53" customWidth="1"/>
+    <col min="5" max="5" width="12.26953125" style="55" customWidth="1"/>
+    <col min="6" max="6" width="12.26953125" style="54" customWidth="1"/>
+    <col min="7" max="8" width="9.90625" style="55" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.90625" style="55" customWidth="1"/>
+    <col min="10" max="10" width="9.90625" style="55" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="26.08984375" style="54" customWidth="1"/>
     <col min="12" max="19" width="9.90625" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="10.453125" bestFit="1" customWidth="1"/>
     <col min="21" max="25" width="10.08984375" hidden="1" customWidth="1"/>
@@ -7089,43 +7657,43 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="91"/>
-      <c r="L1" s="91"/>
-      <c r="M1" s="91"/>
-      <c r="N1" s="91"/>
-      <c r="O1" s="91"/>
+      <c r="K1" s="78"/>
+      <c r="L1" s="78"/>
+      <c r="M1" s="78"/>
+      <c r="N1" s="78"/>
+      <c r="O1" s="78"/>
     </row>
     <row r="2" spans="1:28" s="11" customFormat="1" ht="29" x14ac:dyDescent="0.35">
-      <c r="A2" s="51" t="s">
+      <c r="A2" s="50" t="s">
         <v>58</v>
       </c>
-      <c r="B2" s="60" t="s">
+      <c r="B2" s="59" t="s">
         <v>53</v>
       </c>
-      <c r="C2" s="61" t="s">
+      <c r="C2" s="60" t="s">
         <v>54</v>
       </c>
-      <c r="D2" s="62" t="s">
+      <c r="D2" s="61" t="s">
         <v>55</v>
       </c>
-      <c r="E2" s="61" t="s">
+      <c r="E2" s="60" t="s">
         <v>117</v>
       </c>
-      <c r="F2" s="61" t="s">
+      <c r="F2" s="60" t="s">
         <v>56</v>
       </c>
-      <c r="H2" s="58"/>
-      <c r="I2" s="58"/>
-      <c r="J2" s="58"/>
+      <c r="H2" s="57"/>
+      <c r="I2" s="57"/>
+      <c r="J2" s="57"/>
       <c r="P2"/>
       <c r="Q2"/>
-      <c r="V2" s="59" t="s">
+      <c r="V2" s="58" t="s">
         <v>119</v>
       </c>
-      <c r="W2" s="57"/>
+      <c r="W2" s="56"/>
       <c r="X2"/>
       <c r="Y2"/>
-      <c r="AA2" s="51" t="s">
+      <c r="AA2" s="50" t="s">
         <v>58</v>
       </c>
       <c r="AB2" t="s">
@@ -7136,7 +7704,7 @@
       <c r="A3" t="s">
         <v>126</v>
       </c>
-      <c r="E3" s="54">
+      <c r="E3" s="53">
         <v>0</v>
       </c>
       <c r="U3" s="11"/>
@@ -7148,10 +7716,10 @@
       <c r="B4" t="s">
         <v>126</v>
       </c>
-      <c r="E4" s="54">
+      <c r="E4" s="53">
         <v>0</v>
       </c>
-      <c r="U4" s="51" t="s">
+      <c r="U4" s="50" t="s">
         <v>125</v>
       </c>
       <c r="V4" t="s">
@@ -7160,7 +7728,7 @@
       <c r="W4" t="s">
         <v>55</v>
       </c>
-      <c r="AA4" s="51" t="s">
+      <c r="AA4" s="50" t="s">
         <v>124</v>
       </c>
       <c r="AB4" t="s">
@@ -7171,7 +7739,7 @@
       <c r="A5" t="s">
         <v>57</v>
       </c>
-      <c r="E5" s="54">
+      <c r="E5" s="53">
         <v>0</v>
       </c>
       <c r="U5" s="17" t="s">
@@ -7180,7 +7748,7 @@
       <c r="AA5" s="17" t="s">
         <v>126</v>
       </c>
-      <c r="AB5" s="54"/>
+      <c r="AB5" s="53"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.35">
       <c r="C6"/>
@@ -7194,7 +7762,7 @@
       <c r="AA6" s="17" t="s">
         <v>57</v>
       </c>
-      <c r="AB6" s="54"/>
+      <c r="AB6" s="53"/>
     </row>
     <row r="7" spans="1:28" x14ac:dyDescent="0.35">
       <c r="C7"/>
@@ -7345,13 +7913,13 @@
       <c r="K25"/>
     </row>
     <row r="26" spans="2:11" ht="16" x14ac:dyDescent="0.4">
-      <c r="B26" s="92" t="s">
+      <c r="B26" s="79" t="s">
         <v>120</v>
       </c>
-      <c r="C26" s="92"/>
-      <c r="D26" s="92"/>
-      <c r="E26" s="92"/>
-      <c r="F26" s="92"/>
+      <c r="C26" s="79"/>
+      <c r="D26" s="79"/>
+      <c r="E26" s="79"/>
+      <c r="F26" s="79"/>
       <c r="G26"/>
       <c r="H26"/>
       <c r="I26"/>
@@ -7359,19 +7927,19 @@
       <c r="K26"/>
     </row>
     <row r="27" spans="2:11" ht="29" x14ac:dyDescent="0.35">
-      <c r="B27" s="60" t="s">
+      <c r="B27" s="59" t="s">
         <v>118</v>
       </c>
-      <c r="C27" s="61" t="s">
+      <c r="C27" s="60" t="s">
         <v>54</v>
       </c>
-      <c r="D27" s="61" t="s">
+      <c r="D27" s="60" t="s">
         <v>55</v>
       </c>
-      <c r="E27" s="61" t="s">
+      <c r="E27" s="60" t="s">
         <v>117</v>
       </c>
-      <c r="F27" s="61" t="s">
+      <c r="F27" s="60" t="s">
         <v>56</v>
       </c>
       <c r="G27"/>
@@ -7384,7 +7952,7 @@
       <c r="B28" s="17" t="s">
         <v>126</v>
       </c>
-      <c r="E28" s="54">
+      <c r="E28" s="53">
         <v>0</v>
       </c>
       <c r="G28"/>
@@ -7394,10 +7962,10 @@
       <c r="K28"/>
     </row>
     <row r="29" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B29" s="63" t="s">
+      <c r="B29" s="62" t="s">
         <v>126</v>
       </c>
-      <c r="E29" s="54">
+      <c r="E29" s="53">
         <v>0</v>
       </c>
       <c r="G29"/>
@@ -7407,10 +7975,10 @@
       <c r="K29"/>
     </row>
     <row r="30" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B30" s="64" t="s">
+      <c r="B30" s="63" t="s">
         <v>126</v>
       </c>
-      <c r="E30" s="54">
+      <c r="E30" s="53">
         <v>0</v>
       </c>
       <c r="J30"/>
@@ -7420,7 +7988,7 @@
       <c r="B31" s="17" t="s">
         <v>57</v>
       </c>
-      <c r="E31" s="54">
+      <c r="E31" s="53">
         <v>0</v>
       </c>
       <c r="J31"/>
@@ -8032,7 +8600,7 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" s="24" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
@@ -8069,7 +8637,7 @@
       <c r="A8" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="45">
+      <c r="B8" s="44">
         <v>4800</v>
       </c>
     </row>
@@ -8102,7 +8670,7 @@
       <c r="D13" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="E13" s="52" t="s">
+      <c r="E13" s="51" t="s">
         <v>14</v>
       </c>
     </row>
@@ -8111,7 +8679,7 @@
         <v>15</v>
       </c>
       <c r="B14" s="24" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="C14" s="33" t="s">
         <v>16</v>
@@ -8128,7 +8696,7 @@
         <v>18</v>
       </c>
       <c r="B15" s="24" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="C15" s="33" t="s">
         <v>16</v>
@@ -8143,20 +8711,22 @@
         <v>133</v>
       </c>
       <c r="B16" s="24" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="C16" s="33" t="s">
         <v>16</v>
       </c>
       <c r="D16" s="26"/>
-      <c r="E16" s="21"/>
+      <c r="E16" s="21" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="17" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A17" s="24" t="s">
         <v>136</v>
       </c>
       <c r="B17" s="24" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="C17" s="33" t="s">
         <v>16</v>
@@ -8171,7 +8741,7 @@
         <v>134</v>
       </c>
       <c r="B18" s="24" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="C18" s="33" t="s">
         <v>16</v>
@@ -8186,7 +8756,7 @@
         <v>27</v>
       </c>
       <c r="B19" s="24" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="C19" s="33" t="s">
         <v>25</v>
@@ -8201,7 +8771,7 @@
         <v>29</v>
       </c>
       <c r="B20" s="24" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="C20" s="33" t="s">
         <v>30</v>
@@ -8218,7 +8788,7 @@
         <v>137</v>
       </c>
       <c r="B21" s="24" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="C21" s="33" t="s">
         <v>25</v>
@@ -8233,7 +8803,7 @@
         <v>129</v>
       </c>
       <c r="B22" s="24" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="C22" s="33" t="s">
         <v>25</v>
@@ -8248,7 +8818,7 @@
         <v>130</v>
       </c>
       <c r="B23" s="24" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="C23" s="33" t="s">
         <v>25</v>
@@ -8263,7 +8833,7 @@
         <v>131</v>
       </c>
       <c r="B24" s="24" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="C24" s="33" t="s">
         <v>25</v>
@@ -8278,7 +8848,7 @@
         <v>128</v>
       </c>
       <c r="B25" s="24" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="C25" s="33" t="s">
         <v>25</v>
@@ -8293,7 +8863,7 @@
         <v>135</v>
       </c>
       <c r="B26" s="24" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="C26" s="33" t="s">
         <v>22</v>
@@ -8308,7 +8878,7 @@
         <v>21</v>
       </c>
       <c r="B27" s="24" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="C27" s="33" t="s">
         <v>22</v>
@@ -8323,7 +8893,7 @@
         <v>132</v>
       </c>
       <c r="B28" s="24" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C28" s="33" t="s">
         <v>32</v>
@@ -8394,7 +8964,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" s="1" customFormat="1" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="74" t="s">
+      <c r="A1" s="72" t="s">
         <v>52</v>
       </c>
       <c r="B1" s="22" t="s">
@@ -8408,216 +8978,216 @@
       </c>
     </row>
     <row r="2" spans="1:4" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="80">
+      <c r="A2" s="76">
         <v>45627</v>
       </c>
-      <c r="B2" s="100"/>
-      <c r="C2" s="99"/>
-      <c r="D2" s="99"/>
+      <c r="B2" s="81"/>
+      <c r="C2" s="80"/>
+      <c r="D2" s="80"/>
     </row>
     <row r="3" spans="1:4" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="80">
+      <c r="A3" s="76">
         <v>45658</v>
       </c>
-      <c r="B3" s="100"/>
-      <c r="C3" s="99"/>
-      <c r="D3" s="99"/>
+      <c r="B3" s="81"/>
+      <c r="C3" s="80"/>
+      <c r="D3" s="80"/>
     </row>
     <row r="4" spans="1:4" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="80">
+      <c r="A4" s="76">
         <v>45689</v>
       </c>
-      <c r="B4" s="100"/>
-      <c r="C4" s="99"/>
-      <c r="D4" s="99"/>
+      <c r="B4" s="81"/>
+      <c r="C4" s="80"/>
+      <c r="D4" s="80"/>
     </row>
     <row r="5" spans="1:4" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="80">
+      <c r="A5" s="76">
         <v>45717</v>
       </c>
-      <c r="B5" s="100"/>
-      <c r="C5" s="99"/>
-      <c r="D5" s="99"/>
+      <c r="B5" s="81"/>
+      <c r="C5" s="80"/>
+      <c r="D5" s="80"/>
     </row>
     <row r="6" spans="1:4" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="80">
+      <c r="A6" s="76">
         <v>45748</v>
       </c>
-      <c r="B6" s="100"/>
-      <c r="C6" s="99"/>
-      <c r="D6" s="99"/>
+      <c r="B6" s="81"/>
+      <c r="C6" s="80"/>
+      <c r="D6" s="80"/>
     </row>
     <row r="7" spans="1:4" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="80">
+      <c r="A7" s="76">
         <v>45778</v>
       </c>
-      <c r="B7" s="100"/>
-      <c r="C7" s="99"/>
-      <c r="D7" s="99"/>
+      <c r="B7" s="81"/>
+      <c r="C7" s="80"/>
+      <c r="D7" s="80"/>
     </row>
     <row r="8" spans="1:4" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="80">
+      <c r="A8" s="76">
         <v>45809</v>
       </c>
-      <c r="B8" s="100"/>
-      <c r="C8" s="99"/>
-      <c r="D8" s="99"/>
+      <c r="B8" s="81"/>
+      <c r="C8" s="80"/>
+      <c r="D8" s="80"/>
     </row>
     <row r="9" spans="1:4" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="80">
+      <c r="A9" s="76">
         <v>45839</v>
       </c>
-      <c r="B9" s="100"/>
-      <c r="C9" s="99"/>
-      <c r="D9" s="99"/>
+      <c r="B9" s="81"/>
+      <c r="C9" s="80"/>
+      <c r="D9" s="80"/>
     </row>
     <row r="10" spans="1:4" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="80">
+      <c r="A10" s="76">
         <v>45870</v>
       </c>
-      <c r="B10" s="100"/>
-      <c r="C10" s="99"/>
-      <c r="D10" s="99"/>
+      <c r="B10" s="81"/>
+      <c r="C10" s="80"/>
+      <c r="D10" s="80"/>
     </row>
     <row r="11" spans="1:4" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="80">
+      <c r="A11" s="76">
         <v>45901</v>
       </c>
-      <c r="B11" s="100"/>
-      <c r="C11" s="99"/>
-      <c r="D11" s="99"/>
+      <c r="B11" s="81"/>
+      <c r="C11" s="80"/>
+      <c r="D11" s="80"/>
     </row>
     <row r="12" spans="1:4" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="80">
+      <c r="A12" s="76">
         <v>45931</v>
       </c>
-      <c r="B12" s="100"/>
-      <c r="C12" s="99"/>
-      <c r="D12" s="99"/>
+      <c r="B12" s="81"/>
+      <c r="C12" s="80"/>
+      <c r="D12" s="80"/>
     </row>
     <row r="13" spans="1:4" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="80">
+      <c r="A13" s="76">
         <v>45962</v>
       </c>
-      <c r="B13" s="100"/>
-      <c r="C13" s="99"/>
-      <c r="D13" s="99"/>
+      <c r="B13" s="81"/>
+      <c r="C13" s="80"/>
+      <c r="D13" s="80"/>
     </row>
     <row r="14" spans="1:4" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="80">
+      <c r="A14" s="76">
         <v>45992</v>
       </c>
-      <c r="B14" s="100"/>
-      <c r="C14" s="99"/>
-      <c r="D14" s="99"/>
+      <c r="B14" s="81"/>
+      <c r="C14" s="80"/>
+      <c r="D14" s="80"/>
     </row>
     <row r="15" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="80">
+      <c r="A15" s="76">
         <v>46023</v>
       </c>
-      <c r="B15" s="100">
+      <c r="B15" s="81">
         <v>1562</v>
       </c>
-      <c r="C15" s="99">
+      <c r="C15" s="80">
         <v>8.3000000000000007</v>
       </c>
-      <c r="D15" s="99">
+      <c r="D15" s="80">
         <v>9.1229999999999993</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="80">
+      <c r="A16" s="76">
         <v>46054</v>
       </c>
-      <c r="B16" s="100">
+      <c r="B16" s="81">
         <v>1763</v>
       </c>
-      <c r="C16" s="99">
+      <c r="C16" s="80">
         <v>12.898</v>
       </c>
-      <c r="D16" s="99">
+      <c r="D16" s="80">
         <v>12.324999999999999</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="80">
+      <c r="A17" s="76">
         <v>46082</v>
       </c>
-      <c r="B17" s="100"/>
-      <c r="C17" s="99"/>
-      <c r="D17" s="99"/>
+      <c r="B17" s="81"/>
+      <c r="C17" s="80"/>
+      <c r="D17" s="80"/>
     </row>
     <row r="18" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="80">
+      <c r="A18" s="76">
         <v>46113</v>
       </c>
-      <c r="B18" s="100"/>
-      <c r="C18" s="99"/>
-      <c r="D18" s="99"/>
+      <c r="B18" s="81"/>
+      <c r="C18" s="80"/>
+      <c r="D18" s="80"/>
     </row>
     <row r="19" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="80">
+      <c r="A19" s="76">
         <v>46143</v>
       </c>
-      <c r="B19" s="100"/>
-      <c r="C19" s="99"/>
-      <c r="D19" s="99"/>
+      <c r="B19" s="81"/>
+      <c r="C19" s="80"/>
+      <c r="D19" s="80"/>
     </row>
     <row r="20" spans="1:4" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="80">
+      <c r="A20" s="76">
         <v>46174</v>
       </c>
-      <c r="B20" s="100"/>
-      <c r="C20" s="99"/>
-      <c r="D20" s="99"/>
+      <c r="B20" s="81"/>
+      <c r="C20" s="80"/>
+      <c r="D20" s="80"/>
     </row>
     <row r="21" spans="1:4" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="80">
+      <c r="A21" s="76">
         <v>46204</v>
       </c>
-      <c r="B21" s="100"/>
-      <c r="C21" s="99"/>
-      <c r="D21" s="99"/>
+      <c r="B21" s="81"/>
+      <c r="C21" s="80"/>
+      <c r="D21" s="80"/>
     </row>
     <row r="22" spans="1:4" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="80">
+      <c r="A22" s="76">
         <v>46235</v>
       </c>
-      <c r="B22" s="100"/>
-      <c r="C22" s="99"/>
-      <c r="D22" s="99"/>
+      <c r="B22" s="81"/>
+      <c r="C22" s="80"/>
+      <c r="D22" s="80"/>
     </row>
     <row r="23" spans="1:4" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="80">
+      <c r="A23" s="76">
         <v>46266</v>
       </c>
-      <c r="B23" s="100"/>
-      <c r="C23" s="99"/>
-      <c r="D23" s="99"/>
+      <c r="B23" s="81"/>
+      <c r="C23" s="80"/>
+      <c r="D23" s="80"/>
     </row>
     <row r="24" spans="1:4" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="80">
+      <c r="A24" s="76">
         <v>46296</v>
       </c>
-      <c r="B24" s="100"/>
-      <c r="C24" s="99"/>
-      <c r="D24" s="99"/>
+      <c r="B24" s="81"/>
+      <c r="C24" s="80"/>
+      <c r="D24" s="80"/>
     </row>
     <row r="25" spans="1:4" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="80">
+      <c r="A25" s="76">
         <v>46327</v>
       </c>
-      <c r="B25" s="100"/>
-      <c r="C25" s="99"/>
-      <c r="D25" s="99"/>
+      <c r="B25" s="81"/>
+      <c r="C25" s="80"/>
+      <c r="D25" s="80"/>
     </row>
     <row r="26" spans="1:4" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="80">
+      <c r="A26" s="76">
         <v>46357</v>
       </c>
-      <c r="B26" s="100"/>
-      <c r="C26" s="99"/>
-      <c r="D26" s="99"/>
+      <c r="B26" s="81"/>
+      <c r="C26" s="80"/>
+      <c r="D26" s="80"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8656,121 +9226,121 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:40" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="52" t="s">
+      <c r="A1" s="51" t="s">
         <v>75</v>
       </c>
-      <c r="B1" s="52" t="s">
+      <c r="B1" s="51" t="s">
         <v>76</v>
       </c>
-      <c r="C1" s="101">
+      <c r="C1" s="82">
         <v>45292</v>
       </c>
-      <c r="D1" s="101">
+      <c r="D1" s="82">
         <v>45323</v>
       </c>
-      <c r="E1" s="101">
+      <c r="E1" s="82">
         <v>45352</v>
       </c>
-      <c r="F1" s="101">
+      <c r="F1" s="82">
         <v>45383</v>
       </c>
-      <c r="G1" s="101">
+      <c r="G1" s="82">
         <v>45413</v>
       </c>
-      <c r="H1" s="101">
+      <c r="H1" s="82">
         <v>45444</v>
       </c>
-      <c r="I1" s="101">
+      <c r="I1" s="82">
         <v>45474</v>
       </c>
-      <c r="J1" s="101">
+      <c r="J1" s="82">
         <v>45505</v>
       </c>
-      <c r="K1" s="101">
+      <c r="K1" s="82">
         <v>45536</v>
       </c>
-      <c r="L1" s="101">
+      <c r="L1" s="82">
         <v>45566</v>
       </c>
-      <c r="M1" s="101">
+      <c r="M1" s="82">
         <v>45597</v>
       </c>
-      <c r="N1" s="101">
+      <c r="N1" s="82">
         <v>45627</v>
       </c>
-      <c r="O1" s="101">
+      <c r="O1" s="82">
         <v>45658</v>
       </c>
-      <c r="P1" s="101">
+      <c r="P1" s="82">
         <v>45689</v>
       </c>
-      <c r="Q1" s="101">
+      <c r="Q1" s="82">
         <v>45717</v>
       </c>
-      <c r="R1" s="101">
+      <c r="R1" s="82">
         <v>45748</v>
       </c>
-      <c r="S1" s="101">
+      <c r="S1" s="82">
         <v>45778</v>
       </c>
-      <c r="T1" s="101">
+      <c r="T1" s="82">
         <v>45809</v>
       </c>
-      <c r="U1" s="101">
+      <c r="U1" s="82">
         <v>45839</v>
       </c>
-      <c r="V1" s="101">
+      <c r="V1" s="82">
         <v>45870</v>
       </c>
-      <c r="W1" s="101">
+      <c r="W1" s="82">
         <v>45901</v>
       </c>
-      <c r="X1" s="101">
+      <c r="X1" s="82">
         <v>45931</v>
       </c>
-      <c r="Y1" s="101">
+      <c r="Y1" s="82">
         <v>45962</v>
       </c>
-      <c r="Z1" s="101">
+      <c r="Z1" s="82">
         <v>45992</v>
       </c>
-      <c r="AA1" s="101">
+      <c r="AA1" s="82">
         <v>46023</v>
       </c>
-      <c r="AB1" s="101">
+      <c r="AB1" s="82">
         <v>46054</v>
       </c>
-      <c r="AC1" s="101">
+      <c r="AC1" s="82">
         <v>46082</v>
       </c>
-      <c r="AD1" s="101">
+      <c r="AD1" s="82">
         <v>46113</v>
       </c>
-      <c r="AE1" s="101">
+      <c r="AE1" s="82">
         <v>46143</v>
       </c>
-      <c r="AF1" s="101">
+      <c r="AF1" s="82">
         <v>46174</v>
       </c>
-      <c r="AG1" s="101">
+      <c r="AG1" s="82">
         <v>46204</v>
       </c>
-      <c r="AH1" s="101">
+      <c r="AH1" s="82">
         <v>46235</v>
       </c>
-      <c r="AI1" s="101">
+      <c r="AI1" s="82">
         <v>46266</v>
       </c>
-      <c r="AJ1" s="101">
+      <c r="AJ1" s="82">
         <v>46296</v>
       </c>
-      <c r="AK1" s="101">
+      <c r="AK1" s="82">
         <v>46327</v>
       </c>
-      <c r="AL1" s="101">
+      <c r="AL1" s="82">
         <v>46357</v>
       </c>
-      <c r="AM1" s="52" t="s">
+      <c r="AM1" s="51" t="s">
         <v>77</v>
       </c>
     </row>
@@ -8781,119 +9351,119 @@
       <c r="B2" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="C2" s="38">
+      <c r="C2" s="37">
         <v>3.36</v>
       </c>
-      <c r="D2" s="38">
+      <c r="D2" s="37">
         <v>3.36</v>
       </c>
-      <c r="E2" s="38">
+      <c r="E2" s="37">
         <v>3.36</v>
       </c>
-      <c r="F2" s="38">
+      <c r="F2" s="37">
         <v>3.36</v>
       </c>
-      <c r="G2" s="38">
+      <c r="G2" s="37">
         <v>3.36</v>
       </c>
-      <c r="H2" s="38">
+      <c r="H2" s="37">
         <v>3.36</v>
       </c>
-      <c r="I2" s="38">
+      <c r="I2" s="37">
         <v>3.67</v>
       </c>
-      <c r="J2" s="38">
+      <c r="J2" s="37">
         <v>3.67</v>
       </c>
-      <c r="K2" s="38">
+      <c r="K2" s="37">
         <v>3.67</v>
       </c>
-      <c r="L2" s="38">
+      <c r="L2" s="37">
         <v>3.67</v>
       </c>
-      <c r="M2" s="38">
+      <c r="M2" s="37">
         <v>3.67</v>
       </c>
-      <c r="N2" s="38">
+      <c r="N2" s="37">
         <v>3.67</v>
       </c>
-      <c r="O2" s="38">
+      <c r="O2" s="37">
         <v>3.67</v>
       </c>
-      <c r="P2" s="38">
+      <c r="P2" s="37">
         <v>3.67</v>
       </c>
-      <c r="Q2" s="38">
+      <c r="Q2" s="37">
         <v>3.67</v>
       </c>
-      <c r="R2" s="38">
+      <c r="R2" s="37">
         <v>3.67</v>
       </c>
-      <c r="S2" s="38">
+      <c r="S2" s="37">
         <v>3.67</v>
       </c>
-      <c r="T2" s="38">
+      <c r="T2" s="37">
         <v>3.67</v>
       </c>
-      <c r="U2" s="38">
+      <c r="U2" s="37">
         <v>4.13</v>
       </c>
-      <c r="V2" s="38">
+      <c r="V2" s="37">
         <v>4.13</v>
       </c>
-      <c r="W2" s="38">
+      <c r="W2" s="37">
         <v>4.13</v>
       </c>
-      <c r="X2" s="38">
+      <c r="X2" s="37">
         <v>4.13</v>
       </c>
-      <c r="Y2" s="38">
+      <c r="Y2" s="37">
         <v>4.13</v>
       </c>
-      <c r="Z2" s="38">
+      <c r="Z2" s="37">
         <v>4.13</v>
       </c>
-      <c r="AA2" s="38">
+      <c r="AA2" s="37">
         <v>4.2</v>
       </c>
-      <c r="AB2" s="38">
+      <c r="AB2" s="37">
         <v>4.2</v>
       </c>
-      <c r="AC2" s="38">
+      <c r="AC2" s="37">
         <v>4.2</v>
       </c>
-      <c r="AD2" s="38">
+      <c r="AD2" s="37">
         <v>4.2</v>
       </c>
-      <c r="AE2" s="38">
+      <c r="AE2" s="37">
         <v>4.2</v>
       </c>
-      <c r="AF2" s="38">
+      <c r="AF2" s="37">
         <v>4.2</v>
       </c>
-      <c r="AG2" s="38">
+      <c r="AG2" s="37">
         <v>4.2</v>
       </c>
-      <c r="AH2" s="38">
+      <c r="AH2" s="37">
         <v>4.2</v>
       </c>
-      <c r="AI2" s="38">
+      <c r="AI2" s="37">
         <v>4.2</v>
       </c>
-      <c r="AJ2" s="38">
+      <c r="AJ2" s="37">
         <v>4.67</v>
       </c>
-      <c r="AK2" s="38">
+      <c r="AK2" s="37">
         <v>4.67</v>
       </c>
-      <c r="AL2" s="38">
+      <c r="AL2" s="37">
         <v>4.67</v>
       </c>
       <c r="AM2" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="AN2" s="107" t="s">
-        <v>152</v>
+      <c r="AN2" s="85" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="3" spans="1:40" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -8903,112 +9473,112 @@
       <c r="B3" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="C3" s="38">
+      <c r="C3" s="37">
         <v>4.71</v>
       </c>
-      <c r="D3" s="38">
+      <c r="D3" s="37">
         <v>4.71</v>
       </c>
-      <c r="E3" s="38">
+      <c r="E3" s="37">
         <v>4.71</v>
       </c>
-      <c r="F3" s="38">
+      <c r="F3" s="37">
         <v>4.71</v>
       </c>
-      <c r="G3" s="38">
+      <c r="G3" s="37">
         <v>4.71</v>
       </c>
-      <c r="H3" s="38">
+      <c r="H3" s="37">
         <v>4.71</v>
       </c>
-      <c r="I3" s="38">
+      <c r="I3" s="37">
         <v>5.12</v>
       </c>
-      <c r="J3" s="38">
+      <c r="J3" s="37">
         <v>5.12</v>
       </c>
-      <c r="K3" s="38">
+      <c r="K3" s="37">
         <v>5.12</v>
       </c>
-      <c r="L3" s="38">
+      <c r="L3" s="37">
         <v>5.12</v>
       </c>
-      <c r="M3" s="38">
+      <c r="M3" s="37">
         <v>5.12</v>
       </c>
-      <c r="N3" s="38">
+      <c r="N3" s="37">
         <v>5.12</v>
       </c>
-      <c r="O3" s="38">
+      <c r="O3" s="37">
         <v>5.12</v>
       </c>
-      <c r="P3" s="38">
+      <c r="P3" s="37">
         <v>5.12</v>
       </c>
-      <c r="Q3" s="38">
+      <c r="Q3" s="37">
         <v>5.12</v>
       </c>
-      <c r="R3" s="38">
+      <c r="R3" s="37">
         <v>5.12</v>
       </c>
-      <c r="S3" s="38">
+      <c r="S3" s="37">
         <v>5.12</v>
       </c>
-      <c r="T3" s="38">
+      <c r="T3" s="37">
         <v>5.12</v>
       </c>
-      <c r="U3" s="38">
+      <c r="U3" s="37">
         <v>5.76</v>
       </c>
-      <c r="V3" s="38">
+      <c r="V3" s="37">
         <v>5.76</v>
       </c>
-      <c r="W3" s="38">
+      <c r="W3" s="37">
         <v>5.76</v>
       </c>
-      <c r="X3" s="38">
+      <c r="X3" s="37">
         <v>5.76</v>
       </c>
-      <c r="Y3" s="38">
+      <c r="Y3" s="37">
         <v>5.76</v>
       </c>
-      <c r="Z3" s="38">
+      <c r="Z3" s="37">
         <v>5.76</v>
       </c>
-      <c r="AA3" s="38">
+      <c r="AA3" s="37">
         <v>5.72</v>
       </c>
-      <c r="AB3" s="38">
+      <c r="AB3" s="37">
         <v>5.72</v>
       </c>
-      <c r="AC3" s="38">
+      <c r="AC3" s="37">
         <v>5.72</v>
       </c>
-      <c r="AD3" s="38">
+      <c r="AD3" s="37">
         <v>5.72</v>
       </c>
-      <c r="AE3" s="38">
+      <c r="AE3" s="37">
         <v>5.72</v>
       </c>
-      <c r="AF3" s="38">
+      <c r="AF3" s="37">
         <v>5.72</v>
       </c>
-      <c r="AG3" s="38">
+      <c r="AG3" s="37">
         <v>5.72</v>
       </c>
-      <c r="AH3" s="38">
+      <c r="AH3" s="37">
         <v>5.72</v>
       </c>
-      <c r="AI3" s="38">
+      <c r="AI3" s="37">
         <v>5.72</v>
       </c>
-      <c r="AJ3" s="38">
+      <c r="AJ3" s="37">
         <v>6.48</v>
       </c>
-      <c r="AK3" s="38">
+      <c r="AK3" s="37">
         <v>6.48</v>
       </c>
-      <c r="AL3" s="38">
+      <c r="AL3" s="37">
         <v>6.48</v>
       </c>
       <c r="AM3" s="4"/>
@@ -9020,119 +9590,119 @@
       <c r="B4" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="C4" s="38">
+      <c r="C4" s="37">
         <v>51.62</v>
       </c>
-      <c r="D4" s="38">
+      <c r="D4" s="37">
         <v>51.62</v>
       </c>
-      <c r="E4" s="38">
+      <c r="E4" s="37">
         <v>51.62</v>
       </c>
-      <c r="F4" s="38">
+      <c r="F4" s="37">
         <v>51.62</v>
       </c>
-      <c r="G4" s="38">
+      <c r="G4" s="37">
         <v>51.62</v>
       </c>
-      <c r="H4" s="38">
+      <c r="H4" s="37">
         <v>51.62</v>
       </c>
-      <c r="I4" s="38">
+      <c r="I4" s="37">
         <v>56.52</v>
       </c>
-      <c r="J4" s="38">
+      <c r="J4" s="37">
         <v>56.52</v>
       </c>
-      <c r="K4" s="38">
+      <c r="K4" s="37">
         <v>56.52</v>
       </c>
-      <c r="L4" s="38">
+      <c r="L4" s="37">
         <v>56.52</v>
       </c>
-      <c r="M4" s="38">
+      <c r="M4" s="37">
         <v>56.52</v>
       </c>
-      <c r="N4" s="38">
+      <c r="N4" s="37">
         <v>56.52</v>
       </c>
-      <c r="O4" s="38">
+      <c r="O4" s="37">
         <v>56.52</v>
       </c>
-      <c r="P4" s="38">
+      <c r="P4" s="37">
         <v>56.52</v>
       </c>
-      <c r="Q4" s="38">
+      <c r="Q4" s="37">
         <v>56.52</v>
       </c>
-      <c r="R4" s="38">
+      <c r="R4" s="37">
         <v>56.52</v>
       </c>
-      <c r="S4" s="38">
+      <c r="S4" s="37">
         <v>56.52</v>
       </c>
-      <c r="T4" s="38">
+      <c r="T4" s="37">
         <v>56.52</v>
       </c>
-      <c r="U4" s="38">
+      <c r="U4" s="37">
         <v>61.94</v>
       </c>
-      <c r="V4" s="38">
+      <c r="V4" s="37">
         <v>61.94</v>
       </c>
-      <c r="W4" s="38">
+      <c r="W4" s="37">
         <v>61.94</v>
       </c>
-      <c r="X4" s="38">
+      <c r="X4" s="37">
         <v>61.94</v>
       </c>
-      <c r="Y4" s="38">
+      <c r="Y4" s="37">
         <v>61.94</v>
       </c>
-      <c r="Z4" s="38">
+      <c r="Z4" s="37">
         <v>61.94</v>
       </c>
-      <c r="AA4" s="38">
+      <c r="AA4" s="37">
         <v>62.98</v>
       </c>
-      <c r="AB4" s="38">
+      <c r="AB4" s="37">
         <v>62.98</v>
       </c>
-      <c r="AC4" s="38">
+      <c r="AC4" s="37">
         <v>62.98</v>
       </c>
-      <c r="AD4" s="38">
+      <c r="AD4" s="37">
         <v>62.98</v>
       </c>
-      <c r="AE4" s="38">
+      <c r="AE4" s="37">
         <v>62.98</v>
       </c>
-      <c r="AF4" s="38">
+      <c r="AF4" s="37">
         <v>62.98</v>
       </c>
-      <c r="AG4" s="38">
+      <c r="AG4" s="37">
         <v>62.98</v>
       </c>
-      <c r="AH4" s="38">
+      <c r="AH4" s="37">
         <v>62.98</v>
       </c>
-      <c r="AI4" s="38">
+      <c r="AI4" s="37">
         <v>62.98</v>
       </c>
-      <c r="AJ4" s="38">
+      <c r="AJ4" s="37">
         <v>69.150000000000006</v>
       </c>
-      <c r="AK4" s="38">
+      <c r="AK4" s="37">
         <v>69.150000000000006</v>
       </c>
-      <c r="AL4" s="38">
+      <c r="AL4" s="37">
         <v>69.150000000000006</v>
       </c>
       <c r="AM4" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="AN4" s="107" t="s">
-        <v>153</v>
+      <c r="AN4" s="85" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="5" spans="1:40" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -9142,112 +9712,112 @@
       <c r="B5" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="C5" s="38">
+      <c r="C5" s="37">
         <v>36.159999999999997</v>
       </c>
-      <c r="D5" s="38">
+      <c r="D5" s="37">
         <v>36.159999999999997</v>
       </c>
-      <c r="E5" s="38">
+      <c r="E5" s="37">
         <v>36.159999999999997</v>
       </c>
-      <c r="F5" s="38">
+      <c r="F5" s="37">
         <v>36.159999999999997</v>
       </c>
-      <c r="G5" s="38">
+      <c r="G5" s="37">
         <v>36.159999999999997</v>
       </c>
-      <c r="H5" s="38">
+      <c r="H5" s="37">
         <v>36.159999999999997</v>
       </c>
-      <c r="I5" s="38">
+      <c r="I5" s="37">
         <v>39.590000000000003</v>
       </c>
-      <c r="J5" s="38">
+      <c r="J5" s="37">
         <v>39.590000000000003</v>
       </c>
-      <c r="K5" s="38">
+      <c r="K5" s="37">
         <v>39.590000000000003</v>
       </c>
-      <c r="L5" s="38">
+      <c r="L5" s="37">
         <v>39.590000000000003</v>
       </c>
-      <c r="M5" s="38">
+      <c r="M5" s="37">
         <v>39.590000000000003</v>
       </c>
-      <c r="N5" s="38">
+      <c r="N5" s="37">
         <v>39.590000000000003</v>
       </c>
-      <c r="O5" s="38">
+      <c r="O5" s="37">
         <v>39.590000000000003</v>
       </c>
-      <c r="P5" s="38">
+      <c r="P5" s="37">
         <v>39.590000000000003</v>
       </c>
-      <c r="Q5" s="38">
+      <c r="Q5" s="37">
         <v>39.590000000000003</v>
       </c>
-      <c r="R5" s="38">
+      <c r="R5" s="37">
         <v>39.590000000000003</v>
       </c>
-      <c r="S5" s="38">
+      <c r="S5" s="37">
         <v>39.590000000000003</v>
       </c>
-      <c r="T5" s="38">
+      <c r="T5" s="37">
         <v>39.590000000000003</v>
       </c>
-      <c r="U5" s="38">
+      <c r="U5" s="37">
         <v>43.39</v>
       </c>
-      <c r="V5" s="38">
+      <c r="V5" s="37">
         <v>43.39</v>
       </c>
-      <c r="W5" s="38">
+      <c r="W5" s="37">
         <v>43.39</v>
       </c>
-      <c r="X5" s="38">
+      <c r="X5" s="37">
         <v>43.39</v>
       </c>
-      <c r="Y5" s="38">
+      <c r="Y5" s="37">
         <v>43.39</v>
       </c>
-      <c r="Z5" s="38">
+      <c r="Z5" s="37">
         <v>43.39</v>
       </c>
-      <c r="AA5" s="38">
+      <c r="AA5" s="37">
         <v>44.12</v>
       </c>
-      <c r="AB5" s="38">
+      <c r="AB5" s="37">
         <v>44.12</v>
       </c>
-      <c r="AC5" s="38">
+      <c r="AC5" s="37">
         <v>44.12</v>
       </c>
-      <c r="AD5" s="38">
+      <c r="AD5" s="37">
         <v>44.12</v>
       </c>
-      <c r="AE5" s="38">
+      <c r="AE5" s="37">
         <v>44.12</v>
       </c>
-      <c r="AF5" s="38">
+      <c r="AF5" s="37">
         <v>44.12</v>
       </c>
-      <c r="AG5" s="38">
+      <c r="AG5" s="37">
         <v>44.12</v>
       </c>
-      <c r="AH5" s="38">
+      <c r="AH5" s="37">
         <v>44.12</v>
       </c>
-      <c r="AI5" s="38">
+      <c r="AI5" s="37">
         <v>44.12</v>
       </c>
-      <c r="AJ5" s="38">
+      <c r="AJ5" s="37">
         <v>48.43</v>
       </c>
-      <c r="AK5" s="38">
+      <c r="AK5" s="37">
         <v>48.43</v>
       </c>
-      <c r="AL5" s="38">
+      <c r="AL5" s="37">
         <v>48.43</v>
       </c>
       <c r="AM5" s="4" t="s">
@@ -9261,112 +9831,112 @@
       <c r="B6" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="C6" s="38">
+      <c r="C6" s="37">
         <v>184.96</v>
       </c>
-      <c r="D6" s="38">
+      <c r="D6" s="37">
         <v>184.96</v>
       </c>
-      <c r="E6" s="38">
+      <c r="E6" s="37">
         <v>184.96</v>
       </c>
-      <c r="F6" s="38">
+      <c r="F6" s="37">
         <v>184.96</v>
       </c>
-      <c r="G6" s="38">
+      <c r="G6" s="37">
         <v>184.96</v>
       </c>
-      <c r="H6" s="38">
+      <c r="H6" s="37">
         <v>184.96</v>
       </c>
-      <c r="I6" s="38">
+      <c r="I6" s="37">
         <v>202.53</v>
       </c>
-      <c r="J6" s="38">
+      <c r="J6" s="37">
         <v>202.53</v>
       </c>
-      <c r="K6" s="38">
+      <c r="K6" s="37">
         <v>202.53</v>
       </c>
-      <c r="L6" s="38">
+      <c r="L6" s="37">
         <v>202.53</v>
       </c>
-      <c r="M6" s="38">
+      <c r="M6" s="37">
         <v>202.53</v>
       </c>
-      <c r="N6" s="38">
+      <c r="N6" s="37">
         <v>202.53</v>
       </c>
-      <c r="O6" s="38">
+      <c r="O6" s="37">
         <v>202.53</v>
       </c>
-      <c r="P6" s="38">
+      <c r="P6" s="37">
         <v>202.53</v>
       </c>
-      <c r="Q6" s="38">
+      <c r="Q6" s="37">
         <v>202.53</v>
       </c>
-      <c r="R6" s="38">
+      <c r="R6" s="37">
         <v>202.53</v>
       </c>
-      <c r="S6" s="38">
+      <c r="S6" s="37">
         <v>202.53</v>
       </c>
-      <c r="T6" s="38">
+      <c r="T6" s="37">
         <v>202.53</v>
       </c>
-      <c r="U6" s="38">
+      <c r="U6" s="37">
         <v>202.53</v>
       </c>
-      <c r="V6" s="38">
+      <c r="V6" s="37">
         <v>202.53</v>
       </c>
-      <c r="W6" s="38">
+      <c r="W6" s="37">
         <v>202.53</v>
       </c>
-      <c r="X6" s="38">
+      <c r="X6" s="37">
         <v>202.53</v>
       </c>
-      <c r="Y6" s="38">
+      <c r="Y6" s="37">
         <v>202.53</v>
       </c>
-      <c r="Z6" s="38">
+      <c r="Z6" s="37">
         <v>202.53</v>
       </c>
-      <c r="AA6" s="38">
+      <c r="AA6" s="37">
         <v>227.18</v>
       </c>
-      <c r="AB6" s="38">
+      <c r="AB6" s="37">
         <v>227.18</v>
       </c>
-      <c r="AC6" s="38">
+      <c r="AC6" s="37">
         <v>227.18</v>
       </c>
-      <c r="AD6" s="38">
+      <c r="AD6" s="37">
         <v>227.18</v>
       </c>
-      <c r="AE6" s="38">
+      <c r="AE6" s="37">
         <v>227.18</v>
       </c>
-      <c r="AF6" s="38">
+      <c r="AF6" s="37">
         <v>227.18</v>
       </c>
-      <c r="AG6" s="38">
+      <c r="AG6" s="37">
         <v>227.18</v>
       </c>
-      <c r="AH6" s="38">
+      <c r="AH6" s="37">
         <v>227.18</v>
       </c>
-      <c r="AI6" s="38">
+      <c r="AI6" s="37">
         <v>227.18</v>
       </c>
-      <c r="AJ6" s="38">
+      <c r="AJ6" s="37">
         <v>227.18</v>
       </c>
-      <c r="AK6" s="38">
+      <c r="AK6" s="37">
         <v>227.18</v>
       </c>
-      <c r="AL6" s="38">
+      <c r="AL6" s="37">
         <v>227.18</v>
       </c>
       <c r="AM6" s="4" t="s">
@@ -9380,102 +9950,102 @@
       <c r="B7" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="C7" s="38">
+      <c r="C7" s="37">
         <v>2889.93</v>
       </c>
-      <c r="D7" s="38">
+      <c r="D7" s="37">
         <v>2889.93</v>
       </c>
-      <c r="E7" s="38">
+      <c r="E7" s="37">
         <v>2889.93</v>
       </c>
-      <c r="F7" s="38">
+      <c r="F7" s="37">
         <v>2889.93</v>
       </c>
-      <c r="G7" s="38">
+      <c r="G7" s="37">
         <v>2889.93</v>
       </c>
-      <c r="H7" s="38">
+      <c r="H7" s="37">
         <v>2889.93</v>
       </c>
-      <c r="I7" s="38">
+      <c r="I7" s="37">
         <v>3164.47</v>
       </c>
-      <c r="J7" s="38">
+      <c r="J7" s="37">
         <v>3164.47</v>
       </c>
-      <c r="K7" s="38">
+      <c r="K7" s="37">
         <v>3164.47</v>
       </c>
-      <c r="L7" s="38">
+      <c r="L7" s="37">
         <v>3164.47</v>
       </c>
-      <c r="M7" s="38">
+      <c r="M7" s="37">
         <v>3164.47</v>
       </c>
-      <c r="N7" s="38">
+      <c r="N7" s="37">
         <v>3164.47</v>
       </c>
-      <c r="O7" s="38">
+      <c r="O7" s="37">
         <v>3164.47</v>
       </c>
-      <c r="P7" s="38">
+      <c r="P7" s="37">
         <v>3164.47</v>
       </c>
-      <c r="Q7" s="38">
+      <c r="Q7" s="37">
         <v>3164.47</v>
       </c>
-      <c r="R7" s="38">
+      <c r="R7" s="37">
         <v>3164.47</v>
       </c>
-      <c r="S7" s="38">
+      <c r="S7" s="37">
         <v>3164.47</v>
       </c>
-      <c r="T7" s="38">
+      <c r="T7" s="37">
         <v>3164.47</v>
       </c>
-      <c r="U7" s="38">
+      <c r="U7" s="37">
         <v>3164.47</v>
       </c>
-      <c r="V7" s="38">
+      <c r="V7" s="37">
         <v>3164.47</v>
       </c>
-      <c r="W7" s="38">
+      <c r="W7" s="37">
         <v>3164.47</v>
       </c>
-      <c r="X7" s="38">
+      <c r="X7" s="37">
         <v>3164.47</v>
       </c>
-      <c r="Y7" s="38">
+      <c r="Y7" s="37">
         <v>3164.47</v>
       </c>
-      <c r="Z7" s="38">
+      <c r="Z7" s="37">
         <v>3164.47</v>
       </c>
-      <c r="AA7" s="38">
+      <c r="AA7" s="37">
         <v>3549.74</v>
       </c>
-      <c r="AB7" s="38">
+      <c r="AB7" s="37">
         <v>3549.74</v>
       </c>
-      <c r="AC7" s="38">
+      <c r="AC7" s="37">
         <v>3549.74</v>
       </c>
-      <c r="AD7" s="38">
+      <c r="AD7" s="37">
         <v>3549.74</v>
       </c>
-      <c r="AE7" s="38"/>
-      <c r="AF7" s="38"/>
-      <c r="AG7" s="38"/>
-      <c r="AH7" s="38"/>
-      <c r="AI7" s="38"/>
-      <c r="AJ7" s="38">
+      <c r="AE7" s="37"/>
+      <c r="AF7" s="37"/>
+      <c r="AG7" s="37"/>
+      <c r="AH7" s="37"/>
+      <c r="AI7" s="37"/>
+      <c r="AJ7" s="37">
         <v>3549.74</v>
       </c>
-      <c r="AK7" s="38">
+      <c r="AK7" s="37">
         <v>3549.74</v>
       </c>
-      <c r="AL7" s="38">
+      <c r="AL7" s="37">
         <v>3549.74</v>
       </c>
       <c r="AM7" s="4" t="s">
@@ -9489,112 +10059,112 @@
       <c r="B8" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="C8" s="38">
+      <c r="C8" s="37">
         <v>9.81</v>
       </c>
-      <c r="D8" s="38">
+      <c r="D8" s="37">
         <v>10.08</v>
       </c>
-      <c r="E8" s="38">
+      <c r="E8" s="37">
         <v>10.55</v>
       </c>
-      <c r="F8" s="38">
+      <c r="F8" s="37">
         <v>10.55</v>
       </c>
-      <c r="G8" s="38">
+      <c r="G8" s="37">
         <v>10.55</v>
       </c>
-      <c r="H8" s="38">
+      <c r="H8" s="37">
         <v>10.55</v>
       </c>
-      <c r="I8" s="38">
+      <c r="I8" s="37">
         <v>10.55</v>
       </c>
-      <c r="J8" s="38">
+      <c r="J8" s="37">
         <v>10.55</v>
       </c>
-      <c r="K8" s="38">
+      <c r="K8" s="37">
         <v>10.55</v>
       </c>
-      <c r="L8" s="38">
+      <c r="L8" s="37">
         <v>10.55</v>
       </c>
-      <c r="M8" s="38">
+      <c r="M8" s="37">
         <v>10.55</v>
       </c>
-      <c r="N8" s="38">
+      <c r="N8" s="37">
         <v>10.55</v>
       </c>
-      <c r="O8" s="38">
+      <c r="O8" s="37">
         <v>11.08</v>
       </c>
-      <c r="P8" s="38">
+      <c r="P8" s="37">
         <v>11.08</v>
       </c>
-      <c r="Q8" s="38">
+      <c r="Q8" s="37">
         <v>11.08</v>
       </c>
-      <c r="R8" s="38">
+      <c r="R8" s="37">
         <v>11.08</v>
       </c>
-      <c r="S8" s="38">
+      <c r="S8" s="37">
         <v>11.08</v>
       </c>
-      <c r="T8" s="38">
+      <c r="T8" s="37">
         <v>11.08</v>
       </c>
-      <c r="U8" s="38">
+      <c r="U8" s="37">
         <v>11.08</v>
       </c>
-      <c r="V8" s="38">
+      <c r="V8" s="37">
         <v>11.08</v>
       </c>
-      <c r="W8" s="38">
+      <c r="W8" s="37">
         <v>11.08</v>
       </c>
-      <c r="X8" s="38">
+      <c r="X8" s="37">
         <v>11.08</v>
       </c>
-      <c r="Y8" s="38">
+      <c r="Y8" s="37">
         <v>11.08</v>
       </c>
-      <c r="Z8" s="38">
+      <c r="Z8" s="37">
         <v>11.08</v>
       </c>
-      <c r="AA8" s="38">
+      <c r="AA8" s="37">
         <v>11.08</v>
       </c>
-      <c r="AB8" s="38">
+      <c r="AB8" s="37">
         <v>11.08</v>
       </c>
-      <c r="AC8" s="38">
+      <c r="AC8" s="37">
         <v>11.08</v>
       </c>
-      <c r="AD8" s="38">
+      <c r="AD8" s="37">
         <v>11.08</v>
       </c>
-      <c r="AE8" s="38">
+      <c r="AE8" s="37">
         <v>11.08</v>
       </c>
-      <c r="AF8" s="38">
+      <c r="AF8" s="37">
         <v>11.08</v>
       </c>
-      <c r="AG8" s="38">
+      <c r="AG8" s="37">
         <v>11.08</v>
       </c>
-      <c r="AH8" s="38">
+      <c r="AH8" s="37">
         <v>11.08</v>
       </c>
-      <c r="AI8" s="38">
+      <c r="AI8" s="37">
         <v>11.08</v>
       </c>
-      <c r="AJ8" s="38">
+      <c r="AJ8" s="37">
         <v>11.08</v>
       </c>
-      <c r="AK8" s="38">
+      <c r="AK8" s="37">
         <v>11.08</v>
       </c>
-      <c r="AL8" s="38">
+      <c r="AL8" s="37">
         <v>11.08</v>
       </c>
       <c r="AM8" s="4" t="s">
@@ -9608,112 +10178,112 @@
       <c r="B9" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="C9" s="38">
+      <c r="C9" s="37">
         <v>5.44</v>
       </c>
-      <c r="D9" s="38">
+      <c r="D9" s="37">
         <v>5.44</v>
       </c>
-      <c r="E9" s="38">
+      <c r="E9" s="37">
         <v>5.7</v>
       </c>
-      <c r="F9" s="38">
+      <c r="F9" s="37">
         <v>5.7</v>
       </c>
-      <c r="G9" s="38">
+      <c r="G9" s="37">
         <v>5.7</v>
       </c>
-      <c r="H9" s="38">
+      <c r="H9" s="37">
         <v>5.7</v>
       </c>
-      <c r="I9" s="38">
+      <c r="I9" s="37">
         <v>5.7</v>
       </c>
-      <c r="J9" s="38">
+      <c r="J9" s="37">
         <v>5.7</v>
       </c>
-      <c r="K9" s="38">
+      <c r="K9" s="37">
         <v>5.7</v>
       </c>
-      <c r="L9" s="38">
+      <c r="L9" s="37">
         <v>5.7</v>
       </c>
-      <c r="M9" s="38">
+      <c r="M9" s="37">
         <v>5.7</v>
       </c>
-      <c r="N9" s="38">
+      <c r="N9" s="37">
         <v>5.7</v>
       </c>
-      <c r="O9" s="38">
+      <c r="O9" s="37">
         <v>5.98</v>
       </c>
-      <c r="P9" s="38">
+      <c r="P9" s="37">
         <v>5.98</v>
       </c>
-      <c r="Q9" s="38">
+      <c r="Q9" s="37">
         <v>5.98</v>
       </c>
-      <c r="R9" s="38">
+      <c r="R9" s="37">
         <v>5.98</v>
       </c>
-      <c r="S9" s="38">
+      <c r="S9" s="37">
         <v>5.98</v>
       </c>
-      <c r="T9" s="38">
+      <c r="T9" s="37">
         <v>5.98</v>
       </c>
-      <c r="U9" s="38">
+      <c r="U9" s="37">
         <v>5.98</v>
       </c>
-      <c r="V9" s="38">
+      <c r="V9" s="37">
         <v>5.98</v>
       </c>
-      <c r="W9" s="38">
+      <c r="W9" s="37">
         <v>5.98</v>
       </c>
-      <c r="X9" s="38">
+      <c r="X9" s="37">
         <v>5.98</v>
       </c>
-      <c r="Y9" s="38">
+      <c r="Y9" s="37">
         <v>5.98</v>
       </c>
-      <c r="Z9" s="38">
+      <c r="Z9" s="37">
         <v>5.98</v>
       </c>
-      <c r="AA9" s="38">
+      <c r="AA9" s="37">
         <v>5.98</v>
       </c>
-      <c r="AB9" s="38">
+      <c r="AB9" s="37">
         <v>5.98</v>
       </c>
-      <c r="AC9" s="38">
+      <c r="AC9" s="37">
         <v>5.98</v>
       </c>
-      <c r="AD9" s="38">
+      <c r="AD9" s="37">
         <v>5.98</v>
       </c>
-      <c r="AE9" s="38">
+      <c r="AE9" s="37">
         <v>5.98</v>
       </c>
-      <c r="AF9" s="38">
+      <c r="AF9" s="37">
         <v>5.98</v>
       </c>
-      <c r="AG9" s="38">
+      <c r="AG9" s="37">
         <v>5.98</v>
       </c>
-      <c r="AH9" s="38">
+      <c r="AH9" s="37">
         <v>5.98</v>
       </c>
-      <c r="AI9" s="38">
+      <c r="AI9" s="37">
         <v>5.98</v>
       </c>
-      <c r="AJ9" s="38">
+      <c r="AJ9" s="37">
         <v>5.98</v>
       </c>
-      <c r="AK9" s="38">
+      <c r="AK9" s="37">
         <v>5.98</v>
       </c>
-      <c r="AL9" s="38">
+      <c r="AL9" s="37">
         <v>5.98</v>
       </c>
       <c r="AM9" s="4" t="s">
@@ -9727,155 +10297,155 @@
       <c r="B10" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="C10" s="38">
+      <c r="C10" s="37">
         <f>$C$38</f>
         <v>132.34105224799995</v>
       </c>
-      <c r="D10" s="38">
+      <c r="D10" s="37">
         <f t="shared" ref="D10:H10" si="0">$C$38</f>
         <v>132.34105224799995</v>
       </c>
-      <c r="E10" s="38">
+      <c r="E10" s="37">
         <f t="shared" si="0"/>
         <v>132.34105224799995</v>
       </c>
-      <c r="F10" s="38">
+      <c r="F10" s="37">
         <f t="shared" si="0"/>
         <v>132.34105224799995</v>
       </c>
-      <c r="G10" s="38">
+      <c r="G10" s="37">
         <f t="shared" si="0"/>
         <v>132.34105224799995</v>
       </c>
-      <c r="H10" s="38">
+      <c r="H10" s="37">
         <f t="shared" si="0"/>
         <v>132.34105224799995</v>
       </c>
-      <c r="I10" s="38">
+      <c r="I10" s="37">
         <f>$I$38</f>
         <v>144.91470621139999</v>
       </c>
-      <c r="J10" s="38">
+      <c r="J10" s="37">
         <f t="shared" ref="J10:N10" si="1">$I$38</f>
         <v>144.91470621139999</v>
       </c>
-      <c r="K10" s="38">
+      <c r="K10" s="37">
         <f t="shared" si="1"/>
         <v>144.91470621139999</v>
       </c>
-      <c r="L10" s="38">
+      <c r="L10" s="37">
         <f t="shared" si="1"/>
         <v>144.91470621139999</v>
       </c>
-      <c r="M10" s="38">
+      <c r="M10" s="37">
         <f t="shared" si="1"/>
         <v>144.91470621139999</v>
       </c>
-      <c r="N10" s="38">
+      <c r="N10" s="37">
         <f t="shared" si="1"/>
         <v>144.91470621139999</v>
       </c>
-      <c r="O10" s="38">
+      <c r="O10" s="37">
         <f>$O$38</f>
         <v>171.78310199199996</v>
       </c>
-      <c r="P10" s="38">
+      <c r="P10" s="37">
         <f t="shared" ref="P10:T10" si="2">$O$38</f>
         <v>171.78310199199996</v>
       </c>
-      <c r="Q10" s="38">
+      <c r="Q10" s="37">
         <f t="shared" si="2"/>
         <v>171.78310199199996</v>
       </c>
-      <c r="R10" s="38">
+      <c r="R10" s="37">
         <f t="shared" si="2"/>
         <v>171.78310199199996</v>
       </c>
-      <c r="S10" s="38">
+      <c r="S10" s="37">
         <f t="shared" si="2"/>
         <v>171.78310199199996</v>
       </c>
-      <c r="T10" s="38">
+      <c r="T10" s="37">
         <f t="shared" si="2"/>
         <v>171.78310199199996</v>
       </c>
-      <c r="U10" s="38">
+      <c r="U10" s="37">
         <f>$U$38</f>
         <v>158.82299893999999</v>
       </c>
-      <c r="V10" s="38">
+      <c r="V10" s="37">
         <f t="shared" ref="V10:Z10" si="3">$U$38</f>
         <v>158.82299893999999</v>
       </c>
-      <c r="W10" s="38">
+      <c r="W10" s="37">
         <f t="shared" si="3"/>
         <v>158.82299893999999</v>
       </c>
-      <c r="X10" s="38">
+      <c r="X10" s="37">
         <f t="shared" si="3"/>
         <v>158.82299893999999</v>
       </c>
-      <c r="Y10" s="38">
+      <c r="Y10" s="37">
         <f t="shared" si="3"/>
         <v>158.82299893999999</v>
       </c>
-      <c r="Z10" s="38">
+      <c r="Z10" s="37">
         <f t="shared" si="3"/>
         <v>158.82299893999999</v>
       </c>
-      <c r="AA10" s="38">
+      <c r="AA10" s="37">
         <f>$AA$38</f>
         <v>161.52257251624999</v>
       </c>
-      <c r="AB10" s="38">
+      <c r="AB10" s="37">
         <f t="shared" ref="AB10:AF10" si="4">$AA$38</f>
         <v>161.52257251624999</v>
       </c>
-      <c r="AC10" s="38">
+      <c r="AC10" s="37">
         <f t="shared" si="4"/>
         <v>161.52257251624999</v>
       </c>
-      <c r="AD10" s="38">
+      <c r="AD10" s="37">
         <f t="shared" si="4"/>
         <v>161.52257251624999</v>
       </c>
-      <c r="AE10" s="38">
+      <c r="AE10" s="37">
         <f t="shared" si="4"/>
         <v>161.52257251624999</v>
       </c>
-      <c r="AF10" s="38">
+      <c r="AF10" s="37">
         <f t="shared" si="4"/>
         <v>161.52257251624999</v>
       </c>
-      <c r="AG10" s="38">
+      <c r="AG10" s="37">
         <f>$AG$38</f>
         <v>161.52257251624999</v>
       </c>
-      <c r="AH10" s="38">
+      <c r="AH10" s="37">
         <f t="shared" ref="AH10:AL10" si="5">$AG$38</f>
         <v>161.52257251624999</v>
       </c>
-      <c r="AI10" s="38">
+      <c r="AI10" s="37">
         <f t="shared" si="5"/>
         <v>161.52257251624999</v>
       </c>
-      <c r="AJ10" s="38">
+      <c r="AJ10" s="37">
         <f t="shared" si="5"/>
         <v>161.52257251624999</v>
       </c>
-      <c r="AK10" s="38">
+      <c r="AK10" s="37">
         <f t="shared" si="5"/>
         <v>161.52257251624999</v>
       </c>
-      <c r="AL10" s="38">
+      <c r="AL10" s="37">
         <f t="shared" si="5"/>
         <v>161.52257251624999</v>
       </c>
       <c r="AM10" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="AN10" s="107" t="s">
-        <v>154</v>
+      <c r="AN10" s="85" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="11" spans="1:40" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -9885,119 +10455,119 @@
       <c r="B11" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="C11" s="38">
+      <c r="C11" s="37">
         <v>12.61</v>
       </c>
-      <c r="D11" s="38">
+      <c r="D11" s="37">
         <v>12.61</v>
       </c>
-      <c r="E11" s="38">
+      <c r="E11" s="37">
         <v>12.61</v>
       </c>
-      <c r="F11" s="38">
+      <c r="F11" s="37">
         <v>12.61</v>
       </c>
-      <c r="G11" s="38">
+      <c r="G11" s="37">
         <v>12.61</v>
       </c>
-      <c r="H11" s="38">
+      <c r="H11" s="37">
         <v>12.61</v>
       </c>
-      <c r="I11" s="38">
+      <c r="I11" s="37">
         <v>12.61</v>
       </c>
-      <c r="J11" s="38">
+      <c r="J11" s="37">
         <v>14.08</v>
       </c>
-      <c r="K11" s="38">
+      <c r="K11" s="37">
         <v>14.08</v>
       </c>
-      <c r="L11" s="38">
+      <c r="L11" s="37">
         <v>14.08</v>
       </c>
-      <c r="M11" s="38">
+      <c r="M11" s="37">
         <v>14.08</v>
       </c>
-      <c r="N11" s="38">
+      <c r="N11" s="37">
         <v>14.08</v>
       </c>
-      <c r="O11" s="38">
+      <c r="O11" s="37">
         <v>14.08</v>
       </c>
-      <c r="P11" s="38">
+      <c r="P11" s="37">
         <v>14.08</v>
       </c>
-      <c r="Q11" s="38">
+      <c r="Q11" s="37">
         <v>14.08</v>
       </c>
-      <c r="R11" s="38">
+      <c r="R11" s="37">
         <v>14.08</v>
       </c>
-      <c r="S11" s="38">
+      <c r="S11" s="37">
         <v>14.08</v>
       </c>
-      <c r="T11" s="38">
+      <c r="T11" s="37">
         <v>14.08</v>
       </c>
-      <c r="U11" s="38">
+      <c r="U11" s="37">
         <v>14.08</v>
       </c>
-      <c r="V11" s="38">
+      <c r="V11" s="37">
         <v>14.08</v>
       </c>
-      <c r="W11" s="38">
+      <c r="W11" s="37">
         <v>14.08</v>
       </c>
-      <c r="X11" s="38">
+      <c r="X11" s="37">
         <v>14.08</v>
       </c>
-      <c r="Y11" s="38">
+      <c r="Y11" s="37">
         <v>14.08</v>
       </c>
-      <c r="Z11" s="38">
+      <c r="Z11" s="37">
         <v>15.15</v>
       </c>
-      <c r="AA11" s="38">
+      <c r="AA11" s="37">
         <v>15.15</v>
       </c>
-      <c r="AB11" s="38">
+      <c r="AB11" s="37">
         <v>15.15</v>
       </c>
-      <c r="AC11" s="38">
+      <c r="AC11" s="37">
         <v>15.15</v>
       </c>
-      <c r="AD11" s="38">
+      <c r="AD11" s="37">
         <v>15.15</v>
       </c>
-      <c r="AE11" s="38">
+      <c r="AE11" s="37">
         <v>15.15</v>
       </c>
-      <c r="AF11" s="38">
+      <c r="AF11" s="37">
         <v>15.15</v>
       </c>
-      <c r="AG11" s="38">
+      <c r="AG11" s="37">
         <v>15.15</v>
       </c>
-      <c r="AH11" s="38">
+      <c r="AH11" s="37">
         <v>15.15</v>
       </c>
-      <c r="AI11" s="38">
+      <c r="AI11" s="37">
         <v>15.15</v>
       </c>
-      <c r="AJ11" s="38">
+      <c r="AJ11" s="37">
         <v>15.15</v>
       </c>
-      <c r="AK11" s="38">
+      <c r="AK11" s="37">
         <v>15.15</v>
       </c>
-      <c r="AL11" s="38">
+      <c r="AL11" s="37">
         <v>15.15</v>
       </c>
       <c r="AM11" s="4" t="s">
-        <v>156</v>
-      </c>
-      <c r="AN11" s="107" t="s">
-        <v>155</v>
+        <v>152</v>
+      </c>
+      <c r="AN11" s="85" t="s">
+        <v>151</v>
       </c>
     </row>
     <row r="12" spans="1:40" x14ac:dyDescent="0.35">
@@ -10168,7 +10738,7 @@
     </row>
     <row r="17" spans="1:39" x14ac:dyDescent="0.35">
       <c r="A17" s="11" t="s">
-        <v>157</v>
+        <v>129</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>46</v>
@@ -10437,12 +11007,12 @@
         <v>16.2</v>
       </c>
       <c r="AM18" s="3" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="19" spans="1:39" ht="29" x14ac:dyDescent="0.35">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="19" spans="1:39" x14ac:dyDescent="0.35">
       <c r="A19" s="11" t="s">
-        <v>158</v>
+        <v>128</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>45</v>
@@ -10597,7 +11167,7 @@
     </row>
     <row r="20" spans="1:39" x14ac:dyDescent="0.35">
       <c r="A20" s="11" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>46</v>
@@ -10752,7 +11322,7 @@
     </row>
     <row r="21" spans="1:39" x14ac:dyDescent="0.35">
       <c r="A21" s="11" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>46</v>
@@ -10932,7 +11502,7 @@
       <c r="B25" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="C25" s="68">
+      <c r="C25" s="67">
         <f>info!$B$6</f>
         <v>2</v>
       </c>
@@ -11073,10 +11643,10 @@
         <v>104</v>
       </c>
       <c r="AA34" s="3" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="AG34" s="3" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
     </row>
     <row r="35" spans="1:33" x14ac:dyDescent="0.35">
@@ -11161,27 +11731,27 @@
       <c r="B38" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="C38" s="111">
+      <c r="C38" s="86">
         <f>C37*C36*C35/12</f>
         <v>132.34105224799995</v>
       </c>
-      <c r="I38" s="111">
+      <c r="I38" s="86">
         <f>I37*I36*I35/12</f>
         <v>144.91470621139999</v>
       </c>
-      <c r="O38" s="111">
+      <c r="O38" s="86">
         <f>O37*O36*O35/12</f>
         <v>171.78310199199996</v>
       </c>
-      <c r="U38" s="111">
+      <c r="U38" s="86">
         <f>U37*U36*U35/12</f>
         <v>158.82299893999999</v>
       </c>
-      <c r="AA38" s="111">
+      <c r="AA38" s="86">
         <f t="shared" ref="AA38:AB38" si="6">AA37*AA36*AA35/12</f>
         <v>161.52257251624999</v>
       </c>
-      <c r="AG38" s="111">
+      <c r="AG38" s="86">
         <f>AG37*AG36*AG35/12</f>
         <v>161.52257251624999</v>
       </c>
@@ -11240,14 +11810,14 @@
     <col min="12" max="12" width="11" style="17" customWidth="1"/>
     <col min="13" max="13" width="13.54296875" style="17" customWidth="1"/>
     <col min="14" max="14" width="12.08984375" style="17" customWidth="1"/>
-    <col min="15" max="15" width="12.08984375" style="67" customWidth="1"/>
+    <col min="15" max="15" width="12.08984375" style="66" customWidth="1"/>
     <col min="16" max="17" width="11.08984375" style="17" customWidth="1"/>
     <col min="18" max="18" width="9.1796875" style="17"/>
     <col min="19" max="19" width="10.7265625" style="17" customWidth="1"/>
     <col min="20" max="16384" width="9.1796875" style="17"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" s="53" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:20" s="52" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="16" t="s">
         <v>59</v>
       </c>
@@ -11290,7 +11860,7 @@
       <c r="N1" s="16" t="s">
         <v>72</v>
       </c>
-      <c r="O1" s="65" t="s">
+      <c r="O1" s="64" t="s">
         <v>73</v>
       </c>
       <c r="P1" s="16" t="s">
@@ -11299,34 +11869,34 @@
       <c r="Q1" s="16" t="s">
         <v>122</v>
       </c>
-      <c r="R1" s="53" t="s">
+      <c r="R1" s="52" t="s">
         <v>58</v>
       </c>
-      <c r="S1" s="53" t="s">
+      <c r="S1" s="52" t="s">
         <v>74</v>
       </c>
-      <c r="T1" s="53" t="s">
+      <c r="T1" s="52" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A2" s="15"/>
       <c r="B2" s="18"/>
-      <c r="C2" s="43"/>
-      <c r="D2" s="43"/>
-      <c r="E2" s="43"/>
-      <c r="F2" s="43"/>
-      <c r="G2" s="44"/>
-      <c r="H2" s="43"/>
-      <c r="I2" s="43"/>
-      <c r="J2" s="43"/>
-      <c r="K2" s="43"/>
+      <c r="C2" s="42"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="42"/>
+      <c r="F2" s="42"/>
+      <c r="G2" s="43"/>
+      <c r="H2" s="42"/>
+      <c r="I2" s="42"/>
+      <c r="J2" s="42"/>
+      <c r="K2" s="42"/>
       <c r="L2" s="15"/>
       <c r="M2" s="19"/>
       <c r="N2" s="18"/>
-      <c r="O2" s="66"/>
-      <c r="P2" s="43"/>
-      <c r="Q2" s="43"/>
+      <c r="O2" s="65"/>
+      <c r="P2" s="42"/>
+      <c r="Q2" s="42"/>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A3" s="15"/>
@@ -11343,7 +11913,7 @@
       <c r="L3" s="15"/>
       <c r="M3" s="19"/>
       <c r="N3" s="18"/>
-      <c r="O3" s="66"/>
+      <c r="O3" s="65"/>
       <c r="P3" s="15"/>
       <c r="Q3" s="15"/>
     </row>
@@ -11362,7 +11932,7 @@
       <c r="L4" s="15"/>
       <c r="M4" s="19"/>
       <c r="N4" s="18"/>
-      <c r="O4" s="66"/>
+      <c r="O4" s="65"/>
       <c r="P4" s="15"/>
       <c r="Q4" s="15"/>
     </row>
@@ -11381,7 +11951,7 @@
       <c r="L5" s="15"/>
       <c r="M5" s="19"/>
       <c r="N5" s="18"/>
-      <c r="O5" s="66"/>
+      <c r="O5" s="65"/>
       <c r="P5" s="15"/>
       <c r="Q5" s="15"/>
     </row>
@@ -11400,7 +11970,7 @@
       <c r="L6" s="15"/>
       <c r="M6" s="19"/>
       <c r="N6" s="18"/>
-      <c r="O6" s="66"/>
+      <c r="O6" s="65"/>
       <c r="P6" s="15"/>
       <c r="Q6" s="15"/>
     </row>
@@ -11419,7 +11989,7 @@
       <c r="L7" s="15"/>
       <c r="M7" s="19"/>
       <c r="N7" s="18"/>
-      <c r="O7" s="66"/>
+      <c r="O7" s="65"/>
       <c r="P7" s="15"/>
       <c r="Q7" s="15"/>
     </row>
@@ -11438,7 +12008,7 @@
       <c r="L8" s="15"/>
       <c r="M8" s="19"/>
       <c r="N8" s="18"/>
-      <c r="O8" s="66"/>
+      <c r="O8" s="65"/>
       <c r="P8" s="15"/>
       <c r="Q8" s="15"/>
     </row>
@@ -11457,7 +12027,7 @@
       <c r="L9" s="15"/>
       <c r="M9" s="19"/>
       <c r="N9" s="18"/>
-      <c r="O9" s="66"/>
+      <c r="O9" s="65"/>
       <c r="P9" s="15"/>
       <c r="Q9" s="15"/>
     </row>
@@ -11476,7 +12046,7 @@
       <c r="L10" s="15"/>
       <c r="M10" s="19"/>
       <c r="N10" s="18"/>
-      <c r="O10" s="66"/>
+      <c r="O10" s="65"/>
       <c r="P10" s="15"/>
       <c r="Q10" s="15"/>
     </row>
@@ -11495,7 +12065,7 @@
       <c r="L11" s="15"/>
       <c r="M11" s="19"/>
       <c r="N11" s="18"/>
-      <c r="O11" s="66"/>
+      <c r="O11" s="65"/>
       <c r="P11" s="15"/>
       <c r="Q11" s="15"/>
     </row>
@@ -11514,7 +12084,7 @@
       <c r="L12" s="15"/>
       <c r="M12" s="19"/>
       <c r="N12" s="18"/>
-      <c r="O12" s="66"/>
+      <c r="O12" s="65"/>
       <c r="P12" s="15"/>
       <c r="Q12" s="15"/>
     </row>
@@ -11533,7 +12103,7 @@
       <c r="L13" s="15"/>
       <c r="M13" s="19"/>
       <c r="N13" s="18"/>
-      <c r="O13" s="66"/>
+      <c r="O13" s="65"/>
       <c r="P13" s="15"/>
       <c r="Q13" s="15"/>
     </row>
@@ -11552,7 +12122,7 @@
       <c r="L14" s="15"/>
       <c r="M14" s="19"/>
       <c r="N14" s="18"/>
-      <c r="O14" s="66"/>
+      <c r="O14" s="65"/>
       <c r="P14" s="15"/>
       <c r="Q14" s="15"/>
     </row>
@@ -11571,7 +12141,7 @@
       <c r="L15" s="15"/>
       <c r="M15" s="19"/>
       <c r="N15" s="18"/>
-      <c r="O15" s="66"/>
+      <c r="O15" s="65"/>
       <c r="P15" s="15"/>
       <c r="Q15" s="15"/>
     </row>
@@ -11590,7 +12160,7 @@
       <c r="L16" s="15"/>
       <c r="M16" s="19"/>
       <c r="N16" s="18"/>
-      <c r="O16" s="66"/>
+      <c r="O16" s="65"/>
       <c r="P16" s="15"/>
       <c r="Q16" s="15"/>
     </row>
@@ -11609,7 +12179,7 @@
       <c r="L17" s="15"/>
       <c r="M17" s="19"/>
       <c r="N17" s="18"/>
-      <c r="O17" s="66"/>
+      <c r="O17" s="65"/>
       <c r="P17" s="15"/>
       <c r="Q17" s="15"/>
     </row>
@@ -11628,7 +12198,7 @@
       <c r="L18" s="15"/>
       <c r="M18" s="19"/>
       <c r="N18" s="18"/>
-      <c r="O18" s="66"/>
+      <c r="O18" s="65"/>
       <c r="P18" s="15"/>
       <c r="Q18" s="15"/>
     </row>
@@ -11647,7 +12217,7 @@
       <c r="L19" s="15"/>
       <c r="M19" s="19"/>
       <c r="N19" s="18"/>
-      <c r="O19" s="66"/>
+      <c r="O19" s="65"/>
       <c r="P19" s="15"/>
       <c r="Q19" s="15"/>
     </row>
@@ -11666,7 +12236,7 @@
       <c r="L20" s="15"/>
       <c r="M20" s="19"/>
       <c r="N20" s="18"/>
-      <c r="O20" s="66"/>
+      <c r="O20" s="65"/>
       <c r="P20" s="15"/>
       <c r="Q20" s="15"/>
     </row>
@@ -11685,7 +12255,7 @@
       <c r="L21" s="15"/>
       <c r="M21" s="19"/>
       <c r="N21" s="18"/>
-      <c r="O21" s="66"/>
+      <c r="O21" s="65"/>
       <c r="P21" s="15"/>
       <c r="Q21" s="15"/>
     </row>
@@ -11704,7 +12274,7 @@
       <c r="L22" s="15"/>
       <c r="M22" s="19"/>
       <c r="N22" s="18"/>
-      <c r="O22" s="66"/>
+      <c r="O22" s="65"/>
       <c r="P22" s="15"/>
       <c r="Q22" s="15"/>
     </row>
@@ -11723,7 +12293,7 @@
       <c r="L23" s="15"/>
       <c r="M23" s="19"/>
       <c r="N23" s="18"/>
-      <c r="O23" s="66"/>
+      <c r="O23" s="65"/>
       <c r="P23" s="15"/>
       <c r="Q23" s="15"/>
     </row>
@@ -11742,7 +12312,7 @@
       <c r="L24" s="15"/>
       <c r="M24" s="19"/>
       <c r="N24" s="18"/>
-      <c r="O24" s="66"/>
+      <c r="O24" s="65"/>
       <c r="P24" s="15"/>
       <c r="Q24" s="15"/>
     </row>
@@ -11761,7 +12331,7 @@
       <c r="L25" s="15"/>
       <c r="M25" s="19"/>
       <c r="N25" s="18"/>
-      <c r="O25" s="66"/>
+      <c r="O25" s="65"/>
       <c r="P25" s="15"/>
       <c r="Q25" s="15"/>
     </row>
@@ -11780,7 +12350,7 @@
       <c r="L26" s="15"/>
       <c r="M26" s="19"/>
       <c r="N26" s="18"/>
-      <c r="O26" s="66"/>
+      <c r="O26" s="65"/>
       <c r="P26" s="15"/>
       <c r="Q26" s="15"/>
     </row>
@@ -11799,7 +12369,7 @@
       <c r="L27" s="15"/>
       <c r="M27" s="19"/>
       <c r="N27" s="18"/>
-      <c r="O27" s="66"/>
+      <c r="O27" s="65"/>
       <c r="P27" s="15"/>
       <c r="Q27" s="15"/>
     </row>
@@ -11818,7 +12388,7 @@
       <c r="L28" s="15"/>
       <c r="M28" s="19"/>
       <c r="N28" s="18"/>
-      <c r="O28" s="66"/>
+      <c r="O28" s="65"/>
       <c r="P28" s="15"/>
       <c r="Q28" s="15"/>
     </row>
@@ -11837,7 +12407,7 @@
       <c r="L29" s="15"/>
       <c r="M29" s="19"/>
       <c r="N29" s="18"/>
-      <c r="O29" s="66"/>
+      <c r="O29" s="65"/>
       <c r="P29" s="15"/>
       <c r="Q29" s="15"/>
     </row>
@@ -11856,7 +12426,7 @@
       <c r="L30" s="15"/>
       <c r="M30" s="19"/>
       <c r="N30" s="18"/>
-      <c r="O30" s="66"/>
+      <c r="O30" s="65"/>
       <c r="P30" s="15"/>
       <c r="Q30" s="15"/>
     </row>
@@ -11875,7 +12445,7 @@
       <c r="L31" s="15"/>
       <c r="M31" s="19"/>
       <c r="N31" s="18"/>
-      <c r="O31" s="66"/>
+      <c r="O31" s="65"/>
       <c r="P31" s="15"/>
       <c r="Q31" s="15"/>
     </row>
@@ -11894,7 +12464,7 @@
       <c r="L32" s="15"/>
       <c r="M32" s="19"/>
       <c r="N32" s="18"/>
-      <c r="O32" s="66"/>
+      <c r="O32" s="65"/>
       <c r="P32" s="15"/>
       <c r="Q32" s="15"/>
     </row>
@@ -11913,7 +12483,7 @@
       <c r="L33" s="15"/>
       <c r="M33" s="19"/>
       <c r="N33" s="18"/>
-      <c r="O33" s="66"/>
+      <c r="O33" s="65"/>
       <c r="P33" s="15"/>
       <c r="Q33" s="15"/>
     </row>
@@ -11932,7 +12502,7 @@
       <c r="L34" s="15"/>
       <c r="M34" s="19"/>
       <c r="N34" s="18"/>
-      <c r="O34" s="66"/>
+      <c r="O34" s="65"/>
       <c r="P34" s="15"/>
       <c r="Q34" s="15"/>
     </row>
@@ -11951,7 +12521,7 @@
       <c r="L35" s="15"/>
       <c r="M35" s="19"/>
       <c r="N35" s="18"/>
-      <c r="O35" s="66"/>
+      <c r="O35" s="65"/>
       <c r="P35" s="15"/>
       <c r="Q35" s="15"/>
     </row>
@@ -11970,7 +12540,7 @@
       <c r="L36" s="15"/>
       <c r="M36" s="19"/>
       <c r="N36" s="18"/>
-      <c r="O36" s="66"/>
+      <c r="O36" s="65"/>
       <c r="P36" s="15"/>
       <c r="Q36" s="15"/>
     </row>
@@ -11989,7 +12559,7 @@
       <c r="L37" s="15"/>
       <c r="M37" s="19"/>
       <c r="N37" s="18"/>
-      <c r="O37" s="66"/>
+      <c r="O37" s="65"/>
       <c r="P37" s="15"/>
       <c r="Q37" s="15"/>
     </row>
@@ -12008,7 +12578,7 @@
       <c r="L38" s="15"/>
       <c r="M38" s="19"/>
       <c r="N38" s="18"/>
-      <c r="O38" s="66"/>
+      <c r="O38" s="65"/>
       <c r="P38" s="15"/>
       <c r="Q38" s="15"/>
     </row>
@@ -12027,7 +12597,7 @@
       <c r="L39" s="15"/>
       <c r="M39" s="19"/>
       <c r="N39" s="18"/>
-      <c r="O39" s="66"/>
+      <c r="O39" s="65"/>
       <c r="P39" s="15"/>
       <c r="Q39" s="15"/>
     </row>
@@ -12046,7 +12616,7 @@
       <c r="L40" s="15"/>
       <c r="M40" s="19"/>
       <c r="N40" s="18"/>
-      <c r="O40" s="66"/>
+      <c r="O40" s="65"/>
       <c r="P40" s="15"/>
       <c r="Q40" s="15"/>
     </row>
@@ -12109,9 +12679,9 @@
         <v>47</v>
       </c>
       <c r="E2" t="s">
-        <v>148</v>
-      </c>
-      <c r="F2" s="69">
+        <v>144</v>
+      </c>
+      <c r="F2" s="68">
         <v>45627</v>
       </c>
     </row>
@@ -12129,9 +12699,9 @@
         <v>46</v>
       </c>
       <c r="E3" t="s">
-        <v>149</v>
-      </c>
-      <c r="F3" s="69">
+        <v>145</v>
+      </c>
+      <c r="F3" s="68">
         <v>45658</v>
       </c>
     </row>
@@ -12149,9 +12719,9 @@
         <v>45</v>
       </c>
       <c r="E4" t="s">
-        <v>142</v>
-      </c>
-      <c r="F4" s="69">
+        <v>139</v>
+      </c>
+      <c r="F4" s="68">
         <v>45689</v>
       </c>
     </row>
@@ -12169,9 +12739,9 @@
         <v>48</v>
       </c>
       <c r="E5" t="s">
-        <v>143</v>
-      </c>
-      <c r="F5" s="69">
+        <v>140</v>
+      </c>
+      <c r="F5" s="68">
         <v>45717</v>
       </c>
     </row>
@@ -12191,7 +12761,7 @@
       <c r="E6" t="s">
         <v>34</v>
       </c>
-      <c r="F6" s="69">
+      <c r="F6" s="68">
         <v>45748</v>
       </c>
     </row>
@@ -12202,7 +12772,7 @@
       <c r="B7" t="s">
         <v>27</v>
       </c>
-      <c r="F7" s="69">
+      <c r="F7" s="68">
         <v>45778</v>
       </c>
     </row>
@@ -12213,7 +12783,7 @@
       <c r="B8" t="s">
         <v>29</v>
       </c>
-      <c r="F8" s="69">
+      <c r="F8" s="68">
         <v>45809</v>
       </c>
     </row>
@@ -12224,7 +12794,7 @@
       <c r="B9" t="s">
         <v>137</v>
       </c>
-      <c r="F9" s="69">
+      <c r="F9" s="68">
         <v>45839</v>
       </c>
     </row>
@@ -12235,7 +12805,7 @@
       <c r="B10" t="s">
         <v>129</v>
       </c>
-      <c r="F10" s="69">
+      <c r="F10" s="68">
         <v>45870</v>
       </c>
     </row>
@@ -12246,7 +12816,7 @@
       <c r="B11" t="s">
         <v>130</v>
       </c>
-      <c r="F11" s="69">
+      <c r="F11" s="68">
         <v>45901</v>
       </c>
     </row>
@@ -12257,7 +12827,7 @@
       <c r="B12" t="s">
         <v>131</v>
       </c>
-      <c r="F12" s="69">
+      <c r="F12" s="68">
         <v>45931</v>
       </c>
     </row>
@@ -12268,7 +12838,7 @@
       <c r="B13" t="s">
         <v>128</v>
       </c>
-      <c r="F13" s="69">
+      <c r="F13" s="68">
         <v>45962</v>
       </c>
     </row>
@@ -12279,7 +12849,7 @@
       <c r="B14" t="s">
         <v>135</v>
       </c>
-      <c r="F14" s="69">
+      <c r="F14" s="68">
         <v>45992</v>
       </c>
     </row>
@@ -12290,7 +12860,7 @@
       <c r="B15" t="s">
         <v>21</v>
       </c>
-      <c r="F15" s="69">
+      <c r="F15" s="68">
         <v>46023</v>
       </c>
     </row>
@@ -12301,7 +12871,7 @@
       <c r="B16" t="s">
         <v>132</v>
       </c>
-      <c r="F16" s="69">
+      <c r="F16" s="68">
         <v>46054</v>
       </c>
     </row>
@@ -12312,1236 +12882,1236 @@
       <c r="B17" t="s">
         <v>34</v>
       </c>
-      <c r="F17" s="69">
+      <c r="F17" s="68">
         <v>46082</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="F18" s="69">
+      <c r="F18" s="68">
         <v>46113</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="F19" s="69">
+      <c r="F19" s="68">
         <v>46143</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="F20" s="69">
+      <c r="F20" s="68">
         <v>46174</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="F21" s="69">
+      <c r="F21" s="68">
         <v>46204</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="F22" s="69">
+      <c r="F22" s="68">
         <v>46235</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="F23" s="69">
+      <c r="F23" s="68">
         <v>46266</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="F24" s="69">
+      <c r="F24" s="68">
         <v>46296</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="F25" s="69">
+      <c r="F25" s="68">
         <v>46327</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="F26" s="69">
+      <c r="F26" s="68">
         <v>46357</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="F27" s="69"/>
+      <c r="F27" s="68"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="F28" s="69"/>
+      <c r="F28" s="68"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="F29" s="69"/>
+      <c r="F29" s="68"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="F30" s="69"/>
+      <c r="F30" s="68"/>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="F31" s="69"/>
+      <c r="F31" s="68"/>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="F32" s="69"/>
+      <c r="F32" s="68"/>
     </row>
     <row r="33" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F33" s="69"/>
+      <c r="F33" s="68"/>
     </row>
     <row r="34" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F34" s="69"/>
+      <c r="F34" s="68"/>
     </row>
     <row r="35" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F35" s="69"/>
+      <c r="F35" s="68"/>
     </row>
     <row r="36" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F36" s="69"/>
+      <c r="F36" s="68"/>
     </row>
     <row r="37" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F37" s="69"/>
+      <c r="F37" s="68"/>
     </row>
     <row r="38" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F38" s="69"/>
+      <c r="F38" s="68"/>
     </row>
     <row r="39" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F39" s="69"/>
+      <c r="F39" s="68"/>
     </row>
     <row r="40" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F40" s="69"/>
+      <c r="F40" s="68"/>
     </row>
     <row r="41" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F41" s="69"/>
+      <c r="F41" s="68"/>
     </row>
     <row r="42" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F42" s="69"/>
+      <c r="F42" s="68"/>
     </row>
     <row r="43" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F43" s="69"/>
+      <c r="F43" s="68"/>
     </row>
     <row r="44" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F44" s="69"/>
+      <c r="F44" s="68"/>
     </row>
     <row r="45" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F45" s="69"/>
+      <c r="F45" s="68"/>
     </row>
     <row r="46" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F46" s="69"/>
+      <c r="F46" s="68"/>
     </row>
     <row r="47" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F47" s="69"/>
+      <c r="F47" s="68"/>
     </row>
     <row r="48" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F48" s="69"/>
+      <c r="F48" s="68"/>
     </row>
     <row r="49" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F49" s="69"/>
+      <c r="F49" s="68"/>
     </row>
     <row r="50" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F50" s="69"/>
+      <c r="F50" s="68"/>
     </row>
     <row r="51" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F51" s="69"/>
+      <c r="F51" s="68"/>
     </row>
     <row r="52" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F52" s="69"/>
+      <c r="F52" s="68"/>
     </row>
     <row r="53" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F53" s="69"/>
+      <c r="F53" s="68"/>
     </row>
     <row r="54" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F54" s="69"/>
+      <c r="F54" s="68"/>
     </row>
     <row r="55" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F55" s="69"/>
+      <c r="F55" s="68"/>
     </row>
     <row r="56" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F56" s="69"/>
+      <c r="F56" s="68"/>
     </row>
     <row r="57" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F57" s="69"/>
+      <c r="F57" s="68"/>
     </row>
     <row r="58" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F58" s="69"/>
+      <c r="F58" s="68"/>
     </row>
     <row r="59" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F59" s="69"/>
+      <c r="F59" s="68"/>
     </row>
     <row r="60" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F60" s="69"/>
+      <c r="F60" s="68"/>
     </row>
     <row r="61" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F61" s="69"/>
+      <c r="F61" s="68"/>
     </row>
     <row r="62" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F62" s="69"/>
+      <c r="F62" s="68"/>
     </row>
     <row r="63" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F63" s="69"/>
+      <c r="F63" s="68"/>
     </row>
     <row r="64" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F64" s="69"/>
+      <c r="F64" s="68"/>
     </row>
     <row r="65" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F65" s="69"/>
+      <c r="F65" s="68"/>
     </row>
     <row r="66" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F66" s="69"/>
+      <c r="F66" s="68"/>
     </row>
     <row r="67" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F67" s="69"/>
+      <c r="F67" s="68"/>
     </row>
     <row r="68" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F68" s="69"/>
+      <c r="F68" s="68"/>
     </row>
     <row r="69" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F69" s="69"/>
+      <c r="F69" s="68"/>
     </row>
     <row r="70" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F70" s="69"/>
+      <c r="F70" s="68"/>
     </row>
     <row r="71" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F71" s="69"/>
+      <c r="F71" s="68"/>
     </row>
     <row r="72" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F72" s="69"/>
+      <c r="F72" s="68"/>
     </row>
     <row r="73" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F73" s="69"/>
+      <c r="F73" s="68"/>
     </row>
     <row r="74" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F74" s="69"/>
+      <c r="F74" s="68"/>
     </row>
     <row r="75" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F75" s="69"/>
+      <c r="F75" s="68"/>
     </row>
     <row r="76" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F76" s="69"/>
+      <c r="F76" s="68"/>
     </row>
     <row r="77" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F77" s="69"/>
+      <c r="F77" s="68"/>
     </row>
     <row r="78" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F78" s="69"/>
+      <c r="F78" s="68"/>
     </row>
     <row r="79" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F79" s="69"/>
+      <c r="F79" s="68"/>
     </row>
     <row r="80" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F80" s="69"/>
+      <c r="F80" s="68"/>
     </row>
     <row r="81" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F81" s="69"/>
+      <c r="F81" s="68"/>
     </row>
     <row r="82" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F82" s="69"/>
+      <c r="F82" s="68"/>
     </row>
     <row r="83" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F83" s="69"/>
+      <c r="F83" s="68"/>
     </row>
     <row r="84" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F84" s="69"/>
+      <c r="F84" s="68"/>
     </row>
     <row r="85" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F85" s="69"/>
+      <c r="F85" s="68"/>
     </row>
     <row r="86" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F86" s="69"/>
+      <c r="F86" s="68"/>
     </row>
     <row r="87" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F87" s="69"/>
+      <c r="F87" s="68"/>
     </row>
     <row r="88" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F88" s="69"/>
+      <c r="F88" s="68"/>
     </row>
     <row r="89" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F89" s="69"/>
+      <c r="F89" s="68"/>
     </row>
     <row r="90" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F90" s="69"/>
+      <c r="F90" s="68"/>
     </row>
     <row r="91" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F91" s="69"/>
+      <c r="F91" s="68"/>
     </row>
     <row r="92" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F92" s="69"/>
+      <c r="F92" s="68"/>
     </row>
     <row r="93" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F93" s="69"/>
+      <c r="F93" s="68"/>
     </row>
     <row r="94" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F94" s="69"/>
+      <c r="F94" s="68"/>
     </row>
     <row r="95" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F95" s="69"/>
+      <c r="F95" s="68"/>
     </row>
     <row r="96" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F96" s="69"/>
+      <c r="F96" s="68"/>
     </row>
     <row r="97" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F97" s="69"/>
+      <c r="F97" s="68"/>
     </row>
     <row r="98" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F98" s="69"/>
+      <c r="F98" s="68"/>
     </row>
     <row r="99" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F99" s="69"/>
+      <c r="F99" s="68"/>
     </row>
     <row r="100" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F100" s="69"/>
+      <c r="F100" s="68"/>
     </row>
     <row r="101" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F101" s="69"/>
+      <c r="F101" s="68"/>
     </row>
     <row r="102" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F102" s="69"/>
+      <c r="F102" s="68"/>
     </row>
     <row r="103" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F103" s="69"/>
+      <c r="F103" s="68"/>
     </row>
     <row r="104" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F104" s="69"/>
+      <c r="F104" s="68"/>
     </row>
     <row r="105" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F105" s="69"/>
+      <c r="F105" s="68"/>
     </row>
     <row r="106" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F106" s="69"/>
+      <c r="F106" s="68"/>
     </row>
     <row r="107" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F107" s="69"/>
+      <c r="F107" s="68"/>
     </row>
     <row r="108" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F108" s="69"/>
+      <c r="F108" s="68"/>
     </row>
     <row r="109" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F109" s="69"/>
+      <c r="F109" s="68"/>
     </row>
     <row r="110" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F110" s="69"/>
+      <c r="F110" s="68"/>
     </row>
     <row r="111" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F111" s="69"/>
+      <c r="F111" s="68"/>
     </row>
     <row r="112" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F112" s="69"/>
+      <c r="F112" s="68"/>
     </row>
     <row r="113" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F113" s="69"/>
+      <c r="F113" s="68"/>
     </row>
     <row r="114" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F114" s="69"/>
+      <c r="F114" s="68"/>
     </row>
     <row r="115" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F115" s="69"/>
+      <c r="F115" s="68"/>
     </row>
     <row r="116" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F116" s="69"/>
+      <c r="F116" s="68"/>
     </row>
     <row r="117" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F117" s="69"/>
+      <c r="F117" s="68"/>
     </row>
     <row r="118" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F118" s="69"/>
+      <c r="F118" s="68"/>
     </row>
     <row r="119" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F119" s="69"/>
+      <c r="F119" s="68"/>
     </row>
     <row r="120" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F120" s="69"/>
+      <c r="F120" s="68"/>
     </row>
     <row r="121" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F121" s="69"/>
+      <c r="F121" s="68"/>
     </row>
     <row r="122" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F122" s="69"/>
+      <c r="F122" s="68"/>
     </row>
     <row r="123" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F123" s="69"/>
+      <c r="F123" s="68"/>
     </row>
     <row r="124" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F124" s="69"/>
+      <c r="F124" s="68"/>
     </row>
     <row r="125" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F125" s="69"/>
+      <c r="F125" s="68"/>
     </row>
     <row r="126" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F126" s="69"/>
+      <c r="F126" s="68"/>
     </row>
     <row r="127" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F127" s="69"/>
+      <c r="F127" s="68"/>
     </row>
     <row r="128" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F128" s="69"/>
+      <c r="F128" s="68"/>
     </row>
     <row r="129" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F129" s="69"/>
+      <c r="F129" s="68"/>
     </row>
     <row r="130" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F130" s="69"/>
+      <c r="F130" s="68"/>
     </row>
     <row r="131" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F131" s="69"/>
+      <c r="F131" s="68"/>
     </row>
     <row r="132" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F132" s="69"/>
+      <c r="F132" s="68"/>
     </row>
     <row r="133" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F133" s="69"/>
+      <c r="F133" s="68"/>
     </row>
     <row r="134" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F134" s="69"/>
+      <c r="F134" s="68"/>
     </row>
     <row r="135" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F135" s="69"/>
+      <c r="F135" s="68"/>
     </row>
     <row r="136" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F136" s="69"/>
+      <c r="F136" s="68"/>
     </row>
     <row r="137" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F137" s="69"/>
+      <c r="F137" s="68"/>
     </row>
     <row r="138" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F138" s="69"/>
+      <c r="F138" s="68"/>
     </row>
     <row r="139" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F139" s="69"/>
+      <c r="F139" s="68"/>
     </row>
     <row r="140" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F140" s="69"/>
+      <c r="F140" s="68"/>
     </row>
     <row r="141" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F141" s="69"/>
+      <c r="F141" s="68"/>
     </row>
     <row r="142" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F142" s="69"/>
+      <c r="F142" s="68"/>
     </row>
     <row r="143" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F143" s="69"/>
+      <c r="F143" s="68"/>
     </row>
     <row r="144" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F144" s="69"/>
+      <c r="F144" s="68"/>
     </row>
     <row r="145" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F145" s="69"/>
+      <c r="F145" s="68"/>
     </row>
     <row r="146" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F146" s="69"/>
+      <c r="F146" s="68"/>
     </row>
     <row r="147" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F147" s="69"/>
+      <c r="F147" s="68"/>
     </row>
     <row r="148" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F148" s="69"/>
+      <c r="F148" s="68"/>
     </row>
     <row r="149" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F149" s="69"/>
+      <c r="F149" s="68"/>
     </row>
     <row r="150" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F150" s="69"/>
+      <c r="F150" s="68"/>
     </row>
     <row r="151" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F151" s="69"/>
+      <c r="F151" s="68"/>
     </row>
     <row r="152" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F152" s="69"/>
+      <c r="F152" s="68"/>
     </row>
     <row r="153" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F153" s="69"/>
+      <c r="F153" s="68"/>
     </row>
     <row r="154" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F154" s="69"/>
+      <c r="F154" s="68"/>
     </row>
     <row r="155" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F155" s="69"/>
+      <c r="F155" s="68"/>
     </row>
     <row r="156" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F156" s="69"/>
+      <c r="F156" s="68"/>
     </row>
     <row r="157" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F157" s="69"/>
+      <c r="F157" s="68"/>
     </row>
     <row r="158" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F158" s="69"/>
+      <c r="F158" s="68"/>
     </row>
     <row r="159" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F159" s="69"/>
+      <c r="F159" s="68"/>
     </row>
     <row r="160" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F160" s="69"/>
+      <c r="F160" s="68"/>
     </row>
     <row r="161" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F161" s="69"/>
+      <c r="F161" s="68"/>
     </row>
     <row r="162" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F162" s="69"/>
+      <c r="F162" s="68"/>
     </row>
     <row r="163" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F163" s="69"/>
+      <c r="F163" s="68"/>
     </row>
     <row r="164" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F164" s="69"/>
+      <c r="F164" s="68"/>
     </row>
     <row r="165" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F165" s="69"/>
+      <c r="F165" s="68"/>
     </row>
     <row r="166" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F166" s="69"/>
+      <c r="F166" s="68"/>
     </row>
     <row r="167" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F167" s="69"/>
+      <c r="F167" s="68"/>
     </row>
     <row r="168" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F168" s="69"/>
+      <c r="F168" s="68"/>
     </row>
     <row r="169" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F169" s="69"/>
+      <c r="F169" s="68"/>
     </row>
     <row r="170" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F170" s="69"/>
+      <c r="F170" s="68"/>
     </row>
     <row r="171" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F171" s="69"/>
+      <c r="F171" s="68"/>
     </row>
     <row r="172" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F172" s="69"/>
+      <c r="F172" s="68"/>
     </row>
     <row r="173" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F173" s="69"/>
+      <c r="F173" s="68"/>
     </row>
     <row r="174" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F174" s="69"/>
+      <c r="F174" s="68"/>
     </row>
     <row r="175" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F175" s="69"/>
+      <c r="F175" s="68"/>
     </row>
     <row r="176" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F176" s="69"/>
+      <c r="F176" s="68"/>
     </row>
     <row r="177" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F177" s="69"/>
+      <c r="F177" s="68"/>
     </row>
     <row r="178" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F178" s="69"/>
+      <c r="F178" s="68"/>
     </row>
     <row r="179" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F179" s="69"/>
+      <c r="F179" s="68"/>
     </row>
     <row r="180" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F180" s="69"/>
+      <c r="F180" s="68"/>
     </row>
     <row r="181" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F181" s="69"/>
+      <c r="F181" s="68"/>
     </row>
     <row r="182" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F182" s="69"/>
+      <c r="F182" s="68"/>
     </row>
     <row r="183" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F183" s="69"/>
+      <c r="F183" s="68"/>
     </row>
     <row r="184" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F184" s="69"/>
+      <c r="F184" s="68"/>
     </row>
     <row r="185" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F185" s="69"/>
+      <c r="F185" s="68"/>
     </row>
     <row r="186" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F186" s="69"/>
+      <c r="F186" s="68"/>
     </row>
     <row r="187" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F187" s="69"/>
+      <c r="F187" s="68"/>
     </row>
     <row r="188" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F188" s="69"/>
+      <c r="F188" s="68"/>
     </row>
     <row r="189" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F189" s="69"/>
+      <c r="F189" s="68"/>
     </row>
     <row r="190" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F190" s="69"/>
+      <c r="F190" s="68"/>
     </row>
     <row r="191" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F191" s="69"/>
+      <c r="F191" s="68"/>
     </row>
     <row r="192" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F192" s="69"/>
+      <c r="F192" s="68"/>
     </row>
     <row r="193" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F193" s="69"/>
+      <c r="F193" s="68"/>
     </row>
     <row r="194" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F194" s="69"/>
+      <c r="F194" s="68"/>
     </row>
     <row r="195" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F195" s="69"/>
+      <c r="F195" s="68"/>
     </row>
     <row r="196" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F196" s="69"/>
+      <c r="F196" s="68"/>
     </row>
     <row r="197" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F197" s="69"/>
+      <c r="F197" s="68"/>
     </row>
     <row r="198" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F198" s="69"/>
+      <c r="F198" s="68"/>
     </row>
     <row r="199" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F199" s="69"/>
+      <c r="F199" s="68"/>
     </row>
     <row r="200" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F200" s="69"/>
+      <c r="F200" s="68"/>
     </row>
     <row r="201" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F201" s="69"/>
+      <c r="F201" s="68"/>
     </row>
     <row r="202" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F202" s="69"/>
+      <c r="F202" s="68"/>
     </row>
     <row r="203" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F203" s="69"/>
+      <c r="F203" s="68"/>
     </row>
     <row r="204" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F204" s="69"/>
+      <c r="F204" s="68"/>
     </row>
     <row r="205" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F205" s="69"/>
+      <c r="F205" s="68"/>
     </row>
     <row r="206" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F206" s="69"/>
+      <c r="F206" s="68"/>
     </row>
     <row r="207" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F207" s="69"/>
+      <c r="F207" s="68"/>
     </row>
     <row r="208" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F208" s="69"/>
+      <c r="F208" s="68"/>
     </row>
     <row r="209" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F209" s="69"/>
+      <c r="F209" s="68"/>
     </row>
     <row r="210" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F210" s="69"/>
+      <c r="F210" s="68"/>
     </row>
     <row r="211" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F211" s="69"/>
+      <c r="F211" s="68"/>
     </row>
     <row r="212" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F212" s="69"/>
+      <c r="F212" s="68"/>
     </row>
     <row r="213" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F213" s="69"/>
+      <c r="F213" s="68"/>
     </row>
     <row r="214" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F214" s="69"/>
+      <c r="F214" s="68"/>
     </row>
     <row r="215" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F215" s="69"/>
+      <c r="F215" s="68"/>
     </row>
     <row r="216" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F216" s="69"/>
+      <c r="F216" s="68"/>
     </row>
     <row r="217" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F217" s="69"/>
+      <c r="F217" s="68"/>
     </row>
     <row r="218" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F218" s="69"/>
+      <c r="F218" s="68"/>
     </row>
     <row r="219" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F219" s="69"/>
+      <c r="F219" s="68"/>
     </row>
     <row r="220" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F220" s="69"/>
+      <c r="F220" s="68"/>
     </row>
     <row r="221" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F221" s="69"/>
+      <c r="F221" s="68"/>
     </row>
     <row r="222" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F222" s="69"/>
+      <c r="F222" s="68"/>
     </row>
     <row r="223" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F223" s="69"/>
+      <c r="F223" s="68"/>
     </row>
     <row r="224" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F224" s="69"/>
+      <c r="F224" s="68"/>
     </row>
     <row r="225" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F225" s="69"/>
+      <c r="F225" s="68"/>
     </row>
     <row r="226" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F226" s="69"/>
+      <c r="F226" s="68"/>
     </row>
     <row r="227" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F227" s="69"/>
+      <c r="F227" s="68"/>
     </row>
     <row r="228" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F228" s="69"/>
+      <c r="F228" s="68"/>
     </row>
     <row r="229" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F229" s="69"/>
+      <c r="F229" s="68"/>
     </row>
     <row r="230" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F230" s="69"/>
+      <c r="F230" s="68"/>
     </row>
     <row r="231" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F231" s="69"/>
+      <c r="F231" s="68"/>
     </row>
     <row r="232" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F232" s="69"/>
+      <c r="F232" s="68"/>
     </row>
     <row r="233" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F233" s="69"/>
+      <c r="F233" s="68"/>
     </row>
     <row r="234" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F234" s="69"/>
+      <c r="F234" s="68"/>
     </row>
     <row r="235" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F235" s="69"/>
+      <c r="F235" s="68"/>
     </row>
     <row r="236" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F236" s="69"/>
+      <c r="F236" s="68"/>
     </row>
     <row r="237" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F237" s="69"/>
+      <c r="F237" s="68"/>
     </row>
     <row r="238" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F238" s="69"/>
+      <c r="F238" s="68"/>
     </row>
     <row r="239" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F239" s="69"/>
+      <c r="F239" s="68"/>
     </row>
     <row r="240" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F240" s="69"/>
+      <c r="F240" s="68"/>
     </row>
     <row r="241" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F241" s="69"/>
+      <c r="F241" s="68"/>
     </row>
     <row r="242" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F242" s="69"/>
+      <c r="F242" s="68"/>
     </row>
     <row r="243" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F243" s="69"/>
+      <c r="F243" s="68"/>
     </row>
     <row r="244" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F244" s="69"/>
+      <c r="F244" s="68"/>
     </row>
     <row r="245" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F245" s="69"/>
+      <c r="F245" s="68"/>
     </row>
     <row r="246" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F246" s="69"/>
+      <c r="F246" s="68"/>
     </row>
     <row r="247" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F247" s="69"/>
+      <c r="F247" s="68"/>
     </row>
     <row r="248" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F248" s="69"/>
+      <c r="F248" s="68"/>
     </row>
     <row r="249" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F249" s="69"/>
+      <c r="F249" s="68"/>
     </row>
     <row r="250" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F250" s="69"/>
+      <c r="F250" s="68"/>
     </row>
     <row r="251" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F251" s="69"/>
+      <c r="F251" s="68"/>
     </row>
     <row r="252" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F252" s="69"/>
+      <c r="F252" s="68"/>
     </row>
     <row r="253" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F253" s="69"/>
+      <c r="F253" s="68"/>
     </row>
     <row r="254" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F254" s="69"/>
+      <c r="F254" s="68"/>
     </row>
     <row r="255" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F255" s="69"/>
+      <c r="F255" s="68"/>
     </row>
     <row r="256" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F256" s="69"/>
+      <c r="F256" s="68"/>
     </row>
     <row r="257" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F257" s="69"/>
+      <c r="F257" s="68"/>
     </row>
     <row r="258" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F258" s="69"/>
+      <c r="F258" s="68"/>
     </row>
     <row r="259" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F259" s="69"/>
+      <c r="F259" s="68"/>
     </row>
     <row r="260" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F260" s="69"/>
+      <c r="F260" s="68"/>
     </row>
     <row r="261" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F261" s="69"/>
+      <c r="F261" s="68"/>
     </row>
     <row r="262" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F262" s="69"/>
+      <c r="F262" s="68"/>
     </row>
     <row r="263" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F263" s="69"/>
+      <c r="F263" s="68"/>
     </row>
     <row r="264" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F264" s="69"/>
+      <c r="F264" s="68"/>
     </row>
     <row r="265" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F265" s="69"/>
+      <c r="F265" s="68"/>
     </row>
     <row r="266" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F266" s="69"/>
+      <c r="F266" s="68"/>
     </row>
     <row r="267" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F267" s="69"/>
+      <c r="F267" s="68"/>
     </row>
     <row r="268" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F268" s="69"/>
+      <c r="F268" s="68"/>
     </row>
     <row r="269" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F269" s="69"/>
+      <c r="F269" s="68"/>
     </row>
     <row r="270" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F270" s="69"/>
+      <c r="F270" s="68"/>
     </row>
     <row r="271" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F271" s="69"/>
+      <c r="F271" s="68"/>
     </row>
     <row r="272" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F272" s="69"/>
+      <c r="F272" s="68"/>
     </row>
     <row r="273" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F273" s="69"/>
+      <c r="F273" s="68"/>
     </row>
     <row r="274" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F274" s="69"/>
+      <c r="F274" s="68"/>
     </row>
     <row r="275" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F275" s="69"/>
+      <c r="F275" s="68"/>
     </row>
     <row r="276" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F276" s="69"/>
+      <c r="F276" s="68"/>
     </row>
     <row r="277" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F277" s="69"/>
+      <c r="F277" s="68"/>
     </row>
     <row r="278" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F278" s="69"/>
+      <c r="F278" s="68"/>
     </row>
     <row r="279" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F279" s="69"/>
+      <c r="F279" s="68"/>
     </row>
     <row r="280" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F280" s="69"/>
+      <c r="F280" s="68"/>
     </row>
     <row r="281" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F281" s="69"/>
+      <c r="F281" s="68"/>
     </row>
     <row r="282" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F282" s="69"/>
+      <c r="F282" s="68"/>
     </row>
     <row r="283" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F283" s="69"/>
+      <c r="F283" s="68"/>
     </row>
     <row r="284" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F284" s="69"/>
+      <c r="F284" s="68"/>
     </row>
     <row r="285" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F285" s="69"/>
+      <c r="F285" s="68"/>
     </row>
     <row r="286" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F286" s="69"/>
+      <c r="F286" s="68"/>
     </row>
     <row r="287" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F287" s="69"/>
+      <c r="F287" s="68"/>
     </row>
     <row r="288" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F288" s="69"/>
+      <c r="F288" s="68"/>
     </row>
     <row r="289" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F289" s="69"/>
+      <c r="F289" s="68"/>
     </row>
     <row r="290" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F290" s="69"/>
+      <c r="F290" s="68"/>
     </row>
     <row r="291" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F291" s="69"/>
+      <c r="F291" s="68"/>
     </row>
     <row r="292" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F292" s="69"/>
+      <c r="F292" s="68"/>
     </row>
     <row r="293" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F293" s="69"/>
+      <c r="F293" s="68"/>
     </row>
     <row r="294" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F294" s="69"/>
+      <c r="F294" s="68"/>
     </row>
     <row r="295" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F295" s="69"/>
+      <c r="F295" s="68"/>
     </row>
     <row r="296" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F296" s="69"/>
+      <c r="F296" s="68"/>
     </row>
     <row r="297" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F297" s="69"/>
+      <c r="F297" s="68"/>
     </row>
     <row r="298" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F298" s="69"/>
+      <c r="F298" s="68"/>
     </row>
     <row r="299" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F299" s="69"/>
+      <c r="F299" s="68"/>
     </row>
     <row r="300" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F300" s="69"/>
+      <c r="F300" s="68"/>
     </row>
     <row r="301" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F301" s="69"/>
+      <c r="F301" s="68"/>
     </row>
     <row r="302" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F302" s="69"/>
+      <c r="F302" s="68"/>
     </row>
     <row r="303" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F303" s="69"/>
+      <c r="F303" s="68"/>
     </row>
     <row r="304" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F304" s="69"/>
+      <c r="F304" s="68"/>
     </row>
     <row r="305" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F305" s="69"/>
+      <c r="F305" s="68"/>
     </row>
     <row r="306" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F306" s="69"/>
+      <c r="F306" s="68"/>
     </row>
     <row r="307" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F307" s="69"/>
+      <c r="F307" s="68"/>
     </row>
     <row r="308" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F308" s="69"/>
+      <c r="F308" s="68"/>
     </row>
     <row r="309" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F309" s="69"/>
+      <c r="F309" s="68"/>
     </row>
     <row r="310" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F310" s="69"/>
+      <c r="F310" s="68"/>
     </row>
     <row r="311" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F311" s="69"/>
+      <c r="F311" s="68"/>
     </row>
     <row r="312" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F312" s="69"/>
+      <c r="F312" s="68"/>
     </row>
     <row r="313" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F313" s="69"/>
+      <c r="F313" s="68"/>
     </row>
     <row r="314" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F314" s="69"/>
+      <c r="F314" s="68"/>
     </row>
     <row r="315" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F315" s="69"/>
+      <c r="F315" s="68"/>
     </row>
     <row r="316" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F316" s="69"/>
+      <c r="F316" s="68"/>
     </row>
     <row r="317" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F317" s="69"/>
+      <c r="F317" s="68"/>
     </row>
     <row r="318" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F318" s="69"/>
+      <c r="F318" s="68"/>
     </row>
     <row r="319" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F319" s="69"/>
+      <c r="F319" s="68"/>
     </row>
     <row r="320" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F320" s="69"/>
+      <c r="F320" s="68"/>
     </row>
     <row r="321" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F321" s="69"/>
+      <c r="F321" s="68"/>
     </row>
     <row r="322" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F322" s="69"/>
+      <c r="F322" s="68"/>
     </row>
     <row r="323" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F323" s="69"/>
+      <c r="F323" s="68"/>
     </row>
     <row r="324" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F324" s="69"/>
+      <c r="F324" s="68"/>
     </row>
     <row r="325" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F325" s="69"/>
+      <c r="F325" s="68"/>
     </row>
     <row r="326" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F326" s="69"/>
+      <c r="F326" s="68"/>
     </row>
     <row r="327" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F327" s="69"/>
+      <c r="F327" s="68"/>
     </row>
     <row r="328" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F328" s="69"/>
+      <c r="F328" s="68"/>
     </row>
     <row r="329" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F329" s="69"/>
+      <c r="F329" s="68"/>
     </row>
     <row r="330" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F330" s="69"/>
+      <c r="F330" s="68"/>
     </row>
     <row r="331" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F331" s="69"/>
+      <c r="F331" s="68"/>
     </row>
     <row r="332" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F332" s="69"/>
+      <c r="F332" s="68"/>
     </row>
     <row r="333" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F333" s="69"/>
+      <c r="F333" s="68"/>
     </row>
     <row r="334" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F334" s="69"/>
+      <c r="F334" s="68"/>
     </row>
     <row r="335" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F335" s="69"/>
+      <c r="F335" s="68"/>
     </row>
     <row r="336" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F336" s="69"/>
+      <c r="F336" s="68"/>
     </row>
     <row r="337" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F337" s="69"/>
+      <c r="F337" s="68"/>
     </row>
     <row r="338" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F338" s="69"/>
+      <c r="F338" s="68"/>
     </row>
     <row r="339" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F339" s="69"/>
+      <c r="F339" s="68"/>
     </row>
     <row r="340" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F340" s="69"/>
+      <c r="F340" s="68"/>
     </row>
     <row r="341" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F341" s="69"/>
+      <c r="F341" s="68"/>
     </row>
     <row r="342" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F342" s="69"/>
+      <c r="F342" s="68"/>
     </row>
     <row r="343" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F343" s="69"/>
+      <c r="F343" s="68"/>
     </row>
     <row r="344" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F344" s="69"/>
+      <c r="F344" s="68"/>
     </row>
     <row r="345" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F345" s="69"/>
+      <c r="F345" s="68"/>
     </row>
     <row r="346" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F346" s="69"/>
+      <c r="F346" s="68"/>
     </row>
     <row r="347" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F347" s="69"/>
+      <c r="F347" s="68"/>
     </row>
     <row r="348" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F348" s="69"/>
+      <c r="F348" s="68"/>
     </row>
     <row r="349" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F349" s="69"/>
+      <c r="F349" s="68"/>
     </row>
     <row r="350" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F350" s="69"/>
+      <c r="F350" s="68"/>
     </row>
     <row r="351" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F351" s="69"/>
+      <c r="F351" s="68"/>
     </row>
     <row r="352" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F352" s="69"/>
+      <c r="F352" s="68"/>
     </row>
     <row r="353" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F353" s="69"/>
+      <c r="F353" s="68"/>
     </row>
     <row r="354" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F354" s="69"/>
+      <c r="F354" s="68"/>
     </row>
     <row r="355" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F355" s="69"/>
+      <c r="F355" s="68"/>
     </row>
     <row r="356" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F356" s="69"/>
+      <c r="F356" s="68"/>
     </row>
     <row r="357" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F357" s="69"/>
+      <c r="F357" s="68"/>
     </row>
     <row r="358" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F358" s="69"/>
+      <c r="F358" s="68"/>
     </row>
     <row r="359" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F359" s="69"/>
+      <c r="F359" s="68"/>
     </row>
     <row r="360" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F360" s="69"/>
+      <c r="F360" s="68"/>
     </row>
     <row r="361" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F361" s="69"/>
+      <c r="F361" s="68"/>
     </row>
     <row r="362" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F362" s="69"/>
+      <c r="F362" s="68"/>
     </row>
     <row r="363" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F363" s="69"/>
+      <c r="F363" s="68"/>
     </row>
     <row r="364" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F364" s="69"/>
+      <c r="F364" s="68"/>
     </row>
     <row r="365" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F365" s="69"/>
+      <c r="F365" s="68"/>
     </row>
     <row r="366" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F366" s="69"/>
+      <c r="F366" s="68"/>
     </row>
     <row r="367" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F367" s="69"/>
+      <c r="F367" s="68"/>
     </row>
     <row r="368" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F368" s="69"/>
+      <c r="F368" s="68"/>
     </row>
     <row r="369" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F369" s="69"/>
+      <c r="F369" s="68"/>
     </row>
     <row r="370" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F370" s="69"/>
+      <c r="F370" s="68"/>
     </row>
     <row r="371" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F371" s="69"/>
+      <c r="F371" s="68"/>
     </row>
     <row r="372" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F372" s="69"/>
+      <c r="F372" s="68"/>
     </row>
     <row r="373" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F373" s="69"/>
+      <c r="F373" s="68"/>
     </row>
     <row r="374" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F374" s="69"/>
+      <c r="F374" s="68"/>
     </row>
     <row r="375" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F375" s="69"/>
+      <c r="F375" s="68"/>
     </row>
     <row r="376" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F376" s="69"/>
+      <c r="F376" s="68"/>
     </row>
     <row r="377" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F377" s="69"/>
+      <c r="F377" s="68"/>
     </row>
     <row r="378" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F378" s="69"/>
+      <c r="F378" s="68"/>
     </row>
     <row r="379" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F379" s="69"/>
+      <c r="F379" s="68"/>
     </row>
     <row r="380" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F380" s="69"/>
+      <c r="F380" s="68"/>
     </row>
     <row r="381" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F381" s="69"/>
+      <c r="F381" s="68"/>
     </row>
     <row r="382" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F382" s="69"/>
+      <c r="F382" s="68"/>
     </row>
     <row r="383" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F383" s="69"/>
+      <c r="F383" s="68"/>
     </row>
     <row r="384" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F384" s="69"/>
+      <c r="F384" s="68"/>
     </row>
     <row r="385" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F385" s="69"/>
+      <c r="F385" s="68"/>
     </row>
     <row r="386" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F386" s="69"/>
+      <c r="F386" s="68"/>
     </row>
     <row r="387" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F387" s="69"/>
+      <c r="F387" s="68"/>
     </row>
     <row r="388" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F388" s="69"/>
+      <c r="F388" s="68"/>
     </row>
     <row r="389" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F389" s="69"/>
+      <c r="F389" s="68"/>
     </row>
     <row r="390" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F390" s="69"/>
+      <c r="F390" s="68"/>
     </row>
     <row r="391" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F391" s="69"/>
+      <c r="F391" s="68"/>
     </row>
     <row r="392" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F392" s="69"/>
+      <c r="F392" s="68"/>
     </row>
     <row r="393" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F393" s="69"/>
+      <c r="F393" s="68"/>
     </row>
     <row r="394" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F394" s="69"/>
+      <c r="F394" s="68"/>
     </row>
     <row r="395" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F395" s="69"/>
+      <c r="F395" s="68"/>
     </row>
     <row r="396" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F396" s="69"/>
+      <c r="F396" s="68"/>
     </row>
     <row r="397" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F397" s="69"/>
+      <c r="F397" s="68"/>
     </row>
     <row r="398" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F398" s="69"/>
+      <c r="F398" s="68"/>
     </row>
     <row r="399" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F399" s="69"/>
+      <c r="F399" s="68"/>
     </row>
     <row r="400" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F400" s="69"/>
+      <c r="F400" s="68"/>
     </row>
     <row r="401" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F401" s="69"/>
+      <c r="F401" s="68"/>
     </row>
     <row r="402" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F402" s="69"/>
+      <c r="F402" s="68"/>
     </row>
     <row r="403" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F403" s="69"/>
+      <c r="F403" s="68"/>
     </row>
     <row r="404" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F404" s="69"/>
+      <c r="F404" s="68"/>
     </row>
     <row r="405" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F405" s="69"/>
+      <c r="F405" s="68"/>
     </row>
     <row r="406" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F406" s="69"/>
+      <c r="F406" s="68"/>
     </row>
     <row r="407" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F407" s="69"/>
+      <c r="F407" s="68"/>
     </row>
     <row r="408" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F408" s="69"/>
+      <c r="F408" s="68"/>
     </row>
     <row r="409" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F409" s="69"/>
+      <c r="F409" s="68"/>
     </row>
     <row r="410" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F410" s="69"/>
+      <c r="F410" s="68"/>
     </row>
     <row r="411" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F411" s="69"/>
+      <c r="F411" s="68"/>
     </row>
     <row r="412" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F412" s="69"/>
+      <c r="F412" s="68"/>
     </row>
     <row r="413" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F413" s="69"/>
+      <c r="F413" s="68"/>
     </row>
     <row r="414" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F414" s="69"/>
+      <c r="F414" s="68"/>
     </row>
     <row r="415" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F415" s="69"/>
+      <c r="F415" s="68"/>
     </row>
     <row r="416" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F416" s="69"/>
+      <c r="F416" s="68"/>
     </row>
     <row r="417" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F417" s="69"/>
+      <c r="F417" s="68"/>
     </row>
     <row r="418" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F418" s="69"/>
+      <c r="F418" s="68"/>
     </row>
     <row r="419" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F419" s="69"/>
+      <c r="F419" s="68"/>
     </row>
     <row r="420" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F420" s="69"/>
+      <c r="F420" s="68"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/bill-checker-demo.xlsx
+++ b/bill-checker-demo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alinaaleks\Downloads\GitHub\bill-checker\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{553D1359-A41E-40EE-887F-D6392D611513}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D0F4EBE-4F58-44EE-B5E3-4E7EE5455264}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -521,16 +521,17 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="7">
+  <numFmts count="8">
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="[$-409]mmm\-yy;@"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
     <numFmt numFmtId="166" formatCode="#,##0.0"/>
     <numFmt numFmtId="167" formatCode="yyyy\-mm"/>
-    <numFmt numFmtId="169" formatCode="#,##0.000"/>
-    <numFmt numFmtId="170" formatCode="#,##0.0000"/>
-    <numFmt numFmtId="172" formatCode="0.0000"/>
+    <numFmt numFmtId="168" formatCode="#,##0.000"/>
+    <numFmt numFmtId="169" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="170" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -578,6 +579,13 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -904,9 +912,10 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="124">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -1116,9 +1125,6 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="0" fillId="8" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1131,13 +1137,7 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1155,17 +1155,8 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="172" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1176,13 +1167,10 @@
     <xf numFmtId="1" fontId="0" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="5" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1191,62 +1179,14 @@
     <xf numFmtId="2" fontId="0" fillId="5" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="3" borderId="15" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="9" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="8" borderId="16" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="1" fillId="9" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="0" fillId="8" borderId="16" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="0" fillId="8" borderId="16" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="0" fillId="8" borderId="16" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="8" borderId="16" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="8" borderId="18" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="0" fillId="8" borderId="19" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="1" fillId="9" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1269,90 +1209,82 @@
     <xf numFmtId="4" fontId="0" fillId="6" borderId="15" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="3" borderId="12" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="3" borderId="15" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="1" fillId="9" borderId="17" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="1" fillId="9" borderId="20" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="8" borderId="16" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="8" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="8" borderId="16" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="0" fillId="8" borderId="16" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="8" borderId="16" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="8" borderId="16" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="8" borderId="18" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="8" borderId="19" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
+    <cellStyle name="Comma" xfId="2" builtinId="3"/>
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="105">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC00000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC00000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="9" tint="-0.499984740745262"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC00000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC00000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="62">
     <dxf>
       <font>
         <color theme="9" tint="-0.499984740745262"/>
@@ -1391,319 +1323,9 @@
       </fill>
     </dxf>
     <dxf>
-      <font>
-        <color theme="9" tint="-0.499984740745262"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC00000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
       <fill>
         <patternFill>
           <bgColor theme="8" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC00000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="9" tint="-0.499984740745262"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC00000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="9" tint="-0.499984740745262"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC00000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="9" tint="-0.499984740745262"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC00000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="9" tint="-0.499984740745262"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC00000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="9" tint="-0.499984740745262"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC00000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="9" tint="-0.499984740745262"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC00000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="9" tint="-0.499984740745262"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC00000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="9" tint="-0.499984740745262"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="9" tint="-0.499984740745262"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1805,6 +1427,39 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="4" formatCode="#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="4" formatCode="#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="4" formatCode="#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="4" formatCode="#,##0.00"/>
+    </dxf>
+    <dxf>
       <alignment vertical="center"/>
     </dxf>
     <dxf>
@@ -1863,39 +1518,6 @@
     </dxf>
     <dxf>
       <numFmt numFmtId="4" formatCode="#,##0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="4" formatCode="#,##0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="4" formatCode="#,##0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="4" formatCode="#,##0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="4" formatCode="#,##0.00"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="4" formatCode="#,##0.00"/>
@@ -4968,8 +4590,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="5826397" y="123009"/>
-              <a:ext cx="4503963" cy="2947488"/>
+              <a:off x="5841637" y="124279"/>
+              <a:ext cx="4505233" cy="2928438"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -5335,6 +4957,193 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{4747A43B-033B-44E1-A183-5A9895611AE7}" name="отклонения по месяцам" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" showError="1" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" outline="1" outlineData="1" compactData="0" multipleFieldFilters="0">
+  <location ref="A2:F5" firstHeaderRow="0" firstDataRow="1" firstDataCol="2"/>
+  <pivotFields count="22">
+    <pivotField compact="0" showAll="0"/>
+    <pivotField compact="0" showAll="0"/>
+    <pivotField compact="0" showAll="0"/>
+    <pivotField compact="0" showAll="0"/>
+    <pivotField dataField="1" compact="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField compact="0" showAll="0"/>
+    <pivotField compact="0" showAll="0"/>
+    <pivotField compact="0" showAll="0"/>
+    <pivotField compact="0" showAll="0"/>
+    <pivotField compact="0" showAll="0"/>
+    <pivotField dataField="1" compact="0" showAll="0"/>
+    <pivotField compact="0" showAll="0"/>
+    <pivotField compact="0" numFmtId="14" showAll="0"/>
+    <pivotField compact="0" showAll="0"/>
+    <pivotField compact="0" showAll="0"/>
+    <pivotField compact="0" showAll="0"/>
+    <pivotField compact="0" showAll="0"/>
+    <pivotField axis="axisRow" compact="0" showAll="0">
+      <items count="4">
+        <item m="1" x="2"/>
+        <item m="1" x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField compact="0" showAll="0"/>
+    <pivotField axis="axisRow" compact="0" showAll="0">
+      <items count="14">
+        <item m="1" x="4"/>
+        <item m="1" x="3"/>
+        <item m="1" x="2"/>
+        <item m="1" x="1"/>
+        <item m="1" x="12"/>
+        <item m="1" x="11"/>
+        <item m="1" x="10"/>
+        <item m="1" x="9"/>
+        <item m="1" x="8"/>
+        <item m="1" x="7"/>
+        <item m="1" x="6"/>
+        <item m="1" x="5"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" compact="0" dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField dataField="1" compact="0" dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
+  </pivotFields>
+  <rowFields count="2">
+    <field x="17"/>
+    <field x="19"/>
+  </rowFields>
+  <rowItems count="3">
+    <i>
+      <x v="2"/>
+    </i>
+    <i r="1">
+      <x v="12"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="-2"/>
+  </colFields>
+  <colItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i i="1">
+      <x v="1"/>
+    </i>
+    <i i="2">
+      <x v="2"/>
+    </i>
+    <i i="3">
+      <x v="3"/>
+    </i>
+  </colItems>
+  <dataFields count="4">
+    <dataField name="План (начисления)" fld="10" baseField="17" baseItem="0"/>
+    <dataField name="Факт (начисления)" fld="4" baseField="17" baseItem="0" numFmtId="4"/>
+    <dataField name="Отклонение (руб)" fld="20" baseField="17" baseItem="0"/>
+    <dataField name="Отклонение (%)" fld="21" baseField="17" baseItem="0" numFmtId="10"/>
+  </dataFields>
+  <formats count="11">
+    <format dxfId="37">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="36">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="35">
+      <pivotArea outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="34">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="33">
+      <pivotArea outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="32">
+      <pivotArea field="19" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="1"/>
+    </format>
+    <format dxfId="31">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="4">
+            <x v="0"/>
+            <x v="1"/>
+            <x v="2"/>
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="30">
+      <pivotArea field="19" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="1"/>
+    </format>
+    <format dxfId="29">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="4">
+            <x v="0"/>
+            <x v="1"/>
+            <x v="2"/>
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="28">
+      <pivotArea field="19" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="1"/>
+    </format>
+    <format dxfId="27">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="4">
+            <x v="0"/>
+            <x v="1"/>
+            <x v="2"/>
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleMedium9" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{78231426-3946-4FAE-A363-072197D8DAF2}" name="PivotTable36" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3" rowHeaderCaption="Месяц">
   <location ref="AA4:AB6" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="22">
@@ -5428,7 +5237,7 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{83BBBD9A-9D48-47B7-8427-426296D86302}" name="PivotTable1" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" showError="1" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="B27:F31" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="22">
@@ -5532,10 +5341,10 @@
     <dataField name="Отклонение (%)" fld="21" baseField="13" baseItem="1" numFmtId="10"/>
   </dataFields>
   <formats count="6">
-    <format dxfId="75">
+    <format dxfId="43">
       <pivotArea field="17" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="74">
+    <format dxfId="42">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="4">
@@ -5547,10 +5356,10 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="73">
+    <format dxfId="41">
       <pivotArea field="17" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="72">
+    <format dxfId="40">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="4">
@@ -5562,10 +5371,10 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="71">
+    <format dxfId="39">
       <pivotArea field="17" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="70">
+    <format dxfId="38">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="4">
@@ -5590,7 +5399,7 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{36734D62-F45A-43F2-8842-27AFF588CCB5}" name="отклонения по услугам" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" showError="1" updatedVersion="8" minRefreshableVersion="3" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1" rowHeaderCaption="Услуга">
   <location ref="U2:W6" firstHeaderRow="1" firstDataRow="3" firstDataCol="1"/>
   <pivotFields count="22">
@@ -5663,7 +5472,7 @@
     <dataField name="Факт (начисления)" fld="4" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="18">
-    <format dxfId="93">
+    <format dxfId="61">
       <pivotArea outline="0" fieldPosition="0">
         <references count="2">
           <reference field="4294967294" count="1" selected="0">
@@ -5675,10 +5484,10 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="92">
+    <format dxfId="60">
       <pivotArea field="17" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
     </format>
-    <format dxfId="91">
+    <format dxfId="59">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="17" count="1">
@@ -5687,7 +5496,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="90">
+    <format dxfId="58">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="4294967294" count="1">
@@ -5699,7 +5508,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="89">
+    <format dxfId="57">
       <pivotArea outline="0" fieldPosition="0">
         <references count="2">
           <reference field="4294967294" count="1" selected="0">
@@ -5711,13 +5520,13 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="88">
+    <format dxfId="56">
       <pivotArea field="-2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="1"/>
     </format>
-    <format dxfId="87">
+    <format dxfId="55">
       <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="86">
+    <format dxfId="54">
       <pivotArea outline="0" fieldPosition="0">
         <references count="2">
           <reference field="4294967294" count="2" selected="0">
@@ -5730,7 +5539,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="85">
+    <format dxfId="53">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="4294967294" count="1" selected="0">
@@ -5742,31 +5551,31 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="84">
+    <format dxfId="52">
       <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="83">
+    <format dxfId="51">
       <pivotArea field="-2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="1"/>
     </format>
-    <format dxfId="82">
+    <format dxfId="50">
       <pivotArea field="17" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
     </format>
-    <format dxfId="81">
+    <format dxfId="49">
       <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="80">
+    <format dxfId="48">
       <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="79">
+    <format dxfId="47">
       <pivotArea field="-2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="1"/>
     </format>
-    <format dxfId="78">
+    <format dxfId="46">
       <pivotArea field="17" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
     </format>
-    <format dxfId="77">
+    <format dxfId="45">
       <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="76">
+    <format dxfId="44">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="17" count="1">
@@ -5862,227 +5671,40 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{4747A43B-033B-44E1-A183-5A9895611AE7}" name="отклонения по месяцам" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" showError="1" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" outline="1" outlineData="1" compactData="0" multipleFieldFilters="0">
-  <location ref="A2:F5" firstHeaderRow="0" firstDataRow="1" firstDataCol="2"/>
-  <pivotFields count="22">
-    <pivotField compact="0" showAll="0"/>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField dataField="1" compact="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField dataField="1" compact="0" showAll="0"/>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField compact="0" numFmtId="14" showAll="0"/>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField axis="axisRow" compact="0" showAll="0">
-      <items count="4">
-        <item m="1" x="2"/>
-        <item m="1" x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField axis="axisRow" compact="0" showAll="0">
-      <items count="14">
-        <item m="1" x="4"/>
-        <item m="1" x="3"/>
-        <item m="1" x="2"/>
-        <item m="1" x="1"/>
-        <item m="1" x="12"/>
-        <item m="1" x="11"/>
-        <item m="1" x="10"/>
-        <item m="1" x="9"/>
-        <item m="1" x="8"/>
-        <item m="1" x="7"/>
-        <item m="1" x="6"/>
-        <item m="1" x="5"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField dataField="1" compact="0" dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField dataField="1" compact="0" dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
-  </pivotFields>
-  <rowFields count="2">
-    <field x="17"/>
-    <field x="19"/>
-  </rowFields>
-  <rowItems count="3">
-    <i>
-      <x v="2"/>
-    </i>
-    <i r="1">
-      <x v="12"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="-2"/>
-  </colFields>
-  <colItems count="4">
-    <i>
-      <x/>
-    </i>
-    <i i="1">
-      <x v="1"/>
-    </i>
-    <i i="2">
-      <x v="2"/>
-    </i>
-    <i i="3">
-      <x v="3"/>
-    </i>
-  </colItems>
-  <dataFields count="4">
-    <dataField name="План (начисления)" fld="10" baseField="17" baseItem="0"/>
-    <dataField name="Факт (начисления)" fld="4" baseField="17" baseItem="0" numFmtId="4"/>
-    <dataField name="Отклонение (руб)" fld="20" baseField="17" baseItem="0"/>
-    <dataField name="Отклонение (%)" fld="21" baseField="17" baseItem="0" numFmtId="10"/>
-  </dataFields>
-  <formats count="11">
-    <format dxfId="104">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="103">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="102">
-      <pivotArea outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="101">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="100">
-      <pivotArea outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1">
-            <x v="3"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="99">
-      <pivotArea field="19" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="1"/>
-    </format>
-    <format dxfId="98">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="4">
-            <x v="0"/>
-            <x v="1"/>
-            <x v="2"/>
-            <x v="3"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="97">
-      <pivotArea field="19" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="1"/>
-    </format>
-    <format dxfId="96">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="4">
-            <x v="0"/>
-            <x v="1"/>
-            <x v="2"/>
-            <x v="3"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="95">
-      <pivotArea field="19" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="1"/>
-    </format>
-    <format dxfId="94">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="4">
-            <x v="0"/>
-            <x v="1"/>
-            <x v="2"/>
-            <x v="3"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-  </formats>
-  <pivotTableStyleInfo name="PivotStyleMedium9" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{038A7D06-120E-408B-AEDA-813F2FAAD501}" name="Table2" displayName="Table2" ref="A1:T2" insertRow="1" totalsRowShown="0" headerRowDxfId="69" dataDxfId="68">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{038A7D06-120E-408B-AEDA-813F2FAAD501}" name="Table2" displayName="Table2" ref="A1:T2" insertRow="1" totalsRowShown="0" headerRowDxfId="26" dataDxfId="25">
   <autoFilter ref="A1:T2" xr:uid="{038A7D06-120E-408B-AEDA-813F2FAAD501}"/>
   <tableColumns count="20">
-    <tableColumn id="1" xr3:uid="{A040E5F1-B940-434F-8642-3D7965B0C906}" name="услуга" dataDxfId="67"/>
-    <tableColumn id="2" xr3:uid="{F1E9BBF3-FF65-4BCE-A746-A764AA053336}" name="ед_изм" dataDxfId="66"/>
-    <tableColumn id="3" xr3:uid="{95BCA9F7-93A8-474A-B486-B60193571EE3}" name="объем_квит" dataDxfId="65"/>
-    <tableColumn id="4" xr3:uid="{68D5AF23-9C08-4C25-A70E-D5B9C5258B85}" name="тариф_квит" dataDxfId="64"/>
-    <tableColumn id="5" xr3:uid="{1AE3F8D2-8628-41AA-B125-5D9318037FFC}" name="начислено_квит" dataDxfId="63"/>
-    <tableColumn id="6" xr3:uid="{2352EB12-E5C2-4AD6-8516-1C5A276F0128}" name="объем_откл" dataDxfId="62"/>
-    <tableColumn id="7" xr3:uid="{7BC866F5-0902-4D0A-9F28-F44EC965920C}" name="тариф_откл" dataDxfId="61"/>
-    <tableColumn id="8" xr3:uid="{DCE0FDDD-E687-4FB1-A515-511A0D4227D7}" name="начислено_откл" dataDxfId="60"/>
-    <tableColumn id="9" xr3:uid="{ABA713D2-6A48-414E-8866-3C6F39D5A490}" name="объем_расчет" dataDxfId="59"/>
-    <tableColumn id="10" xr3:uid="{EB157C1F-294F-4DFA-B0C3-E5402FF488C6}" name="тариф_расчет" dataDxfId="58"/>
-    <tableColumn id="11" xr3:uid="{16FD8211-F0B8-47DC-B4C9-EE5186864112}" name="насчислено_расчет" dataDxfId="57"/>
-    <tableColumn id="12" xr3:uid="{E9403770-B09D-40E2-BEFE-72B760354FEB}" name="норматив" dataDxfId="56"/>
-    <tableColumn id="13" xr3:uid="{5E21BED0-908D-4682-8E01-9D5911F61AB9}" name="период" dataDxfId="55"/>
-    <tableColumn id="14" xr3:uid="{6C555CCE-FDE0-4600-A16A-E7977D4C1331}" name="поставщик" dataDxfId="54"/>
-    <tableColumn id="18" xr3:uid="{70B0664C-2BB9-44F5-A956-B8CFF607EBD0}" name="начислено_откл%" dataDxfId="53">
+    <tableColumn id="1" xr3:uid="{A040E5F1-B940-434F-8642-3D7965B0C906}" name="услуга" dataDxfId="24"/>
+    <tableColumn id="2" xr3:uid="{F1E9BBF3-FF65-4BCE-A746-A764AA053336}" name="ед_изм" dataDxfId="23"/>
+    <tableColumn id="3" xr3:uid="{95BCA9F7-93A8-474A-B486-B60193571EE3}" name="объем_квит" dataDxfId="22"/>
+    <tableColumn id="4" xr3:uid="{68D5AF23-9C08-4C25-A70E-D5B9C5258B85}" name="тариф_квит" dataDxfId="21"/>
+    <tableColumn id="5" xr3:uid="{1AE3F8D2-8628-41AA-B125-5D9318037FFC}" name="начислено_квит" dataDxfId="20"/>
+    <tableColumn id="6" xr3:uid="{2352EB12-E5C2-4AD6-8516-1C5A276F0128}" name="объем_откл" dataDxfId="19"/>
+    <tableColumn id="7" xr3:uid="{7BC866F5-0902-4D0A-9F28-F44EC965920C}" name="тариф_откл" dataDxfId="18"/>
+    <tableColumn id="8" xr3:uid="{DCE0FDDD-E687-4FB1-A515-511A0D4227D7}" name="начислено_откл" dataDxfId="17"/>
+    <tableColumn id="9" xr3:uid="{ABA713D2-6A48-414E-8866-3C6F39D5A490}" name="объем_расчет" dataDxfId="16"/>
+    <tableColumn id="10" xr3:uid="{EB157C1F-294F-4DFA-B0C3-E5402FF488C6}" name="тариф_расчет" dataDxfId="15"/>
+    <tableColumn id="11" xr3:uid="{16FD8211-F0B8-47DC-B4C9-EE5186864112}" name="насчислено_расчет" dataDxfId="14"/>
+    <tableColumn id="12" xr3:uid="{E9403770-B09D-40E2-BEFE-72B760354FEB}" name="норматив" dataDxfId="13"/>
+    <tableColumn id="13" xr3:uid="{5E21BED0-908D-4682-8E01-9D5911F61AB9}" name="период" dataDxfId="12"/>
+    <tableColumn id="14" xr3:uid="{6C555CCE-FDE0-4600-A16A-E7977D4C1331}" name="поставщик" dataDxfId="11"/>
+    <tableColumn id="18" xr3:uid="{70B0664C-2BB9-44F5-A956-B8CFF607EBD0}" name="начислено_откл%" dataDxfId="10">
       <calculatedColumnFormula>IF(Table2[[#This Row],[начислено_откл]]=0,0,(Table2[[#This Row],[начислено_квит]]-Table2[[#This Row],[насчислено_расчет]])/Table2[[#This Row],[насчислено_расчет]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="19" xr3:uid="{725C5E98-3B75-474D-9C6F-E06942598B1D}" name="положит_откл" dataDxfId="52">
+    <tableColumn id="19" xr3:uid="{725C5E98-3B75-474D-9C6F-E06942598B1D}" name="положит_откл" dataDxfId="9">
       <calculatedColumnFormula>IF(Table2[[#This Row],[начислено_откл]]&gt;0,Table2[[#This Row],[начислено_откл]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="20" xr3:uid="{307D926C-82F4-46F4-AC93-88CE44B6AD40}" name="отриц_откл" dataDxfId="51">
+    <tableColumn id="20" xr3:uid="{307D926C-82F4-46F4-AC93-88CE44B6AD40}" name="отриц_откл" dataDxfId="8">
       <calculatedColumnFormula>IF(Table2[[#This Row],[начислено_откл]]&lt;0,Table2[[#This Row],[начислено_откл]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{5780D1EA-A409-449C-BCA3-DC86372888EC}" name="год" dataDxfId="50">
+    <tableColumn id="15" xr3:uid="{5780D1EA-A409-449C-BCA3-DC86372888EC}" name="год" dataDxfId="7">
       <calculatedColumnFormula>YEAR(M2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{3889E082-3447-4F9E-A275-7FE45FCFD6FB}" name="месяц_№" dataDxfId="49">
+    <tableColumn id="16" xr3:uid="{3889E082-3447-4F9E-A275-7FE45FCFD6FB}" name="месяц_№" dataDxfId="6">
       <calculatedColumnFormula>MONTH(M2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{E6E9DC5E-485F-4A72-A2BF-41BAB4F90D1B}" name="месяц" dataDxfId="48">
+    <tableColumn id="17" xr3:uid="{E6E9DC5E-485F-4A72-A2BF-41BAB4F90D1B}" name="месяц" dataDxfId="5">
       <calculatedColumnFormula>CHOOSE(S2,"январь","февраль","март","апрель","май","июнь","июль","август","сентябрь","октябрь","ноябрь","декабрь")</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -6408,20 +6030,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8273ECE3-36C8-4C46-AC21-390A7CBD00EF}">
   <dimension ref="A1:N32"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" outlineLevelCol="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="21.26953125" style="3" customWidth="1"/>
     <col min="2" max="2" width="11.36328125" style="3" customWidth="1"/>
     <col min="3" max="3" width="9" style="3" customWidth="1"/>
     <col min="4" max="4" width="11" style="3" customWidth="1"/>
     <col min="5" max="5" width="11.26953125" style="3" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="11.26953125" style="3" customWidth="1"/>
-    <col min="8" max="8" width="11.36328125" style="3" customWidth="1"/>
-    <col min="9" max="10" width="11.26953125" style="3" customWidth="1"/>
+    <col min="6" max="7" width="11.26953125" style="3" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="8" max="8" width="11.36328125" style="3" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="9" max="9" width="11.26953125" style="3" customWidth="1" collapsed="1"/>
+    <col min="10" max="10" width="11.26953125" style="3" customWidth="1"/>
     <col min="11" max="11" width="11.36328125" style="3" customWidth="1"/>
     <col min="12" max="12" width="14.90625" style="3" customWidth="1"/>
     <col min="13" max="13" width="11.26953125" style="3" hidden="1" customWidth="1"/>
-    <col min="14" max="14" width="16.7265625" style="3" customWidth="1"/>
+    <col min="14" max="14" width="16.7265625" style="3" hidden="1" customWidth="1"/>
     <col min="15" max="15" width="59.1796875" style="3" customWidth="1"/>
     <col min="16" max="16384" width="9.1796875" style="3"/>
   </cols>
@@ -6453,7 +6076,7 @@
       <c r="A4" s="5" t="s">
         <v>141</v>
       </c>
-      <c r="B4" s="77">
+      <c r="B4" s="76">
         <f>info!B7</f>
         <v>55.2</v>
       </c>
@@ -6463,7 +6086,7 @@
       <c r="A5" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="B5" s="75">
+      <c r="B5" s="74">
         <f>info!B6</f>
         <v>2</v>
       </c>
@@ -6474,21 +6097,21 @@
     <row r="7" spans="1:14" s="5" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A7" s="3"/>
       <c r="B7" s="3"/>
-      <c r="C7" s="87" t="s">
+      <c r="C7" s="101" t="s">
         <v>36</v>
       </c>
-      <c r="D7" s="88"/>
-      <c r="E7" s="89"/>
-      <c r="F7" s="99" t="s">
+      <c r="D7" s="102"/>
+      <c r="E7" s="103"/>
+      <c r="F7" s="104" t="s">
         <v>37</v>
       </c>
-      <c r="G7" s="100"/>
-      <c r="H7" s="101"/>
-      <c r="I7" s="114" t="s">
+      <c r="G7" s="105"/>
+      <c r="H7" s="106"/>
+      <c r="I7" s="107" t="s">
         <v>155</v>
       </c>
-      <c r="J7" s="115"/>
-      <c r="K7" s="116"/>
+      <c r="J7" s="108"/>
+      <c r="K7" s="109"/>
       <c r="M7" s="7"/>
       <c r="N7" s="7"/>
     </row>
@@ -6499,34 +6122,34 @@
       <c r="B8" s="70" t="s">
         <v>39</v>
       </c>
-      <c r="C8" s="90" t="s">
+      <c r="C8" s="84" t="s">
         <v>40</v>
       </c>
       <c r="D8" s="72" t="s">
         <v>41</v>
       </c>
-      <c r="E8" s="91" t="s">
+      <c r="E8" s="85" t="s">
         <v>42</v>
       </c>
-      <c r="F8" s="102" t="s">
+      <c r="F8" s="91" t="s">
         <v>40</v>
       </c>
-      <c r="G8" s="74" t="s">
+      <c r="G8" s="73" t="s">
         <v>41</v>
       </c>
-      <c r="H8" s="103" t="s">
+      <c r="H8" s="92" t="s">
         <v>42</v>
       </c>
-      <c r="I8" s="117" t="s">
+      <c r="I8" s="94" t="s">
         <v>40</v>
       </c>
       <c r="J8" s="69" t="s">
         <v>41</v>
       </c>
-      <c r="K8" s="118" t="s">
+      <c r="K8" s="95" t="s">
         <v>42</v>
       </c>
-      <c r="L8" s="113" t="s">
+      <c r="L8" s="93" t="s">
         <v>138</v>
       </c>
       <c r="M8" s="8" t="s">
@@ -6543,28 +6166,28 @@
       <c r="B9" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="C9" s="92">
+      <c r="C9" s="86">
         <v>204</v>
       </c>
-      <c r="D9" s="83">
+      <c r="D9" s="80">
         <v>4.2</v>
       </c>
-      <c r="E9" s="93">
+      <c r="E9" s="112">
         <v>856.80000000000007</v>
       </c>
-      <c r="F9" s="104">
+      <c r="F9" s="116">
         <f>IFERROR(INDEX(usage!B:B, MATCH(CHECK!$B$3, usage!A:A, 0)) - INDEX(usage!B:B, MATCH(CHECK!$B$1, usage!A:A, 0)),"")</f>
         <v>201</v>
       </c>
-      <c r="G9" s="73">
+      <c r="G9" s="117">
         <f>IF(F9&lt;M9, INDEX(tariffs!2:2, MATCH(CHECK!$B$3,tariffs!$1:$1, 0)), INDEX(tariffs!3:3, MATCH(CHECK!$B$3,tariffs!$1:$1, 0)))</f>
         <v>4.2</v>
       </c>
-      <c r="H9" s="105">
+      <c r="H9" s="114">
         <f>IFERROR(F9*G9,"")</f>
         <v>844.2</v>
       </c>
-      <c r="I9" s="119">
+      <c r="I9" s="96">
         <f>IF(C9="", "", C9-F9)</f>
         <v>3</v>
       </c>
@@ -6572,7 +6195,7 @@
         <f t="shared" ref="J9:K24" si="0">IF(D9="", "", D9-G9)</f>
         <v>0</v>
       </c>
-      <c r="K9" s="120">
+      <c r="K9" s="97">
         <f t="shared" si="0"/>
         <v>12.600000000000023</v>
       </c>
@@ -6596,28 +6219,28 @@
       <c r="B10" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="C10" s="94">
+      <c r="C10" s="87">
         <v>4.597999999999999</v>
       </c>
-      <c r="D10" s="83">
+      <c r="D10" s="80">
         <v>62.98</v>
       </c>
-      <c r="E10" s="93">
+      <c r="E10" s="112">
         <v>289.58203999999995</v>
       </c>
-      <c r="F10" s="106">
+      <c r="F10" s="118">
         <f>IFERROR(INDEX(usage!C:C, MATCH(CHECK!$B$3, usage!A:A, 0)) - INDEX(usage!C:C, MATCH(CHECK!$B$1, usage!A:A, 0)),"")</f>
         <v>4.597999999999999</v>
       </c>
-      <c r="G10" s="73">
+      <c r="G10" s="117">
         <f>INDEX(tariffs!4:4, MATCH(CHECK!$B$3,tariffs!$1:$1, 0))</f>
         <v>62.98</v>
       </c>
-      <c r="H10" s="105">
+      <c r="H10" s="114">
         <f t="shared" ref="H10:H24" si="1">IFERROR(F10*G10,"")</f>
         <v>289.58203999999995</v>
       </c>
-      <c r="I10" s="119">
+      <c r="I10" s="96">
         <f t="shared" ref="I10:I24" si="2">IF(C10="", "", C10-F10)</f>
         <v>0</v>
       </c>
@@ -6625,7 +6248,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K10" s="120">
+      <c r="K10" s="97">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -6646,28 +6269,28 @@
       <c r="B11" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="C11" s="94">
+      <c r="C11" s="87">
         <v>4.597999999999999</v>
       </c>
-      <c r="D11" s="83">
+      <c r="D11" s="80">
         <v>44.12</v>
       </c>
-      <c r="E11" s="93">
+      <c r="E11" s="112">
         <v>202.86375999999996</v>
       </c>
-      <c r="F11" s="106">
+      <c r="F11" s="118">
         <f>F10</f>
         <v>4.597999999999999</v>
       </c>
-      <c r="G11" s="73">
+      <c r="G11" s="117">
         <f>INDEX(tariffs!5:5, MATCH(CHECK!$B$3,tariffs!$1:$1, 0))</f>
         <v>44.12</v>
       </c>
-      <c r="H11" s="105">
+      <c r="H11" s="114">
         <f t="shared" si="1"/>
         <v>202.86375999999996</v>
       </c>
-      <c r="I11" s="119">
+      <c r="I11" s="96">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -6675,7 +6298,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K11" s="120">
+      <c r="K11" s="97">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -6695,28 +6318,28 @@
       <c r="B12" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="C12" s="94">
+      <c r="C12" s="87">
         <v>3.202</v>
       </c>
-      <c r="D12" s="83">
+      <c r="D12" s="80">
         <v>62.98</v>
       </c>
-      <c r="E12" s="93">
+      <c r="E12" s="112">
         <v>201.66195999999999</v>
       </c>
-      <c r="F12" s="106">
+      <c r="F12" s="118">
         <f>IFERROR(INDEX(usage!D:D, MATCH(CHECK!$B$3, usage!A:A, 0)) - INDEX(usage!D:D, MATCH(CHECK!$B$1, usage!A:A, 0)),"")</f>
         <v>3.202</v>
       </c>
-      <c r="G12" s="73">
+      <c r="G12" s="117">
         <f>INDEX(tariffs!4:4, MATCH(CHECK!$B$3,tariffs!$1:$1, 0))</f>
         <v>62.98</v>
       </c>
-      <c r="H12" s="105">
+      <c r="H12" s="114">
         <f t="shared" si="1"/>
         <v>201.66195999999999</v>
       </c>
-      <c r="I12" s="119">
+      <c r="I12" s="96">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -6724,7 +6347,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K12" s="120">
+      <c r="K12" s="97">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -6744,28 +6367,28 @@
       <c r="B13" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="C13" s="94">
+      <c r="C13" s="87">
         <v>3.202</v>
       </c>
-      <c r="D13" s="83">
+      <c r="D13" s="80">
         <v>44.12</v>
       </c>
-      <c r="E13" s="93">
+      <c r="E13" s="112">
         <v>141.27223999999998</v>
       </c>
-      <c r="F13" s="106">
+      <c r="F13" s="118">
         <f>F12</f>
         <v>3.202</v>
       </c>
-      <c r="G13" s="73">
+      <c r="G13" s="117">
         <f>INDEX(tariffs!5:5, MATCH(CHECK!$B$3,tariffs!$1:$1, 0))</f>
         <v>44.12</v>
       </c>
-      <c r="H13" s="105">
+      <c r="H13" s="114">
         <f t="shared" si="1"/>
         <v>141.27223999999998</v>
       </c>
-      <c r="I13" s="119">
+      <c r="I13" s="96">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -6773,7 +6396,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K13" s="120">
+      <c r="K13" s="97">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -6794,28 +6417,28 @@
       <c r="B14" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="C14" s="95">
+      <c r="C14" s="88">
         <v>6.952</v>
       </c>
-      <c r="D14" s="84">
+      <c r="D14" s="81">
         <v>227.18</v>
       </c>
-      <c r="E14" s="93">
+      <c r="E14" s="112">
         <v>1579.35536</v>
       </c>
-      <c r="F14" s="106">
+      <c r="F14" s="118">
         <f>IFERROR(C14,"")</f>
         <v>6.952</v>
       </c>
-      <c r="G14" s="73">
+      <c r="G14" s="117">
         <f>INDEX(tariffs!6:6, MATCH(CHECK!$B$3,tariffs!$1:$1, 0))</f>
         <v>227.18</v>
       </c>
-      <c r="H14" s="105">
+      <c r="H14" s="114">
         <f t="shared" si="1"/>
         <v>1579.35536</v>
       </c>
-      <c r="I14" s="119">
+      <c r="I14" s="96">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -6823,7 +6446,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K14" s="120">
+      <c r="K14" s="97">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -6847,28 +6470,28 @@
       <c r="B15" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="C15" s="94">
+      <c r="C15" s="87">
         <v>1.7152000000000001</v>
       </c>
-      <c r="D15" s="84">
+      <c r="D15" s="81">
         <v>3549.74</v>
       </c>
-      <c r="E15" s="93">
+      <c r="E15" s="112">
         <v>6535.25</v>
       </c>
-      <c r="F15" s="107">
+      <c r="F15" s="119">
         <f>IFERROR(C15,"")</f>
         <v>1.7152000000000001</v>
       </c>
-      <c r="G15" s="73">
+      <c r="G15" s="117">
         <f>INDEX(tariffs!7:7, MATCH(CHECK!$B$3,tariffs!$1:$1, 0))</f>
         <v>3549.74</v>
       </c>
-      <c r="H15" s="105">
+      <c r="H15" s="114">
         <f t="shared" si="1"/>
         <v>6088.514048</v>
       </c>
-      <c r="I15" s="119">
+      <c r="I15" s="96">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -6876,7 +6499,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K15" s="120">
+      <c r="K15" s="97">
         <f t="shared" si="0"/>
         <v>446.735952</v>
       </c>
@@ -6897,28 +6520,28 @@
       <c r="B16" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="C16" s="94">
+      <c r="C16" s="87">
         <v>3</v>
       </c>
-      <c r="D16" s="83">
+      <c r="D16" s="80">
         <v>227.18</v>
       </c>
-      <c r="E16" s="93">
+      <c r="E16" s="112">
         <v>681.54</v>
       </c>
-      <c r="F16" s="106">
+      <c r="F16" s="118">
         <f t="shared" ref="F16:F20" si="4">IFERROR(C16,"")</f>
         <v>3</v>
       </c>
-      <c r="G16" s="73">
+      <c r="G16" s="117">
         <f>INDEX(tariffs!6:6, MATCH(CHECK!$B$3,tariffs!$1:$1, 0))</f>
         <v>227.18</v>
       </c>
-      <c r="H16" s="105">
+      <c r="H16" s="114">
         <f t="shared" si="1"/>
         <v>681.54</v>
       </c>
-      <c r="I16" s="119">
+      <c r="I16" s="96">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -6926,7 +6549,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K16" s="120">
+      <c r="K16" s="97">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -6947,28 +6570,28 @@
       <c r="B17" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="C17" s="94">
+      <c r="C17" s="87">
         <v>0.68</v>
       </c>
-      <c r="D17" s="83">
+      <c r="D17" s="80">
         <v>62.98</v>
       </c>
-      <c r="E17" s="93">
+      <c r="E17" s="112">
         <v>42.8264</v>
       </c>
-      <c r="F17" s="106">
+      <c r="F17" s="118">
         <f t="shared" si="4"/>
         <v>0.68</v>
       </c>
-      <c r="G17" s="73">
+      <c r="G17" s="117">
         <f>INDEX(tariffs!4:4, MATCH(CHECK!$B$3,tariffs!$1:$1, 0))</f>
         <v>62.98</v>
       </c>
-      <c r="H17" s="105">
+      <c r="H17" s="114">
         <f t="shared" si="1"/>
         <v>42.8264</v>
       </c>
-      <c r="I17" s="119">
+      <c r="I17" s="96">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -6976,7 +6599,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K17" s="120">
+      <c r="K17" s="97">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -7000,28 +6623,28 @@
       <c r="B18" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="C18" s="94">
+      <c r="C18" s="87">
         <v>1.36</v>
       </c>
-      <c r="D18" s="84">
+      <c r="D18" s="81">
         <v>62.98</v>
       </c>
-      <c r="E18" s="93">
+      <c r="E18" s="112">
         <v>85.652799999999999</v>
       </c>
-      <c r="F18" s="106">
+      <c r="F18" s="118">
         <f t="shared" si="4"/>
         <v>1.36</v>
       </c>
-      <c r="G18" s="73">
+      <c r="G18" s="117">
         <f>INDEX(tariffs!4:4, MATCH(CHECK!$B$3,tariffs!$1:$1, 0))</f>
         <v>62.98</v>
       </c>
-      <c r="H18" s="105">
+      <c r="H18" s="114">
         <f t="shared" si="1"/>
         <v>85.652799999999999</v>
       </c>
-      <c r="I18" s="119">
+      <c r="I18" s="96">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -7029,7 +6652,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K18" s="120">
+      <c r="K18" s="97">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -7053,28 +6676,28 @@
       <c r="B19" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="C19" s="94">
+      <c r="C19" s="87">
         <v>1.36</v>
       </c>
-      <c r="D19" s="84">
+      <c r="D19" s="81">
         <v>44.12</v>
       </c>
-      <c r="E19" s="93">
+      <c r="E19" s="112">
         <v>60.0032</v>
       </c>
-      <c r="F19" s="106">
+      <c r="F19" s="118">
         <f t="shared" si="4"/>
         <v>1.36</v>
       </c>
-      <c r="G19" s="73">
+      <c r="G19" s="117">
         <f>INDEX(tariffs!5:5, MATCH(CHECK!$B$3,tariffs!$1:$1, 0))</f>
         <v>44.12</v>
       </c>
-      <c r="H19" s="105">
+      <c r="H19" s="114">
         <f t="shared" si="1"/>
         <v>60.0032</v>
       </c>
-      <c r="I19" s="119">
+      <c r="I19" s="96">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -7082,7 +6705,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K19" s="120">
+      <c r="K19" s="97">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -7106,28 +6729,28 @@
       <c r="B20" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="C20" s="94">
+      <c r="C20" s="87">
         <v>26.83</v>
       </c>
-      <c r="D20" s="83">
+      <c r="D20" s="80">
         <v>4.2</v>
       </c>
-      <c r="E20" s="93">
+      <c r="E20" s="112">
         <v>112.68599999999999</v>
       </c>
-      <c r="F20" s="108">
+      <c r="F20" s="120">
         <f t="shared" si="4"/>
         <v>26.83</v>
       </c>
-      <c r="G20" s="73">
+      <c r="G20" s="117">
         <f>INDEX(tariffs!2:2, MATCH(CHECK!$B$3,tariffs!$1:$1, 0))</f>
         <v>4.2</v>
       </c>
-      <c r="H20" s="105">
+      <c r="H20" s="114">
         <f t="shared" si="1"/>
         <v>112.68599999999999</v>
       </c>
-      <c r="I20" s="119">
+      <c r="I20" s="96">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -7135,7 +6758,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K20" s="120">
+      <c r="K20" s="97">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -7159,28 +6782,28 @@
       <c r="B21" s="23" t="s">
         <v>47</v>
       </c>
-      <c r="C21" s="94">
+      <c r="C21" s="87">
         <v>55.2</v>
       </c>
-      <c r="D21" s="83">
+      <c r="D21" s="80">
         <v>11.08</v>
       </c>
-      <c r="E21" s="93">
+      <c r="E21" s="112">
         <v>611.61599999999999</v>
       </c>
-      <c r="F21" s="109">
+      <c r="F21" s="121">
         <f>IFERROR(info!$B$7,"")</f>
         <v>55.2</v>
       </c>
-      <c r="G21" s="73">
+      <c r="G21" s="117">
         <f>INDEX(tariffs!8:8, MATCH(CHECK!$B$3,tariffs!$1:$1, 0))</f>
         <v>11.08</v>
       </c>
-      <c r="H21" s="105">
+      <c r="H21" s="114">
         <f t="shared" si="1"/>
         <v>611.61599999999999</v>
       </c>
-      <c r="I21" s="119">
+      <c r="I21" s="96">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -7188,7 +6811,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K21" s="120">
+      <c r="K21" s="97">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -7209,28 +6832,28 @@
       <c r="B22" s="23" t="s">
         <v>47</v>
       </c>
-      <c r="C22" s="94">
+      <c r="C22" s="87">
         <v>55.2</v>
       </c>
-      <c r="D22" s="83">
+      <c r="D22" s="80">
         <v>5.98</v>
       </c>
-      <c r="E22" s="93">
+      <c r="E22" s="112">
         <v>330.09600000000006</v>
       </c>
-      <c r="F22" s="109">
+      <c r="F22" s="121">
         <f>IFERROR(info!$B$7,"")</f>
         <v>55.2</v>
       </c>
-      <c r="G22" s="73">
+      <c r="G22" s="117">
         <f>INDEX(tariffs!9:9, MATCH(CHECK!$B$3,tariffs!$1:$1, 0))</f>
         <v>5.98</v>
       </c>
-      <c r="H22" s="105">
+      <c r="H22" s="114">
         <f t="shared" si="1"/>
         <v>330.09600000000006</v>
       </c>
-      <c r="I22" s="119">
+      <c r="I22" s="96">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -7238,7 +6861,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K22" s="120">
+      <c r="K22" s="97">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -7259,28 +6882,28 @@
       <c r="B23" s="23" t="s">
         <v>49</v>
       </c>
-      <c r="C23" s="94">
+      <c r="C23" s="87">
         <v>2</v>
       </c>
-      <c r="D23" s="83">
+      <c r="D23" s="80">
         <v>158</v>
       </c>
-      <c r="E23" s="93">
+      <c r="E23" s="112">
         <v>316</v>
       </c>
-      <c r="F23" s="104">
+      <c r="F23" s="116">
         <f>IFERROR(info!$B$6,"")</f>
         <v>2</v>
       </c>
-      <c r="G23" s="73">
+      <c r="G23" s="117">
         <f>INDEX(tariffs!10:10, MATCH(CHECK!$B$3,tariffs!$1:$1, 0))</f>
         <v>161.52257251624999</v>
       </c>
-      <c r="H23" s="105">
+      <c r="H23" s="114">
         <f t="shared" si="1"/>
         <v>323.04514503249999</v>
       </c>
-      <c r="I23" s="119">
+      <c r="I23" s="96">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -7288,7 +6911,7 @@
         <f t="shared" si="0"/>
         <v>-3.5225725162499941</v>
       </c>
-      <c r="K23" s="120">
+      <c r="K23" s="97">
         <f t="shared" si="0"/>
         <v>-7.0451450324999882</v>
       </c>
@@ -7312,36 +6935,36 @@
       <c r="B24" s="23" t="s">
         <v>47</v>
       </c>
-      <c r="C24" s="96">
+      <c r="C24" s="89">
         <v>55.2</v>
       </c>
-      <c r="D24" s="97">
+      <c r="D24" s="90">
         <v>15.15</v>
       </c>
-      <c r="E24" s="98">
+      <c r="E24" s="113">
         <v>836.28000000000009</v>
       </c>
-      <c r="F24" s="110">
+      <c r="F24" s="122">
         <f>IFERROR(info!$B$7,"")</f>
         <v>55.2</v>
       </c>
-      <c r="G24" s="111">
+      <c r="G24" s="123">
         <f>INDEX(tariffs!11:11, MATCH(CHECK!$B$3,tariffs!$1:$1, 0))</f>
         <v>15.15</v>
       </c>
-      <c r="H24" s="112">
+      <c r="H24" s="115">
         <f t="shared" si="1"/>
         <v>836.28000000000009</v>
       </c>
-      <c r="I24" s="121">
+      <c r="I24" s="98">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J24" s="122">
+      <c r="J24" s="99">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K24" s="123">
+      <c r="K24" s="100">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -7393,7 +7016,7 @@
         <v>452.29080696750003</v>
       </c>
       <c r="L26" s="3" t="str">
-        <f t="shared" ref="L10:L32" si="5">IF(ABS(K26)&lt;=1,"✔ ОК",IF(K26&gt;1,"❗ Превышение","❗ Недосчет"))</f>
+        <f t="shared" ref="L26" si="5">IF(ABS(K26)&lt;=1,"✔ ОК",IF(K26&gt;1,"❗ Превышение","❗ Недосчет"))</f>
         <v>❗ Превышение</v>
       </c>
       <c r="M26" s="40"/>
@@ -7543,33 +7166,33 @@
     <mergeCell ref="F7:H7"/>
     <mergeCell ref="I7:K7"/>
   </mergeCells>
+  <conditionalFormatting sqref="I9:K24 K26 K28:K32">
+    <cfRule type="expression" dxfId="4" priority="1">
+      <formula>AND($K9&lt;&gt;"",$K9&lt;-0.1)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="3" priority="2">
+      <formula>AND($K9&lt;&gt;"",$K9&gt;0.1)</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="L1:L24 L26:L1048576">
-    <cfRule type="containsText" dxfId="9" priority="7" operator="containsText" text="✔ ОК">
+    <cfRule type="containsText" dxfId="2" priority="5" operator="containsText" text="❗ Недосчет">
+      <formula>NOT(ISERROR(SEARCH("❗ Недосчет",L1)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="1" priority="6" operator="containsText" text="❗ Превышение">
+      <formula>NOT(ISERROR(SEARCH("❗ Превышение",L1)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="0" priority="7" operator="containsText" text="✔ ОК">
       <formula>NOT(ISERROR(SEARCH("✔ ОК",L1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="8" priority="6" operator="containsText" text="❗ Превышение">
-      <formula>NOT(ISERROR(SEARCH("❗ Превышение",L1)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="7" priority="5" operator="containsText" text="❗ Недосчет">
-      <formula>NOT(ISERROR(SEARCH("❗ Недосчет",L1)))</formula>
-    </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I9:K24 K26 K28:K32">
-    <cfRule type="expression" dxfId="6" priority="2">
-      <formula>AND($K9&lt;&gt;"",$K9&gt;0.1)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="5" priority="1">
-      <formula>AND($K9&lt;&gt;"",$K9&lt;-0.1)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <dataValidations disablePrompts="1" count="1">
+  <dataValidations count="1">
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C9:D9" xr:uid="{EEAF0B01-A716-45A5-80B9-6D59D6176D06}"/>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" disablePrompts="1" count="4">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="4">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{6E04C081-2925-4DDE-9260-64EC5751E787}">
           <x14:formula1>
             <xm:f>helper!$E$2:$E$10</xm:f>
@@ -7657,11 +7280,11 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="78"/>
-      <c r="L1" s="78"/>
-      <c r="M1" s="78"/>
-      <c r="N1" s="78"/>
-      <c r="O1" s="78"/>
+      <c r="K1" s="110"/>
+      <c r="L1" s="110"/>
+      <c r="M1" s="110"/>
+      <c r="N1" s="110"/>
+      <c r="O1" s="110"/>
     </row>
     <row r="2" spans="1:28" s="11" customFormat="1" ht="29" x14ac:dyDescent="0.35">
       <c r="A2" s="50" t="s">
@@ -7913,13 +7536,13 @@
       <c r="K25"/>
     </row>
     <row r="26" spans="2:11" ht="16" x14ac:dyDescent="0.4">
-      <c r="B26" s="79" t="s">
+      <c r="B26" s="111" t="s">
         <v>120</v>
       </c>
-      <c r="C26" s="79"/>
-      <c r="D26" s="79"/>
-      <c r="E26" s="79"/>
-      <c r="F26" s="79"/>
+      <c r="C26" s="111"/>
+      <c r="D26" s="111"/>
+      <c r="E26" s="111"/>
+      <c r="F26" s="111"/>
       <c r="G26"/>
       <c r="H26"/>
       <c r="I26"/>
@@ -8978,216 +8601,216 @@
       </c>
     </row>
     <row r="2" spans="1:4" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="76">
+      <c r="A2" s="75">
         <v>45627</v>
       </c>
-      <c r="B2" s="81"/>
-      <c r="C2" s="80"/>
-      <c r="D2" s="80"/>
+      <c r="B2" s="78"/>
+      <c r="C2" s="77"/>
+      <c r="D2" s="77"/>
     </row>
     <row r="3" spans="1:4" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="76">
+      <c r="A3" s="75">
         <v>45658</v>
       </c>
-      <c r="B3" s="81"/>
-      <c r="C3" s="80"/>
-      <c r="D3" s="80"/>
+      <c r="B3" s="78"/>
+      <c r="C3" s="77"/>
+      <c r="D3" s="77"/>
     </row>
     <row r="4" spans="1:4" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="76">
+      <c r="A4" s="75">
         <v>45689</v>
       </c>
-      <c r="B4" s="81"/>
-      <c r="C4" s="80"/>
-      <c r="D4" s="80"/>
+      <c r="B4" s="78"/>
+      <c r="C4" s="77"/>
+      <c r="D4" s="77"/>
     </row>
     <row r="5" spans="1:4" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="76">
+      <c r="A5" s="75">
         <v>45717</v>
       </c>
-      <c r="B5" s="81"/>
-      <c r="C5" s="80"/>
-      <c r="D5" s="80"/>
+      <c r="B5" s="78"/>
+      <c r="C5" s="77"/>
+      <c r="D5" s="77"/>
     </row>
     <row r="6" spans="1:4" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="76">
+      <c r="A6" s="75">
         <v>45748</v>
       </c>
-      <c r="B6" s="81"/>
-      <c r="C6" s="80"/>
-      <c r="D6" s="80"/>
+      <c r="B6" s="78"/>
+      <c r="C6" s="77"/>
+      <c r="D6" s="77"/>
     </row>
     <row r="7" spans="1:4" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="76">
+      <c r="A7" s="75">
         <v>45778</v>
       </c>
-      <c r="B7" s="81"/>
-      <c r="C7" s="80"/>
-      <c r="D7" s="80"/>
+      <c r="B7" s="78"/>
+      <c r="C7" s="77"/>
+      <c r="D7" s="77"/>
     </row>
     <row r="8" spans="1:4" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="76">
+      <c r="A8" s="75">
         <v>45809</v>
       </c>
-      <c r="B8" s="81"/>
-      <c r="C8" s="80"/>
-      <c r="D8" s="80"/>
+      <c r="B8" s="78"/>
+      <c r="C8" s="77"/>
+      <c r="D8" s="77"/>
     </row>
     <row r="9" spans="1:4" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="76">
+      <c r="A9" s="75">
         <v>45839</v>
       </c>
-      <c r="B9" s="81"/>
-      <c r="C9" s="80"/>
-      <c r="D9" s="80"/>
+      <c r="B9" s="78"/>
+      <c r="C9" s="77"/>
+      <c r="D9" s="77"/>
     </row>
     <row r="10" spans="1:4" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="76">
+      <c r="A10" s="75">
         <v>45870</v>
       </c>
-      <c r="B10" s="81"/>
-      <c r="C10" s="80"/>
-      <c r="D10" s="80"/>
+      <c r="B10" s="78"/>
+      <c r="C10" s="77"/>
+      <c r="D10" s="77"/>
     </row>
     <row r="11" spans="1:4" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="76">
+      <c r="A11" s="75">
         <v>45901</v>
       </c>
-      <c r="B11" s="81"/>
-      <c r="C11" s="80"/>
-      <c r="D11" s="80"/>
+      <c r="B11" s="78"/>
+      <c r="C11" s="77"/>
+      <c r="D11" s="77"/>
     </row>
     <row r="12" spans="1:4" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="76">
+      <c r="A12" s="75">
         <v>45931</v>
       </c>
-      <c r="B12" s="81"/>
-      <c r="C12" s="80"/>
-      <c r="D12" s="80"/>
+      <c r="B12" s="78"/>
+      <c r="C12" s="77"/>
+      <c r="D12" s="77"/>
     </row>
     <row r="13" spans="1:4" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="76">
+      <c r="A13" s="75">
         <v>45962</v>
       </c>
-      <c r="B13" s="81"/>
-      <c r="C13" s="80"/>
-      <c r="D13" s="80"/>
+      <c r="B13" s="78"/>
+      <c r="C13" s="77"/>
+      <c r="D13" s="77"/>
     </row>
     <row r="14" spans="1:4" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="76">
+      <c r="A14" s="75">
         <v>45992</v>
       </c>
-      <c r="B14" s="81"/>
-      <c r="C14" s="80"/>
-      <c r="D14" s="80"/>
+      <c r="B14" s="78"/>
+      <c r="C14" s="77"/>
+      <c r="D14" s="77"/>
     </row>
     <row r="15" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="76">
+      <c r="A15" s="75">
         <v>46023</v>
       </c>
-      <c r="B15" s="81">
+      <c r="B15" s="78">
         <v>1562</v>
       </c>
-      <c r="C15" s="80">
+      <c r="C15" s="77">
         <v>8.3000000000000007</v>
       </c>
-      <c r="D15" s="80">
+      <c r="D15" s="77">
         <v>9.1229999999999993</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="76">
+      <c r="A16" s="75">
         <v>46054</v>
       </c>
-      <c r="B16" s="81">
+      <c r="B16" s="78">
         <v>1763</v>
       </c>
-      <c r="C16" s="80">
+      <c r="C16" s="77">
         <v>12.898</v>
       </c>
-      <c r="D16" s="80">
+      <c r="D16" s="77">
         <v>12.324999999999999</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="76">
+      <c r="A17" s="75">
         <v>46082</v>
       </c>
-      <c r="B17" s="81"/>
-      <c r="C17" s="80"/>
-      <c r="D17" s="80"/>
+      <c r="B17" s="78"/>
+      <c r="C17" s="77"/>
+      <c r="D17" s="77"/>
     </row>
     <row r="18" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="76">
+      <c r="A18" s="75">
         <v>46113</v>
       </c>
-      <c r="B18" s="81"/>
-      <c r="C18" s="80"/>
-      <c r="D18" s="80"/>
+      <c r="B18" s="78"/>
+      <c r="C18" s="77"/>
+      <c r="D18" s="77"/>
     </row>
     <row r="19" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="76">
+      <c r="A19" s="75">
         <v>46143</v>
       </c>
-      <c r="B19" s="81"/>
-      <c r="C19" s="80"/>
-      <c r="D19" s="80"/>
+      <c r="B19" s="78"/>
+      <c r="C19" s="77"/>
+      <c r="D19" s="77"/>
     </row>
     <row r="20" spans="1:4" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="76">
+      <c r="A20" s="75">
         <v>46174</v>
       </c>
-      <c r="B20" s="81"/>
-      <c r="C20" s="80"/>
-      <c r="D20" s="80"/>
+      <c r="B20" s="78"/>
+      <c r="C20" s="77"/>
+      <c r="D20" s="77"/>
     </row>
     <row r="21" spans="1:4" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="76">
+      <c r="A21" s="75">
         <v>46204</v>
       </c>
-      <c r="B21" s="81"/>
-      <c r="C21" s="80"/>
-      <c r="D21" s="80"/>
+      <c r="B21" s="78"/>
+      <c r="C21" s="77"/>
+      <c r="D21" s="77"/>
     </row>
     <row r="22" spans="1:4" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="76">
+      <c r="A22" s="75">
         <v>46235</v>
       </c>
-      <c r="B22" s="81"/>
-      <c r="C22" s="80"/>
-      <c r="D22" s="80"/>
+      <c r="B22" s="78"/>
+      <c r="C22" s="77"/>
+      <c r="D22" s="77"/>
     </row>
     <row r="23" spans="1:4" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="76">
+      <c r="A23" s="75">
         <v>46266</v>
       </c>
-      <c r="B23" s="81"/>
-      <c r="C23" s="80"/>
-      <c r="D23" s="80"/>
+      <c r="B23" s="78"/>
+      <c r="C23" s="77"/>
+      <c r="D23" s="77"/>
     </row>
     <row r="24" spans="1:4" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="76">
+      <c r="A24" s="75">
         <v>46296</v>
       </c>
-      <c r="B24" s="81"/>
-      <c r="C24" s="80"/>
-      <c r="D24" s="80"/>
+      <c r="B24" s="78"/>
+      <c r="C24" s="77"/>
+      <c r="D24" s="77"/>
     </row>
     <row r="25" spans="1:4" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="76">
+      <c r="A25" s="75">
         <v>46327</v>
       </c>
-      <c r="B25" s="81"/>
-      <c r="C25" s="80"/>
-      <c r="D25" s="80"/>
+      <c r="B25" s="78"/>
+      <c r="C25" s="77"/>
+      <c r="D25" s="77"/>
     </row>
     <row r="26" spans="1:4" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="76">
+      <c r="A26" s="75">
         <v>46357</v>
       </c>
-      <c r="B26" s="81"/>
-      <c r="C26" s="80"/>
-      <c r="D26" s="80"/>
+      <c r="B26" s="78"/>
+      <c r="C26" s="77"/>
+      <c r="D26" s="77"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9232,112 +8855,112 @@
       <c r="B1" s="51" t="s">
         <v>76</v>
       </c>
-      <c r="C1" s="82">
+      <c r="C1" s="79">
         <v>45292</v>
       </c>
-      <c r="D1" s="82">
+      <c r="D1" s="79">
         <v>45323</v>
       </c>
-      <c r="E1" s="82">
+      <c r="E1" s="79">
         <v>45352</v>
       </c>
-      <c r="F1" s="82">
+      <c r="F1" s="79">
         <v>45383</v>
       </c>
-      <c r="G1" s="82">
+      <c r="G1" s="79">
         <v>45413</v>
       </c>
-      <c r="H1" s="82">
+      <c r="H1" s="79">
         <v>45444</v>
       </c>
-      <c r="I1" s="82">
+      <c r="I1" s="79">
         <v>45474</v>
       </c>
-      <c r="J1" s="82">
+      <c r="J1" s="79">
         <v>45505</v>
       </c>
-      <c r="K1" s="82">
+      <c r="K1" s="79">
         <v>45536</v>
       </c>
-      <c r="L1" s="82">
+      <c r="L1" s="79">
         <v>45566</v>
       </c>
-      <c r="M1" s="82">
+      <c r="M1" s="79">
         <v>45597</v>
       </c>
-      <c r="N1" s="82">
+      <c r="N1" s="79">
         <v>45627</v>
       </c>
-      <c r="O1" s="82">
+      <c r="O1" s="79">
         <v>45658</v>
       </c>
-      <c r="P1" s="82">
+      <c r="P1" s="79">
         <v>45689</v>
       </c>
-      <c r="Q1" s="82">
+      <c r="Q1" s="79">
         <v>45717</v>
       </c>
-      <c r="R1" s="82">
+      <c r="R1" s="79">
         <v>45748</v>
       </c>
-      <c r="S1" s="82">
+      <c r="S1" s="79">
         <v>45778</v>
       </c>
-      <c r="T1" s="82">
+      <c r="T1" s="79">
         <v>45809</v>
       </c>
-      <c r="U1" s="82">
+      <c r="U1" s="79">
         <v>45839</v>
       </c>
-      <c r="V1" s="82">
+      <c r="V1" s="79">
         <v>45870</v>
       </c>
-      <c r="W1" s="82">
+      <c r="W1" s="79">
         <v>45901</v>
       </c>
-      <c r="X1" s="82">
+      <c r="X1" s="79">
         <v>45931</v>
       </c>
-      <c r="Y1" s="82">
+      <c r="Y1" s="79">
         <v>45962</v>
       </c>
-      <c r="Z1" s="82">
+      <c r="Z1" s="79">
         <v>45992</v>
       </c>
-      <c r="AA1" s="82">
+      <c r="AA1" s="79">
         <v>46023</v>
       </c>
-      <c r="AB1" s="82">
+      <c r="AB1" s="79">
         <v>46054</v>
       </c>
-      <c r="AC1" s="82">
+      <c r="AC1" s="79">
         <v>46082</v>
       </c>
-      <c r="AD1" s="82">
+      <c r="AD1" s="79">
         <v>46113</v>
       </c>
-      <c r="AE1" s="82">
+      <c r="AE1" s="79">
         <v>46143</v>
       </c>
-      <c r="AF1" s="82">
+      <c r="AF1" s="79">
         <v>46174</v>
       </c>
-      <c r="AG1" s="82">
+      <c r="AG1" s="79">
         <v>46204</v>
       </c>
-      <c r="AH1" s="82">
+      <c r="AH1" s="79">
         <v>46235</v>
       </c>
-      <c r="AI1" s="82">
+      <c r="AI1" s="79">
         <v>46266</v>
       </c>
-      <c r="AJ1" s="82">
+      <c r="AJ1" s="79">
         <v>46296</v>
       </c>
-      <c r="AK1" s="82">
+      <c r="AK1" s="79">
         <v>46327</v>
       </c>
-      <c r="AL1" s="82">
+      <c r="AL1" s="79">
         <v>46357</v>
       </c>
       <c r="AM1" s="51" t="s">
@@ -9462,7 +9085,7 @@
       <c r="AM2" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="AN2" s="85" t="s">
+      <c r="AN2" s="82" t="s">
         <v>148</v>
       </c>
     </row>
@@ -9701,7 +9324,7 @@
       <c r="AM4" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="AN4" s="85" t="s">
+      <c r="AN4" s="82" t="s">
         <v>149</v>
       </c>
     </row>
@@ -10444,7 +10067,7 @@
       <c r="AM10" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="AN10" s="85" t="s">
+      <c r="AN10" s="82" t="s">
         <v>150</v>
       </c>
     </row>
@@ -10566,7 +10189,7 @@
       <c r="AM11" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="AN11" s="85" t="s">
+      <c r="AN11" s="82" t="s">
         <v>151</v>
       </c>
     </row>
@@ -11731,27 +11354,27 @@
       <c r="B38" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="C38" s="86">
+      <c r="C38" s="83">
         <f>C37*C36*C35/12</f>
         <v>132.34105224799995</v>
       </c>
-      <c r="I38" s="86">
+      <c r="I38" s="83">
         <f>I37*I36*I35/12</f>
         <v>144.91470621139999</v>
       </c>
-      <c r="O38" s="86">
+      <c r="O38" s="83">
         <f>O37*O36*O35/12</f>
         <v>171.78310199199996</v>
       </c>
-      <c r="U38" s="86">
+      <c r="U38" s="83">
         <f>U37*U36*U35/12</f>
         <v>158.82299893999999</v>
       </c>
-      <c r="AA38" s="86">
-        <f t="shared" ref="AA38:AB38" si="6">AA37*AA36*AA35/12</f>
+      <c r="AA38" s="83">
+        <f t="shared" ref="AA38" si="6">AA37*AA36*AA35/12</f>
         <v>161.52257251624999</v>
       </c>
-      <c r="AG38" s="86">
+      <c r="AG38" s="83">
         <f>AG37*AG36*AG35/12</f>
         <v>161.52257251624999</v>
       </c>

--- a/bill-checker-demo.xlsx
+++ b/bill-checker-demo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alinaaleks\Downloads\GitHub\bill-checker\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{961B5253-F0CD-425C-92F3-83AFBD41F43E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{414D04C1-FFAC-4D71-801B-AD5147F344EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="462" uniqueCount="198">
   <si>
     <t>РЕГИОН</t>
   </si>
@@ -530,6 +530,114 @@
   </si>
   <si>
     <t>Отклонение по месяцам</t>
+  </si>
+  <si>
+    <t>204,0</t>
+  </si>
+  <si>
+    <t>4,2</t>
+  </si>
+  <si>
+    <t>856,8</t>
+  </si>
+  <si>
+    <t>4,598</t>
+  </si>
+  <si>
+    <t>62,98</t>
+  </si>
+  <si>
+    <t>289,6</t>
+  </si>
+  <si>
+    <t>44,12</t>
+  </si>
+  <si>
+    <t>202,86</t>
+  </si>
+  <si>
+    <t>3,202</t>
+  </si>
+  <si>
+    <t>201,66</t>
+  </si>
+  <si>
+    <t>141,27</t>
+  </si>
+  <si>
+    <t>6,952</t>
+  </si>
+  <si>
+    <t>227,18</t>
+  </si>
+  <si>
+    <t>1579,36</t>
+  </si>
+  <si>
+    <t>1,7152</t>
+  </si>
+  <si>
+    <t>3549,74</t>
+  </si>
+  <si>
+    <t>6535,25</t>
+  </si>
+  <si>
+    <t>3,000</t>
+  </si>
+  <si>
+    <t>681,54</t>
+  </si>
+  <si>
+    <t>0,680</t>
+  </si>
+  <si>
+    <t>42,83</t>
+  </si>
+  <si>
+    <t>1,360</t>
+  </si>
+  <si>
+    <t>85,65</t>
+  </si>
+  <si>
+    <t>60,00</t>
+  </si>
+  <si>
+    <t>26,83</t>
+  </si>
+  <si>
+    <t>112,69</t>
+  </si>
+  <si>
+    <t>55,2</t>
+  </si>
+  <si>
+    <t>11,08</t>
+  </si>
+  <si>
+    <t>611,62</t>
+  </si>
+  <si>
+    <t>5,98</t>
+  </si>
+  <si>
+    <t>330,10</t>
+  </si>
+  <si>
+    <t>2,0</t>
+  </si>
+  <si>
+    <t>161,5226</t>
+  </si>
+  <si>
+    <t>316,00</t>
+  </si>
+  <si>
+    <t>15,15</t>
+  </si>
+  <si>
+    <t>836,28</t>
   </si>
 </sst>
 </file>
@@ -7083,13 +7191,14 @@
     <col min="3" max="3" width="9" style="3" customWidth="1"/>
     <col min="4" max="4" width="11" style="3" customWidth="1"/>
     <col min="5" max="5" width="11.26953125" style="3" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="11.26953125" style="3" customWidth="1" outlineLevel="1"/>
-    <col min="8" max="8" width="11.36328125" style="3" customWidth="1" outlineLevel="1"/>
-    <col min="9" max="10" width="11.26953125" style="3" customWidth="1"/>
+    <col min="6" max="7" width="11.26953125" style="3" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="8" max="8" width="11.36328125" style="3" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="9" max="9" width="11.26953125" style="3" customWidth="1" collapsed="1"/>
+    <col min="10" max="10" width="11.26953125" style="3" customWidth="1"/>
     <col min="11" max="11" width="11.36328125" style="3" customWidth="1"/>
     <col min="12" max="12" width="14.90625" style="3" customWidth="1"/>
-    <col min="13" max="13" width="16.7265625" style="3" customWidth="1"/>
-    <col min="14" max="14" width="10.36328125" style="3" customWidth="1"/>
+    <col min="13" max="13" width="16.7265625" style="3" hidden="1" customWidth="1"/>
+    <col min="14" max="14" width="10.36328125" style="3" hidden="1" customWidth="1"/>
     <col min="15" max="16384" width="9.1796875" style="3"/>
   </cols>
   <sheetData>
@@ -7097,9 +7206,9 @@
       <c r="A1" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="B1" s="62" t="e">
+      <c r="B1" s="62">
         <f>EDATE(B3, -1)</f>
-        <v>#NUM!</v>
+        <v>46023</v>
       </c>
       <c r="F1"/>
     </row>
@@ -7111,7 +7220,9 @@
       <c r="A3" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B3" s="62"/>
+      <c r="B3" s="62">
+        <v>46054</v>
+      </c>
       <c r="F3"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.35">
@@ -7210,44 +7321,50 @@
       <c r="B9" s="20" t="s">
         <v>44</v>
       </c>
-      <c r="C9" s="80"/>
-      <c r="D9" s="74"/>
-      <c r="E9" s="94"/>
-      <c r="F9" s="98" t="str">
+      <c r="C9" s="80" t="s">
+        <v>162</v>
+      </c>
+      <c r="D9" s="74" t="s">
+        <v>163</v>
+      </c>
+      <c r="E9" s="94" t="s">
+        <v>164</v>
+      </c>
+      <c r="F9" s="98">
         <f>IFERROR(INDEX(usage!B:B, MATCH(CHECK!$B$3, usage!A:A, 0)) - INDEX(usage!B:B, MATCH(CHECK!$B$1, usage!A:A, 0)),"")</f>
-        <v/>
-      </c>
-      <c r="G9" s="99" t="str">
+        <v>201</v>
+      </c>
+      <c r="G9" s="99">
         <f>IFERROR(IF(F9&lt;INDEX(tariffs!16:16,MATCH(CHECK!$B$3,tariffs!$1:$1,0)),INDEX(tariffs!2:2,MATCH(CHECK!$B$3,tariffs!$1:$1,0)),INDEX(tariffs!3:3,MATCH(CHECK!$B$3,tariffs!$1:$1,0))),"")</f>
-        <v/>
-      </c>
-      <c r="H9" s="96" t="str">
+        <v>4.2</v>
+      </c>
+      <c r="H9" s="96">
         <f>IFERROR(F9*G9,"")</f>
-        <v/>
-      </c>
-      <c r="I9" s="89" t="str">
+        <v>844.2</v>
+      </c>
+      <c r="I9" s="89">
         <f>IF(C9="", "", C9-F9)</f>
-        <v/>
-      </c>
-      <c r="J9" s="33" t="str">
+        <v>3</v>
+      </c>
+      <c r="J9" s="33">
         <f t="shared" ref="J9:K24" si="0">IF(D9="", "", D9-G9)</f>
-        <v/>
-      </c>
-      <c r="K9" s="90" t="str">
+        <v>0</v>
+      </c>
+      <c r="K9" s="90">
         <f t="shared" si="0"/>
-        <v/>
+        <v>12.599999999999909</v>
       </c>
       <c r="L9" s="3" t="str">
         <f>IF(K9="","",IF(ABS(K9)&lt;=1,"✔ ОК",IF(K9&gt;1,"❗ Превышение","❗ Недосчет")))</f>
-        <v/>
+        <v>❗ Превышение</v>
       </c>
       <c r="M9" s="123" t="str">
         <f>VLOOKUP(A9,info!A13:B29, 2,FALSE)</f>
         <v>Поставщик света</v>
       </c>
-      <c r="N9" s="124" t="str">
+      <c r="N9" s="124">
         <f>IF($B$3="","",IFERROR($B$3,""))</f>
-        <v/>
+        <v>46054</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -7257,44 +7374,50 @@
       <c r="B10" s="20" t="s">
         <v>45</v>
       </c>
-      <c r="C10" s="81"/>
-      <c r="D10" s="74"/>
-      <c r="E10" s="94"/>
-      <c r="F10" s="100" t="str">
+      <c r="C10" s="81" t="s">
+        <v>165</v>
+      </c>
+      <c r="D10" s="74" t="s">
+        <v>166</v>
+      </c>
+      <c r="E10" s="94" t="s">
+        <v>167</v>
+      </c>
+      <c r="F10" s="100">
         <f>IFERROR(INDEX(usage!C:C, MATCH(CHECK!$B$3, usage!A:A, 0)) - INDEX(usage!C:C, MATCH(CHECK!$B$1, usage!A:A, 0)),"")</f>
-        <v/>
-      </c>
-      <c r="G10" s="99" t="str">
+        <v>4.597999999999999</v>
+      </c>
+      <c r="G10" s="99">
         <f>IFERROR(INDEX(tariffs!4:4,MATCH(CHECK!$B$3,tariffs!$1:$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H10" s="96" t="str">
+        <v>62.98</v>
+      </c>
+      <c r="H10" s="96">
         <f t="shared" ref="H10:H24" si="1">IFERROR(F10*G10,"")</f>
-        <v/>
-      </c>
-      <c r="I10" s="89" t="str">
+        <v>289.58203999999995</v>
+      </c>
+      <c r="I10" s="89">
         <f t="shared" ref="I10:I24" si="2">IF(C10="", "", C10-F10)</f>
-        <v/>
-      </c>
-      <c r="J10" s="33" t="str">
+        <v>8.8817841970012523E-16</v>
+      </c>
+      <c r="J10" s="33">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K10" s="90" t="str">
+        <v>0</v>
+      </c>
+      <c r="K10" s="90">
         <f t="shared" si="0"/>
-        <v/>
+        <v>1.7960000000073251E-2</v>
       </c>
       <c r="L10" s="3" t="str">
         <f t="shared" ref="L10:L24" si="3">IF(K10="","",IF(ABS(K10)&lt;=1,"✔ ОК",IF(K10&gt;1,"❗ Превышение","❗ Недосчет")))</f>
-        <v/>
+        <v>✔ ОК</v>
       </c>
       <c r="M10" s="123" t="str">
         <f>VLOOKUP(A10,info!A14:B30, 2,FALSE)</f>
         <v>Поставщик воды</v>
       </c>
-      <c r="N10" s="124" t="str">
+      <c r="N10" s="124">
         <f t="shared" ref="N10:N24" si="4">IF($B$3="","",IFERROR($B$3,""))</f>
-        <v/>
+        <v>46054</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -7304,44 +7427,50 @@
       <c r="B11" s="20" t="s">
         <v>45</v>
       </c>
-      <c r="C11" s="81"/>
-      <c r="D11" s="74"/>
-      <c r="E11" s="94"/>
-      <c r="F11" s="100" t="str">
+      <c r="C11" s="81" t="s">
+        <v>165</v>
+      </c>
+      <c r="D11" s="74" t="s">
+        <v>168</v>
+      </c>
+      <c r="E11" s="94" t="s">
+        <v>169</v>
+      </c>
+      <c r="F11" s="100">
         <f>F10</f>
-        <v/>
-      </c>
-      <c r="G11" s="99" t="str">
+        <v>4.597999999999999</v>
+      </c>
+      <c r="G11" s="99">
         <f>IFERROR(INDEX(tariffs!5:5,MATCH(CHECK!$B$3,tariffs!$1:$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H11" s="96" t="str">
+        <v>44.12</v>
+      </c>
+      <c r="H11" s="96">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="I11" s="89" t="str">
+        <v>202.86375999999996</v>
+      </c>
+      <c r="I11" s="89">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J11" s="33" t="str">
+        <v>8.8817841970012523E-16</v>
+      </c>
+      <c r="J11" s="33">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K11" s="90" t="str">
+        <v>0</v>
+      </c>
+      <c r="K11" s="90">
         <f t="shared" si="0"/>
-        <v/>
+        <v>-3.7599999999429201E-3</v>
       </c>
       <c r="L11" s="3" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>✔ ОК</v>
       </c>
       <c r="M11" s="123" t="str">
         <f>VLOOKUP(A11,info!A15:B31, 2,FALSE)</f>
         <v>Поставщик воды</v>
       </c>
-      <c r="N11" s="124" t="str">
+      <c r="N11" s="124">
         <f t="shared" si="4"/>
-        <v/>
+        <v>46054</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -7351,44 +7480,50 @@
       <c r="B12" s="20" t="s">
         <v>45</v>
       </c>
-      <c r="C12" s="81"/>
-      <c r="D12" s="74"/>
-      <c r="E12" s="94"/>
-      <c r="F12" s="100" t="str">
+      <c r="C12" s="81" t="s">
+        <v>170</v>
+      </c>
+      <c r="D12" s="74" t="s">
+        <v>166</v>
+      </c>
+      <c r="E12" s="94" t="s">
+        <v>171</v>
+      </c>
+      <c r="F12" s="100">
         <f>IFERROR(INDEX(usage!D:D, MATCH(CHECK!$B$3, usage!A:A, 0)) - INDEX(usage!D:D, MATCH(CHECK!$B$1, usage!A:A, 0)),"")</f>
-        <v/>
-      </c>
-      <c r="G12" s="99" t="str">
+        <v>3.202</v>
+      </c>
+      <c r="G12" s="99">
         <f>IFERROR(INDEX(tariffs!4:4,MATCH(CHECK!$B$3,tariffs!$1:$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H12" s="96" t="str">
+        <v>62.98</v>
+      </c>
+      <c r="H12" s="96">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="I12" s="89" t="str">
+        <v>201.66195999999999</v>
+      </c>
+      <c r="I12" s="89">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J12" s="33" t="str">
+        <v>0</v>
+      </c>
+      <c r="J12" s="33">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K12" s="90" t="str">
+        <v>0</v>
+      </c>
+      <c r="K12" s="90">
         <f t="shared" si="0"/>
-        <v/>
+        <v>-1.9599999999968531E-3</v>
       </c>
       <c r="L12" s="3" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>✔ ОК</v>
       </c>
       <c r="M12" s="123" t="str">
         <f>VLOOKUP(A12,info!A16:B32, 2,FALSE)</f>
         <v>Поставщик воды</v>
       </c>
-      <c r="N12" s="124" t="str">
+      <c r="N12" s="124">
         <f t="shared" si="4"/>
-        <v/>
+        <v>46054</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -7398,44 +7533,50 @@
       <c r="B13" s="20" t="s">
         <v>45</v>
       </c>
-      <c r="C13" s="81"/>
-      <c r="D13" s="74"/>
-      <c r="E13" s="94"/>
-      <c r="F13" s="100" t="str">
+      <c r="C13" s="81" t="s">
+        <v>170</v>
+      </c>
+      <c r="D13" s="74" t="s">
+        <v>168</v>
+      </c>
+      <c r="E13" s="94" t="s">
+        <v>172</v>
+      </c>
+      <c r="F13" s="100">
         <f>F12</f>
-        <v/>
-      </c>
-      <c r="G13" s="99" t="str">
+        <v>3.202</v>
+      </c>
+      <c r="G13" s="99">
         <f>IFERROR(INDEX(tariffs!5:5,MATCH(CHECK!$B$3,tariffs!$1:$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H13" s="96" t="str">
+        <v>44.12</v>
+      </c>
+      <c r="H13" s="96">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="I13" s="89" t="str">
+        <v>141.27223999999998</v>
+      </c>
+      <c r="I13" s="89">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J13" s="33" t="str">
+        <v>0</v>
+      </c>
+      <c r="J13" s="33">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K13" s="90" t="str">
+        <v>0</v>
+      </c>
+      <c r="K13" s="90">
         <f t="shared" si="0"/>
-        <v/>
+        <v>-2.2399999999720421E-3</v>
       </c>
       <c r="L13" s="3" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>✔ ОК</v>
       </c>
       <c r="M13" s="123" t="str">
         <f>VLOOKUP(A13,info!A17:B33, 2,FALSE)</f>
         <v>Поставщик воды</v>
       </c>
-      <c r="N13" s="124" t="str">
+      <c r="N13" s="124">
         <f t="shared" si="4"/>
-        <v/>
+        <v>46054</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -7445,44 +7586,50 @@
       <c r="B14" s="20" t="s">
         <v>45</v>
       </c>
-      <c r="C14" s="82"/>
-      <c r="D14" s="75"/>
-      <c r="E14" s="94"/>
+      <c r="C14" s="82" t="s">
+        <v>173</v>
+      </c>
+      <c r="D14" s="75" t="s">
+        <v>174</v>
+      </c>
+      <c r="E14" s="94" t="s">
+        <v>175</v>
+      </c>
       <c r="F14" s="100" t="str">
         <f>IF(C14="","",IFERROR(C14,""))</f>
-        <v/>
-      </c>
-      <c r="G14" s="99" t="str">
+        <v>6,952</v>
+      </c>
+      <c r="G14" s="99">
         <f>IFERROR(INDEX(tariffs!6:6,MATCH(CHECK!$B$3,tariffs!$1:$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H14" s="96" t="str">
+        <v>227.18</v>
+      </c>
+      <c r="H14" s="96">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="I14" s="89" t="str">
+        <v>1579.35536</v>
+      </c>
+      <c r="I14" s="89">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J14" s="33" t="str">
+        <v>0</v>
+      </c>
+      <c r="J14" s="33">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K14" s="90" t="str">
+        <v>0</v>
+      </c>
+      <c r="K14" s="90">
         <f t="shared" si="0"/>
-        <v/>
+        <v>4.6399999998811836E-3</v>
       </c>
       <c r="L14" s="3" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>✔ ОК</v>
       </c>
       <c r="M14" s="123" t="str">
         <f>VLOOKUP(A14,info!A18:B34, 2,FALSE)</f>
         <v>Управляющая</v>
       </c>
-      <c r="N14" s="124" t="str">
+      <c r="N14" s="124">
         <f t="shared" si="4"/>
-        <v/>
+        <v>46054</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -7492,44 +7639,50 @@
       <c r="B15" s="20" t="s">
         <v>47</v>
       </c>
-      <c r="C15" s="81"/>
-      <c r="D15" s="75"/>
-      <c r="E15" s="94"/>
+      <c r="C15" s="81" t="s">
+        <v>176</v>
+      </c>
+      <c r="D15" s="75" t="s">
+        <v>177</v>
+      </c>
+      <c r="E15" s="94" t="s">
+        <v>178</v>
+      </c>
       <c r="F15" s="100" t="str">
         <f>IF(C15="","",IFERROR(C15,""))</f>
-        <v/>
-      </c>
-      <c r="G15" s="99" t="str">
+        <v>1,7152</v>
+      </c>
+      <c r="G15" s="99">
         <f>IFERROR(INDEX(tariffs!7:7,MATCH(CHECK!$B$3,tariffs!$1:$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H15" s="96" t="str">
+        <v>3549.74</v>
+      </c>
+      <c r="H15" s="96">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="I15" s="89" t="str">
+        <v>6088.514048</v>
+      </c>
+      <c r="I15" s="89">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J15" s="33" t="str">
+        <v>0</v>
+      </c>
+      <c r="J15" s="33">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K15" s="90" t="str">
+        <v>0</v>
+      </c>
+      <c r="K15" s="90">
         <f t="shared" si="0"/>
-        <v/>
+        <v>446.735952</v>
       </c>
       <c r="L15" s="3" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>❗ Превышение</v>
       </c>
       <c r="M15" s="123" t="str">
         <f>VLOOKUP(A15,info!A19:B35, 2,FALSE)</f>
         <v>Управляющая</v>
       </c>
-      <c r="N15" s="124" t="str">
+      <c r="N15" s="124">
         <f t="shared" si="4"/>
-        <v/>
+        <v>46054</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -7539,44 +7692,50 @@
       <c r="B16" s="20" t="s">
         <v>45</v>
       </c>
-      <c r="C16" s="81"/>
-      <c r="D16" s="74"/>
-      <c r="E16" s="94"/>
+      <c r="C16" s="81" t="s">
+        <v>179</v>
+      </c>
+      <c r="D16" s="74" t="s">
+        <v>174</v>
+      </c>
+      <c r="E16" s="94" t="s">
+        <v>180</v>
+      </c>
       <c r="F16" s="100" t="str">
         <f t="shared" ref="F16:F20" si="5">IF(C16="","",IFERROR(C16,""))</f>
-        <v/>
-      </c>
-      <c r="G16" s="99" t="str">
+        <v>3,000</v>
+      </c>
+      <c r="G16" s="99">
         <f>IFERROR(INDEX(tariffs!6:6,MATCH(CHECK!$B$3,tariffs!$1:$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H16" s="96" t="str">
+        <v>227.18</v>
+      </c>
+      <c r="H16" s="96">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="I16" s="89" t="str">
+        <v>681.54</v>
+      </c>
+      <c r="I16" s="89">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J16" s="33" t="str">
+        <v>0</v>
+      </c>
+      <c r="J16" s="33">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K16" s="90" t="str">
+        <v>0</v>
+      </c>
+      <c r="K16" s="90">
         <f t="shared" si="0"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="L16" s="3" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>✔ ОК</v>
       </c>
       <c r="M16" s="123" t="str">
         <f>VLOOKUP(A16,info!A20:B36, 2,FALSE)</f>
         <v>Управляющая</v>
       </c>
-      <c r="N16" s="124" t="str">
+      <c r="N16" s="124">
         <f t="shared" si="4"/>
-        <v/>
+        <v>46054</v>
       </c>
     </row>
     <row r="17" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -7586,44 +7745,50 @@
       <c r="B17" s="20" t="s">
         <v>45</v>
       </c>
-      <c r="C17" s="81"/>
-      <c r="D17" s="74"/>
-      <c r="E17" s="94"/>
+      <c r="C17" s="81" t="s">
+        <v>181</v>
+      </c>
+      <c r="D17" s="74" t="s">
+        <v>166</v>
+      </c>
+      <c r="E17" s="94" t="s">
+        <v>182</v>
+      </c>
       <c r="F17" s="100" t="str">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G17" s="99" t="str">
+        <v>0,680</v>
+      </c>
+      <c r="G17" s="99">
         <f>IFERROR(INDEX(tariffs!4:4,MATCH(CHECK!$B$3,tariffs!$1:$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H17" s="96" t="str">
+        <v>62.98</v>
+      </c>
+      <c r="H17" s="96">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="I17" s="89" t="str">
+        <v>42.8264</v>
+      </c>
+      <c r="I17" s="89">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J17" s="33" t="str">
+        <v>0</v>
+      </c>
+      <c r="J17" s="33">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K17" s="90" t="str">
+        <v>0</v>
+      </c>
+      <c r="K17" s="90">
         <f t="shared" si="0"/>
-        <v/>
+        <v>3.5999999999987153E-3</v>
       </c>
       <c r="L17" s="3" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>✔ ОК</v>
       </c>
       <c r="M17" s="123" t="str">
         <f>VLOOKUP(A17,info!A21:B37, 2,FALSE)</f>
         <v>Управляющая</v>
       </c>
-      <c r="N17" s="124" t="str">
+      <c r="N17" s="124">
         <f t="shared" si="4"/>
-        <v/>
+        <v>46054</v>
       </c>
     </row>
     <row r="18" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -7633,44 +7798,50 @@
       <c r="B18" s="20" t="s">
         <v>45</v>
       </c>
-      <c r="C18" s="81"/>
-      <c r="D18" s="75"/>
-      <c r="E18" s="94"/>
+      <c r="C18" s="81" t="s">
+        <v>183</v>
+      </c>
+      <c r="D18" s="75" t="s">
+        <v>166</v>
+      </c>
+      <c r="E18" s="94" t="s">
+        <v>184</v>
+      </c>
       <c r="F18" s="100" t="str">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G18" s="99" t="str">
+        <v>1,360</v>
+      </c>
+      <c r="G18" s="99">
         <f>IFERROR(INDEX(tariffs!4:4,MATCH(CHECK!$B$3,tariffs!$1:$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H18" s="96" t="str">
+        <v>62.98</v>
+      </c>
+      <c r="H18" s="96">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="I18" s="89" t="str">
+        <v>85.652799999999999</v>
+      </c>
+      <c r="I18" s="89">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J18" s="33" t="str">
+        <v>0</v>
+      </c>
+      <c r="J18" s="33">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K18" s="90" t="str">
+        <v>0</v>
+      </c>
+      <c r="K18" s="90">
         <f t="shared" si="0"/>
-        <v/>
+        <v>-2.7999999999934744E-3</v>
       </c>
       <c r="L18" s="3" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>✔ ОК</v>
       </c>
       <c r="M18" s="123" t="str">
         <f>VLOOKUP(A18,info!A22:B38, 2,FALSE)</f>
         <v>Управляющая</v>
       </c>
-      <c r="N18" s="124" t="str">
+      <c r="N18" s="124">
         <f t="shared" si="4"/>
-        <v/>
+        <v>46054</v>
       </c>
     </row>
     <row r="19" spans="1:14" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -7680,44 +7851,50 @@
       <c r="B19" s="20" t="s">
         <v>45</v>
       </c>
-      <c r="C19" s="81"/>
-      <c r="D19" s="75"/>
-      <c r="E19" s="94"/>
+      <c r="C19" s="81" t="s">
+        <v>183</v>
+      </c>
+      <c r="D19" s="75" t="s">
+        <v>168</v>
+      </c>
+      <c r="E19" s="94" t="s">
+        <v>185</v>
+      </c>
       <c r="F19" s="100" t="str">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G19" s="99" t="str">
+        <v>1,360</v>
+      </c>
+      <c r="G19" s="99">
         <f>IFERROR(INDEX(tariffs!5:5,MATCH(CHECK!$B$3,tariffs!$1:$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H19" s="96" t="str">
+        <v>44.12</v>
+      </c>
+      <c r="H19" s="96">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="I19" s="89" t="str">
+        <v>60.0032</v>
+      </c>
+      <c r="I19" s="89">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J19" s="33" t="str">
+        <v>0</v>
+      </c>
+      <c r="J19" s="33">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K19" s="90" t="str">
+        <v>0</v>
+      </c>
+      <c r="K19" s="90">
         <f t="shared" si="0"/>
-        <v/>
+        <v>-3.1999999999996476E-3</v>
       </c>
       <c r="L19" s="3" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>✔ ОК</v>
       </c>
       <c r="M19" s="123" t="str">
         <f>VLOOKUP(A19,info!A23:B39, 2,FALSE)</f>
         <v>Управляющая</v>
       </c>
-      <c r="N19" s="124" t="str">
+      <c r="N19" s="124">
         <f t="shared" si="4"/>
-        <v/>
+        <v>46054</v>
       </c>
     </row>
     <row r="20" spans="1:14" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -7727,44 +7904,50 @@
       <c r="B20" s="20" t="s">
         <v>44</v>
       </c>
-      <c r="C20" s="81"/>
-      <c r="D20" s="74"/>
-      <c r="E20" s="94"/>
+      <c r="C20" s="81" t="s">
+        <v>186</v>
+      </c>
+      <c r="D20" s="74" t="s">
+        <v>163</v>
+      </c>
+      <c r="E20" s="94" t="s">
+        <v>187</v>
+      </c>
       <c r="F20" s="100" t="str">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G20" s="99" t="str">
+        <v>26,83</v>
+      </c>
+      <c r="G20" s="99">
         <f>IFERROR(INDEX(tariffs!2:2,MATCH(CHECK!$B$3,tariffs!$1:$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H20" s="96" t="str">
+        <v>4.2</v>
+      </c>
+      <c r="H20" s="96">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="I20" s="89" t="str">
+        <v>112.68599999999999</v>
+      </c>
+      <c r="I20" s="89">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J20" s="33" t="str">
+        <v>0</v>
+      </c>
+      <c r="J20" s="33">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K20" s="90" t="str">
+        <v>0</v>
+      </c>
+      <c r="K20" s="90">
         <f t="shared" si="0"/>
-        <v/>
+        <v>4.0000000000048885E-3</v>
       </c>
       <c r="L20" s="3" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>✔ ОК</v>
       </c>
       <c r="M20" s="123" t="str">
         <f>VLOOKUP(A20,info!A24:B40, 2,FALSE)</f>
         <v>Управляющая</v>
       </c>
-      <c r="N20" s="124" t="str">
+      <c r="N20" s="124">
         <f t="shared" si="4"/>
-        <v/>
+        <v>46054</v>
       </c>
     </row>
     <row r="21" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -7774,44 +7957,50 @@
       <c r="B21" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="C21" s="81"/>
-      <c r="D21" s="74"/>
-      <c r="E21" s="94"/>
+      <c r="C21" s="81" t="s">
+        <v>188</v>
+      </c>
+      <c r="D21" s="74" t="s">
+        <v>189</v>
+      </c>
+      <c r="E21" s="94" t="s">
+        <v>190</v>
+      </c>
       <c r="F21" s="101">
         <f>IF($B$4="","",IFERROR($B$4,""))</f>
         <v>55.2</v>
       </c>
-      <c r="G21" s="99" t="str">
+      <c r="G21" s="99">
         <f>IFERROR(INDEX(tariffs!8:8,MATCH(CHECK!$B$3,tariffs!$1:$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H21" s="96" t="str">
+        <v>11.08</v>
+      </c>
+      <c r="H21" s="96">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="I21" s="89" t="str">
+        <v>611.61599999999999</v>
+      </c>
+      <c r="I21" s="89">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J21" s="33" t="str">
+        <v>0</v>
+      </c>
+      <c r="J21" s="33">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K21" s="90" t="str">
+        <v>0</v>
+      </c>
+      <c r="K21" s="90">
         <f t="shared" si="0"/>
-        <v/>
+        <v>4.0000000000190994E-3</v>
       </c>
       <c r="L21" s="3" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>✔ ОК</v>
       </c>
       <c r="M21" s="123" t="str">
         <f>VLOOKUP(A21,info!A25:B41, 2,FALSE)</f>
         <v>Управляющая</v>
       </c>
-      <c r="N21" s="124" t="str">
+      <c r="N21" s="124">
         <f t="shared" si="4"/>
-        <v/>
+        <v>46054</v>
       </c>
     </row>
     <row r="22" spans="1:14" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -7821,44 +8010,50 @@
       <c r="B22" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="C22" s="81"/>
-      <c r="D22" s="74"/>
-      <c r="E22" s="94"/>
+      <c r="C22" s="81" t="s">
+        <v>188</v>
+      </c>
+      <c r="D22" s="74" t="s">
+        <v>191</v>
+      </c>
+      <c r="E22" s="94" t="s">
+        <v>192</v>
+      </c>
       <c r="F22" s="101">
         <f>IF($B$4="","",IFERROR($B$4,""))</f>
         <v>55.2</v>
       </c>
-      <c r="G22" s="99" t="str">
+      <c r="G22" s="99">
         <f>IFERROR(INDEX(tariffs!9:9, MATCH(CHECK!$B$3,tariffs!$1:$1, 0)),"")</f>
-        <v/>
-      </c>
-      <c r="H22" s="96" t="str">
+        <v>5.98</v>
+      </c>
+      <c r="H22" s="96">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="I22" s="89" t="str">
+        <v>330.09600000000006</v>
+      </c>
+      <c r="I22" s="89">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J22" s="33" t="str">
+        <v>0</v>
+      </c>
+      <c r="J22" s="33">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K22" s="90" t="str">
+        <v>0</v>
+      </c>
+      <c r="K22" s="90">
         <f t="shared" si="0"/>
-        <v/>
+        <v>3.999999999962256E-3</v>
       </c>
       <c r="L22" s="3" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>✔ ОК</v>
       </c>
       <c r="M22" s="123" t="str">
         <f>VLOOKUP(A22,info!A26:B42, 2,FALSE)</f>
         <v>Управляющая</v>
       </c>
-      <c r="N22" s="124" t="str">
+      <c r="N22" s="124">
         <f t="shared" si="4"/>
-        <v/>
+        <v>46054</v>
       </c>
     </row>
     <row r="23" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -7868,44 +8063,50 @@
       <c r="B23" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="C23" s="81"/>
-      <c r="D23" s="74"/>
-      <c r="E23" s="94"/>
+      <c r="C23" s="81" t="s">
+        <v>193</v>
+      </c>
+      <c r="D23" s="74" t="s">
+        <v>194</v>
+      </c>
+      <c r="E23" s="94" t="s">
+        <v>195</v>
+      </c>
       <c r="F23" s="101">
         <f>IF($B$5="","",IFERROR($B$5,""))</f>
         <v>2</v>
       </c>
-      <c r="G23" s="99" t="str">
+      <c r="G23" s="99">
         <f>IFERROR(INDEX(tariffs!10:10, MATCH(CHECK!$B$3,tariffs!$1:$1, 0)),"")</f>
-        <v/>
-      </c>
-      <c r="H23" s="96" t="str">
+        <v>161.52257251624999</v>
+      </c>
+      <c r="H23" s="96">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="I23" s="89" t="str">
+        <v>323.04514503249999</v>
+      </c>
+      <c r="I23" s="89">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J23" s="33" t="str">
+        <v>0</v>
+      </c>
+      <c r="J23" s="33">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K23" s="90" t="str">
+        <v>2.7483750017154307E-5</v>
+      </c>
+      <c r="K23" s="90">
         <f t="shared" si="0"/>
-        <v/>
+        <v>-7.0451450324999882</v>
       </c>
       <c r="L23" s="3" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>❗ Недосчет</v>
       </c>
       <c r="M23" s="123" t="str">
         <f>VLOOKUP(A23,info!A27:B43, 2,FALSE)</f>
         <v>ТКО</v>
       </c>
-      <c r="N23" s="124" t="str">
+      <c r="N23" s="124">
         <f t="shared" si="4"/>
-        <v/>
+        <v>46054</v>
       </c>
     </row>
     <row r="24" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -7915,44 +8116,50 @@
       <c r="B24" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="C24" s="83"/>
-      <c r="D24" s="84"/>
-      <c r="E24" s="95"/>
+      <c r="C24" s="83" t="s">
+        <v>188</v>
+      </c>
+      <c r="D24" s="84" t="s">
+        <v>196</v>
+      </c>
+      <c r="E24" s="95" t="s">
+        <v>197</v>
+      </c>
       <c r="F24" s="102">
         <f>IF($B$4="","",IFERROR($B$4,""))</f>
         <v>55.2</v>
       </c>
-      <c r="G24" s="103" t="str">
+      <c r="G24" s="103">
         <f>IFERROR(INDEX(tariffs!11:11, MATCH(CHECK!$B$3,tariffs!$1:$1, 0)),"")</f>
-        <v/>
-      </c>
-      <c r="H24" s="97" t="str">
+        <v>15.15</v>
+      </c>
+      <c r="H24" s="97">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="I24" s="91" t="str">
+        <v>836.28000000000009</v>
+      </c>
+      <c r="I24" s="91">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J24" s="92" t="str">
+        <v>0</v>
+      </c>
+      <c r="J24" s="92">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K24" s="93" t="str">
+        <v>0</v>
+      </c>
+      <c r="K24" s="93">
         <f t="shared" si="0"/>
-        <v/>
+        <v>-1.1368683772161603E-13</v>
       </c>
       <c r="L24" s="3" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>✔ ОК</v>
       </c>
       <c r="M24" s="125" t="str">
         <f>VLOOKUP(A24,info!A28:B44, 2,FALSE)</f>
         <v>Капремонт</v>
       </c>
-      <c r="N24" s="126" t="str">
+      <c r="N24" s="126">
         <f t="shared" si="4"/>
-        <v/>
+        <v>46054</v>
       </c>
     </row>
     <row r="25" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -7983,17 +8190,17 @@
       <c r="G26" s="36"/>
       <c r="H26" s="36">
         <f>SUM(H9:H24)</f>
-        <v>0</v>
+        <v>12431.1949530325</v>
       </c>
       <c r="I26" s="36"/>
       <c r="J26" s="36"/>
       <c r="K26" s="36">
         <f>SUM(K9:K24)</f>
-        <v>0</v>
+        <v>452.31504696749988</v>
       </c>
       <c r="L26" s="3" t="str">
         <f t="shared" ref="L26" si="6">IF(ABS(K26)&lt;=1,"✔ ОК",IF(K26&gt;1,"❗ Превышение","❗ Недосчет"))</f>
-        <v>✔ ОК</v>
+        <v>❗ Превышение</v>
       </c>
       <c r="M26" s="3"/>
       <c r="N26" s="3"/>
@@ -8034,7 +8241,7 @@
       <c r="J28" s="36"/>
       <c r="K28" s="36">
         <f>SUMIF($M:$M,$A28,K:K)</f>
-        <v>0</v>
+        <v>12.599999999999909</v>
       </c>
       <c r="L28" s="36"/>
       <c r="M28" s="3"/>
@@ -8058,7 +8265,7 @@
       <c r="J29" s="36"/>
       <c r="K29" s="36">
         <f>SUMIF($M:$M,$A29,K:K)</f>
-        <v>0</v>
+        <v>1.0000000000161435E-2</v>
       </c>
       <c r="L29" s="36"/>
       <c r="M29" s="3"/>
@@ -8082,7 +8289,7 @@
       <c r="J30" s="36"/>
       <c r="K30" s="36">
         <f>SUMIF($M:$M,$A30,K:K)</f>
-        <v>0</v>
+        <v>446.75019199999991</v>
       </c>
       <c r="L30" s="36"/>
       <c r="M30" s="3"/>
@@ -8106,7 +8313,7 @@
       <c r="J31" s="36"/>
       <c r="K31" s="36">
         <f>SUMIF($M:$M,$A31,K:K)</f>
-        <v>0</v>
+        <v>-7.0451450324999882</v>
       </c>
       <c r="L31" s="36"/>
       <c r="M31" s="3"/>
@@ -8130,7 +8337,7 @@
       <c r="J32" s="36"/>
       <c r="K32" s="36">
         <f>SUMIF($M:$M,$A32,K:K)</f>
-        <v>0</v>
+        <v>-1.1368683772161603E-13</v>
       </c>
       <c r="L32" s="36"/>
       <c r="M32" s="3"/>
@@ -8190,7 +8397,7 @@
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{B36B768B-FEB0-40B2-85F8-0293102B9A5E}">
           <x14:formula1>
-            <xm:f>helper!$A$2:$A$166</xm:f>
+            <xm:f>helper!$A$2:$A$26</xm:f>
           </x14:formula1>
           <xm:sqref>B3</xm:sqref>
         </x14:dataValidation>
